--- a/public/data/files/XAUUSD_forecast.xlsx
+++ b/public/data/files/XAUUSD_forecast.xlsx
@@ -357,7 +357,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B65"/>
+  <dimension ref="A1:B66"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" style="1" customWidth="1"/>
@@ -416,7 +416,7 @@
         <v>45849</v>
       </c>
       <c r="B7">
-        <v>3664.005600171392</v>
+        <v>3664.444175541129</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -424,7 +424,7 @@
         <v>45856</v>
       </c>
       <c r="B8">
-        <v>3559.503526251512</v>
+        <v>3560.092216314815</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -432,7 +432,7 @@
         <v>45863</v>
       </c>
       <c r="B9">
-        <v>3504.127828400284</v>
+        <v>3504.803999972018</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -440,7 +440,7 @@
         <v>45870</v>
       </c>
       <c r="B10">
-        <v>3476.130428157731</v>
+        <v>3476.842222423119</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -448,7 +448,7 @@
         <v>45877</v>
       </c>
       <c r="B11">
-        <v>3484.449657094291</v>
+        <v>3485.179175749054</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -456,7 +456,7 @@
         <v>45884</v>
       </c>
       <c r="B12">
-        <v>3497.144653783064</v>
+        <v>3497.883144777755</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -464,7 +464,7 @@
         <v>45891</v>
       </c>
       <c r="B13">
-        <v>3511.719662093885</v>
+        <v>3512.452794720757</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -472,7 +472,7 @@
         <v>45898</v>
       </c>
       <c r="B14">
-        <v>3524.349127525533</v>
+        <v>3525.070510875266</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -480,7 +480,7 @@
         <v>45905</v>
       </c>
       <c r="B15">
-        <v>3542.486674912636</v>
+        <v>3542.998635437324</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -488,7 +488,7 @@
         <v>45912</v>
       </c>
       <c r="B16">
-        <v>3454.180721963972</v>
+        <v>3454.033881834794</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -496,7 +496,7 @@
         <v>45919</v>
       </c>
       <c r="B17">
-        <v>3451.604023369897</v>
+        <v>3451.473740037852</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -504,7 +504,7 @@
         <v>45926</v>
       </c>
       <c r="B18">
-        <v>3451.587990081369</v>
+        <v>3451.466924856458</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -512,7 +512,7 @@
         <v>45933</v>
       </c>
       <c r="B19">
-        <v>3539.069173546592</v>
+        <v>3538.444108037637</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -520,7 +520,7 @@
         <v>45940</v>
       </c>
       <c r="B20">
-        <v>3641.778300204636</v>
+        <v>3640.590592358745</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -528,7 +528,7 @@
         <v>45947</v>
       </c>
       <c r="B21">
-        <v>3799.760678936371</v>
+        <v>3797.987731871332</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -536,7 +536,7 @@
         <v>45954</v>
       </c>
       <c r="B22">
-        <v>3868.945391221896</v>
+        <v>3867.367032555298</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -544,7 +544,7 @@
         <v>45961</v>
       </c>
       <c r="B23">
-        <v>3914.350705687865</v>
+        <v>3912.929118996219</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -552,7 +552,7 @@
         <v>45968</v>
       </c>
       <c r="B24">
-        <v>3897.60498667616</v>
+        <v>3896.399332650598</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -560,7 +560,7 @@
         <v>45975</v>
       </c>
       <c r="B25">
-        <v>3892.448072405083</v>
+        <v>3891.971904232414</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -568,7 +568,7 @@
         <v>45982</v>
       </c>
       <c r="B26">
-        <v>3995.338505806975</v>
+        <v>3995.200358137936</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -576,7 +576,7 @@
         <v>45989</v>
       </c>
       <c r="B27">
-        <v>4073.761978450223</v>
+        <v>4073.249291972137</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -584,7 +584,7 @@
         <v>45996</v>
       </c>
       <c r="B28">
-        <v>4115.094929511298</v>
+        <v>4114.460531784015</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -592,7 +592,7 @@
         <v>46003</v>
       </c>
       <c r="B29">
-        <v>4207.285379901633</v>
+        <v>4207.188174612504</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -600,7 +600,7 @@
         <v>46010</v>
       </c>
       <c r="B30">
-        <v>4202.716127934125</v>
+        <v>4202.395885990976</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -608,7 +608,7 @@
         <v>46017</v>
       </c>
       <c r="B31">
-        <v>4232.48691228801</v>
+        <v>4231.655668346753</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -616,7 +616,7 @@
         <v>46024</v>
       </c>
       <c r="B32">
-        <v>4253.277729762087</v>
+        <v>4252.459174289233</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -624,7 +624,7 @@
         <v>46031</v>
       </c>
       <c r="B33">
-        <v>4321.101515520813</v>
+        <v>4319.974643489277</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -632,7 +632,7 @@
         <v>46038</v>
       </c>
       <c r="B34">
-        <v>4416.365315767839</v>
+        <v>4414.971385417278</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -640,7 +640,7 @@
         <v>46045</v>
       </c>
       <c r="B35">
-        <v>4453.504887015173</v>
+        <v>4452.018063628538</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -648,7 +648,7 @@
         <v>46052</v>
       </c>
       <c r="B36">
-        <v>4560.123382347932</v>
+        <v>4558.170505534332</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -656,7 +656,7 @@
         <v>46059</v>
       </c>
       <c r="B37">
-        <v>4700.003035908181</v>
+        <v>4697.624452049504</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -664,7 +664,7 @@
         <v>46066</v>
       </c>
       <c r="B38">
-        <v>4787.872719260286</v>
+        <v>4784.993026086137</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -672,7 +672,7 @@
         <v>46073</v>
       </c>
       <c r="B39">
-        <v>4911.881830576152</v>
+        <v>4910.103354404802</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -680,7 +680,7 @@
         <v>46080</v>
       </c>
       <c r="B40">
-        <v>4954.842199156359</v>
+        <v>4952.889960219639</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -688,7 +688,7 @@
         <v>46087</v>
       </c>
       <c r="B41">
-        <v>5067.293441320599</v>
+        <v>5064.793858666447</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -696,7 +696,7 @@
         <v>46094</v>
       </c>
       <c r="B42">
-        <v>5223.431564000285</v>
+        <v>5222.112128487312</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -704,7 +704,7 @@
         <v>46101</v>
       </c>
       <c r="B43">
-        <v>5252.204930962942</v>
+        <v>5252.270208687364</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -712,7 +712,7 @@
         <v>46108</v>
       </c>
       <c r="B44">
-        <v>5274.300339691275</v>
+        <v>5276.245137013325</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -720,7 +720,7 @@
         <v>46115</v>
       </c>
       <c r="B45">
-        <v>5337.995035490958</v>
+        <v>5341.183448048207</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -728,7 +728,7 @@
         <v>46122</v>
       </c>
       <c r="B46">
-        <v>5405.782100871307</v>
+        <v>5409.863677483161</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -736,7 +736,7 @@
         <v>46129</v>
       </c>
       <c r="B47">
-        <v>5532.421835082043</v>
+        <v>5536.847778862666</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -744,7 +744,7 @@
         <v>46136</v>
       </c>
       <c r="B48">
-        <v>5461.550862451293</v>
+        <v>5466.962815687039</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -752,7 +752,7 @@
         <v>46143</v>
       </c>
       <c r="B49">
-        <v>5274.076380326548</v>
+        <v>5280.665230522969</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -760,7 +760,7 @@
         <v>46150</v>
       </c>
       <c r="B50">
-        <v>5161.809535463935</v>
+        <v>5167.92452986469</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -768,7 +768,7 @@
         <v>46157</v>
       </c>
       <c r="B51">
-        <v>5072.178033162105</v>
+        <v>5030.244937840209</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -776,7 +776,7 @@
         <v>46164</v>
       </c>
       <c r="B52">
-        <v>5015.94501048592</v>
+        <v>4922.388978668611</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -784,7 +784,7 @@
         <v>46171</v>
       </c>
       <c r="B53">
-        <v>4985.538744434831</v>
+        <v>4882.300007826566</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -792,7 +792,7 @@
         <v>46178</v>
       </c>
       <c r="B54">
-        <v>4998.213353408681</v>
+        <v>4867.578193428148</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -800,7 +800,7 @@
         <v>46185</v>
       </c>
       <c r="B55">
-        <v>4899.602486084065</v>
+        <v>4773.225599644018</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -808,7 +808,7 @@
         <v>46192</v>
       </c>
       <c r="B56">
-        <v>4775.962811125333</v>
+        <v>4675.437835419022</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -816,7 +816,7 @@
         <v>46199</v>
       </c>
       <c r="B57">
-        <v>4664.703002869599</v>
+        <v>4596.366735150846</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -824,7 +824,7 @@
         <v>46206</v>
       </c>
       <c r="B58">
-        <v>4670.638734199234</v>
+        <v>4601.400610576747</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -832,7 +832,7 @@
         <v>46213</v>
       </c>
       <c r="B59">
-        <v>4674.917131088943</v>
+        <v>4578.363700105248</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -840,7 +840,7 @@
         <v>46220</v>
       </c>
       <c r="B60">
-        <v>4674.71070853019</v>
+        <v>4522.740675266157</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -848,7 +848,7 @@
         <v>46227</v>
       </c>
       <c r="B61">
-        <v>4662.252902111473</v>
+        <v>4458.471482882841</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -856,7 +856,7 @@
         <v>46234</v>
       </c>
       <c r="B62">
-        <v>4635.707533423516</v>
+        <v>4397.669537532322</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -864,7 +864,7 @@
         <v>46241</v>
       </c>
       <c r="B63">
-        <v>4621.910233028388</v>
+        <v>4364.914445352502</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -872,7 +872,7 @@
         <v>46248</v>
       </c>
       <c r="B64">
-        <v>4625.118142620495</v>
+        <v>4369.324254179108</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -880,7 +880,15 @@
         <v>46255</v>
       </c>
       <c r="B65">
-        <v>4540.07</v>
+        <v>4275.098104253333</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2">
+      <c r="A66" s="2">
+        <v>46262</v>
+      </c>
+      <c r="B66">
+        <v>4391.450265115967</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/XAUUSD_forecast.xlsx
+++ b/public/data/files/XAUUSD_forecast.xlsx
@@ -357,7 +357,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B66"/>
+  <dimension ref="A1:B67"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" style="1" customWidth="1"/>
@@ -416,7 +416,7 @@
         <v>45849</v>
       </c>
       <c r="B7">
-        <v>3664.444175541129</v>
+        <v>3664.647027292277</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -424,7 +424,7 @@
         <v>45856</v>
       </c>
       <c r="B8">
-        <v>3560.092216314815</v>
+        <v>3560.36469358466</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -432,7 +432,7 @@
         <v>45863</v>
       </c>
       <c r="B9">
-        <v>3504.803999972018</v>
+        <v>3505.117177111559</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -440,7 +440,7 @@
         <v>45870</v>
       </c>
       <c r="B10">
-        <v>3476.842222423119</v>
+        <v>3477.172182507191</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -448,7 +448,7 @@
         <v>45877</v>
       </c>
       <c r="B11">
-        <v>3485.179175749054</v>
+        <v>3485.517342044122</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -456,7 +456,7 @@
         <v>45884</v>
       </c>
       <c r="B12">
-        <v>3497.883144777755</v>
+        <v>3498.225458938951</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -464,7 +464,7 @@
         <v>45891</v>
       </c>
       <c r="B13">
-        <v>3512.452794720757</v>
+        <v>3512.792618842491</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -472,7 +472,7 @@
         <v>45898</v>
       </c>
       <c r="B14">
-        <v>3525.070510875266</v>
+        <v>3525.404888350845</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -480,7 +480,7 @@
         <v>45905</v>
       </c>
       <c r="B15">
-        <v>3542.998635437324</v>
+        <v>3543.236675241633</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -488,7 +488,7 @@
         <v>45912</v>
       </c>
       <c r="B16">
-        <v>3454.033881834794</v>
+        <v>3453.966183953818</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -496,7 +496,7 @@
         <v>45919</v>
       </c>
       <c r="B17">
-        <v>3451.473740037852</v>
+        <v>3451.413703827388</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -504,7 +504,7 @@
         <v>45926</v>
       </c>
       <c r="B18">
-        <v>3451.466924856458</v>
+        <v>3451.411156175122</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -512,7 +512,7 @@
         <v>45933</v>
       </c>
       <c r="B19">
-        <v>3538.444108037637</v>
+        <v>3538.155648942087</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -520,7 +520,7 @@
         <v>45940</v>
       </c>
       <c r="B20">
-        <v>3640.590592358745</v>
+        <v>3640.04200660561</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -528,7 +528,7 @@
         <v>45947</v>
       </c>
       <c r="B21">
-        <v>3797.987731871332</v>
+        <v>3797.167853680818</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -536,7 +536,7 @@
         <v>45954</v>
       </c>
       <c r="B22">
-        <v>3867.367032555298</v>
+        <v>3866.636795811013</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -544,7 +544,7 @@
         <v>45961</v>
       </c>
       <c r="B23">
-        <v>3912.929118996219</v>
+        <v>3912.269374049087</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -552,7 +552,7 @@
         <v>45968</v>
       </c>
       <c r="B24">
-        <v>3896.399332650598</v>
+        <v>3895.83882024499</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -560,7 +560,7 @@
         <v>45975</v>
       </c>
       <c r="B25">
-        <v>3891.971904232414</v>
+        <v>3891.749461080058</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -568,7 +568,7 @@
         <v>45982</v>
       </c>
       <c r="B26">
-        <v>3995.200358137936</v>
+        <v>3995.135154877543</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -576,7 +576,7 @@
         <v>45989</v>
       </c>
       <c r="B27">
-        <v>4073.249291972137</v>
+        <v>4073.011304379615</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -584,7 +584,7 @@
         <v>45996</v>
       </c>
       <c r="B28">
-        <v>4114.460531784015</v>
+        <v>4114.166087077748</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -592,7 +592,7 @@
         <v>46003</v>
       </c>
       <c r="B29">
-        <v>4207.188174612504</v>
+        <v>4207.144191319035</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -600,7 +600,7 @@
         <v>46010</v>
       </c>
       <c r="B30">
-        <v>4202.395885990976</v>
+        <v>4202.249279940562</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -608,7 +608,7 @@
         <v>46017</v>
       </c>
       <c r="B31">
-        <v>4231.655668346753</v>
+        <v>4231.273506872812</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -616,7 +616,7 @@
         <v>46024</v>
       </c>
       <c r="B32">
-        <v>4252.459174289233</v>
+        <v>4252.082043084896</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -624,7 +624,7 @@
         <v>46031</v>
       </c>
       <c r="B33">
-        <v>4319.974643489277</v>
+        <v>4319.454698564838</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -632,7 +632,7 @@
         <v>46038</v>
       </c>
       <c r="B34">
-        <v>4414.971385417278</v>
+        <v>4414.327174158602</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -640,7 +640,7 @@
         <v>46045</v>
       </c>
       <c r="B35">
-        <v>4452.018063628538</v>
+        <v>4451.330062616447</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -648,7 +648,7 @@
         <v>46052</v>
       </c>
       <c r="B36">
-        <v>4558.170505534332</v>
+        <v>4557.265765432097</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -656,7 +656,7 @@
         <v>46059</v>
       </c>
       <c r="B37">
-        <v>4697.624452049504</v>
+        <v>4696.522670282431</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -664,7 +664,7 @@
         <v>46066</v>
       </c>
       <c r="B38">
-        <v>4784.993026086137</v>
+        <v>4783.653045343154</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -672,7 +672,7 @@
         <v>46073</v>
       </c>
       <c r="B39">
-        <v>4910.103354404802</v>
+        <v>4909.278889816272</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -680,7 +680,7 @@
         <v>46080</v>
       </c>
       <c r="B40">
-        <v>4952.889960219639</v>
+        <v>4951.984855755507</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -688,7 +688,7 @@
         <v>46087</v>
       </c>
       <c r="B41">
-        <v>5064.793858666447</v>
+        <v>5063.633019670595</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -696,7 +696,7 @@
         <v>46094</v>
       </c>
       <c r="B42">
-        <v>5222.112128487312</v>
+        <v>5221.495832053994</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -704,7 +704,7 @@
         <v>46101</v>
       </c>
       <c r="B43">
-        <v>5252.270208687364</v>
+        <v>5252.289549595489</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -712,7 +712,7 @@
         <v>46108</v>
       </c>
       <c r="B44">
-        <v>5276.245137013325</v>
+        <v>5277.132680246401</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -720,7 +720,7 @@
         <v>46115</v>
       </c>
       <c r="B45">
-        <v>5341.183448048207</v>
+        <v>5342.650845625592</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -728,7 +728,7 @@
         <v>46122</v>
       </c>
       <c r="B46">
-        <v>5409.863677483161</v>
+        <v>5411.744085805539</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -736,7 +736,7 @@
         <v>46129</v>
       </c>
       <c r="B47">
-        <v>5536.847778862666</v>
+        <v>5538.888107219228</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -744,7 +744,7 @@
         <v>46136</v>
       </c>
       <c r="B48">
-        <v>5466.962815687039</v>
+        <v>5469.465534128366</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -752,7 +752,7 @@
         <v>46143</v>
       </c>
       <c r="B49">
-        <v>5280.665230522969</v>
+        <v>5283.71831942984</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -760,7 +760,7 @@
         <v>46150</v>
       </c>
       <c r="B50">
-        <v>5167.92452986469</v>
+        <v>5170.761943288412</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -768,7 +768,7 @@
         <v>46157</v>
       </c>
       <c r="B51">
-        <v>5030.244937840209</v>
+        <v>5033.236093312287</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -776,7 +776,7 @@
         <v>46164</v>
       </c>
       <c r="B52">
-        <v>4922.388978668611</v>
+        <v>4925.060469171502</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -784,7 +784,7 @@
         <v>46171</v>
       </c>
       <c r="B53">
-        <v>4882.300007826566</v>
+        <v>4852.836721943941</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -792,7 +792,7 @@
         <v>46178</v>
       </c>
       <c r="B54">
-        <v>4867.578193428148</v>
+        <v>4845.081712395488</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -800,7 +800,7 @@
         <v>46185</v>
       </c>
       <c r="B55">
-        <v>4773.225599644018</v>
+        <v>4760.000936180529</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -808,7 +808,7 @@
         <v>46192</v>
       </c>
       <c r="B56">
-        <v>4675.437835419022</v>
+        <v>4667.050464296646</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -816,7 +816,7 @@
         <v>46199</v>
       </c>
       <c r="B57">
-        <v>4596.366735150846</v>
+        <v>4616.151009840944</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -824,7 +824,7 @@
         <v>46206</v>
       </c>
       <c r="B58">
-        <v>4601.400610576747</v>
+        <v>4758.856412828557</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -832,7 +832,7 @@
         <v>46213</v>
       </c>
       <c r="B59">
-        <v>4578.363700105248</v>
+        <v>5124.549772975758</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -840,7 +840,7 @@
         <v>46220</v>
       </c>
       <c r="B60">
-        <v>4522.740675266157</v>
+        <v>5822.217870422006</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -848,7 +848,7 @@
         <v>46227</v>
       </c>
       <c r="B61">
-        <v>4458.471482882841</v>
+        <v>6960.143304456755</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -856,7 +856,7 @@
         <v>46234</v>
       </c>
       <c r="B62">
-        <v>4397.669537532322</v>
+        <v>9348.329775481554</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -864,7 +864,7 @@
         <v>46241</v>
       </c>
       <c r="B63">
-        <v>4364.914445352502</v>
+        <v>11734.73153168645</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -872,7 +872,7 @@
         <v>46248</v>
       </c>
       <c r="B64">
-        <v>4369.324254179108</v>
+        <v>14410.7881393375</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -880,7 +880,7 @@
         <v>46255</v>
       </c>
       <c r="B65">
-        <v>4275.098104253333</v>
+        <v>17828.14472563376</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -888,7 +888,15 @@
         <v>46262</v>
       </c>
       <c r="B66">
-        <v>4391.450265115967</v>
+        <v>34361.23513993267</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2">
+      <c r="A67" s="2">
+        <v>46269</v>
+      </c>
+      <c r="B67">
+        <v>64402.59609057724</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/XAUUSD_forecast.xlsx
+++ b/public/data/files/XAUUSD_forecast.xlsx
@@ -792,7 +792,7 @@
         <v>46178</v>
       </c>
       <c r="B54">
-        <v>4845.081712395488</v>
+        <v>4838.149255187519</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -800,7 +800,7 @@
         <v>46185</v>
       </c>
       <c r="B55">
-        <v>4760.000936180529</v>
+        <v>4751.129175107797</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -808,7 +808,7 @@
         <v>46192</v>
       </c>
       <c r="B56">
-        <v>4667.050464296646</v>
+        <v>4661.322762527784</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -816,7 +816,7 @@
         <v>46199</v>
       </c>
       <c r="B57">
-        <v>4616.151009840944</v>
+        <v>4593.859642477672</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -824,7 +824,7 @@
         <v>46206</v>
       </c>
       <c r="B58">
-        <v>4758.856412828557</v>
+        <v>4604.273612586134</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -832,7 +832,7 @@
         <v>46213</v>
       </c>
       <c r="B59">
-        <v>5124.549772975758</v>
+        <v>4587.329479255117</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -840,7 +840,7 @@
         <v>46220</v>
       </c>
       <c r="B60">
-        <v>5822.217870422006</v>
+        <v>4538.575190361526</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -848,7 +848,7 @@
         <v>46227</v>
       </c>
       <c r="B61">
-        <v>6960.143304456755</v>
+        <v>4472.455508747864</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -856,7 +856,7 @@
         <v>46234</v>
       </c>
       <c r="B62">
-        <v>9348.329775481554</v>
+        <v>4398.160060905313</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -864,7 +864,7 @@
         <v>46241</v>
       </c>
       <c r="B63">
-        <v>11734.73153168645</v>
+        <v>4346.227305486467</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -872,7 +872,7 @@
         <v>46248</v>
       </c>
       <c r="B64">
-        <v>14410.7881393375</v>
+        <v>4328.429983738952</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -880,7 +880,7 @@
         <v>46255</v>
       </c>
       <c r="B65">
-        <v>17828.14472563376</v>
+        <v>4267.784046945184</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -888,7 +888,7 @@
         <v>46262</v>
       </c>
       <c r="B66">
-        <v>34361.23513993267</v>
+        <v>4371.208601618608</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -896,7 +896,7 @@
         <v>46269</v>
       </c>
       <c r="B67">
-        <v>64402.59609057724</v>
+        <v>4451.176210768752</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/XAUUSD_forecast.xlsx
+++ b/public/data/files/XAUUSD_forecast.xlsx
@@ -357,7 +357,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B67"/>
+  <dimension ref="A1:B68"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" style="1" customWidth="1"/>
@@ -888,7 +888,7 @@
         <v>46262</v>
       </c>
       <c r="B66">
-        <v>4371.208601618608</v>
+        <v>4371.208601618606</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -896,7 +896,15 @@
         <v>46269</v>
       </c>
       <c r="B67">
-        <v>4451.176210768752</v>
+        <v>4451.176210768751</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2">
+      <c r="A68" s="2">
+        <v>46276</v>
+      </c>
+      <c r="B68">
+        <v>4518.774627988358</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/XAUUSD_forecast.xlsx
+++ b/public/data/files/XAUUSD_forecast.xlsx
@@ -357,7 +357,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B68"/>
+  <dimension ref="A1:B69"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" style="1" customWidth="1"/>
@@ -416,7 +416,7 @@
         <v>45849</v>
       </c>
       <c r="B7">
-        <v>3664.647027292277</v>
+        <v>3664.839989871063</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -424,7 +424,7 @@
         <v>45856</v>
       </c>
       <c r="B8">
-        <v>3560.36469358466</v>
+        <v>3560.624000885839</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -432,7 +432,7 @@
         <v>45863</v>
       </c>
       <c r="B9">
-        <v>3505.117177111559</v>
+        <v>3505.415339234902</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -440,7 +440,7 @@
         <v>45870</v>
       </c>
       <c r="B10">
-        <v>3477.172182507191</v>
+        <v>3477.486489009494</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -448,7 +448,7 @@
         <v>45877</v>
       </c>
       <c r="B11">
-        <v>3485.517342044122</v>
+        <v>3485.839459494145</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -456,7 +456,7 @@
         <v>45884</v>
       </c>
       <c r="B12">
-        <v>3498.225458938951</v>
+        <v>3498.551520819715</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -464,7 +464,7 @@
         <v>45891</v>
       </c>
       <c r="B13">
-        <v>3512.792618842491</v>
+        <v>3513.11630524926</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -472,7 +472,7 @@
         <v>45898</v>
       </c>
       <c r="B14">
-        <v>3525.404888350845</v>
+        <v>3525.723386437448</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -480,7 +480,7 @@
         <v>45905</v>
       </c>
       <c r="B15">
-        <v>3543.236675241633</v>
+        <v>3543.463840910521</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -488,7 +488,7 @@
         <v>45912</v>
       </c>
       <c r="B16">
-        <v>3453.966183953818</v>
+        <v>3453.901915339371</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -496,7 +496,7 @@
         <v>45919</v>
       </c>
       <c r="B17">
-        <v>3451.413703827388</v>
+        <v>3451.356725550008</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -504,7 +504,7 @@
         <v>45926</v>
       </c>
       <c r="B18">
-        <v>3451.411156175122</v>
+        <v>3451.358239677457</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -512,7 +512,7 @@
         <v>45933</v>
       </c>
       <c r="B19">
-        <v>3538.155648942087</v>
+        <v>3537.881635189933</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -520,7 +520,7 @@
         <v>45940</v>
       </c>
       <c r="B20">
-        <v>3640.04200660561</v>
+        <v>3639.520615671939</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -528,7 +528,7 @@
         <v>45947</v>
       </c>
       <c r="B21">
-        <v>3797.167853680818</v>
+        <v>3796.388043884617</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -536,7 +536,7 @@
         <v>45954</v>
       </c>
       <c r="B22">
-        <v>3866.636795811013</v>
+        <v>3865.942042331926</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -544,7 +544,7 @@
         <v>45961</v>
       </c>
       <c r="B23">
-        <v>3912.269374049087</v>
+        <v>3911.640493946191</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -552,7 +552,7 @@
         <v>45968</v>
       </c>
       <c r="B24">
-        <v>3895.83882024499</v>
+        <v>3895.303956683412</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -560,7 +560,7 @@
         <v>45975</v>
       </c>
       <c r="B25">
-        <v>3891.749461080058</v>
+        <v>3891.536568702174</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -568,7 +568,7 @@
         <v>45982</v>
       </c>
       <c r="B26">
-        <v>3995.135154877543</v>
+        <v>3995.072361495094</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -576,7 +576,7 @@
         <v>45989</v>
       </c>
       <c r="B27">
-        <v>4073.011304379615</v>
+        <v>4072.784413406933</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -584,7 +584,7 @@
         <v>45996</v>
       </c>
       <c r="B28">
-        <v>4114.166087077748</v>
+        <v>4113.88539740291</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -592,7 +592,7 @@
         <v>46003</v>
       </c>
       <c r="B29">
-        <v>4207.144191319035</v>
+        <v>4207.102926723109</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -600,7 +600,7 @@
         <v>46010</v>
       </c>
       <c r="B30">
-        <v>4202.249279940562</v>
+        <v>4202.110715220241</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -608,7 +608,7 @@
         <v>46017</v>
       </c>
       <c r="B31">
-        <v>4231.273506872812</v>
+        <v>4230.9113455934</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -616,7 +616,7 @@
         <v>46024</v>
       </c>
       <c r="B32">
-        <v>4252.082043084896</v>
+        <v>4251.724181043764</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -624,7 +624,7 @@
         <v>46031</v>
       </c>
       <c r="B33">
-        <v>4319.454698564838</v>
+        <v>4318.960870978537</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -632,7 +632,7 @@
         <v>46038</v>
       </c>
       <c r="B34">
-        <v>4414.327174158602</v>
+        <v>4413.714709832966</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -640,7 +640,7 @@
         <v>46045</v>
       </c>
       <c r="B35">
-        <v>4451.330062616447</v>
+        <v>4450.675451668535</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -648,7 +648,7 @@
         <v>46052</v>
       </c>
       <c r="B36">
-        <v>4557.265765432097</v>
+        <v>4556.404289744754</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -656,7 +656,7 @@
         <v>46059</v>
       </c>
       <c r="B37">
-        <v>4696.522670282431</v>
+        <v>4695.473688241235</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -664,7 +664,7 @@
         <v>46066</v>
       </c>
       <c r="B38">
-        <v>4783.653045343154</v>
+        <v>4782.373680037523</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -672,7 +672,7 @@
         <v>46073</v>
       </c>
       <c r="B39">
-        <v>4909.278889816272</v>
+        <v>4908.493551654667</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -680,7 +680,7 @@
         <v>46080</v>
       </c>
       <c r="B40">
-        <v>4951.984855755507</v>
+        <v>4951.122653011536</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -688,7 +688,7 @@
         <v>46087</v>
       </c>
       <c r="B41">
-        <v>5063.633019670595</v>
+        <v>5062.526059531417</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -696,7 +696,7 @@
         <v>46094</v>
       </c>
       <c r="B42">
-        <v>5221.495832053994</v>
+        <v>5220.906062563634</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -704,7 +704,7 @@
         <v>46101</v>
       </c>
       <c r="B43">
-        <v>5252.289549595489</v>
+        <v>5252.301574137586</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -712,7 +712,7 @@
         <v>46108</v>
       </c>
       <c r="B44">
-        <v>5277.132680246401</v>
+        <v>5277.969878372809</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -720,7 +720,7 @@
         <v>46115</v>
       </c>
       <c r="B45">
-        <v>5342.650845625592</v>
+        <v>5344.042341323167</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -728,7 +728,7 @@
         <v>46122</v>
       </c>
       <c r="B46">
-        <v>5411.744085805539</v>
+        <v>5413.528360035106</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -736,7 +736,7 @@
         <v>46129</v>
       </c>
       <c r="B47">
-        <v>5538.888107219228</v>
+        <v>5540.824891084845</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -744,7 +744,7 @@
         <v>46136</v>
       </c>
       <c r="B48">
-        <v>5469.465534128366</v>
+        <v>5471.845882325876</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -752,7 +752,7 @@
         <v>46143</v>
       </c>
       <c r="B49">
-        <v>5283.71831942984</v>
+        <v>5286.625687752085</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -760,7 +760,7 @@
         <v>46150</v>
       </c>
       <c r="B50">
-        <v>5170.761943288412</v>
+        <v>5173.46621371784</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -768,7 +768,7 @@
         <v>46157</v>
       </c>
       <c r="B51">
-        <v>5033.236093312287</v>
+        <v>5036.090373708416</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -776,7 +776,7 @@
         <v>46164</v>
       </c>
       <c r="B52">
-        <v>4925.060469171502</v>
+        <v>4927.611403678315</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -784,7 +784,7 @@
         <v>46171</v>
       </c>
       <c r="B53">
-        <v>4852.836721943941</v>
+        <v>4827.454704101947</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -792,7 +792,7 @@
         <v>46178</v>
       </c>
       <c r="B54">
-        <v>4838.149255187519</v>
+        <v>4813.967396991517</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -800,7 +800,7 @@
         <v>46185</v>
       </c>
       <c r="B55">
-        <v>4751.129175107797</v>
+        <v>4734.651300138319</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -808,7 +808,7 @@
         <v>46192</v>
       </c>
       <c r="B56">
-        <v>4661.322762527784</v>
+        <v>4653.206408787352</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -816,7 +816,7 @@
         <v>46199</v>
       </c>
       <c r="B57">
-        <v>4593.859642477672</v>
+        <v>4592.154371054872</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -824,7 +824,7 @@
         <v>46206</v>
       </c>
       <c r="B58">
-        <v>4604.273612586134</v>
+        <v>4601.18379110119</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -832,7 +832,7 @@
         <v>46213</v>
       </c>
       <c r="B59">
-        <v>4587.329479255117</v>
+        <v>4584.303530093928</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -840,7 +840,7 @@
         <v>46220</v>
       </c>
       <c r="B60">
-        <v>4538.575190361526</v>
+        <v>4541.903481304567</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -848,7 +848,7 @@
         <v>46227</v>
       </c>
       <c r="B61">
-        <v>4472.455508747864</v>
+        <v>4483.493245864989</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -856,7 +856,7 @@
         <v>46234</v>
       </c>
       <c r="B62">
-        <v>4398.160060905313</v>
+        <v>4418.538606493264</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -864,7 +864,7 @@
         <v>46241</v>
       </c>
       <c r="B63">
-        <v>4346.227305486467</v>
+        <v>4375.301775644893</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -872,7 +872,7 @@
         <v>46248</v>
       </c>
       <c r="B64">
-        <v>4328.429983738952</v>
+        <v>4362.407577434295</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -880,7 +880,7 @@
         <v>46255</v>
       </c>
       <c r="B65">
-        <v>4267.784046945184</v>
+        <v>4337.242031895871</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -888,7 +888,7 @@
         <v>46262</v>
       </c>
       <c r="B66">
-        <v>4371.208601618606</v>
+        <v>4480.432010211978</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -896,7 +896,7 @@
         <v>46269</v>
       </c>
       <c r="B67">
-        <v>4451.176210768751</v>
+        <v>4518.188513095243</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -904,7 +904,15 @@
         <v>46276</v>
       </c>
       <c r="B68">
-        <v>4518.774627988358</v>
+        <v>4552.005231879381</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2">
+      <c r="A69" s="2">
+        <v>46283</v>
+      </c>
+      <c r="B69">
+        <v>4560.011514066039</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/XAUUSD_forecast.xlsx
+++ b/public/data/files/XAUUSD_forecast.xlsx
@@ -416,7 +416,7 @@
         <v>45849</v>
       </c>
       <c r="B7">
-        <v>3664.839989871063</v>
+        <v>3665.023769092816</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -424,7 +424,7 @@
         <v>45856</v>
       </c>
       <c r="B8">
-        <v>3560.624000885839</v>
+        <v>3560.871070105127</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -432,7 +432,7 @@
         <v>45863</v>
       </c>
       <c r="B9">
-        <v>3505.415339234902</v>
+        <v>3505.69954000329</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -440,7 +440,7 @@
         <v>45870</v>
       </c>
       <c r="B10">
-        <v>3477.486489009494</v>
+        <v>3477.786228424488</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -448,7 +448,7 @@
         <v>45877</v>
       </c>
       <c r="B11">
-        <v>3485.839459494145</v>
+        <v>3486.146642440194</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -456,7 +456,7 @@
         <v>45884</v>
       </c>
       <c r="B12">
-        <v>3498.551520819715</v>
+        <v>3498.862459356472</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -464,7 +464,7 @@
         <v>45891</v>
       </c>
       <c r="B13">
-        <v>3513.11630524926</v>
+        <v>3513.424975189836</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -472,7 +472,7 @@
         <v>45898</v>
       </c>
       <c r="B14">
-        <v>3525.723386437448</v>
+        <v>3526.027108467442</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -480,7 +480,7 @@
         <v>45905</v>
       </c>
       <c r="B15">
-        <v>3543.463840910521</v>
+        <v>3543.680857184332</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -488,7 +488,7 @@
         <v>45912</v>
       </c>
       <c r="B16">
-        <v>3453.901915339371</v>
+        <v>3453.840822404238</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -496,7 +496,7 @@
         <v>45919</v>
       </c>
       <c r="B17">
-        <v>3451.356725550008</v>
+        <v>3451.302577955344</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -504,7 +504,7 @@
         <v>45926</v>
       </c>
       <c r="B18">
-        <v>3451.358239677457</v>
+        <v>3451.307962630554</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -512,7 +512,7 @@
         <v>45933</v>
       </c>
       <c r="B19">
-        <v>3537.881635189933</v>
+        <v>3537.621010269175</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -520,7 +520,7 @@
         <v>45940</v>
       </c>
       <c r="B20">
-        <v>3639.520615671939</v>
+        <v>3639.024450902927</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -528,7 +528,7 @@
         <v>45947</v>
       </c>
       <c r="B21">
-        <v>3796.388043884617</v>
+        <v>3795.645441490095</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -536,7 +536,7 @@
         <v>45954</v>
       </c>
       <c r="B22">
-        <v>3865.942042331926</v>
+        <v>3865.280251176598</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -544,7 +544,7 @@
         <v>45961</v>
       </c>
       <c r="B23">
-        <v>3911.640493946191</v>
+        <v>3911.040371868654</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -552,7 +552,7 @@
         <v>45968</v>
       </c>
       <c r="B24">
-        <v>3895.303956683412</v>
+        <v>3894.793032727933</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -560,7 +560,7 @@
         <v>45975</v>
       </c>
       <c r="B25">
-        <v>3891.536568702174</v>
+        <v>3891.332635731365</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -568,7 +568,7 @@
         <v>45982</v>
       </c>
       <c r="B26">
-        <v>3995.072361495094</v>
+        <v>3995.011858434494</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -576,7 +576,7 @@
         <v>45989</v>
       </c>
       <c r="B27">
-        <v>4072.784413406933</v>
+        <v>4072.567861040345</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -584,7 +584,7 @@
         <v>45996</v>
       </c>
       <c r="B28">
-        <v>4113.88539740291</v>
+        <v>4113.617522559274</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -592,7 +592,7 @@
         <v>46003</v>
       </c>
       <c r="B29">
-        <v>4207.102926723109</v>
+        <v>4207.064147503957</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -600,7 +600,7 @@
         <v>46010</v>
       </c>
       <c r="B30">
-        <v>4202.110715220241</v>
+        <v>4201.979559095043</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -608,7 +608,7 @@
         <v>46017</v>
       </c>
       <c r="B31">
-        <v>4230.9113455934</v>
+        <v>4230.567670406525</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -616,7 +616,7 @@
         <v>46024</v>
       </c>
       <c r="B32">
-        <v>4251.724181043764</v>
+        <v>4251.384164141835</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -624,7 +624,7 @@
         <v>46031</v>
       </c>
       <c r="B33">
-        <v>4318.960870978537</v>
+        <v>4318.491261628405</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -632,7 +632,7 @@
         <v>46038</v>
       </c>
       <c r="B34">
-        <v>4413.714709832966</v>
+        <v>4413.131727179916</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -640,7 +640,7 @@
         <v>46045</v>
       </c>
       <c r="B35">
-        <v>4450.675451668535</v>
+        <v>4450.051877724635</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -648,7 +648,7 @@
         <v>46052</v>
       </c>
       <c r="B36">
-        <v>4556.404289744754</v>
+        <v>4555.583068734443</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -656,7 +656,7 @@
         <v>46059</v>
       </c>
       <c r="B37">
-        <v>4695.473688241235</v>
+        <v>4694.473828552872</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -664,7 +664,7 @@
         <v>46066</v>
       </c>
       <c r="B38">
-        <v>4782.373680037523</v>
+        <v>4781.150943480357</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -672,7 +672,7 @@
         <v>46073</v>
       </c>
       <c r="B39">
-        <v>4908.493551654667</v>
+        <v>4907.744643626509</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -680,7 +680,7 @@
         <v>46080</v>
       </c>
       <c r="B40">
-        <v>4951.122653011536</v>
+        <v>4950.300398864851</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -688,7 +688,7 @@
         <v>46087</v>
       </c>
       <c r="B41">
-        <v>5062.526059531417</v>
+        <v>5061.469359226667</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -696,7 +696,7 @@
         <v>46094</v>
       </c>
       <c r="B42">
-        <v>5220.906062563634</v>
+        <v>5220.341184242559</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -704,7 +704,7 @@
         <v>46101</v>
       </c>
       <c r="B43">
-        <v>5252.301574137586</v>
+        <v>5252.307247132976</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -712,7 +712,7 @@
         <v>46108</v>
       </c>
       <c r="B44">
-        <v>5277.969878372809</v>
+        <v>5278.760787873743</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -720,7 +720,7 @@
         <v>46115</v>
       </c>
       <c r="B45">
-        <v>5344.042341323167</v>
+        <v>5345.363614256521</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -728,7 +728,7 @@
         <v>46122</v>
       </c>
       <c r="B46">
-        <v>5413.528360035106</v>
+        <v>5415.223605341969</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -736,7 +736,7 @@
         <v>46129</v>
       </c>
       <c r="B47">
-        <v>5540.824891084845</v>
+        <v>5542.665743257263</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -744,7 +744,7 @@
         <v>46136</v>
       </c>
       <c r="B48">
-        <v>5471.845882325876</v>
+        <v>5474.112555087485</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -752,7 +752,7 @@
         <v>46143</v>
       </c>
       <c r="B49">
-        <v>5286.625687752085</v>
+        <v>5289.397417603077</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -760,7 +760,7 @@
         <v>46150</v>
       </c>
       <c r="B50">
-        <v>5173.46621371784</v>
+        <v>5176.04638908275</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -768,7 +768,7 @@
         <v>46157</v>
       </c>
       <c r="B51">
-        <v>5036.090373708416</v>
+        <v>5038.816835239984</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -776,7 +776,7 @@
         <v>46164</v>
       </c>
       <c r="B52">
-        <v>4927.611403678315</v>
+        <v>4930.049662824094</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -784,7 +784,7 @@
         <v>46171</v>
       </c>
       <c r="B53">
-        <v>4827.454704101947</v>
+        <v>4829.741191843256</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -792,7 +792,7 @@
         <v>46178</v>
       </c>
       <c r="B54">
-        <v>4813.967396991517</v>
+        <v>4775.516897112477</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -800,7 +800,7 @@
         <v>46185</v>
       </c>
       <c r="B55">
-        <v>4734.651300138319</v>
+        <v>4696.662785180153</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -808,7 +808,7 @@
         <v>46192</v>
       </c>
       <c r="B56">
-        <v>4653.206408787352</v>
+        <v>4621.334366455494</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -816,7 +816,7 @@
         <v>46199</v>
       </c>
       <c r="B57">
-        <v>4592.154371054872</v>
+        <v>4565.665408425746</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -824,7 +824,7 @@
         <v>46206</v>
       </c>
       <c r="B58">
-        <v>4601.18379110119</v>
+        <v>4575.120061188069</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -832,7 +832,7 @@
         <v>46213</v>
       </c>
       <c r="B59">
-        <v>4584.303530093928</v>
+        <v>4546.864667594489</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -840,7 +840,7 @@
         <v>46220</v>
       </c>
       <c r="B60">
-        <v>4541.903481304567</v>
+        <v>4508.710740985933</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -848,7 +848,7 @@
         <v>46227</v>
       </c>
       <c r="B61">
-        <v>4483.493245864989</v>
+        <v>4438.11575639481</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -856,7 +856,7 @@
         <v>46234</v>
       </c>
       <c r="B62">
-        <v>4418.538606493264</v>
+        <v>4359.151488336532</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -864,7 +864,7 @@
         <v>46241</v>
       </c>
       <c r="B63">
-        <v>4375.301775644893</v>
+        <v>4293.821218424537</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -872,7 +872,7 @@
         <v>46248</v>
       </c>
       <c r="B64">
-        <v>4362.407577434295</v>
+        <v>4265.171009642359</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -880,7 +880,7 @@
         <v>46255</v>
       </c>
       <c r="B65">
-        <v>4337.242031895871</v>
+        <v>4234.511366445819</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -888,7 +888,7 @@
         <v>46262</v>
       </c>
       <c r="B66">
-        <v>4480.432010211978</v>
+        <v>4312.72604269486</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -896,7 +896,7 @@
         <v>46269</v>
       </c>
       <c r="B67">
-        <v>4518.188513095243</v>
+        <v>4293.615059831229</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -904,7 +904,7 @@
         <v>46276</v>
       </c>
       <c r="B68">
-        <v>4552.005231879381</v>
+        <v>4308.75890511681</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -912,7 +912,7 @@
         <v>46283</v>
       </c>
       <c r="B69">
-        <v>4560.011514066039</v>
+        <v>4174.250678414472</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/XAUUSD_forecast.xlsx
+++ b/public/data/files/XAUUSD_forecast.xlsx
@@ -416,7 +416,7 @@
         <v>45849</v>
       </c>
       <c r="B7">
-        <v>3665.023769092816</v>
+        <v>3665.199005177788</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -424,7 +424,7 @@
         <v>45856</v>
       </c>
       <c r="B8">
-        <v>3560.871070105127</v>
+        <v>3561.106747274279</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -432,7 +432,7 @@
         <v>45863</v>
       </c>
       <c r="B9">
-        <v>3505.69954000329</v>
+        <v>3505.970736824405</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -440,7 +440,7 @@
         <v>45870</v>
       </c>
       <c r="B10">
-        <v>3477.786228424488</v>
+        <v>3478.072389117066</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -448,7 +448,7 @@
         <v>45877</v>
       </c>
       <c r="B11">
-        <v>3486.146642440194</v>
+        <v>3486.43990454157</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -456,7 +456,7 @@
         <v>45884</v>
       </c>
       <c r="B12">
-        <v>3498.862459356472</v>
+        <v>3499.159301441448</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -464,7 +464,7 @@
         <v>45891</v>
       </c>
       <c r="B13">
-        <v>3513.424975189836</v>
+        <v>3513.719648537662</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -472,7 +472,7 @@
         <v>45898</v>
       </c>
       <c r="B14">
-        <v>3526.027108467442</v>
+        <v>3526.317058013974</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -480,7 +480,7 @@
         <v>45905</v>
       </c>
       <c r="B15">
-        <v>3543.680857184332</v>
+        <v>3543.88838614943</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -488,7 +488,7 @@
         <v>45912</v>
       </c>
       <c r="B16">
-        <v>3453.840822404238</v>
+        <v>3453.78267591592</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -496,7 +496,7 @@
         <v>45919</v>
       </c>
       <c r="B17">
-        <v>3451.302577955344</v>
+        <v>3451.251055716458</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -504,7 +504,7 @@
         <v>45926</v>
       </c>
       <c r="B18">
-        <v>3451.307962630554</v>
+        <v>3451.260132891587</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -512,7 +512,7 @@
         <v>45933</v>
       </c>
       <c r="B19">
-        <v>3537.621010269175</v>
+        <v>3537.372818065023</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -520,7 +520,7 @@
         <v>45940</v>
       </c>
       <c r="B20">
-        <v>3639.024450902927</v>
+        <v>3638.55172877928</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -528,7 +528,7 @@
         <v>45947</v>
       </c>
       <c r="B21">
-        <v>3795.645441490095</v>
+        <v>3794.937450998883</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -536,7 +536,7 @@
         <v>45954</v>
       </c>
       <c r="B22">
-        <v>3865.280251176598</v>
+        <v>3864.649134328479</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -544,7 +544,7 @@
         <v>45961</v>
       </c>
       <c r="B23">
-        <v>3911.040371868654</v>
+        <v>3910.467087601598</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -552,7 +552,7 @@
         <v>45968</v>
       </c>
       <c r="B24">
-        <v>3894.793032727933</v>
+        <v>3894.304486611611</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -560,7 +560,7 @@
         <v>45975</v>
       </c>
       <c r="B25">
-        <v>3891.332635731365</v>
+        <v>3891.137117572514</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -568,7 +568,7 @@
         <v>45982</v>
       </c>
       <c r="B26">
-        <v>3995.011858434494</v>
+        <v>3994.953532599965</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -576,7 +576,7 @@
         <v>45989</v>
       </c>
       <c r="B27">
-        <v>4072.567861040345</v>
+        <v>4072.360956744952</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -584,7 +584,7 @@
         <v>45996</v>
       </c>
       <c r="B28">
-        <v>4113.617522559274</v>
+        <v>4113.361605982325</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -592,7 +592,7 @@
         <v>46003</v>
       </c>
       <c r="B29">
-        <v>4207.064147503957</v>
+        <v>4207.027645501887</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -600,7 +600,7 @@
         <v>46010</v>
       </c>
       <c r="B30">
-        <v>4201.979559095043</v>
+        <v>4201.855242625677</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -608,7 +608,7 @@
         <v>46017</v>
       </c>
       <c r="B31">
-        <v>4230.567670406525</v>
+        <v>4230.241114955081</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -616,7 +616,7 @@
         <v>46024</v>
       </c>
       <c r="B32">
-        <v>4251.384164141835</v>
+        <v>4251.060703945151</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -624,7 +624,7 @@
         <v>46031</v>
       </c>
       <c r="B33">
-        <v>4318.491261628405</v>
+        <v>4318.044149418174</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -632,7 +632,7 @@
         <v>46038</v>
       </c>
       <c r="B34">
-        <v>4413.131727179916</v>
+        <v>4412.576169267773</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -640,7 +640,7 @@
         <v>46045</v>
       </c>
       <c r="B35">
-        <v>4450.051877724635</v>
+        <v>4449.457201992592</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -648,7 +648,7 @@
         <v>46052</v>
       </c>
       <c r="B36">
-        <v>4555.583068734443</v>
+        <v>4554.799363639628</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -656,7 +656,7 @@
         <v>46059</v>
       </c>
       <c r="B37">
-        <v>4694.473828552872</v>
+        <v>4693.519745011111</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -664,7 +664,7 @@
         <v>46066</v>
       </c>
       <c r="B38">
-        <v>4781.150943480357</v>
+        <v>4779.981187880887</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -672,7 +672,7 @@
         <v>46073</v>
       </c>
       <c r="B39">
-        <v>4907.744643626509</v>
+        <v>4907.029709440691</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -680,7 +680,7 @@
         <v>46080</v>
       </c>
       <c r="B40">
-        <v>4950.300398864851</v>
+        <v>4949.515402773082</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -688,7 +688,7 @@
         <v>46087</v>
       </c>
       <c r="B41">
-        <v>5061.469359226667</v>
+        <v>5060.459612494564</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -696,7 +696,7 @@
         <v>46094</v>
       </c>
       <c r="B42">
-        <v>5220.341184242559</v>
+        <v>5219.799689075102</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -704,7 +704,7 @@
         <v>46101</v>
       </c>
       <c r="B43">
-        <v>5252.307247132976</v>
+        <v>5252.307404083328</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -712,7 +712,7 @@
         <v>46108</v>
       </c>
       <c r="B44">
-        <v>5278.760787873743</v>
+        <v>5279.509049248424</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -720,7 +720,7 @@
         <v>46115</v>
       </c>
       <c r="B45">
-        <v>5345.363614256521</v>
+        <v>5346.619795965039</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -728,7 +728,7 @@
         <v>46122</v>
       </c>
       <c r="B46">
-        <v>5415.223605341969</v>
+        <v>5416.836250624086</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -736,7 +736,7 @@
         <v>46129</v>
       </c>
       <c r="B47">
-        <v>5542.665743257263</v>
+        <v>5544.417554467686</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -744,7 +744,7 @@
         <v>46136</v>
       </c>
       <c r="B48">
-        <v>5474.112555087485</v>
+        <v>5476.27344836844</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -752,7 +752,7 @@
         <v>46143</v>
       </c>
       <c r="B49">
-        <v>5289.397417603077</v>
+        <v>5292.042691554178</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -760,7 +760,7 @@
         <v>46150</v>
       </c>
       <c r="B50">
-        <v>5176.04638908275</v>
+        <v>5178.510725446049</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -768,7 +768,7 @@
         <v>46157</v>
       </c>
       <c r="B51">
-        <v>5038.816835239984</v>
+        <v>5041.423764129474</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -776,7 +776,7 @@
         <v>46164</v>
       </c>
       <c r="B52">
-        <v>4930.049662824094</v>
+        <v>4932.382464122468</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -784,7 +784,7 @@
         <v>46171</v>
       </c>
       <c r="B53">
-        <v>4829.741191843256</v>
+        <v>4831.931311832359</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -792,7 +792,7 @@
         <v>46178</v>
       </c>
       <c r="B54">
-        <v>4775.516897112477</v>
+        <v>4777.988946060454</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -800,7 +800,7 @@
         <v>46185</v>
       </c>
       <c r="B55">
-        <v>4696.662785180153</v>
+        <v>4658.662279356353</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -808,7 +808,7 @@
         <v>46192</v>
       </c>
       <c r="B56">
-        <v>4621.334366455494</v>
+        <v>4583.739718913337</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -816,7 +816,7 @@
         <v>46199</v>
       </c>
       <c r="B57">
-        <v>4565.665408425746</v>
+        <v>4530.558906265468</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -824,7 +824,7 @@
         <v>46206</v>
       </c>
       <c r="B58">
-        <v>4575.120061188069</v>
+        <v>4535.499201951737</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -832,7 +832,7 @@
         <v>46213</v>
       </c>
       <c r="B59">
-        <v>4546.864667594489</v>
+        <v>4506.792742316241</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -840,7 +840,7 @@
         <v>46220</v>
       </c>
       <c r="B60">
-        <v>4508.710740985933</v>
+        <v>4465.217647748474</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -848,7 +848,7 @@
         <v>46227</v>
       </c>
       <c r="B61">
-        <v>4438.11575639481</v>
+        <v>4389.636148759032</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -856,7 +856,7 @@
         <v>46234</v>
       </c>
       <c r="B62">
-        <v>4359.151488336532</v>
+        <v>4303.308438052945</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -864,7 +864,7 @@
         <v>46241</v>
       </c>
       <c r="B63">
-        <v>4293.821218424537</v>
+        <v>4229.682715059384</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -872,7 +872,7 @@
         <v>46248</v>
       </c>
       <c r="B64">
-        <v>4265.171009642359</v>
+        <v>4182.959471849997</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -880,7 +880,7 @@
         <v>46255</v>
       </c>
       <c r="B65">
-        <v>4234.511366445819</v>
+        <v>4142.656927871052</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -888,7 +888,7 @@
         <v>46262</v>
       </c>
       <c r="B66">
-        <v>4312.72604269486</v>
+        <v>4171.101917892369</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -896,7 +896,7 @@
         <v>46269</v>
       </c>
       <c r="B67">
-        <v>4293.615059831229</v>
+        <v>4130.148033946979</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -904,7 +904,7 @@
         <v>46276</v>
       </c>
       <c r="B68">
-        <v>4308.75890511681</v>
+        <v>4123.147475668284</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -912,7 +912,7 @@
         <v>46283</v>
       </c>
       <c r="B69">
-        <v>4174.250678414472</v>
+        <v>3948.913997013959</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/XAUUSD_forecast.xlsx
+++ b/public/data/files/XAUUSD_forecast.xlsx
@@ -30,8 +30,16 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -47,7 +55,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -55,13 +63,31 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -357,22 +383,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B69"/>
+  <dimension ref="A1:B70"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:2">
-      <c r="A2" s="2">
+      <c r="A2" s="3">
         <v>45814</v>
       </c>
       <c r="B2">
@@ -380,7 +406,7 @@
       </c>
     </row>
     <row r="3" spans="1:2">
-      <c r="A3" s="2">
+      <c r="A3" s="3">
         <v>45821</v>
       </c>
       <c r="B3">
@@ -388,7 +414,7 @@
       </c>
     </row>
     <row r="4" spans="1:2">
-      <c r="A4" s="2">
+      <c r="A4" s="3">
         <v>45828</v>
       </c>
       <c r="B4">
@@ -396,7 +422,7 @@
       </c>
     </row>
     <row r="5" spans="1:2">
-      <c r="A5" s="2">
+      <c r="A5" s="3">
         <v>45835</v>
       </c>
       <c r="B5">
@@ -404,7 +430,7 @@
       </c>
     </row>
     <row r="6" spans="1:2">
-      <c r="A6" s="2">
+      <c r="A6" s="3">
         <v>45842</v>
       </c>
       <c r="B6">
@@ -412,507 +438,515 @@
       </c>
     </row>
     <row r="7" spans="1:2">
-      <c r="A7" s="2">
+      <c r="A7" s="3">
         <v>45849</v>
       </c>
       <c r="B7">
-        <v>3665.199005177788</v>
+        <v>3665.366280196959</v>
       </c>
     </row>
     <row r="8" spans="1:2">
-      <c r="A8" s="2">
+      <c r="A8" s="3">
         <v>45856</v>
       </c>
       <c r="B8">
-        <v>3561.106747274279</v>
+        <v>3561.331802230651</v>
       </c>
     </row>
     <row r="9" spans="1:2">
-      <c r="A9" s="2">
+      <c r="A9" s="3">
         <v>45863</v>
       </c>
       <c r="B9">
-        <v>3505.970736824405</v>
+        <v>3506.229801589443</v>
       </c>
     </row>
     <row r="10" spans="1:2">
-      <c r="A10" s="2">
+      <c r="A10" s="3">
         <v>45870</v>
       </c>
       <c r="B10">
-        <v>3478.072389117066</v>
+        <v>3478.34587214034</v>
       </c>
     </row>
     <row r="11" spans="1:2">
-      <c r="A11" s="2">
+      <c r="A11" s="3">
         <v>45877</v>
       </c>
       <c r="B11">
-        <v>3486.43990454157</v>
+        <v>3486.72016987905</v>
       </c>
     </row>
     <row r="12" spans="1:2">
-      <c r="A12" s="2">
+      <c r="A12" s="3">
         <v>45884</v>
       </c>
       <c r="B12">
-        <v>3499.159301441448</v>
+        <v>3499.44298318114</v>
       </c>
     </row>
     <row r="13" spans="1:2">
-      <c r="A13" s="2">
+      <c r="A13" s="3">
         <v>45891</v>
       </c>
       <c r="B13">
-        <v>3513.719648537662</v>
+        <v>3514.00125497858</v>
       </c>
     </row>
     <row r="14" spans="1:2">
-      <c r="A14" s="2">
+      <c r="A14" s="3">
         <v>45898</v>
       </c>
       <c r="B14">
-        <v>3526.317058013974</v>
+        <v>3526.594149900854</v>
       </c>
     </row>
     <row r="15" spans="1:2">
-      <c r="A15" s="2">
+      <c r="A15" s="3">
         <v>45905</v>
       </c>
       <c r="B15">
-        <v>3543.88838614943</v>
+        <v>3544.087033825478</v>
       </c>
     </row>
     <row r="16" spans="1:2">
-      <c r="A16" s="2">
+      <c r="A16" s="3">
         <v>45912</v>
       </c>
       <c r="B16">
-        <v>3453.78267591592</v>
+        <v>3453.727268146337</v>
       </c>
     </row>
     <row r="17" spans="1:2">
-      <c r="A17" s="2">
+      <c r="A17" s="3">
         <v>45919</v>
       </c>
       <c r="B17">
-        <v>3451.251055716458</v>
+        <v>3451.201972853582</v>
       </c>
     </row>
     <row r="18" spans="1:2">
-      <c r="A18" s="2">
+      <c r="A18" s="3">
         <v>45926</v>
       </c>
       <c r="B18">
-        <v>3451.260132891587</v>
+        <v>3451.214576481073</v>
       </c>
     </row>
     <row r="19" spans="1:2">
-      <c r="A19" s="2">
+      <c r="A19" s="3">
         <v>45933</v>
       </c>
       <c r="B19">
-        <v>3537.372818065023</v>
+        <v>3537.136191230269</v>
       </c>
     </row>
     <row r="20" spans="1:2">
-      <c r="A20" s="2">
+      <c r="A20" s="3">
         <v>45940</v>
       </c>
       <c r="B20">
-        <v>3638.55172877928</v>
+        <v>3638.10082969744</v>
       </c>
     </row>
     <row r="21" spans="1:2">
-      <c r="A21" s="2">
+      <c r="A21" s="3">
         <v>45947</v>
       </c>
       <c r="B21">
-        <v>3794.937450998883</v>
+        <v>3794.261712368096</v>
       </c>
     </row>
     <row r="22" spans="1:2">
-      <c r="A22" s="2">
+      <c r="A22" s="3">
         <v>45954</v>
       </c>
       <c r="B22">
-        <v>3864.649134328479</v>
+        <v>3864.046610440113</v>
       </c>
     </row>
     <row r="23" spans="1:2">
-      <c r="A23" s="2">
+      <c r="A23" s="3">
         <v>45961</v>
       </c>
       <c r="B23">
-        <v>3910.467087601598</v>
+        <v>3909.918887420372</v>
       </c>
     </row>
     <row r="24" spans="1:2">
-      <c r="A24" s="2">
+      <c r="A24" s="3">
         <v>45968</v>
       </c>
       <c r="B24">
-        <v>3894.304486611611</v>
+        <v>3893.836888594765</v>
       </c>
     </row>
     <row r="25" spans="1:2">
-      <c r="A25" s="2">
+      <c r="A25" s="3">
         <v>45975</v>
       </c>
       <c r="B25">
-        <v>3891.137117572514</v>
+        <v>3890.949511997986</v>
       </c>
     </row>
     <row r="26" spans="1:2">
-      <c r="A26" s="2">
+      <c r="A26" s="3">
         <v>45982</v>
       </c>
       <c r="B26">
-        <v>3994.953532599965</v>
+        <v>3994.897277125676</v>
       </c>
     </row>
     <row r="27" spans="1:2">
-      <c r="A27" s="2">
+      <c r="A27" s="3">
         <v>45989</v>
       </c>
       <c r="B27">
-        <v>4072.360956744952</v>
+        <v>4072.163070120788</v>
       </c>
     </row>
     <row r="28" spans="1:2">
-      <c r="A28" s="2">
+      <c r="A28" s="3">
         <v>45996</v>
       </c>
       <c r="B28">
-        <v>4113.361605982325</v>
+        <v>4113.116865660926</v>
       </c>
     </row>
     <row r="29" spans="1:2">
-      <c r="A29" s="2">
+      <c r="A29" s="3">
         <v>46003</v>
       </c>
       <c r="B29">
-        <v>4207.027645501887</v>
+        <v>4206.993234488315</v>
       </c>
     </row>
     <row r="30" spans="1:2">
-      <c r="A30" s="2">
+      <c r="A30" s="3">
         <v>46010</v>
       </c>
       <c r="B30">
-        <v>4201.855242625677</v>
+        <v>4201.737252914189</v>
       </c>
     </row>
     <row r="31" spans="1:2">
-      <c r="A31" s="2">
+      <c r="A31" s="3">
         <v>46017</v>
       </c>
       <c r="B31">
-        <v>4230.241114955081</v>
+        <v>4229.930443171439</v>
       </c>
     </row>
     <row r="32" spans="1:2">
-      <c r="A32" s="2">
+      <c r="A32" s="3">
         <v>46024</v>
       </c>
       <c r="B32">
-        <v>4251.060703945151</v>
+        <v>4250.752631988815</v>
       </c>
     </row>
     <row r="33" spans="1:2">
-      <c r="A33" s="2">
+      <c r="A33" s="3">
         <v>46031</v>
       </c>
       <c r="B33">
-        <v>4318.044149418174</v>
+        <v>4317.617971065168</v>
       </c>
     </row>
     <row r="34" spans="1:2">
-      <c r="A34" s="2">
+      <c r="A34" s="3">
         <v>46038</v>
       </c>
       <c r="B34">
-        <v>4412.576169267773</v>
+        <v>4412.046164316412</v>
       </c>
     </row>
     <row r="35" spans="1:2">
-      <c r="A35" s="2">
+      <c r="A35" s="3">
         <v>46045</v>
       </c>
       <c r="B35">
-        <v>4449.457201992592</v>
+        <v>4448.889476291693</v>
       </c>
     </row>
     <row r="36" spans="1:2">
-      <c r="A36" s="2">
+      <c r="A36" s="3">
         <v>46052</v>
       </c>
       <c r="B36">
-        <v>4554.799363639628</v>
+        <v>4554.050677052541</v>
       </c>
     </row>
     <row r="37" spans="1:2">
-      <c r="A37" s="2">
+      <c r="A37" s="3">
         <v>46059</v>
       </c>
       <c r="B37">
-        <v>4693.519745011111</v>
+        <v>4692.608386398038</v>
       </c>
     </row>
     <row r="38" spans="1:2">
-      <c r="A38" s="2">
+      <c r="A38" s="3">
         <v>46066</v>
       </c>
       <c r="B38">
-        <v>4779.981187880887</v>
+        <v>4778.861069442875</v>
       </c>
     </row>
     <row r="39" spans="1:2">
-      <c r="A39" s="2">
+      <c r="A39" s="3">
         <v>46073</v>
       </c>
       <c r="B39">
-        <v>4907.029709440691</v>
+        <v>4906.346506925655</v>
       </c>
     </row>
     <row r="40" spans="1:2">
-      <c r="A40" s="2">
+      <c r="A40" s="3">
         <v>46080</v>
       </c>
       <c r="B40">
-        <v>4949.515402773082</v>
+        <v>4948.765208486164</v>
       </c>
     </row>
     <row r="41" spans="1:2">
-      <c r="A41" s="2">
+      <c r="A41" s="3">
         <v>46087</v>
       </c>
       <c r="B41">
-        <v>5060.459612494564</v>
+        <v>5059.493793238897</v>
       </c>
     </row>
     <row r="42" spans="1:2">
-      <c r="A42" s="2">
+      <c r="A42" s="3">
         <v>46094</v>
       </c>
       <c r="B42">
-        <v>5219.799689075102</v>
+        <v>5219.280185065968</v>
       </c>
     </row>
     <row r="43" spans="1:2">
-      <c r="A43" s="2">
+      <c r="A43" s="3">
         <v>46101</v>
       </c>
       <c r="B43">
-        <v>5252.307404083328</v>
+        <v>5252.302770151703</v>
       </c>
     </row>
     <row r="44" spans="1:2">
-      <c r="A44" s="2">
+      <c r="A44" s="3">
         <v>46108</v>
       </c>
       <c r="B44">
-        <v>5279.509049248424</v>
+        <v>5280.217938187019</v>
       </c>
     </row>
     <row r="45" spans="1:2">
-      <c r="A45" s="2">
+      <c r="A45" s="3">
         <v>46115</v>
       </c>
       <c r="B45">
-        <v>5346.619795965039</v>
+        <v>5347.815534311785</v>
       </c>
     </row>
     <row r="46" spans="1:2">
-      <c r="A46" s="2">
+      <c r="A46" s="3">
         <v>46122</v>
       </c>
       <c r="B46">
-        <v>5416.836250624086</v>
+        <v>5418.372126353801</v>
       </c>
     </row>
     <row r="47" spans="1:2">
-      <c r="A47" s="2">
+      <c r="A47" s="3">
         <v>46129</v>
       </c>
       <c r="B47">
-        <v>5544.417554467686</v>
+        <v>5546.086576335597</v>
       </c>
     </row>
     <row r="48" spans="1:2">
-      <c r="A48" s="2">
+      <c r="A48" s="3">
         <v>46136</v>
       </c>
       <c r="B48">
-        <v>5476.27344836844</v>
+        <v>5478.335748325466</v>
       </c>
     </row>
     <row r="49" spans="1:2">
-      <c r="A49" s="2">
+      <c r="A49" s="3">
         <v>46143</v>
       </c>
       <c r="B49">
-        <v>5292.042691554178</v>
+        <v>5294.569889716116</v>
       </c>
     </row>
     <row r="50" spans="1:2">
-      <c r="A50" s="2">
+      <c r="A50" s="3">
         <v>46150</v>
       </c>
       <c r="B50">
-        <v>5178.510725446049</v>
+        <v>5180.866770687767</v>
       </c>
     </row>
     <row r="51" spans="1:2">
-      <c r="A51" s="2">
+      <c r="A51" s="3">
         <v>46157</v>
       </c>
       <c r="B51">
-        <v>5041.423764129474</v>
+        <v>5043.918755426561</v>
       </c>
     </row>
     <row r="52" spans="1:2">
-      <c r="A52" s="2">
+      <c r="A52" s="3">
         <v>46164</v>
       </c>
       <c r="B52">
-        <v>4932.382464122468</v>
+        <v>4934.616429253658</v>
       </c>
     </row>
     <row r="53" spans="1:2">
-      <c r="A53" s="2">
+      <c r="A53" s="3">
         <v>46171</v>
       </c>
       <c r="B53">
-        <v>4831.931311832359</v>
+        <v>4834.030942840058</v>
       </c>
     </row>
     <row r="54" spans="1:2">
-      <c r="A54" s="2">
+      <c r="A54" s="3">
         <v>46178</v>
       </c>
       <c r="B54">
-        <v>4777.988946060454</v>
+        <v>4780.359155367962</v>
       </c>
     </row>
     <row r="55" spans="1:2">
-      <c r="A55" s="2">
+      <c r="A55" s="3">
         <v>46185</v>
       </c>
       <c r="B55">
-        <v>4658.662279356353</v>
+        <v>4660.57979505898</v>
       </c>
     </row>
     <row r="56" spans="1:2">
-      <c r="A56" s="2">
+      <c r="A56" s="3">
         <v>46192</v>
       </c>
       <c r="B56">
-        <v>4583.739718913337</v>
+        <v>4549.891752001517</v>
       </c>
     </row>
     <row r="57" spans="1:2">
-      <c r="A57" s="2">
+      <c r="A57" s="3">
         <v>46199</v>
       </c>
       <c r="B57">
-        <v>4530.558906265468</v>
+        <v>4495.559696096184</v>
       </c>
     </row>
     <row r="58" spans="1:2">
-      <c r="A58" s="2">
+      <c r="A58" s="3">
         <v>46206</v>
       </c>
       <c r="B58">
-        <v>4535.499201951737</v>
+        <v>4497.243171566681</v>
       </c>
     </row>
     <row r="59" spans="1:2">
-      <c r="A59" s="2">
+      <c r="A59" s="3">
         <v>46213</v>
       </c>
       <c r="B59">
-        <v>4506.792742316241</v>
+        <v>4462.749244602936</v>
       </c>
     </row>
     <row r="60" spans="1:2">
-      <c r="A60" s="2">
+      <c r="A60" s="3">
         <v>46220</v>
       </c>
       <c r="B60">
-        <v>4465.217647748474</v>
+        <v>4419.596797104705</v>
       </c>
     </row>
     <row r="61" spans="1:2">
-      <c r="A61" s="2">
+      <c r="A61" s="3">
         <v>46227</v>
       </c>
       <c r="B61">
-        <v>4389.636148759032</v>
+        <v>4346.212775934705</v>
       </c>
     </row>
     <row r="62" spans="1:2">
-      <c r="A62" s="2">
+      <c r="A62" s="3">
         <v>46234</v>
       </c>
       <c r="B62">
-        <v>4303.308438052945</v>
+        <v>4261.285302610337</v>
       </c>
     </row>
     <row r="63" spans="1:2">
-      <c r="A63" s="2">
+      <c r="A63" s="3">
         <v>46241</v>
       </c>
       <c r="B63">
-        <v>4229.682715059384</v>
+        <v>4190.162123715123</v>
       </c>
     </row>
     <row r="64" spans="1:2">
-      <c r="A64" s="2">
+      <c r="A64" s="3">
         <v>46248</v>
       </c>
       <c r="B64">
-        <v>4182.959471849997</v>
+        <v>4142.861380840877</v>
       </c>
     </row>
     <row r="65" spans="1:2">
-      <c r="A65" s="2">
+      <c r="A65" s="3">
         <v>46255</v>
       </c>
       <c r="B65">
-        <v>4142.656927871052</v>
+        <v>4094.399376033822</v>
       </c>
     </row>
     <row r="66" spans="1:2">
-      <c r="A66" s="2">
+      <c r="A66" s="3">
         <v>46262</v>
       </c>
       <c r="B66">
-        <v>4171.101917892369</v>
+        <v>4096.673502372364</v>
       </c>
     </row>
     <row r="67" spans="1:2">
-      <c r="A67" s="2">
+      <c r="A67" s="3">
         <v>46269</v>
       </c>
       <c r="B67">
-        <v>4130.148033946979</v>
+        <v>4035.083910321087</v>
       </c>
     </row>
     <row r="68" spans="1:2">
-      <c r="A68" s="2">
+      <c r="A68" s="3">
         <v>46276</v>
       </c>
       <c r="B68">
-        <v>4123.147475668284</v>
+        <v>4018.650187580855</v>
       </c>
     </row>
     <row r="69" spans="1:2">
-      <c r="A69" s="2">
+      <c r="A69" s="3">
         <v>46283</v>
       </c>
       <c r="B69">
-        <v>3948.913997013959</v>
+        <v>3848.537412420429</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2">
+      <c r="A70" s="3">
+        <v>46290</v>
+      </c>
+      <c r="B70">
+        <v>3580.536162420429</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/XAUUSD_forecast.xlsx
+++ b/public/data/files/XAUUSD_forecast.xlsx
@@ -383,7 +383,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B70"/>
+  <dimension ref="A1:B71"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" style="1" customWidth="1"/>
@@ -442,7 +442,7 @@
         <v>45849</v>
       </c>
       <c r="B7">
-        <v>3665.366280196959</v>
+        <v>3665.526124526293</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -450,7 +450,7 @@
         <v>45856</v>
       </c>
       <c r="B8">
-        <v>3561.331802230651</v>
+        <v>3561.546937002585</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -458,7 +458,7 @@
         <v>45863</v>
       </c>
       <c r="B9">
-        <v>3506.229801589443</v>
+        <v>3506.477530005397</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -466,7 +466,7 @@
         <v>45870</v>
       </c>
       <c r="B10">
-        <v>3478.34587214034</v>
+        <v>3478.607500655341</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -474,7 +474,7 @@
         <v>45877</v>
       </c>
       <c r="B11">
-        <v>3486.72016987905</v>
+        <v>3486.988282622609</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -482,7 +482,7 @@
         <v>45884</v>
       </c>
       <c r="B12">
-        <v>3499.44298318114</v>
+        <v>3499.714359698522</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -490,7 +490,7 @@
         <v>45891</v>
       </c>
       <c r="B13">
-        <v>3514.00125497858</v>
+        <v>3514.27064375103</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -498,7 +498,7 @@
         <v>45898</v>
       </c>
       <c r="B14">
-        <v>3526.594149900854</v>
+        <v>3526.85921978785</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -506,7 +506,7 @@
         <v>45905</v>
       </c>
       <c r="B15">
-        <v>3544.087033825478</v>
+        <v>3544.277355944153</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -514,7 +514,7 @@
         <v>45912</v>
       </c>
       <c r="B16">
-        <v>3453.727268146337</v>
+        <v>3453.674410412038</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -522,7 +522,7 @@
         <v>45919</v>
       </c>
       <c r="B17">
-        <v>3451.201972853582</v>
+        <v>3451.155160512135</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -530,7 +530,7 @@
         <v>45926</v>
       </c>
       <c r="B18">
-        <v>3451.214576481073</v>
+        <v>3451.171135490767</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -538,7 +538,7 @@
         <v>45933</v>
       </c>
       <c r="B19">
-        <v>3537.136191230269</v>
+        <v>3536.910341133193</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -546,7 +546,7 @@
         <v>45940</v>
       </c>
       <c r="B20">
-        <v>3638.10082969744</v>
+        <v>3637.670279597519</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -554,7 +554,7 @@
         <v>45947</v>
       </c>
       <c r="B21">
-        <v>3794.261712368096</v>
+        <v>3793.616074952135</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -562,7 +562,7 @@
         <v>45954</v>
       </c>
       <c r="B22">
-        <v>3864.046610440113</v>
+        <v>3863.470782045651</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -570,7 +570,7 @@
         <v>45961</v>
       </c>
       <c r="B23">
-        <v>3909.918887420372</v>
+        <v>3909.394166510521</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -578,7 +578,7 @@
         <v>45968</v>
       </c>
       <c r="B24">
-        <v>3893.836888594765</v>
+        <v>3893.388927405438</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -586,7 +586,7 @@
         <v>45975</v>
       </c>
       <c r="B25">
-        <v>3890.949511997986</v>
+        <v>3890.769355212464</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -594,7 +594,7 @@
         <v>45982</v>
       </c>
       <c r="B26">
-        <v>3994.897277125676</v>
+        <v>3994.842991112335</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -602,7 +602,7 @@
         <v>45989</v>
       </c>
       <c r="B27">
-        <v>4072.163070120788</v>
+        <v>4071.973624497567</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -610,7 +610,7 @@
         <v>45996</v>
       </c>
       <c r="B28">
-        <v>4113.116865660926</v>
+        <v>4112.882586211485</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -618,7 +618,7 @@
         <v>46003</v>
       </c>
       <c r="B29">
-        <v>4206.993234488315</v>
+        <v>4206.960747412826</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -626,7 +626,7 @@
         <v>46010</v>
       </c>
       <c r="B30">
-        <v>4201.737252914189</v>
+        <v>4201.625126443373</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -634,7 +634,7 @@
         <v>46017</v>
       </c>
       <c r="B31">
-        <v>4229.930443171439</v>
+        <v>4229.634534223031</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -642,7 +642,7 @@
         <v>46024</v>
       </c>
       <c r="B32">
-        <v>4250.752631988815</v>
+        <v>4250.45888624933</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -650,7 +650,7 @@
         <v>46031</v>
       </c>
       <c r="B33">
-        <v>4317.617971065168</v>
+        <v>4317.211303572447</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -658,7 +658,7 @@
         <v>46038</v>
       </c>
       <c r="B34">
-        <v>4412.046164316412</v>
+        <v>4411.540005517205</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -666,7 +666,7 @@
         <v>46045</v>
       </c>
       <c r="B35">
-        <v>4448.889476291693</v>
+        <v>4448.346922438437</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -674,7 +674,7 @@
         <v>46052</v>
       </c>
       <c r="B36">
-        <v>4554.050677052541</v>
+        <v>4553.334727073527</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -682,7 +682,7 @@
         <v>46059</v>
       </c>
       <c r="B37">
-        <v>4692.608386398038</v>
+        <v>4691.736964911082</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -690,7 +690,7 @@
         <v>46066</v>
       </c>
       <c r="B38">
-        <v>4778.861069442875</v>
+        <v>4777.787517640489</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -698,7 +698,7 @@
         <v>46073</v>
       </c>
       <c r="B39">
-        <v>4906.346506925655</v>
+        <v>4905.692985394227</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -706,7 +706,7 @@
         <v>46080</v>
       </c>
       <c r="B40">
-        <v>4948.765208486164</v>
+        <v>4948.047569303941</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -714,7 +714,7 @@
         <v>46087</v>
       </c>
       <c r="B41">
-        <v>5059.493793238897</v>
+        <v>5058.569126863788</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -722,7 +722,7 @@
         <v>46094</v>
       </c>
       <c r="B42">
-        <v>5219.280185065968</v>
+        <v>5218.7813856994</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>46101</v>
       </c>
       <c r="B43">
-        <v>5252.302770151703</v>
+        <v>5252.293976071873</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>46108</v>
       </c>
       <c r="B44">
-        <v>5280.217938187019</v>
+        <v>5280.890409465843</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>46115</v>
       </c>
       <c r="B45">
-        <v>5347.815534311785</v>
+        <v>5348.955048706393</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>46122</v>
       </c>
       <c r="B46">
-        <v>5418.372126353801</v>
+        <v>5419.836532005717</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>46129</v>
       </c>
       <c r="B47">
-        <v>5546.086576335597</v>
+        <v>5547.678493227982</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>46136</v>
       </c>
       <c r="B48">
-        <v>5478.335748325466</v>
+        <v>5480.306008798579</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>46143</v>
       </c>
       <c r="B49">
-        <v>5294.569889716116</v>
+        <v>5296.986674650409</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>46150</v>
       </c>
       <c r="B50">
-        <v>5180.866770687767</v>
+        <v>5183.12143794038</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>46157</v>
       </c>
       <c r="B51">
-        <v>5043.918755426561</v>
+        <v>5046.308782512795</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>46164</v>
       </c>
       <c r="B52">
-        <v>4934.616429253658</v>
+        <v>4936.757643458633</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>46171</v>
       </c>
       <c r="B53">
-        <v>4834.030942840058</v>
+        <v>4836.045502779358</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>46178</v>
       </c>
       <c r="B54">
-        <v>4780.359155367962</v>
+        <v>4782.633598739699</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>46185</v>
       </c>
       <c r="B55">
-        <v>4660.57979505898</v>
+        <v>4662.419110507833</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>46192</v>
       </c>
       <c r="B56">
-        <v>4549.891752001517</v>
+        <v>4551.204292925441</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>46199</v>
       </c>
       <c r="B57">
-        <v>4495.559696096184</v>
+        <v>4462.938314930931</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>46206</v>
       </c>
       <c r="B58">
-        <v>4497.243171566681</v>
+        <v>4457.771641295265</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>46213</v>
       </c>
       <c r="B59">
-        <v>4462.749244602936</v>
+        <v>4422.304065418466</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>46220</v>
       </c>
       <c r="B60">
-        <v>4419.596797104705</v>
+        <v>4372.198437644472</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>46227</v>
       </c>
       <c r="B61">
-        <v>4346.212775934705</v>
+        <v>4297.828391938236</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>46234</v>
       </c>
       <c r="B62">
-        <v>4261.285302610337</v>
+        <v>4214.160790832328</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>46241</v>
       </c>
       <c r="B63">
-        <v>4190.162123715123</v>
+        <v>4144.177276301447</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46248</v>
       </c>
       <c r="B64">
-        <v>4142.861380840877</v>
+        <v>4096.300106516735</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46255</v>
       </c>
       <c r="B65">
-        <v>4094.399376033822</v>
+        <v>4048.834213667687</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46262</v>
       </c>
       <c r="B66">
-        <v>4096.673502372364</v>
+        <v>4035.235296857698</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46269</v>
       </c>
       <c r="B67">
-        <v>4035.083910321087</v>
+        <v>3969.937540624196</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46276</v>
       </c>
       <c r="B68">
-        <v>4018.650187580855</v>
+        <v>3944.310340308544</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46283</v>
       </c>
       <c r="B69">
-        <v>3848.537412420429</v>
+        <v>3775.265229575036</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,15 @@
         <v>46290</v>
       </c>
       <c r="B70">
-        <v>3580.536162420429</v>
+        <v>3513.507729575035</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2">
+      <c r="A71" s="3">
+        <v>46297</v>
+      </c>
+      <c r="B71">
+        <v>3352.345057132062</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/XAUUSD_forecast.xlsx
+++ b/public/data/files/XAUUSD_forecast.xlsx
@@ -383,7 +383,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B71"/>
+  <dimension ref="A1:B72"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" style="1" customWidth="1"/>
@@ -442,7 +442,7 @@
         <v>45849</v>
       </c>
       <c r="B7">
-        <v>3665.526124526293</v>
+        <v>3665.679022460136</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -450,7 +450,7 @@
         <v>45856</v>
       </c>
       <c r="B8">
-        <v>3561.546937002585</v>
+        <v>3561.752793111688</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -458,7 +458,7 @@
         <v>45863</v>
       </c>
       <c r="B9">
-        <v>3506.477530005397</v>
+        <v>3506.714649732255</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -466,7 +466,7 @@
         <v>45870</v>
       </c>
       <c r="B10">
-        <v>3478.607500655341</v>
+        <v>3478.858028158641</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -474,7 +474,7 @@
         <v>45877</v>
       </c>
       <c r="B11">
-        <v>3486.988282622609</v>
+        <v>3487.245015475254</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -482,7 +482,7 @@
         <v>45884</v>
       </c>
       <c r="B12">
-        <v>3499.714359698522</v>
+        <v>3499.974213693803</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -490,7 +490,7 @@
         <v>45891</v>
       </c>
       <c r="B13">
-        <v>3514.27064375103</v>
+        <v>3514.528592152295</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -498,7 +498,7 @@
         <v>45898</v>
       </c>
       <c r="B14">
-        <v>3526.85921978785</v>
+        <v>3527.113032541578</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -506,7 +506,7 @@
         <v>45905</v>
       </c>
       <c r="B15">
-        <v>3544.277355944153</v>
+        <v>3544.45986303195</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -514,7 +514,7 @@
         <v>45912</v>
       </c>
       <c r="B16">
-        <v>3453.674410412038</v>
+        <v>3453.623930944016</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -522,7 +522,7 @@
         <v>45919</v>
       </c>
       <c r="B17">
-        <v>3451.155160512135</v>
+        <v>3451.110465039589</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -530,7 +530,7 @@
         <v>45926</v>
       </c>
       <c r="B18">
-        <v>3451.171135490767</v>
+        <v>3451.129666273648</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -538,7 +538,7 @@
         <v>45933</v>
       </c>
       <c r="B19">
-        <v>3536.910341133193</v>
+        <v>3536.694549139229</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -546,7 +546,7 @@
         <v>45940</v>
       </c>
       <c r="B20">
-        <v>3637.670279597519</v>
+        <v>3637.258734003628</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -554,7 +554,7 @@
         <v>45947</v>
       </c>
       <c r="B21">
-        <v>3793.616074952135</v>
+        <v>3792.998574824054</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -562,7 +562,7 @@
         <v>45954</v>
       </c>
       <c r="B22">
-        <v>3863.470782045651</v>
+        <v>3862.91991571939</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -570,7 +570,7 @@
         <v>45961</v>
       </c>
       <c r="B23">
-        <v>3909.394166510521</v>
+        <v>3908.891453558732</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -578,7 +578,7 @@
         <v>45968</v>
       </c>
       <c r="B24">
-        <v>3893.388927405438</v>
+        <v>3892.959398303816</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -586,7 +586,7 @@
         <v>45975</v>
       </c>
       <c r="B25">
-        <v>3890.769355212464</v>
+        <v>3890.596218333257</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -594,7 +594,7 @@
         <v>45982</v>
       </c>
       <c r="B26">
-        <v>3994.842991112335</v>
+        <v>3994.790579344961</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -602,7 +602,7 @@
         <v>45989</v>
       </c>
       <c r="B27">
-        <v>4071.973624497567</v>
+        <v>4071.792091331027</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -610,7 +610,7 @@
         <v>45996</v>
       </c>
       <c r="B28">
-        <v>4112.882586211485</v>
+        <v>4112.658111940666</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -618,7 +618,7 @@
         <v>46003</v>
       </c>
       <c r="B29">
-        <v>4206.960747412826</v>
+        <v>4206.930034048102</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -626,7 +626,7 @@
         <v>46010</v>
       </c>
       <c r="B30">
-        <v>4201.625126443373</v>
+        <v>4201.518443335543</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -634,7 +634,7 @@
         <v>46017</v>
       </c>
       <c r="B31">
-        <v>4229.634534223031</v>
+        <v>4229.352369484518</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -642,7 +642,7 @@
         <v>46024</v>
       </c>
       <c r="B32">
-        <v>4250.45888624933</v>
+        <v>4250.17849939266</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -650,7 +650,7 @@
         <v>46031</v>
       </c>
       <c r="B33">
-        <v>4317.211303572447</v>
+        <v>4316.822848967246</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -658,7 +658,7 @@
         <v>46038</v>
       </c>
       <c r="B34">
-        <v>4411.540005517205</v>
+        <v>4411.056133411858</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -666,7 +666,7 @@
         <v>46045</v>
       </c>
       <c r="B35">
-        <v>4448.346922438437</v>
+        <v>4447.827914231251</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -674,7 +674,7 @@
         <v>46052</v>
       </c>
       <c r="B36">
-        <v>4553.334727073527</v>
+        <v>4552.64942469597</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -682,7 +682,7 @@
         <v>46059</v>
       </c>
       <c r="B37">
-        <v>4691.736964911082</v>
+        <v>4690.902928531076</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -690,7 +690,7 @@
         <v>46066</v>
       </c>
       <c r="B38">
-        <v>4777.787517640489</v>
+        <v>4776.757708108302</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -698,7 +698,7 @@
         <v>46073</v>
       </c>
       <c r="B39">
-        <v>4905.692985394227</v>
+        <v>4905.067265795093</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -706,7 +706,7 @@
         <v>46080</v>
       </c>
       <c r="B40">
-        <v>4948.047569303941</v>
+        <v>4947.360426376772</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -714,7 +714,7 @@
         <v>46087</v>
       </c>
       <c r="B41">
-        <v>5058.569126863788</v>
+        <v>5057.683065006054</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -722,7 +722,7 @@
         <v>46094</v>
       </c>
       <c r="B42">
-        <v>5218.7813856994</v>
+        <v>5218.302100468238</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>46101</v>
       </c>
       <c r="B43">
-        <v>5252.293976071873</v>
+        <v>5252.281571531769</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>46108</v>
       </c>
       <c r="B44">
-        <v>5280.890409465843</v>
+        <v>5281.529134731598</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>46115</v>
       </c>
       <c r="B45">
-        <v>5348.955048706393</v>
+        <v>5350.042177985591</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>46122</v>
       </c>
       <c r="B46">
-        <v>5419.836532005717</v>
+        <v>5421.234294643914</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>46129</v>
       </c>
       <c r="B47">
-        <v>5547.678493227982</v>
+        <v>5549.1984847046</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>46136</v>
       </c>
       <c r="B48">
-        <v>5480.306008798579</v>
+        <v>5482.190218925877</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>46143</v>
       </c>
       <c r="B49">
-        <v>5296.986674650409</v>
+        <v>5299.300065833633</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>46150</v>
       </c>
       <c r="B50">
-        <v>5183.12143794038</v>
+        <v>5185.281070188523</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>46157</v>
       </c>
       <c r="B51">
-        <v>5046.308782512795</v>
+        <v>5048.60025852636</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>46164</v>
       </c>
       <c r="B52">
-        <v>4936.757643458633</v>
+        <v>4938.81170807807</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>46171</v>
       </c>
       <c r="B53">
-        <v>4836.045502779358</v>
+        <v>4837.979992145311</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>46178</v>
       </c>
       <c r="B54">
-        <v>4782.633598739699</v>
+        <v>4784.817884295675</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>46185</v>
       </c>
       <c r="B55">
-        <v>4662.419110507833</v>
+        <v>4664.184858568104</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>46192</v>
       </c>
       <c r="B56">
-        <v>4551.204292925441</v>
+        <v>4552.462782469111</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>46199</v>
       </c>
       <c r="B57">
-        <v>4462.938314930931</v>
+        <v>4463.819963969037</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>46206</v>
       </c>
       <c r="B58">
-        <v>4457.771641295265</v>
+        <v>4458.670352555411</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>46213</v>
       </c>
       <c r="B59">
-        <v>4422.304065418466</v>
+        <v>4397.599823781841</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>46220</v>
       </c>
       <c r="B60">
-        <v>4372.198437644472</v>
+        <v>4350.226241798083</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>46227</v>
       </c>
       <c r="B61">
-        <v>4297.828391938236</v>
+        <v>4281.03553044707</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>46234</v>
       </c>
       <c r="B62">
-        <v>4214.160790832328</v>
+        <v>4200.028060639483</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>46241</v>
       </c>
       <c r="B63">
-        <v>4144.177276301447</v>
+        <v>4131.910190381057</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46248</v>
       </c>
       <c r="B64">
-        <v>4096.300106516735</v>
+        <v>4083.211772082779</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46255</v>
       </c>
       <c r="B65">
-        <v>4048.834213667687</v>
+        <v>4037.194992240904</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46262</v>
       </c>
       <c r="B66">
-        <v>4035.235296857698</v>
+        <v>4025.789993208415</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46269</v>
       </c>
       <c r="B67">
-        <v>3969.937540624196</v>
+        <v>3973.220087808256</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46276</v>
       </c>
       <c r="B68">
-        <v>3944.310340308544</v>
+        <v>3949.307124772293</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46283</v>
       </c>
       <c r="B69">
-        <v>3775.265229575036</v>
+        <v>3806.907967528636</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46290</v>
       </c>
       <c r="B70">
-        <v>3513.507729575035</v>
+        <v>3629.004186094284</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,15 @@
         <v>46297</v>
       </c>
       <c r="B71">
-        <v>3352.345057132062</v>
+        <v>3634.203599659087</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2">
+      <c r="A72" s="3">
+        <v>46304</v>
+      </c>
+      <c r="B72">
+        <v>3850.499849659087</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/XAUUSD_forecast.xlsx
+++ b/public/data/files/XAUUSD_forecast.xlsx
@@ -866,7 +866,7 @@
         <v>46220</v>
       </c>
       <c r="B60">
-        <v>4350.226241798083</v>
+        <v>4350.281021282346</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>46227</v>
       </c>
       <c r="B61">
-        <v>4281.03553044707</v>
+        <v>4281.075780087936</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>46234</v>
       </c>
       <c r="B62">
-        <v>4200.028060639483</v>
+        <v>4200.005279393428</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>46241</v>
       </c>
       <c r="B63">
-        <v>4131.910190381057</v>
+        <v>4131.646273889184</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46248</v>
       </c>
       <c r="B64">
-        <v>4083.211772082779</v>
+        <v>4083.052209544641</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46255</v>
       </c>
       <c r="B65">
-        <v>4037.194992240904</v>
+        <v>4037.792371462809</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46262</v>
       </c>
       <c r="B66">
-        <v>4025.789993208415</v>
+        <v>4028.386065622824</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46269</v>
       </c>
       <c r="B67">
-        <v>3973.220087808256</v>
+        <v>3978.143562477785</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46276</v>
       </c>
       <c r="B68">
-        <v>3949.307124772293</v>
+        <v>3956.27476969637</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46283</v>
       </c>
       <c r="B69">
-        <v>3806.907967528636</v>
+        <v>3814.208761597102</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46290</v>
       </c>
       <c r="B70">
-        <v>3629.004186094284</v>
+        <v>3627.718426919945</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46297</v>
       </c>
       <c r="B71">
-        <v>3634.203599659087</v>
+        <v>3630.41879920149</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46304</v>
       </c>
       <c r="B72">
-        <v>3850.499849659087</v>
+        <v>3846.71504920149</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/XAUUSD_forecast.xlsx
+++ b/public/data/files/XAUUSD_forecast.xlsx
@@ -442,7 +442,7 @@
         <v>45849</v>
       </c>
       <c r="B7">
-        <v>3665.679022460136</v>
+        <v>3665.825417108814</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -450,7 +450,7 @@
         <v>45856</v>
       </c>
       <c r="B8">
-        <v>3561.752793111688</v>
+        <v>3561.9499579517</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -458,7 +458,7 @@
         <v>45863</v>
       </c>
       <c r="B9">
-        <v>3506.714649732255</v>
+        <v>3506.94182749978</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -466,7 +466,7 @@
         <v>45870</v>
       </c>
       <c r="B10">
-        <v>3478.858028158641</v>
+        <v>3479.098145690069</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -474,7 +474,7 @@
         <v>45877</v>
       </c>
       <c r="B11">
-        <v>3487.245015475254</v>
+        <v>3487.491077069765</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -482,7 +482,7 @@
         <v>45884</v>
       </c>
       <c r="B12">
-        <v>3499.974213693803</v>
+        <v>3500.223262943125</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -490,7 +490,7 @@
         <v>45891</v>
       </c>
       <c r="B13">
-        <v>3514.528592152295</v>
+        <v>3514.775812989179</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -498,7 +498,7 @@
         <v>45898</v>
       </c>
       <c r="B14">
-        <v>3527.113032541578</v>
+        <v>3527.356289567586</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -506,7 +506,7 @@
         <v>45905</v>
       </c>
       <c r="B15">
-        <v>3544.45986303195</v>
+        <v>3544.635024892219</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -514,7 +514,7 @@
         <v>45912</v>
       </c>
       <c r="B16">
-        <v>3453.623930944016</v>
+        <v>3453.575673036749</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -522,7 +522,7 @@
         <v>45919</v>
       </c>
       <c r="B17">
-        <v>3451.110465039589</v>
+        <v>3451.067746315344</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -530,7 +530,7 @@
         <v>45926</v>
       </c>
       <c r="B18">
-        <v>3451.129666273648</v>
+        <v>3451.090037872704</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -538,7 +538,7 @@
         <v>45933</v>
       </c>
       <c r="B19">
-        <v>3536.694549139229</v>
+        <v>3536.488159024671</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -546,7 +546,7 @@
         <v>45940</v>
       </c>
       <c r="B20">
-        <v>3637.258734003628</v>
+        <v>3636.864964115573</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -554,7 +554,7 @@
         <v>45947</v>
       </c>
       <c r="B21">
-        <v>3792.998574824054</v>
+        <v>3792.407414976839</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -562,7 +562,7 @@
         <v>45954</v>
       </c>
       <c r="B22">
-        <v>3862.91991571939</v>
+        <v>3862.392424745947</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -570,7 +570,7 @@
         <v>45961</v>
       </c>
       <c r="B23">
-        <v>3908.891453558732</v>
+        <v>3908.409397209847</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -578,7 +578,7 @@
         <v>45968</v>
       </c>
       <c r="B24">
-        <v>3892.959398303816</v>
+        <v>3892.54719255016</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -586,7 +586,7 @@
         <v>45975</v>
       </c>
       <c r="B25">
-        <v>3890.596218333257</v>
+        <v>3890.429704238315</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -594,7 +594,7 @@
         <v>45982</v>
       </c>
       <c r="B26">
-        <v>3994.790579344961</v>
+        <v>3994.739952002164</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -602,7 +602,7 @@
         <v>45989</v>
       </c>
       <c r="B27">
-        <v>4071.792091331027</v>
+        <v>4071.617985286198</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -610,7 +610,7 @@
         <v>45996</v>
       </c>
       <c r="B28">
-        <v>4112.658111940666</v>
+        <v>4112.44284075591</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -618,7 +618,7 @@
         <v>46003</v>
       </c>
       <c r="B29">
-        <v>4206.930034048102</v>
+        <v>4206.900958968042</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -626,7 +626,7 @@
         <v>46010</v>
       </c>
       <c r="B30">
-        <v>4201.518443335543</v>
+        <v>4201.416822387064</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -634,7 +634,7 @@
         <v>46017</v>
       </c>
       <c r="B31">
-        <v>4229.352369484518</v>
+        <v>4229.083021227206</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -642,7 +642,7 @@
         <v>46024</v>
       </c>
       <c r="B32">
-        <v>4250.17849939266</v>
+        <v>4249.910588533929</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -650,7 +650,7 @@
         <v>46031</v>
       </c>
       <c r="B33">
-        <v>4316.822848967246</v>
+        <v>4316.451420973786</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -658,7 +658,7 @@
         <v>46038</v>
       </c>
       <c r="B34">
-        <v>4411.056133411858</v>
+        <v>4410.593120462887</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -666,7 +666,7 @@
         <v>46045</v>
       </c>
       <c r="B35">
-        <v>4447.827914231251</v>
+        <v>4447.330961662631</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -674,7 +674,7 @@
         <v>46052</v>
       </c>
       <c r="B36">
-        <v>4552.64942469597</v>
+        <v>4551.992853963331</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -682,7 +682,7 @@
         <v>46059</v>
       </c>
       <c r="B37">
-        <v>4690.902928531076</v>
+        <v>4690.103936773303</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -690,7 +690,7 @@
         <v>46066</v>
       </c>
       <c r="B38">
-        <v>4776.757708108302</v>
+        <v>4775.769038664692</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -698,7 +698,7 @@
         <v>46073</v>
       </c>
       <c r="B39">
-        <v>4905.067265795093</v>
+        <v>4904.467623262426</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -706,7 +706,7 @@
         <v>46080</v>
       </c>
       <c r="B40">
-        <v>4947.360426376772</v>
+        <v>4946.701889625358</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -714,7 +714,7 @@
         <v>46087</v>
       </c>
       <c r="B41">
-        <v>5057.683065006054</v>
+        <v>5056.833263212125</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -722,7 +722,7 @@
         <v>46094</v>
       </c>
       <c r="B42">
-        <v>5218.302100468238</v>
+        <v>5217.841226358334</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>46101</v>
       </c>
       <c r="B43">
-        <v>5252.281571531769</v>
+        <v>5252.266036470277</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>46108</v>
       </c>
       <c r="B44">
-        <v>5281.529134731598</v>
+        <v>5282.136535134327</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>46115</v>
       </c>
       <c r="B45">
-        <v>5350.042177985591</v>
+        <v>5351.080422058005</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>46122</v>
       </c>
       <c r="B46">
-        <v>5421.234294643914</v>
+        <v>5422.569819981321</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>46129</v>
       </c>
       <c r="B47">
-        <v>5549.1984847046</v>
+        <v>5550.651279947756</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>46136</v>
       </c>
       <c r="B48">
-        <v>5482.190218925877</v>
+        <v>5483.993862317343</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>46143</v>
       </c>
       <c r="B49">
-        <v>5299.300065833633</v>
+        <v>5301.516505127747</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>46150</v>
       </c>
       <c r="B50">
-        <v>5185.281070188523</v>
+        <v>5187.351497231594</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>46157</v>
       </c>
       <c r="B51">
-        <v>5048.60025852636</v>
+        <v>5050.799090760469</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>46164</v>
       </c>
       <c r="B52">
-        <v>4938.81170807807</v>
+        <v>4940.783787125106</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>46171</v>
       </c>
       <c r="B53">
-        <v>4837.979992145311</v>
+        <v>4839.839032743495</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>46178</v>
       </c>
       <c r="B54">
-        <v>4784.817884295675</v>
+        <v>4786.917197491745</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>46185</v>
       </c>
       <c r="B55">
-        <v>4664.184858568104</v>
+        <v>4665.881317843631</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>46192</v>
       </c>
       <c r="B56">
-        <v>4552.462782469111</v>
+        <v>4553.670466243902</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>46199</v>
       </c>
       <c r="B57">
-        <v>4463.819963969037</v>
+        <v>4464.66372053279</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>46206</v>
       </c>
       <c r="B58">
-        <v>4458.670352555411</v>
+        <v>4459.530442722473</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>46213</v>
       </c>
       <c r="B59">
-        <v>4397.599823781841</v>
+        <v>4376.130699609882</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>46220</v>
       </c>
       <c r="B60">
-        <v>4350.281021282346</v>
+        <v>4331.366367262599</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>46227</v>
       </c>
       <c r="B61">
-        <v>4281.075780087936</v>
+        <v>4266.728942084519</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>46234</v>
       </c>
       <c r="B62">
-        <v>4200.005279393428</v>
+        <v>4187.99798495404</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>46241</v>
       </c>
       <c r="B63">
-        <v>4131.646273889184</v>
+        <v>4121.139556008696</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46248</v>
       </c>
       <c r="B64">
-        <v>4083.052209544641</v>
+        <v>4072.106479175191</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46255</v>
       </c>
       <c r="B65">
-        <v>4037.792371462809</v>
+        <v>4028.827341686689</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46262</v>
       </c>
       <c r="B66">
-        <v>4028.386065622824</v>
+        <v>4023.07480226476</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46269</v>
       </c>
       <c r="B67">
-        <v>3978.143562477785</v>
+        <v>3984.217710161926</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46276</v>
       </c>
       <c r="B68">
-        <v>3956.27476969637</v>
+        <v>3965.140755258864</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46283</v>
       </c>
       <c r="B69">
-        <v>3814.208761597102</v>
+        <v>3841.805209854482</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46290</v>
       </c>
       <c r="B70">
-        <v>3627.718426919945</v>
+        <v>3704.655548157294</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46297</v>
       </c>
       <c r="B71">
-        <v>3630.41879920149</v>
+        <v>3722.886383690039</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46304</v>
       </c>
       <c r="B72">
-        <v>3846.71504920149</v>
+        <v>3908.53396195068</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/XAUUSD_forecast.xlsx
+++ b/public/data/files/XAUUSD_forecast.xlsx
@@ -383,7 +383,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B72"/>
+  <dimension ref="A1:B73"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" style="1" customWidth="1"/>
@@ -442,7 +442,7 @@
         <v>45849</v>
       </c>
       <c r="B7">
-        <v>3665.825417108814</v>
+        <v>3665.965714684698</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -450,7 +450,7 @@
         <v>45856</v>
       </c>
       <c r="B8">
-        <v>3561.9499579517</v>
+        <v>3562.13897037732</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -458,7 +458,7 @@
         <v>45863</v>
       </c>
       <c r="B9">
-        <v>3506.94182749978</v>
+        <v>3507.159675350025</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -466,7 +466,7 @@
         <v>45870</v>
       </c>
       <c r="B10">
-        <v>3479.098145690069</v>
+        <v>3479.328488164801</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -474,7 +474,7 @@
         <v>45877</v>
       </c>
       <c r="B11">
-        <v>3487.491077069765</v>
+        <v>3487.727118466544</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -482,7 +482,7 @@
         <v>45884</v>
       </c>
       <c r="B12">
-        <v>3500.223262943125</v>
+        <v>3500.462166885603</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -490,7 +490,7 @@
         <v>45891</v>
       </c>
       <c r="B13">
-        <v>3514.775812989179</v>
+        <v>3515.012961122615</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -498,7 +498,7 @@
         <v>45898</v>
       </c>
       <c r="B14">
-        <v>3527.356289567586</v>
+        <v>3527.589635250732</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -506,7 +506,7 @@
         <v>45905</v>
       </c>
       <c r="B15">
-        <v>3544.635024892219</v>
+        <v>3544.803274567213</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -514,7 +514,7 @@
         <v>45912</v>
       </c>
       <c r="B16">
-        <v>3453.575673036749</v>
+        <v>3453.529493434789</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -522,7 +522,7 @@
         <v>45919</v>
       </c>
       <c r="B17">
-        <v>3451.067746315344</v>
+        <v>3451.026876295723</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -530,7 +530,7 @@
         <v>45926</v>
       </c>
       <c r="B18">
-        <v>3451.090037872704</v>
+        <v>3451.052130652582</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -538,7 +538,7 @@
         <v>45933</v>
       </c>
       <c r="B19">
-        <v>3536.488159024671</v>
+        <v>3536.290570354766</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -546,7 +546,7 @@
         <v>45940</v>
       </c>
       <c r="B20">
-        <v>3636.864964115573</v>
+        <v>3636.48784465128</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -554,7 +554,7 @@
         <v>45947</v>
       </c>
       <c r="B21">
-        <v>3792.407414976839</v>
+        <v>3791.840947987487</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -562,7 +562,7 @@
         <v>45954</v>
       </c>
       <c r="B22">
-        <v>3862.392424745947</v>
+        <v>3861.886853939261</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -570,7 +570,7 @@
         <v>45961</v>
       </c>
       <c r="B23">
-        <v>3908.409397209847</v>
+        <v>3907.946754132779</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -578,7 +578,7 @@
         <v>45968</v>
       </c>
       <c r="B24">
-        <v>3892.54719255016</v>
+        <v>3892.151288089049</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -586,7 +586,7 @@
         <v>45975</v>
       </c>
       <c r="B25">
-        <v>3890.429704238315</v>
+        <v>3890.269444739883</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -594,7 +594,7 @@
         <v>45982</v>
       </c>
       <c r="B26">
-        <v>3994.739952002164</v>
+        <v>3994.691024364334</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -602,7 +602,7 @@
         <v>45989</v>
       </c>
       <c r="B27">
-        <v>4071.617985286198</v>
+        <v>4071.450859911333</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -610,7 +610,7 @@
         <v>45996</v>
       </c>
       <c r="B28">
-        <v>4112.44284075591</v>
+        <v>4112.236218805515</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -618,7 +618,7 @@
         <v>46003</v>
       </c>
       <c r="B29">
-        <v>4206.900958968042</v>
+        <v>4206.873399806056</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -626,7 +626,7 @@
         <v>46010</v>
       </c>
       <c r="B30">
-        <v>4201.416822387064</v>
+        <v>4201.319916759981</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -634,7 +634,7 @@
         <v>46017</v>
       </c>
       <c r="B31">
-        <v>4229.083021227206</v>
+        <v>4228.825642768727</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -642,7 +642,7 @@
         <v>46024</v>
       </c>
       <c r="B32">
-        <v>4249.910588533929</v>
+        <v>4249.654346288259</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -650,7 +650,7 @@
         <v>46031</v>
       </c>
       <c r="B33">
-        <v>4316.451420973786</v>
+        <v>4316.095933342481</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -658,7 +658,7 @@
         <v>46038</v>
       </c>
       <c r="B34">
-        <v>4410.593120462887</v>
+        <v>4410.149657506935</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -666,7 +666,7 @@
         <v>46045</v>
       </c>
       <c r="B35">
-        <v>4447.330961662631</v>
+        <v>4446.854697046093</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -674,7 +674,7 @@
         <v>46052</v>
       </c>
       <c r="B36">
-        <v>4551.992853963331</v>
+        <v>4551.363254512205</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -682,7 +682,7 @@
         <v>46059</v>
       </c>
       <c r="B37">
-        <v>4690.103936773303</v>
+        <v>4689.337839351359</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -690,7 +690,7 @@
         <v>46066</v>
       </c>
       <c r="B38">
-        <v>4775.769038664692</v>
+        <v>4774.81910805861</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -698,7 +698,7 @@
         <v>46073</v>
       </c>
       <c r="B39">
-        <v>4904.467623262426</v>
+        <v>4903.892471735255</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -706,7 +706,7 @@
         <v>46080</v>
       </c>
       <c r="B40">
-        <v>4946.701889625358</v>
+        <v>4946.070220921409</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -714,7 +714,7 @@
         <v>46087</v>
       </c>
       <c r="B41">
-        <v>5056.833263212125</v>
+        <v>5056.017561172949</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -722,7 +722,7 @@
         <v>46094</v>
       </c>
       <c r="B42">
-        <v>5217.841226358334</v>
+        <v>5217.397740185603</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>46101</v>
       </c>
       <c r="B43">
-        <v>5252.266036470277</v>
+        <v>5252.247790643612</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>46108</v>
       </c>
       <c r="B44">
-        <v>5282.136535134327</v>
+        <v>5282.714809601872</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>46115</v>
       </c>
       <c r="B45">
-        <v>5351.080422058005</v>
+        <v>5352.072978234413</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>46122</v>
       </c>
       <c r="B46">
-        <v>5422.569819981321</v>
+        <v>5423.847137007542</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>46129</v>
       </c>
       <c r="B47">
-        <v>5550.651279947756</v>
+        <v>5552.041205344083</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>46136</v>
       </c>
       <c r="B48">
-        <v>5483.993862317343</v>
+        <v>5485.721968984441</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>46143</v>
       </c>
       <c r="B49">
-        <v>5301.516505127747</v>
+        <v>5303.641914485765</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>46150</v>
       </c>
       <c r="B50">
-        <v>5187.351497231594</v>
+        <v>5189.338086028414</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>46157</v>
       </c>
       <c r="B51">
-        <v>5050.799090760469</v>
+        <v>5052.910728938534</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>46164</v>
       </c>
       <c r="B52">
-        <v>4940.783787125106</v>
+        <v>4942.678648654383</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>46171</v>
       </c>
       <c r="B53">
-        <v>4839.839032743495</v>
+        <v>4841.626902275815</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>46178</v>
       </c>
       <c r="B54">
-        <v>4786.917197491745</v>
+        <v>4788.936339486594</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>46185</v>
       </c>
       <c r="B55">
-        <v>4665.881317843631</v>
+        <v>4667.512445429507</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>46192</v>
       </c>
       <c r="B56">
-        <v>4553.670466243902</v>
+        <v>4554.830337184348</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>46199</v>
       </c>
       <c r="B57">
-        <v>4464.66372053279</v>
+        <v>4465.471955603531</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>46206</v>
       </c>
       <c r="B58">
-        <v>4459.530442722473</v>
+        <v>4460.354331390161</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>46213</v>
       </c>
       <c r="B59">
-        <v>4376.130699609882</v>
+        <v>4377.136691119367</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>46220</v>
       </c>
       <c r="B60">
-        <v>4331.366367262599</v>
+        <v>4305.026983517295</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>46227</v>
       </c>
       <c r="B61">
-        <v>4266.728942084519</v>
+        <v>4241.352655140632</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>46234</v>
       </c>
       <c r="B62">
-        <v>4187.99798495404</v>
+        <v>4166.370701403982</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>46241</v>
       </c>
       <c r="B63">
-        <v>4121.139556008696</v>
+        <v>4097.585045329775</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46248</v>
       </c>
       <c r="B64">
-        <v>4072.106479175191</v>
+        <v>4047.825590817817</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46255</v>
       </c>
       <c r="B65">
-        <v>4028.827341686689</v>
+        <v>4005.109855551708</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46262</v>
       </c>
       <c r="B66">
-        <v>4023.07480226476</v>
+        <v>3996.094294194774</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46269</v>
       </c>
       <c r="B67">
-        <v>3984.217710161926</v>
+        <v>3958.700560061878</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46276</v>
       </c>
       <c r="B68">
-        <v>3965.140755258864</v>
+        <v>3942.946944722922</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46283</v>
       </c>
       <c r="B69">
-        <v>3841.805209854482</v>
+        <v>3828.081272350092</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46290</v>
       </c>
       <c r="B70">
-        <v>3704.655548157294</v>
+        <v>3706.725431253613</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46297</v>
       </c>
       <c r="B71">
-        <v>3722.886383690039</v>
+        <v>3720.783084330614</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,15 @@
         <v>46304</v>
       </c>
       <c r="B72">
-        <v>3908.53396195068</v>
+        <v>3840.748098653527</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2">
+      <c r="A73" s="3">
+        <v>46311</v>
+      </c>
+      <c r="B73">
+        <v>3738.772360087982</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/XAUUSD_forecast.xlsx
+++ b/public/data/files/XAUUSD_forecast.xlsx
@@ -442,7 +442,7 @@
         <v>45849</v>
       </c>
       <c r="B7">
-        <v>3665.965714684698</v>
+        <v>3666.100288263996</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -450,7 +450,7 @@
         <v>45856</v>
       </c>
       <c r="B8">
-        <v>3562.13897037732</v>
+        <v>3562.320325614821</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -458,7 +458,7 @@
         <v>45863</v>
       </c>
       <c r="B9">
-        <v>3507.159675350025</v>
+        <v>3507.368756128255</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -466,7 +466,7 @@
         <v>45870</v>
       </c>
       <c r="B10">
-        <v>3479.328488164801</v>
+        <v>3479.549639951322</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -474,7 +474,7 @@
         <v>45877</v>
       </c>
       <c r="B11">
-        <v>3487.727118466544</v>
+        <v>3487.953738877338</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -482,7 +482,7 @@
         <v>45884</v>
       </c>
       <c r="B12">
-        <v>3500.462166885603</v>
+        <v>3500.6915324253</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -490,7 +490,7 @@
         <v>45891</v>
       </c>
       <c r="B13">
-        <v>3515.012961122615</v>
+        <v>3515.240639232071</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -498,7 +498,7 @@
         <v>45898</v>
       </c>
       <c r="B14">
-        <v>3527.589635250732</v>
+        <v>3527.813662627763</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -506,7 +506,7 @@
         <v>45905</v>
       </c>
       <c r="B15">
-        <v>3544.803274567213</v>
+        <v>3544.965011848717</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -514,7 +514,7 @@
         <v>45912</v>
       </c>
       <c r="B16">
-        <v>3453.529493434789</v>
+        <v>3453.485260922074</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -522,7 +522,7 @@
         <v>45919</v>
       </c>
       <c r="B17">
-        <v>3451.026876295723</v>
+        <v>3450.987737742424</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -530,7 +530,7 @@
         <v>45926</v>
       </c>
       <c r="B18">
-        <v>3451.052130652582</v>
+        <v>3451.015835104252</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -538,7 +538,7 @@
         <v>45933</v>
       </c>
       <c r="B19">
-        <v>3536.290570354766</v>
+        <v>3536.101232686335</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -546,7 +546,7 @@
         <v>45940</v>
       </c>
       <c r="B20">
-        <v>3636.48784465128</v>
+        <v>3636.126343188508</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -554,7 +554,7 @@
         <v>45947</v>
       </c>
       <c r="B21">
-        <v>3791.840947987487</v>
+        <v>3791.297660794289</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -562,7 +562,7 @@
         <v>45954</v>
       </c>
       <c r="B22">
-        <v>3861.886853939261</v>
+        <v>3861.401866306212</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -570,7 +570,7 @@
         <v>45961</v>
       </c>
       <c r="B23">
-        <v>3907.946754132779</v>
+        <v>3907.502378477617</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -578,7 +578,7 @@
         <v>45968</v>
       </c>
       <c r="B24">
-        <v>3892.151288089049</v>
+        <v>3891.770741290395</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -586,7 +586,7 @@
         <v>45975</v>
       </c>
       <c r="B25">
-        <v>3890.269444739883</v>
+        <v>3890.115098046726</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -594,7 +594,7 @@
         <v>45982</v>
       </c>
       <c r="B26">
-        <v>3994.691024364334</v>
+        <v>3994.643716525984</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -602,7 +602,7 @@
         <v>45989</v>
       </c>
       <c r="B27">
-        <v>4071.450859911333</v>
+        <v>4071.290303821316</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -610,7 +610,7 @@
         <v>45996</v>
       </c>
       <c r="B28">
-        <v>4112.236218805515</v>
+        <v>4112.037735748399</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -618,7 +618,7 @@
         <v>46003</v>
       </c>
       <c r="B29">
-        <v>4206.873399806056</v>
+        <v>4206.847245749806</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -626,7 +626,7 @@
         <v>46010</v>
       </c>
       <c r="B30">
-        <v>4201.319916759981</v>
+        <v>4201.22741023223</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -634,7 +634,7 @@
         <v>46017</v>
       </c>
       <c r="B31">
-        <v>4228.825642768727</v>
+        <v>4228.579459868939</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -642,7 +642,7 @@
         <v>46024</v>
       </c>
       <c r="B32">
-        <v>4249.654346288259</v>
+        <v>4249.409032928057</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -650,7 +650,7 @@
         <v>46031</v>
       </c>
       <c r="B33">
-        <v>4316.095933342481</v>
+        <v>4315.755389601956</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -658,7 +658,7 @@
         <v>46038</v>
       </c>
       <c r="B34">
-        <v>4410.149657506935</v>
+        <v>4409.724541830449</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -666,7 +666,7 @@
         <v>46045</v>
       </c>
       <c r="B35">
-        <v>4446.854697046093</v>
+        <v>4446.397862794212</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -674,7 +674,7 @@
         <v>46052</v>
       </c>
       <c r="B36">
-        <v>4551.363254512205</v>
+        <v>4550.759006175234</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -682,7 +682,7 @@
         <v>46059</v>
       </c>
       <c r="B37">
-        <v>4689.337839351359</v>
+        <v>4688.602657356332</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -690,7 +690,7 @@
         <v>46066</v>
       </c>
       <c r="B38">
-        <v>4774.81910805861</v>
+        <v>4773.905697089151</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -698,7 +698,7 @@
         <v>46073</v>
       </c>
       <c r="B39">
-        <v>4903.892471735255</v>
+        <v>4903.340350368062</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -706,7 +706,7 @@
         <v>46080</v>
       </c>
       <c r="B40">
-        <v>4946.070220921409</v>
+        <v>4945.463819225281</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -714,7 +714,7 @@
         <v>46087</v>
       </c>
       <c r="B41">
-        <v>5056.017561172949</v>
+        <v>5055.233965186215</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -722,7 +722,7 @@
         <v>46094</v>
       </c>
       <c r="B42">
-        <v>5217.397740185603</v>
+        <v>5216.970691693872</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>46101</v>
       </c>
       <c r="B43">
-        <v>5252.247790643612</v>
+        <v>5252.227201751419</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>46108</v>
       </c>
       <c r="B44">
-        <v>5282.714809601872</v>
+        <v>5283.265959413407</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>46115</v>
       </c>
       <c r="B45">
-        <v>5352.072978234413</v>
+        <v>5353.022773013351</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>46122</v>
       </c>
       <c r="B46">
-        <v>5423.847137007542</v>
+        <v>5425.069937104032</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>46129</v>
       </c>
       <c r="B47">
-        <v>5552.041205344083</v>
+        <v>5553.372226196669</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>46136</v>
       </c>
       <c r="B48">
-        <v>5485.721968984441</v>
+        <v>5487.379161033374</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>46143</v>
       </c>
       <c r="B49">
-        <v>5303.641914485765</v>
+        <v>5305.681746935888</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>46150</v>
       </c>
       <c r="B50">
-        <v>5189.338086028414</v>
+        <v>5191.245785292871</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>46157</v>
       </c>
       <c r="B51">
-        <v>5052.910728938534</v>
+        <v>5054.940208141788</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>46164</v>
       </c>
       <c r="B52">
-        <v>4942.678648654383</v>
+        <v>4944.500701582716</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>46171</v>
       </c>
       <c r="B53">
-        <v>4841.626902275815</v>
+        <v>4843.347565278164</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>46178</v>
       </c>
       <c r="B54">
-        <v>4788.936339486594</v>
+        <v>4790.879761492972</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>46185</v>
       </c>
       <c r="B55">
-        <v>4667.512445429507</v>
+        <v>4669.081906154736</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>46192</v>
       </c>
       <c r="B56">
-        <v>4554.830337184348</v>
+        <v>4555.945159463006</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>46199</v>
       </c>
       <c r="B57">
-        <v>4465.471955603531</v>
+        <v>4466.246847963672</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>46206</v>
       </c>
       <c r="B58">
-        <v>4460.354331390161</v>
+        <v>4461.144241518217</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>46213</v>
       </c>
       <c r="B59">
-        <v>4377.136691119367</v>
+        <v>4378.102378569106</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>46220</v>
       </c>
       <c r="B60">
-        <v>4305.026983517295</v>
+        <v>4286.571421330087</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>46227</v>
       </c>
       <c r="B61">
-        <v>4241.352655140632</v>
+        <v>4224.643745015008</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>46234</v>
       </c>
       <c r="B62">
-        <v>4166.370701403982</v>
+        <v>4153.254558725919</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>46241</v>
       </c>
       <c r="B63">
-        <v>4097.585045329775</v>
+        <v>4083.900277334671</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46248</v>
       </c>
       <c r="B64">
-        <v>4047.825590817817</v>
+        <v>4034.267739171648</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46255</v>
       </c>
       <c r="B65">
-        <v>4005.109855551708</v>
+        <v>3992.756106289397</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46262</v>
       </c>
       <c r="B66">
-        <v>3996.094294194774</v>
+        <v>3982.861638729301</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46269</v>
       </c>
       <c r="B67">
-        <v>3958.700560061878</v>
+        <v>3948.048296182874</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46276</v>
       </c>
       <c r="B68">
-        <v>3942.946944722922</v>
+        <v>3934.843877821017</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46283</v>
       </c>
       <c r="B69">
-        <v>3828.081272350092</v>
+        <v>3829.761264646376</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46290</v>
       </c>
       <c r="B70">
-        <v>3706.725431253613</v>
+        <v>3721.995678129739</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46297</v>
       </c>
       <c r="B71">
-        <v>3720.783084330614</v>
+        <v>3733.530401665472</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46304</v>
       </c>
       <c r="B72">
-        <v>3840.748098653527</v>
+        <v>3828.989350943509</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46311</v>
       </c>
       <c r="B73">
-        <v>3738.772360087982</v>
+        <v>3778.549187098513</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/XAUUSD_forecast.xlsx
+++ b/public/data/files/XAUUSD_forecast.xlsx
@@ -442,7 +442,7 @@
         <v>45849</v>
       </c>
       <c r="B7">
-        <v>3666.100288263996</v>
+        <v>3666.229481097565</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -450,7 +450,7 @@
         <v>45856</v>
       </c>
       <c r="B8">
-        <v>3562.320325614821</v>
+        <v>3562.494479588506</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -458,7 +458,7 @@
         <v>45863</v>
       </c>
       <c r="B9">
-        <v>3507.368756128255</v>
+        <v>3507.569588325743</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -466,7 +466,7 @@
         <v>45870</v>
       </c>
       <c r="B10">
-        <v>3479.549639951322</v>
+        <v>3479.762139797886</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -474,7 +474,7 @@
         <v>45877</v>
       </c>
       <c r="B11">
-        <v>3487.953738877338</v>
+        <v>3488.171490720211</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -482,7 +482,7 @@
         <v>45884</v>
       </c>
       <c r="B12">
-        <v>3500.6915324253</v>
+        <v>3500.911919055022</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -490,7 +490,7 @@
         <v>45891</v>
       </c>
       <c r="B13">
-        <v>3515.240639232071</v>
+        <v>3515.459402906019</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -498,7 +498,7 @@
         <v>45898</v>
       </c>
       <c r="B14">
-        <v>3527.813662627763</v>
+        <v>3528.028918396652</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -506,7 +506,7 @@
         <v>45905</v>
       </c>
       <c r="B15">
-        <v>3544.965011848717</v>
+        <v>3545.120606395864</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -514,7 +514,7 @@
         <v>45912</v>
       </c>
       <c r="B16">
-        <v>3453.485260922074</v>
+        <v>3453.442855084921</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -522,7 +522,7 @@
         <v>45919</v>
       </c>
       <c r="B17">
-        <v>3450.987737742424</v>
+        <v>3450.950223108108</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -530,7 +530,7 @@
         <v>45926</v>
       </c>
       <c r="B18">
-        <v>3451.015835104252</v>
+        <v>3450.981050797733</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -538,7 +538,7 @@
         <v>45933</v>
       </c>
       <c r="B19">
-        <v>3536.101232686335</v>
+        <v>3535.919640477704</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -546,7 +546,7 @@
         <v>45940</v>
       </c>
       <c r="B20">
-        <v>3636.126343188508</v>
+        <v>3635.779510794828</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -554,7 +554,7 @@
         <v>45947</v>
       </c>
       <c r="B21">
-        <v>3791.297660794289</v>
+        <v>3790.776161293235</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -562,7 +562,7 @@
         <v>45954</v>
       </c>
       <c r="B22">
-        <v>3861.401866306212</v>
+        <v>3860.936231298871</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -570,7 +570,7 @@
         <v>45961</v>
       </c>
       <c r="B23">
-        <v>3907.502378477617</v>
+        <v>3907.075212539138</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -578,7 +578,7 @@
         <v>45968</v>
       </c>
       <c r="B24">
-        <v>3891.770741290395</v>
+        <v>3891.404679611065</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -586,7 +586,7 @@
         <v>45975</v>
       </c>
       <c r="B25">
-        <v>3890.115098046726</v>
+        <v>3889.966346482371</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -594,7 +594,7 @@
         <v>45982</v>
       </c>
       <c r="B26">
-        <v>3994.643716525984</v>
+        <v>3994.597953115886</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -602,7 +602,7 @@
         <v>45989</v>
       </c>
       <c r="B27">
-        <v>4071.290303821316</v>
+        <v>4071.135937321916</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -610,7 +610,7 @@
         <v>45996</v>
       </c>
       <c r="B28">
-        <v>4112.037735748399</v>
+        <v>4111.846920569042</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -618,7 +618,7 @@
         <v>46003</v>
       </c>
       <c r="B29">
-        <v>4206.847245749806</v>
+        <v>4206.822396236254</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -626,7 +626,7 @@
         <v>46010</v>
       </c>
       <c r="B30">
-        <v>4201.22741023223</v>
+        <v>4201.139013924338</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -634,7 +634,7 @@
         <v>46017</v>
       </c>
       <c r="B31">
-        <v>4228.579459868939</v>
+        <v>4228.343763192846</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -642,7 +642,7 @@
         <v>46024</v>
       </c>
       <c r="B32">
-        <v>4249.409032928057</v>
+        <v>4249.173969491405</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -650,7 +650,7 @@
         <v>46031</v>
       </c>
       <c r="B33">
-        <v>4315.755389601956</v>
+        <v>4315.428874036981</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -658,7 +658,7 @@
         <v>46038</v>
       </c>
       <c r="B34">
-        <v>4409.724541830449</v>
+        <v>4409.316666647296</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -666,7 +666,7 @@
         <v>46045</v>
       </c>
       <c r="B35">
-        <v>4446.397862794212</v>
+        <v>4445.959300624409</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -674,7 +674,7 @@
         <v>46052</v>
       </c>
       <c r="B36">
-        <v>4550.759006175234</v>
+        <v>4550.178615367291</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -682,7 +682,7 @@
         <v>46059</v>
       </c>
       <c r="B37">
-        <v>4688.602657356332</v>
+        <v>4687.896566614185</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -690,7 +690,7 @@
         <v>46066</v>
       </c>
       <c r="B38">
-        <v>4773.905697089151</v>
+        <v>4773.026751797457</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -698,7 +698,7 @@
         <v>46073</v>
       </c>
       <c r="B39">
-        <v>4903.340350368062</v>
+        <v>4902.809911495842</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -706,7 +706,7 @@
         <v>46080</v>
       </c>
       <c r="B40">
-        <v>4945.463819225281</v>
+        <v>4944.881207422066</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -714,7 +714,7 @@
         <v>46087</v>
       </c>
       <c r="B41">
-        <v>5055.233965186215</v>
+        <v>5054.480632562378</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -722,7 +722,7 @@
         <v>46094</v>
       </c>
       <c r="B42">
-        <v>5216.970691693872</v>
+        <v>5216.55919733167</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>46101</v>
       </c>
       <c r="B43">
-        <v>5252.227201751419</v>
+        <v>5252.204592359903</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>46108</v>
       </c>
       <c r="B44">
-        <v>5283.265959413407</v>
+        <v>5283.791809619635</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>46115</v>
       </c>
       <c r="B45">
-        <v>5353.022773013351</v>
+        <v>5353.932489967747</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>46122</v>
       </c>
       <c r="B46">
-        <v>5425.069937104032</v>
+        <v>5426.24160841949</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>46129</v>
       </c>
       <c r="B47">
-        <v>5553.372226196669</v>
+        <v>5554.647983390222</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>46136</v>
       </c>
       <c r="B48">
-        <v>5487.379161033374</v>
+        <v>5488.969692973791</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>46143</v>
       </c>
       <c r="B49">
-        <v>5305.681746935888</v>
+        <v>5307.641031731736</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>46150</v>
       </c>
       <c r="B50">
-        <v>5191.245785292871</v>
+        <v>5193.079165083263</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>46157</v>
       </c>
       <c r="B51">
-        <v>5054.940208141788</v>
+        <v>5056.892187056997</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>46164</v>
       </c>
       <c r="B52">
-        <v>4944.500701582716</v>
+        <v>4946.254028525785</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>46171</v>
       </c>
       <c r="B53">
-        <v>4843.347565278164</v>
+        <v>4845.00470084036</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>46178</v>
       </c>
       <c r="B54">
-        <v>4790.879761492972</v>
+        <v>4792.751595582269</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>46185</v>
       </c>
       <c r="B55">
-        <v>4669.081906154736</v>
+        <v>4670.593098737956</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>46192</v>
       </c>
       <c r="B56">
-        <v>4555.945159463006</v>
+        <v>4557.017489763552</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>46199</v>
       </c>
       <c r="B57">
-        <v>4466.246847963672</v>
+        <v>4466.990403137448</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>46206</v>
       </c>
       <c r="B58">
-        <v>4461.144241518217</v>
+        <v>4461.90221888249</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>46213</v>
       </c>
       <c r="B59">
-        <v>4378.102378569106</v>
+        <v>4379.030116152284</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>46220</v>
       </c>
       <c r="B60">
-        <v>4286.571421330087</v>
+        <v>4270.762012153126</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>46227</v>
       </c>
       <c r="B61">
-        <v>4224.643745015008</v>
+        <v>4210.556016318365</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>46234</v>
       </c>
       <c r="B62">
-        <v>4153.254558725919</v>
+        <v>4142.42420948464</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>46241</v>
       </c>
       <c r="B63">
-        <v>4083.900277334671</v>
+        <v>4072.803238751606</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46248</v>
       </c>
       <c r="B64">
-        <v>4034.267739171648</v>
+        <v>4023.447723684925</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46255</v>
       </c>
       <c r="B65">
-        <v>3992.756106289397</v>
+        <v>3983.145764631714</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46262</v>
       </c>
       <c r="B66">
-        <v>3982.861638729301</v>
+        <v>3972.938917834428</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46269</v>
       </c>
       <c r="B67">
-        <v>3948.048296182874</v>
+        <v>3940.523759610332</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46276</v>
       </c>
       <c r="B68">
-        <v>3934.843877821017</v>
+        <v>3929.35649352222</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46283</v>
       </c>
       <c r="B69">
-        <v>3829.761264646376</v>
+        <v>3832.39899507731</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46290</v>
       </c>
       <c r="B70">
-        <v>3721.995678129739</v>
+        <v>3734.54599896877</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46297</v>
       </c>
       <c r="B71">
-        <v>3733.530401665472</v>
+        <v>3743.96252769783</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46304</v>
       </c>
       <c r="B72">
-        <v>3828.989350943509</v>
+        <v>3824.347437984881</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46311</v>
       </c>
       <c r="B73">
-        <v>3778.549187098513</v>
+        <v>3796.424130873019</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/XAUUSD_forecast.xlsx
+++ b/public/data/files/XAUUSD_forecast.xlsx
@@ -442,7 +442,7 @@
         <v>45849</v>
       </c>
       <c r="B7">
-        <v>3666.229481097565</v>
+        <v>3666.472965597521</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -450,7 +450,7 @@
         <v>45856</v>
       </c>
       <c r="B8">
-        <v>3562.494479588506</v>
+        <v>3562.822833425228</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -458,7 +458,7 @@
         <v>45863</v>
       </c>
       <c r="B9">
-        <v>3507.569588325743</v>
+        <v>3507.948384379858</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -466,7 +466,7 @@
         <v>45870</v>
       </c>
       <c r="B10">
-        <v>3479.762139797886</v>
+        <v>3480.163136243989</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -474,7 +474,7 @@
         <v>45877</v>
       </c>
       <c r="B11">
-        <v>3488.171490720211</v>
+        <v>3488.582390755676</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -482,7 +482,7 @@
         <v>45884</v>
       </c>
       <c r="B12">
-        <v>3500.911919055022</v>
+        <v>3501.327783206485</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -490,7 +490,7 @@
         <v>45891</v>
       </c>
       <c r="B13">
-        <v>3515.459402906019</v>
+        <v>3515.872200378511</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -498,7 +498,7 @@
         <v>45898</v>
       </c>
       <c r="B14">
-        <v>3528.028918396652</v>
+        <v>3528.435096317271</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -506,7 +506,7 @@
         <v>45905</v>
       </c>
       <c r="B15">
-        <v>3545.120606395864</v>
+        <v>3545.414711610734</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -514,7 +514,7 @@
         <v>45912</v>
       </c>
       <c r="B16">
-        <v>3453.442855084921</v>
+        <v>3453.36308939665</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -522,7 +522,7 @@
         <v>45919</v>
       </c>
       <c r="B17">
-        <v>3450.950223108108</v>
+        <v>3450.879678101136</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -530,7 +530,7 @@
         <v>45926</v>
       </c>
       <c r="B18">
-        <v>3450.981050797733</v>
+        <v>3450.915654174059</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -538,7 +538,7 @@
         <v>45933</v>
       </c>
       <c r="B19">
-        <v>3535.919640477704</v>
+        <v>3535.577868418427</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -546,7 +546,7 @@
         <v>45940</v>
       </c>
       <c r="B20">
-        <v>3635.779510794828</v>
+        <v>3635.126426336798</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -554,7 +554,7 @@
         <v>45947</v>
       </c>
       <c r="B21">
-        <v>3790.776161293235</v>
+        <v>3789.793492103876</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -562,7 +562,7 @@
         <v>45954</v>
       </c>
       <c r="B22">
-        <v>3860.936231298871</v>
+        <v>3860.058568132492</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -570,7 +570,7 @@
         <v>45961</v>
       </c>
       <c r="B23">
-        <v>3907.075212539138</v>
+        <v>3906.268670904528</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -578,7 +578,7 @@
         <v>45968</v>
       </c>
       <c r="B24">
-        <v>3891.404679611065</v>
+        <v>3890.71283836914</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -586,7 +586,7 @@
         <v>45975</v>
       </c>
       <c r="B25">
-        <v>3889.966346482371</v>
+        <v>3889.684466483765</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -594,7 +594,7 @@
         <v>45982</v>
       </c>
       <c r="B26">
-        <v>3994.597953115886</v>
+        <v>3994.510779160735</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -602,7 +602,7 @@
         <v>45989</v>
       </c>
       <c r="B27">
-        <v>4071.135937321916</v>
+        <v>4070.844395146123</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -610,7 +610,7 @@
         <v>45996</v>
       </c>
       <c r="B28">
-        <v>4111.846920569042</v>
+        <v>4111.486584551031</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -618,7 +618,7 @@
         <v>46003</v>
       </c>
       <c r="B29">
-        <v>4206.822396236254</v>
+        <v>4206.776253168529</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -626,7 +626,7 @@
         <v>46010</v>
       </c>
       <c r="B30">
-        <v>4201.139013924338</v>
+        <v>4200.973516320397</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -634,7 +634,7 @@
         <v>46017</v>
       </c>
       <c r="B31">
-        <v>4228.343763192846</v>
+        <v>4227.901276764349</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -642,7 +642,7 @@
         <v>46024</v>
       </c>
       <c r="B32">
-        <v>4249.173969491405</v>
+        <v>4248.732144649322</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -650,7 +650,7 @@
         <v>46031</v>
       </c>
       <c r="B33">
-        <v>4315.428874036981</v>
+        <v>4314.814621494605</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -658,7 +658,7 @@
         <v>46038</v>
       </c>
       <c r="B34">
-        <v>4409.316666647296</v>
+        <v>4408.548635463289</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -666,7 +666,7 @@
         <v>46045</v>
       </c>
       <c r="B35">
-        <v>4445.959300624409</v>
+        <v>4445.132799664516</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -674,7 +674,7 @@
         <v>46052</v>
       </c>
       <c r="B36">
-        <v>4550.178615367291</v>
+        <v>4549.083993863149</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -682,7 +682,7 @@
         <v>46059</v>
       </c>
       <c r="B37">
-        <v>4687.896566614185</v>
+        <v>4686.565049006384</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -690,7 +690,7 @@
         <v>46066</v>
       </c>
       <c r="B38">
-        <v>4773.026751797457</v>
+        <v>4771.364780249683</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -698,7 +698,7 @@
         <v>46073</v>
       </c>
       <c r="B39">
-        <v>4902.809911495842</v>
+        <v>4901.809193562985</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -706,7 +706,7 @@
         <v>46080</v>
       </c>
       <c r="B40">
-        <v>4944.881207422066</v>
+        <v>4943.781995831792</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -714,7 +714,7 @@
         <v>46087</v>
       </c>
       <c r="B41">
-        <v>5054.480632562378</v>
+        <v>5053.058059836865</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -722,7 +722,7 @@
         <v>46094</v>
       </c>
       <c r="B42">
-        <v>5216.55919733167</v>
+        <v>5215.779637152216</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>46101</v>
       </c>
       <c r="B43">
-        <v>5252.204592359903</v>
+        <v>5252.15441131863</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>46108</v>
       </c>
       <c r="B44">
-        <v>5283.791809619635</v>
+        <v>5284.774140311971</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>46115</v>
       </c>
       <c r="B45">
-        <v>5353.932489967747</v>
+        <v>5355.641354357665</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>46122</v>
       </c>
       <c r="B46">
-        <v>5426.24160841949</v>
+        <v>5428.443779330773</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>46129</v>
       </c>
       <c r="B47">
-        <v>5554.647983390222</v>
+        <v>5557.046838357327</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>46136</v>
       </c>
       <c r="B48">
-        <v>5488.969692973791</v>
+        <v>5491.966166413318</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>46143</v>
       </c>
       <c r="B49">
-        <v>5307.641031731736</v>
+        <v>5311.336192516288</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>46150</v>
       </c>
       <c r="B50">
-        <v>5193.079165083263</v>
+        <v>5196.539560691025</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>46157</v>
       </c>
       <c r="B51">
-        <v>5056.892187056997</v>
+        <v>5060.580598052876</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>46164</v>
       </c>
       <c r="B52">
-        <v>4946.254028525785</v>
+        <v>4949.569376376774</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>46171</v>
       </c>
       <c r="B53">
-        <v>4845.00470084036</v>
+        <v>4848.141825522122</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>46178</v>
       </c>
       <c r="B54">
-        <v>4792.751595582269</v>
+        <v>4796.29559581471</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>46185</v>
       </c>
       <c r="B55">
-        <v>4670.593098737956</v>
+        <v>4673.453082014773</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>46192</v>
       </c>
       <c r="B56">
-        <v>4557.017489763552</v>
+        <v>4559.043975469232</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>46199</v>
       </c>
       <c r="B57">
-        <v>4466.990403137448</v>
+        <v>4468.39075640076</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>46206</v>
       </c>
       <c r="B58">
-        <v>4461.90221888249</v>
+        <v>4463.329773752035</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>46213</v>
       </c>
       <c r="B59">
-        <v>4379.030116152284</v>
+        <v>4380.780283380563</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>46220</v>
       </c>
       <c r="B60">
-        <v>4270.762012153126</v>
+        <v>4234.733470165222</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>46227</v>
       </c>
       <c r="B61">
-        <v>4210.556016318365</v>
+        <v>4175.785288339195</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>46234</v>
       </c>
       <c r="B62">
-        <v>4142.42420948464</v>
+        <v>4112.422268956569</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>46241</v>
       </c>
       <c r="B63">
-        <v>4072.803238751606</v>
+        <v>4039.410198643744</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46248</v>
       </c>
       <c r="B64">
-        <v>4023.447723684925</v>
+        <v>3987.56972151117</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46255</v>
       </c>
       <c r="B65">
-        <v>3983.145764631714</v>
+        <v>3945.907232993397</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46262</v>
       </c>
       <c r="B66">
-        <v>3972.938917834428</v>
+        <v>3930.842195979498</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46269</v>
       </c>
       <c r="B67">
-        <v>3940.523759610332</v>
+        <v>3898.79539007113</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46276</v>
       </c>
       <c r="B68">
-        <v>3929.35649352222</v>
+        <v>3891.725133864136</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46283</v>
       </c>
       <c r="B69">
-        <v>3832.39899507731</v>
+        <v>3804.195994664109</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46290</v>
       </c>
       <c r="B70">
-        <v>3734.54599896877</v>
+        <v>3717.866932524799</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46297</v>
       </c>
       <c r="B71">
-        <v>3743.96252769783</v>
+        <v>3725.079882163103</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46304</v>
       </c>
       <c r="B72">
-        <v>3824.347437984881</v>
+        <v>3775.340045338263</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46311</v>
       </c>
       <c r="B73">
-        <v>3796.424130873019</v>
+        <v>3747.905000488008</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/XAUUSD_forecast.xlsx
+++ b/public/data/files/XAUUSD_forecast.xlsx
@@ -442,7 +442,7 @@
         <v>45849</v>
       </c>
       <c r="B7">
-        <v>3666.472965597521</v>
+        <v>3666.587819294456</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -450,7 +450,7 @@
         <v>45856</v>
       </c>
       <c r="B8">
-        <v>3562.822833425228</v>
+        <v>3562.977780893806</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -458,7 +458,7 @@
         <v>45863</v>
       </c>
       <c r="B9">
-        <v>3507.948384379858</v>
+        <v>3508.127199619224</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -466,7 +466,7 @@
         <v>45870</v>
       </c>
       <c r="B10">
-        <v>3480.163136243989</v>
+        <v>3480.35251910653</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -474,7 +474,7 @@
         <v>45877</v>
       </c>
       <c r="B11">
-        <v>3488.582390755676</v>
+        <v>3488.776447643046</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -482,7 +482,7 @@
         <v>45884</v>
       </c>
       <c r="B12">
-        <v>3501.327783206485</v>
+        <v>3501.524180996966</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -490,7 +490,7 @@
         <v>45891</v>
       </c>
       <c r="B13">
-        <v>3515.872200378511</v>
+        <v>3516.067147987178</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -498,7 +498,7 @@
         <v>45898</v>
       </c>
       <c r="B14">
-        <v>3528.435096317271</v>
+        <v>3528.626917651973</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -506,7 +506,7 @@
         <v>45905</v>
       </c>
       <c r="B15">
-        <v>3545.414711610734</v>
+        <v>3545.55383444667</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -514,7 +514,7 @@
         <v>45912</v>
       </c>
       <c r="B16">
-        <v>3453.36308939665</v>
+        <v>3453.325533566318</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -522,7 +522,7 @@
         <v>45919</v>
       </c>
       <c r="B17">
-        <v>3450.879678101136</v>
+        <v>3450.846472838733</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -530,7 +530,7 @@
         <v>45926</v>
       </c>
       <c r="B18">
-        <v>3450.915654174059</v>
+        <v>3450.884878643483</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -538,7 +538,7 @@
         <v>45933</v>
       </c>
       <c r="B19">
-        <v>3535.577868418427</v>
+        <v>3535.416864217646</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -546,7 +546,7 @@
         <v>45940</v>
       </c>
       <c r="B20">
-        <v>3635.126426336798</v>
+        <v>3634.818624193514</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -554,7 +554,7 @@
         <v>45947</v>
       </c>
       <c r="B21">
-        <v>3789.793492103876</v>
+        <v>3789.330043124668</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -562,7 +562,7 @@
         <v>45954</v>
       </c>
       <c r="B22">
-        <v>3860.058568132492</v>
+        <v>3859.644523514949</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -570,7 +570,7 @@
         <v>45961</v>
       </c>
       <c r="B23">
-        <v>3906.268670904528</v>
+        <v>3905.887550391694</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -578,7 +578,7 @@
         <v>45968</v>
       </c>
       <c r="B24">
-        <v>3890.71283836914</v>
+        <v>3890.385613776361</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -586,7 +586,7 @@
         <v>45975</v>
       </c>
       <c r="B25">
-        <v>3889.684466483765</v>
+        <v>3889.550805769257</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -594,7 +594,7 @@
         <v>45982</v>
       </c>
       <c r="B26">
-        <v>3994.510779160735</v>
+        <v>3994.469238177464</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -602,7 +602,7 @@
         <v>45989</v>
       </c>
       <c r="B27">
-        <v>4070.844395146123</v>
+        <v>4070.706593218983</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -610,7 +610,7 @@
         <v>45996</v>
       </c>
       <c r="B28">
-        <v>4111.486584551031</v>
+        <v>4111.316286911754</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -618,7 +618,7 @@
         <v>46003</v>
       </c>
       <c r="B29">
-        <v>4206.776253168529</v>
+        <v>4206.754800227453</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -626,7 +626,7 @@
         <v>46010</v>
       </c>
       <c r="B30">
-        <v>4200.973516320397</v>
+        <v>4200.895949891114</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -634,7 +634,7 @@
         <v>46017</v>
       </c>
       <c r="B31">
-        <v>4227.901276764349</v>
+        <v>4227.693337124939</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -642,7 +642,7 @@
         <v>46024</v>
       </c>
       <c r="B32">
-        <v>4248.732144649322</v>
+        <v>4248.524277956008</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -650,7 +650,7 @@
         <v>46031</v>
       </c>
       <c r="B33">
-        <v>4314.814621494605</v>
+        <v>4314.52538967148</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -658,7 +658,7 @@
         <v>46038</v>
       </c>
       <c r="B34">
-        <v>4408.548635463289</v>
+        <v>4408.18666689986</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -666,7 +666,7 @@
         <v>46045</v>
       </c>
       <c r="B35">
-        <v>4445.132799664516</v>
+        <v>4444.742960072415</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -674,7 +674,7 @@
         <v>46052</v>
       </c>
       <c r="B36">
-        <v>4549.083993863149</v>
+        <v>4548.567306883957</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -682,7 +682,7 @@
         <v>46059</v>
       </c>
       <c r="B37">
-        <v>4686.565049006384</v>
+        <v>4685.936622730713</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -690,7 +690,7 @@
         <v>46066</v>
       </c>
       <c r="B38">
-        <v>4771.364780249683</v>
+        <v>4770.578345105914</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -698,7 +698,7 @@
         <v>46073</v>
       </c>
       <c r="B39">
-        <v>4901.809193562985</v>
+        <v>4901.336694681617</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -706,7 +706,7 @@
         <v>46080</v>
       </c>
       <c r="B40">
-        <v>4943.781995831792</v>
+        <v>4943.262962549241</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -714,7 +714,7 @@
         <v>46087</v>
       </c>
       <c r="B41">
-        <v>5053.058059836865</v>
+        <v>5052.385771646736</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -722,7 +722,7 @@
         <v>46094</v>
       </c>
       <c r="B42">
-        <v>5215.779637152216</v>
+        <v>5215.410089851081</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>46101</v>
       </c>
       <c r="B43">
-        <v>5252.15441131863</v>
+        <v>5252.1273082633</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>46108</v>
       </c>
       <c r="B44">
-        <v>5284.774140311971</v>
+        <v>5285.23354704224</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>46115</v>
       </c>
       <c r="B45">
-        <v>5355.641354357665</v>
+        <v>5356.444860999644</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>46122</v>
       </c>
       <c r="B46">
-        <v>5428.443779330773</v>
+        <v>5429.479794445115</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>46129</v>
       </c>
       <c r="B47">
-        <v>5557.046838357327</v>
+        <v>5558.175868295944</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>46136</v>
       </c>
       <c r="B48">
-        <v>5491.966166413318</v>
+        <v>5493.379080045866</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>46143</v>
       </c>
       <c r="B49">
-        <v>5311.336192516288</v>
+        <v>5313.080347217448</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>46150</v>
       </c>
       <c r="B50">
-        <v>5196.539560691025</v>
+        <v>5198.174121677894</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>46157</v>
       </c>
       <c r="B51">
-        <v>5060.580598052876</v>
+        <v>5062.324755225152</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>46164</v>
       </c>
       <c r="B52">
-        <v>4949.569376376774</v>
+        <v>4951.13818005645</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>46171</v>
       </c>
       <c r="B53">
-        <v>4848.141825522122</v>
+        <v>4849.627957197155</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>46178</v>
       </c>
       <c r="B54">
-        <v>4796.29559581471</v>
+        <v>4797.974665820549</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>46185</v>
       </c>
       <c r="B55">
-        <v>4673.453082014773</v>
+        <v>4674.80753878896</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>46192</v>
       </c>
       <c r="B56">
-        <v>4559.043975469232</v>
+        <v>4560.002367576323</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>46199</v>
       </c>
       <c r="B57">
-        <v>4468.39075640076</v>
+        <v>4469.050840862305</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>46206</v>
       </c>
       <c r="B58">
-        <v>4463.329773752035</v>
+        <v>4464.002702176839</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>46213</v>
       </c>
       <c r="B59">
-        <v>4380.780283380563</v>
+        <v>4381.606593806086</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>46220</v>
       </c>
       <c r="B60">
-        <v>4234.733470165222</v>
+        <v>4219.520090336894</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>46227</v>
       </c>
       <c r="B61">
-        <v>4175.785288339195</v>
+        <v>4161.237780109708</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>46234</v>
       </c>
       <c r="B62">
-        <v>4112.422268956569</v>
+        <v>4100.016850365647</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>46241</v>
       </c>
       <c r="B63">
-        <v>4039.410198643744</v>
+        <v>4025.515016014326</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46248</v>
       </c>
       <c r="B64">
-        <v>3987.56972151117</v>
+        <v>3972.160417066356</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46255</v>
       </c>
       <c r="B65">
-        <v>3945.907232993397</v>
+        <v>3929.289953033269</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46262</v>
       </c>
       <c r="B66">
-        <v>3930.842195979498</v>
+        <v>3911.968977117177</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46269</v>
       </c>
       <c r="B67">
-        <v>3898.79539007113</v>
+        <v>3879.957414668317</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46276</v>
       </c>
       <c r="B68">
-        <v>3891.725133864136</v>
+        <v>3874.27982035406</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46283</v>
       </c>
       <c r="B69">
-        <v>3804.195994664109</v>
+        <v>3791.360151952831</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46290</v>
       </c>
       <c r="B70">
-        <v>3717.866932524799</v>
+        <v>3712.206729718474</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46297</v>
       </c>
       <c r="B71">
-        <v>3725.079882163103</v>
+        <v>3718.443855571601</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46304</v>
       </c>
       <c r="B72">
-        <v>3775.340045338263</v>
+        <v>3762.729038754032</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46311</v>
       </c>
       <c r="B73">
-        <v>3747.905000488008</v>
+        <v>3738.405085546048</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/XAUUSD_forecast.xlsx
+++ b/public/data/files/XAUUSD_forecast.xlsx
@@ -383,7 +383,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B73"/>
+  <dimension ref="A1:B74"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" style="1" customWidth="1"/>
@@ -442,7 +442,7 @@
         <v>45849</v>
       </c>
       <c r="B7">
-        <v>3666.587819294456</v>
+        <v>3666.698420637267</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -450,7 +450,7 @@
         <v>45856</v>
       </c>
       <c r="B8">
-        <v>3562.977780893806</v>
+        <v>3563.127027987296</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -458,7 +458,7 @@
         <v>45863</v>
       </c>
       <c r="B9">
-        <v>3508.127199619224</v>
+        <v>3508.299475419175</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -466,7 +466,7 @@
         <v>45870</v>
       </c>
       <c r="B10">
-        <v>3480.35251910653</v>
+        <v>3480.535029069538</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -474,7 +474,7 @@
         <v>45877</v>
       </c>
       <c r="B11">
-        <v>3488.776447643046</v>
+        <v>3488.963460035494</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -482,7 +482,7 @@
         <v>45884</v>
       </c>
       <c r="B12">
-        <v>3501.524180996966</v>
+        <v>3501.713447188307</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -490,7 +490,7 @@
         <v>45891</v>
       </c>
       <c r="B13">
-        <v>3516.067147987178</v>
+        <v>3516.255015509185</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -498,7 +498,7 @@
         <v>45898</v>
       </c>
       <c r="B14">
-        <v>3528.626917651973</v>
+        <v>3528.811772365731</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -506,7 +506,7 @@
         <v>45905</v>
       </c>
       <c r="B15">
-        <v>3545.55383444667</v>
+        <v>3545.688043078393</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -514,7 +514,7 @@
         <v>45912</v>
       </c>
       <c r="B16">
-        <v>3453.325533566318</v>
+        <v>3453.289410854085</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -522,7 +522,7 @@
         <v>45919</v>
       </c>
       <c r="B17">
-        <v>3450.846472838733</v>
+        <v>3450.814540277537</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -530,7 +530,7 @@
         <v>45926</v>
       </c>
       <c r="B18">
-        <v>3450.884878643483</v>
+        <v>3450.855286577835</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -538,7 +538,7 @@
         <v>45933</v>
       </c>
       <c r="B19">
-        <v>3535.416864217646</v>
+        <v>3535.26195017041</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -546,7 +546,7 @@
         <v>45940</v>
       </c>
       <c r="B20">
-        <v>3634.818624193514</v>
+        <v>3634.522378751615</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -554,7 +554,7 @@
         <v>45947</v>
       </c>
       <c r="B21">
-        <v>3789.330043124668</v>
+        <v>3788.883805703677</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -562,7 +562,7 @@
         <v>45954</v>
       </c>
       <c r="B22">
-        <v>3859.644523514949</v>
+        <v>3859.245783200382</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -570,7 +570,7 @@
         <v>45961</v>
       </c>
       <c r="B23">
-        <v>3905.887550391694</v>
+        <v>3905.520137515394</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -578,7 +578,7 @@
         <v>45968</v>
       </c>
       <c r="B24">
-        <v>3890.385613776361</v>
+        <v>3890.069974358428</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -586,7 +586,7 @@
         <v>45975</v>
       </c>
       <c r="B25">
-        <v>3889.550805769257</v>
+        <v>3889.421672438739</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -594,7 +594,7 @@
         <v>45982</v>
       </c>
       <c r="B26">
-        <v>3994.469238177464</v>
+        <v>3994.428980268652</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -602,7 +602,7 @@
         <v>45989</v>
       </c>
       <c r="B27">
-        <v>4070.706593218983</v>
+        <v>4070.573723895528</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -610,7 +610,7 @@
         <v>45996</v>
       </c>
       <c r="B28">
-        <v>4111.316286911754</v>
+        <v>4111.152097984124</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -618,7 +618,7 @@
         <v>46003</v>
       </c>
       <c r="B29">
-        <v>4206.754800227453</v>
+        <v>4206.734331431363</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -626,7 +626,7 @@
         <v>46010</v>
       </c>
       <c r="B30">
-        <v>4200.895949891114</v>
+        <v>4200.821559248156</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -634,7 +634,7 @@
         <v>46017</v>
       </c>
       <c r="B31">
-        <v>4227.693337124939</v>
+        <v>4227.493574230421</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -642,7 +642,7 @@
         <v>46024</v>
       </c>
       <c r="B32">
-        <v>4248.524277956008</v>
+        <v>4248.324441650158</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -650,7 +650,7 @@
         <v>46031</v>
       </c>
       <c r="B33">
-        <v>4314.52538967148</v>
+        <v>4314.247184532569</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -658,7 +658,7 @@
         <v>46038</v>
       </c>
       <c r="B34">
-        <v>4408.18666689986</v>
+        <v>4407.838299841878</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -666,7 +666,7 @@
         <v>46045</v>
       </c>
       <c r="B35">
-        <v>4444.742960072415</v>
+        <v>4444.367576695888</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -674,7 +674,7 @@
         <v>46052</v>
       </c>
       <c r="B36">
-        <v>4548.567306883957</v>
+        <v>4548.069546812937</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -682,7 +682,7 @@
         <v>46059</v>
       </c>
       <c r="B37">
-        <v>4685.936622730713</v>
+        <v>4685.331266811438</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -690,7 +690,7 @@
         <v>46066</v>
       </c>
       <c r="B38">
-        <v>4770.578345105914</v>
+        <v>4769.819535091923</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -698,7 +698,7 @@
         <v>46073</v>
       </c>
       <c r="B39">
-        <v>4901.336694681617</v>
+        <v>4900.881422614668</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -706,7 +706,7 @@
         <v>46080</v>
       </c>
       <c r="B40">
-        <v>4943.262962549241</v>
+        <v>4942.762834618314</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -714,7 +714,7 @@
         <v>46087</v>
       </c>
       <c r="B41">
-        <v>5052.385771646736</v>
+        <v>5051.737629606726</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -722,7 +722,7 @@
         <v>46094</v>
       </c>
       <c r="B42">
-        <v>5215.410089851081</v>
+        <v>5215.053124961069</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>46101</v>
       </c>
       <c r="B43">
-        <v>5252.1273082633</v>
+        <v>5252.099129997709</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>46108</v>
       </c>
       <c r="B44">
-        <v>5285.23354704224</v>
+        <v>5285.673533788412</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>46115</v>
       </c>
       <c r="B45">
-        <v>5356.444860999644</v>
+        <v>5357.217044308942</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>46122</v>
       </c>
       <c r="B46">
-        <v>5429.479794445115</v>
+        <v>5430.475756522993</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>46129</v>
       </c>
       <c r="B47">
-        <v>5558.175868295944</v>
+        <v>5559.261546629691</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>46136</v>
       </c>
       <c r="B48">
-        <v>5493.379080045866</v>
+        <v>5494.739330906457</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>46143</v>
       </c>
       <c r="B49">
-        <v>5313.080347217448</v>
+        <v>5314.76057184166</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>46150</v>
       </c>
       <c r="B50">
-        <v>5198.174121677894</v>
+        <v>5199.749506672069</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>46157</v>
       </c>
       <c r="B51">
-        <v>5062.324755225152</v>
+        <v>5064.006914213819</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>46164</v>
       </c>
       <c r="B52">
-        <v>4951.13818005645</v>
+        <v>4952.651868008785</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>46171</v>
       </c>
       <c r="B53">
-        <v>4849.627957197155</v>
+        <v>4851.062884830191</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>46178</v>
       </c>
       <c r="B54">
-        <v>4797.974665820549</v>
+        <v>4799.595998290261</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>46185</v>
       </c>
       <c r="B55">
-        <v>4674.80753878896</v>
+        <v>4676.11509552492</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>46192</v>
       </c>
       <c r="B56">
-        <v>4560.002367576323</v>
+        <v>4560.926769856015</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>46199</v>
       </c>
       <c r="B57">
-        <v>4469.050840862305</v>
+        <v>4469.686185867409</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>46206</v>
       </c>
       <c r="B58">
-        <v>4464.002702176839</v>
+        <v>4464.650425283093</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>46213</v>
       </c>
       <c r="B59">
-        <v>4381.606593806086</v>
+        <v>4382.40274368961</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>46220</v>
       </c>
       <c r="B60">
-        <v>4219.520090336894</v>
+        <v>4220.554120533217</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>46227</v>
       </c>
       <c r="B61">
-        <v>4161.237780109708</v>
+        <v>4152.050547189132</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>46234</v>
       </c>
       <c r="B62">
-        <v>4100.016850365647</v>
+        <v>4093.628735910744</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>46241</v>
       </c>
       <c r="B63">
-        <v>4025.515016014326</v>
+        <v>4022.810756395485</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46248</v>
       </c>
       <c r="B64">
-        <v>3972.160417066356</v>
+        <v>3968.295870610963</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46255</v>
       </c>
       <c r="B65">
-        <v>3929.289953033269</v>
+        <v>3924.8924336239</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46262</v>
       </c>
       <c r="B66">
-        <v>3911.968977117177</v>
+        <v>3905.551526661799</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46269</v>
       </c>
       <c r="B67">
-        <v>3879.957414668317</v>
+        <v>3874.621365959337</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46276</v>
       </c>
       <c r="B68">
-        <v>3874.27982035406</v>
+        <v>3868.137995375175</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46283</v>
       </c>
       <c r="B69">
-        <v>3791.360151952831</v>
+        <v>3791.93660882413</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46290</v>
       </c>
       <c r="B70">
-        <v>3712.206729718474</v>
+        <v>3720.449001082359</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46297</v>
       </c>
       <c r="B71">
-        <v>3718.443855571601</v>
+        <v>3730.843152574041</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46304</v>
       </c>
       <c r="B72">
-        <v>3762.729038754032</v>
+        <v>3774.932227920644</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,15 @@
         <v>46311</v>
       </c>
       <c r="B73">
-        <v>3738.405085546048</v>
+        <v>3760.69855411063</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2">
+      <c r="A74" s="3">
+        <v>46318</v>
+      </c>
+      <c r="B74">
+        <v>3871.178303779527</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/XAUUSD_forecast.xlsx
+++ b/public/data/files/XAUUSD_forecast.xlsx
@@ -442,7 +442,7 @@
         <v>45849</v>
       </c>
       <c r="B7">
-        <v>3666.698420637267</v>
+        <v>3666.805001467395</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -450,7 +450,7 @@
         <v>45856</v>
       </c>
       <c r="B8">
-        <v>3563.127027987296</v>
+        <v>3563.270883510539</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -458,7 +458,7 @@
         <v>45863</v>
       </c>
       <c r="B9">
-        <v>3508.299475419175</v>
+        <v>3508.46556389901</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -466,7 +466,7 @@
         <v>45870</v>
       </c>
       <c r="B10">
-        <v>3480.535029069538</v>
+        <v>3480.711033291384</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -474,7 +474,7 @@
         <v>45877</v>
       </c>
       <c r="B11">
-        <v>3488.963460035494</v>
+        <v>3489.143804363105</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -482,7 +482,7 @@
         <v>45884</v>
       </c>
       <c r="B12">
-        <v>3501.713447188307</v>
+        <v>3501.895962981002</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -490,7 +490,7 @@
         <v>45891</v>
       </c>
       <c r="B13">
-        <v>3516.255015509185</v>
+        <v>3516.436181455861</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -498,7 +498,7 @@
         <v>45898</v>
       </c>
       <c r="B14">
-        <v>3528.811772365731</v>
+        <v>3528.990032909541</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -506,7 +506,7 @@
         <v>45905</v>
       </c>
       <c r="B15">
-        <v>3545.688043078393</v>
+        <v>3545.817592655548</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -514,7 +514,7 @@
         <v>45912</v>
       </c>
       <c r="B16">
-        <v>3453.289410854085</v>
+        <v>3453.254640869973</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -522,7 +522,7 @@
         <v>45919</v>
       </c>
       <c r="B17">
-        <v>3450.814540277537</v>
+        <v>3450.783808735531</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -530,7 +530,7 @@
         <v>45926</v>
       </c>
       <c r="B18">
-        <v>3450.855286577835</v>
+        <v>3450.826811120183</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -538,7 +538,7 @@
         <v>45933</v>
       </c>
       <c r="B19">
-        <v>3535.26195017041</v>
+        <v>3535.112787539386</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -546,7 +546,7 @@
         <v>45940</v>
       </c>
       <c r="B20">
-        <v>3634.522378751615</v>
+        <v>3634.237052033797</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -554,7 +554,7 @@
         <v>45947</v>
       </c>
       <c r="B21">
-        <v>3788.883805703677</v>
+        <v>3788.453839714752</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -562,7 +562,7 @@
         <v>45954</v>
       </c>
       <c r="B22">
-        <v>3859.245783200382</v>
+        <v>3858.861514814293</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -570,7 +570,7 @@
         <v>45961</v>
       </c>
       <c r="B23">
-        <v>3905.520137515394</v>
+        <v>3905.165707639655</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -578,7 +578,7 @@
         <v>45968</v>
       </c>
       <c r="B24">
-        <v>3890.069974358428</v>
+        <v>3889.765317837015</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -586,7 +586,7 @@
         <v>45975</v>
       </c>
       <c r="B25">
-        <v>3889.421672438739</v>
+        <v>3889.296842298702</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -594,7 +594,7 @@
         <v>45982</v>
       </c>
       <c r="B26">
-        <v>3994.428980268652</v>
+        <v>3994.389948935714</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -602,7 +602,7 @@
         <v>45989</v>
       </c>
       <c r="B27">
-        <v>4070.573723895528</v>
+        <v>4070.445527095382</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -610,7 +610,7 @@
         <v>45996</v>
       </c>
       <c r="B28">
-        <v>4111.152097984124</v>
+        <v>4110.993695204963</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -618,7 +618,7 @@
         <v>46003</v>
       </c>
       <c r="B29">
-        <v>4206.734331431363</v>
+        <v>4206.714783052241</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -626,7 +626,7 @@
         <v>46010</v>
       </c>
       <c r="B30">
-        <v>4200.821559248156</v>
+        <v>4200.750155560661</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -634,7 +634,7 @@
         <v>46017</v>
       </c>
       <c r="B31">
-        <v>4227.493574230421</v>
+        <v>4227.301518246002</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -642,7 +642,7 @@
         <v>46024</v>
       </c>
       <c r="B32">
-        <v>4248.324441650158</v>
+        <v>4248.132182376054</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -650,7 +650,7 @@
         <v>46031</v>
       </c>
       <c r="B33">
-        <v>4314.247184532569</v>
+        <v>4313.979391356958</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -658,7 +658,7 @@
         <v>46038</v>
       </c>
       <c r="B34">
-        <v>4407.838299841878</v>
+        <v>4407.502786708108</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -666,7 +666,7 @@
         <v>46045</v>
       </c>
       <c r="B35">
-        <v>4444.367576695888</v>
+        <v>4444.005864008092</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -674,7 +674,7 @@
         <v>46052</v>
       </c>
       <c r="B36">
-        <v>4548.069546812937</v>
+        <v>4547.589696513831</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -682,7 +682,7 @@
         <v>46059</v>
       </c>
       <c r="B37">
-        <v>4685.331266811438</v>
+        <v>4684.747739448978</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -690,7 +690,7 @@
         <v>46066</v>
       </c>
       <c r="B38">
-        <v>4769.819535091923</v>
+        <v>4769.086926650483</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -698,7 +698,7 @@
         <v>46073</v>
       </c>
       <c r="B39">
-        <v>4900.881422614668</v>
+        <v>4900.442456851832</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -706,7 +706,7 @@
         <v>46080</v>
       </c>
       <c r="B40">
-        <v>4942.762834618314</v>
+        <v>4942.280602748287</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -714,7 +714,7 @@
         <v>46087</v>
       </c>
       <c r="B41">
-        <v>5051.737629606726</v>
+        <v>5051.112364917691</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -722,7 +722,7 @@
         <v>46094</v>
       </c>
       <c r="B42">
-        <v>5215.053124961069</v>
+        <v>5214.708118201571</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>46101</v>
       </c>
       <c r="B43">
-        <v>5252.099129997709</v>
+        <v>5252.070047052601</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>46108</v>
       </c>
       <c r="B44">
-        <v>5285.673533788412</v>
+        <v>5286.095283646877</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>46115</v>
       </c>
       <c r="B45">
-        <v>5357.217044308942</v>
+        <v>5357.959688768765</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>46122</v>
       </c>
       <c r="B46">
-        <v>5430.475756522993</v>
+        <v>5431.433927798225</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>46129</v>
       </c>
       <c r="B47">
-        <v>5559.261546629691</v>
+        <v>5560.306308599962</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>46136</v>
       </c>
       <c r="B48">
-        <v>5494.739330906457</v>
+        <v>5496.0497966606</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>46143</v>
       </c>
       <c r="B49">
-        <v>5314.76057184166</v>
+        <v>5316.380297195889</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>46150</v>
       </c>
       <c r="B50">
-        <v>5199.749506672069</v>
+        <v>5201.26885096988</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>46157</v>
       </c>
       <c r="B51">
-        <v>5064.006914213819</v>
+        <v>5065.630297886497</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>46164</v>
       </c>
       <c r="B52">
-        <v>4952.651868008785</v>
+        <v>4954.113275126112</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>46171</v>
       </c>
       <c r="B53">
-        <v>4851.062884830191</v>
+        <v>4852.449187218346</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>46178</v>
       </c>
       <c r="B54">
-        <v>4799.595998290261</v>
+        <v>4801.162493497739</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>46185</v>
       </c>
       <c r="B55">
-        <v>4676.11509552492</v>
+        <v>4677.378127866468</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>46192</v>
       </c>
       <c r="B56">
-        <v>4560.926769856015</v>
+        <v>4561.818948964057</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>46199</v>
       </c>
       <c r="B57">
-        <v>4469.686185867409</v>
+        <v>4470.298147609563</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>46206</v>
       </c>
       <c r="B58">
-        <v>4464.650425283093</v>
+        <v>4465.274325434651</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>46213</v>
       </c>
       <c r="B59">
-        <v>4382.40274368961</v>
+        <v>4383.170343311758</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>46220</v>
       </c>
       <c r="B60">
-        <v>4220.554120533217</v>
+        <v>4221.552837324403</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>46227</v>
       </c>
       <c r="B61">
-        <v>4152.050547189132</v>
+        <v>4148.443235706554</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>46234</v>
       </c>
       <c r="B62">
-        <v>4093.628735910744</v>
+        <v>4093.825886042125</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>46241</v>
       </c>
       <c r="B63">
-        <v>4022.810756395485</v>
+        <v>4026.832149954696</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46248</v>
       </c>
       <c r="B64">
-        <v>3968.295870610963</v>
+        <v>3972.890146375429</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46255</v>
       </c>
       <c r="B65">
-        <v>3924.8924336239</v>
+        <v>3929.596696772383</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46262</v>
       </c>
       <c r="B66">
-        <v>3905.551526661799</v>
+        <v>3908.965706908962</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46269</v>
       </c>
       <c r="B67">
-        <v>3874.621365959337</v>
+        <v>3879.341354249964</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46276</v>
       </c>
       <c r="B68">
-        <v>3868.137995375175</v>
+        <v>3872.43102339452</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46283</v>
       </c>
       <c r="B69">
-        <v>3791.93660882413</v>
+        <v>3801.968186829748</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46290</v>
       </c>
       <c r="B70">
-        <v>3720.449001082359</v>
+        <v>3742.003907471692</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46297</v>
       </c>
       <c r="B71">
-        <v>3730.843152574041</v>
+        <v>3759.400993652986</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46304</v>
       </c>
       <c r="B72">
-        <v>3774.932227920644</v>
+        <v>3804.959658995497</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46311</v>
       </c>
       <c r="B73">
-        <v>3760.69855411063</v>
+        <v>3803.596395910682</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46318</v>
       </c>
       <c r="B74">
-        <v>3871.178303779527</v>
+        <v>3971.132482634604</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/XAUUSD_forecast.xlsx
+++ b/public/data/files/XAUUSD_forecast.xlsx
@@ -882,7 +882,7 @@
         <v>46234</v>
       </c>
       <c r="B62">
-        <v>4093.825886042125</v>
+        <v>4093.802837477961</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>46241</v>
       </c>
       <c r="B63">
-        <v>4026.832149954696</v>
+        <v>4026.806247509962</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46248</v>
       </c>
       <c r="B64">
-        <v>3972.890146375429</v>
+        <v>3972.985080249204</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46255</v>
       </c>
       <c r="B65">
-        <v>3929.596696772383</v>
+        <v>3929.652768164598</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46262</v>
       </c>
       <c r="B66">
-        <v>3908.965706908962</v>
+        <v>3908.911039679481</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46269</v>
       </c>
       <c r="B67">
-        <v>3879.341354249964</v>
+        <v>3878.970754297473</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46276</v>
       </c>
       <c r="B68">
-        <v>3872.43102339452</v>
+        <v>3872.013495359266</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46283</v>
       </c>
       <c r="B69">
-        <v>3801.968186829748</v>
+        <v>3799.413708143122</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46290</v>
       </c>
       <c r="B70">
-        <v>3742.003907471692</v>
+        <v>3739.694047747037</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46297</v>
       </c>
       <c r="B71">
-        <v>3759.400993652986</v>
+        <v>3757.948786967375</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46304</v>
       </c>
       <c r="B72">
-        <v>3804.959658995497</v>
+        <v>3803.753611121418</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46311</v>
       </c>
       <c r="B73">
-        <v>3803.596395910682</v>
+        <v>3802.576503390783</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46318</v>
       </c>
       <c r="B74">
-        <v>3971.132482634604</v>
+        <v>3968.56276768177</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/XAUUSD_forecast.xlsx
+++ b/public/data/files/XAUUSD_forecast.xlsx
@@ -882,7 +882,7 @@
         <v>46234</v>
       </c>
       <c r="B62">
-        <v>4093.802837477961</v>
+        <v>4093.870000165652</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>46241</v>
       </c>
       <c r="B63">
-        <v>4026.806247509962</v>
+        <v>4026.976948803605</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46248</v>
       </c>
       <c r="B64">
-        <v>3972.985080249204</v>
+        <v>3973.497122868495</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46255</v>
       </c>
       <c r="B65">
-        <v>3929.652768164598</v>
+        <v>3930.457055505917</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46262</v>
       </c>
       <c r="B66">
-        <v>3908.911039679481</v>
+        <v>3910.124803832985</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46269</v>
       </c>
       <c r="B67">
-        <v>3878.970754297473</v>
+        <v>3880.467664561048</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46276</v>
       </c>
       <c r="B68">
-        <v>3872.013495359266</v>
+        <v>3874.930136149907</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46283</v>
       </c>
       <c r="B69">
-        <v>3799.413708143122</v>
+        <v>3801.917370678545</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46290</v>
       </c>
       <c r="B70">
-        <v>3739.694047747037</v>
+        <v>3742.031522665141</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46297</v>
       </c>
       <c r="B71">
-        <v>3757.948786967375</v>
+        <v>3758.180903238913</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46304</v>
       </c>
       <c r="B72">
-        <v>3803.753611121418</v>
+        <v>3804.89804835492</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46311</v>
       </c>
       <c r="B73">
-        <v>3802.576503390783</v>
+        <v>3803.565124716391</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46318</v>
       </c>
       <c r="B74">
-        <v>3968.56276768177</v>
+        <v>3971.071866387134</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/XAUUSD_forecast.xlsx
+++ b/public/data/files/XAUUSD_forecast.xlsx
@@ -442,7 +442,7 @@
         <v>45849</v>
       </c>
       <c r="B7">
-        <v>3666.805001467395</v>
+        <v>3666.907777075309</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -450,7 +450,7 @@
         <v>45856</v>
       </c>
       <c r="B8">
-        <v>3563.270883510539</v>
+        <v>3563.409634364521</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -458,7 +458,7 @@
         <v>45863</v>
       </c>
       <c r="B9">
-        <v>3508.46556389901</v>
+        <v>3508.625792355444</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -466,7 +466,7 @@
         <v>45870</v>
       </c>
       <c r="B10">
-        <v>3480.711033291384</v>
+        <v>3480.880873257582</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -474,7 +474,7 @@
         <v>45877</v>
       </c>
       <c r="B11">
-        <v>3489.143804363105</v>
+        <v>3489.31783072748</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -482,7 +482,7 @@
         <v>45884</v>
       </c>
       <c r="B12">
-        <v>3501.895962981002</v>
+        <v>3502.072082905129</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -490,7 +490,7 @@
         <v>45891</v>
       </c>
       <c r="B13">
-        <v>3516.436181455861</v>
+        <v>3516.610997851548</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -498,7 +498,7 @@
         <v>45898</v>
       </c>
       <c r="B14">
-        <v>3528.990032909541</v>
+        <v>3529.162045670972</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -506,7 +506,7 @@
         <v>45905</v>
       </c>
       <c r="B15">
-        <v>3545.817592655548</v>
+        <v>3545.942721015294</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -514,7 +514,7 @@
         <v>45912</v>
       </c>
       <c r="B16">
-        <v>3453.254640869973</v>
+        <v>3453.221149119131</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -522,7 +522,7 @@
         <v>45919</v>
       </c>
       <c r="B17">
-        <v>3450.783808735531</v>
+        <v>3450.754211807039</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -530,7 +530,7 @@
         <v>45926</v>
       </c>
       <c r="B18">
-        <v>3450.826811120183</v>
+        <v>3450.799390348391</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -538,7 +538,7 @@
         <v>45933</v>
       </c>
       <c r="B19">
-        <v>3535.112787539386</v>
+        <v>3534.969062223913</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -546,7 +546,7 @@
         <v>45940</v>
       </c>
       <c r="B20">
-        <v>3634.237052033797</v>
+        <v>3633.962052112257</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -554,7 +554,7 @@
         <v>45947</v>
       </c>
       <c r="B21">
-        <v>3788.453839714752</v>
+        <v>3788.039272193641</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -562,7 +562,7 @@
         <v>45954</v>
       </c>
       <c r="B22">
-        <v>3858.861514814293</v>
+        <v>3858.490945216459</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -570,7 +570,7 @@
         <v>45961</v>
       </c>
       <c r="B23">
-        <v>3905.165707639655</v>
+        <v>3904.823586191436</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -578,7 +578,7 @@
         <v>45968</v>
       </c>
       <c r="B24">
-        <v>3889.765317837015</v>
+        <v>3889.47108280937</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -586,7 +586,7 @@
         <v>45975</v>
       </c>
       <c r="B25">
-        <v>3889.296842298702</v>
+        <v>3889.176105569643</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -594,7 +594,7 @@
         <v>45982</v>
       </c>
       <c r="B26">
-        <v>3994.389948935714</v>
+        <v>3994.352090784404</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -602,7 +602,7 @@
         <v>45989</v>
       </c>
       <c r="B27">
-        <v>4070.445527095382</v>
+        <v>4070.321760700661</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -610,7 +610,7 @@
         <v>45996</v>
       </c>
       <c r="B28">
-        <v>4110.993695204963</v>
+        <v>4110.840778305908</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -618,7 +618,7 @@
         <v>46003</v>
       </c>
       <c r="B29">
-        <v>4206.714783052241</v>
+        <v>4206.696096608788</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -626,7 +626,7 @@
         <v>46010</v>
       </c>
       <c r="B30">
-        <v>4200.750155560661</v>
+        <v>4200.681564533201</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -634,7 +634,7 @@
         <v>46017</v>
       </c>
       <c r="B31">
-        <v>4227.301518246002</v>
+        <v>4227.116734449025</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -642,7 +642,7 @@
         <v>46024</v>
       </c>
       <c r="B32">
-        <v>4248.132182376054</v>
+        <v>4247.947080063291</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -650,7 +650,7 @@
         <v>46031</v>
       </c>
       <c r="B33">
-        <v>4313.979391356958</v>
+        <v>4313.721440012039</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -658,7 +658,7 @@
         <v>46038</v>
       </c>
       <c r="B34">
-        <v>4407.502786708108</v>
+        <v>4407.17943338456</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -666,7 +666,7 @@
         <v>46045</v>
       </c>
       <c r="B35">
-        <v>4444.005864008092</v>
+        <v>4443.657092114022</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -674,7 +674,7 @@
         <v>46052</v>
       </c>
       <c r="B36">
-        <v>4547.589696513831</v>
+        <v>4547.126810166023</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -682,7 +682,7 @@
         <v>46059</v>
       </c>
       <c r="B37">
-        <v>4684.747739448978</v>
+        <v>4684.184886003792</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -690,7 +690,7 @@
         <v>46066</v>
       </c>
       <c r="B38">
-        <v>4769.086926650483</v>
+        <v>4768.379191899323</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -698,7 +698,7 @@
         <v>46073</v>
       </c>
       <c r="B39">
-        <v>4900.442456851832</v>
+        <v>4900.018940990887</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -706,7 +706,7 @@
         <v>46080</v>
       </c>
       <c r="B40">
-        <v>4942.280602748287</v>
+        <v>4941.815327879025</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -714,7 +714,7 @@
         <v>46087</v>
       </c>
       <c r="B41">
-        <v>5051.112364917691</v>
+        <v>5050.508795508555</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -722,7 +722,7 @@
         <v>46094</v>
       </c>
       <c r="B42">
-        <v>5214.708118201571</v>
+        <v>5214.374485358207</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>46101</v>
       </c>
       <c r="B43">
-        <v>5252.070047052601</v>
+        <v>5252.040209940966</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>46108</v>
       </c>
       <c r="B44">
-        <v>5286.095283646877</v>
+        <v>5286.499886916872</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>46115</v>
       </c>
       <c r="B45">
-        <v>5357.959688768765</v>
+        <v>5358.674446642377</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>46122</v>
       </c>
       <c r="B46">
-        <v>5431.433927798225</v>
+        <v>5432.356404380633</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>46129</v>
       </c>
       <c r="B47">
-        <v>5560.306308599962</v>
+        <v>5561.31241137958</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>46136</v>
       </c>
       <c r="B48">
-        <v>5496.0497966606</v>
+        <v>5497.313149938869</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>46143</v>
       </c>
       <c r="B49">
-        <v>5316.380297195889</v>
+        <v>5317.942714355051</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>46150</v>
       </c>
       <c r="B50">
-        <v>5201.26885096988</v>
+        <v>5202.735073688983</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>46157</v>
       </c>
       <c r="B51">
-        <v>5065.630297886497</v>
+        <v>5067.197911291538</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>46164</v>
       </c>
       <c r="B52">
-        <v>4954.113275126112</v>
+        <v>4955.525046527703</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>46171</v>
       </c>
       <c r="B53">
-        <v>4852.449187218346</v>
+        <v>4853.789274462441</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>46178</v>
       </c>
       <c r="B54">
-        <v>4801.162493497739</v>
+        <v>4802.676862615255</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>46185</v>
       </c>
       <c r="B55">
-        <v>4677.378127866468</v>
+        <v>4678.598855000095</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>46192</v>
       </c>
       <c r="B56">
-        <v>4561.818948964057</v>
+        <v>4562.680551905015</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>46199</v>
       </c>
       <c r="B57">
-        <v>4470.298147609563</v>
+        <v>4470.887985543791</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>46206</v>
       </c>
       <c r="B58">
-        <v>4465.274325434651</v>
+        <v>4465.875686247175</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>46213</v>
       </c>
       <c r="B59">
-        <v>4383.170343311758</v>
+        <v>4383.910891114885</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>46220</v>
       </c>
       <c r="B60">
-        <v>4221.552837324403</v>
+        <v>4222.517995152545</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>46227</v>
       </c>
       <c r="B61">
-        <v>4148.443235706554</v>
+        <v>4148.148454009641</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>46234</v>
       </c>
       <c r="B62">
-        <v>4093.870000165652</v>
+        <v>4097.879775646182</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>46241</v>
       </c>
       <c r="B63">
-        <v>4026.976948803605</v>
+        <v>4034.884824010433</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46248</v>
       </c>
       <c r="B64">
-        <v>3973.497122868495</v>
+        <v>3983.171874198959</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46255</v>
       </c>
       <c r="B65">
-        <v>3930.457055505917</v>
+        <v>3940.824687135705</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46262</v>
       </c>
       <c r="B66">
-        <v>3910.124803832985</v>
+        <v>3919.977566806858</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46269</v>
       </c>
       <c r="B67">
-        <v>3880.467664561048</v>
+        <v>3891.853397165917</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46276</v>
       </c>
       <c r="B68">
-        <v>3874.930136149907</v>
+        <v>3887.211261642009</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46283</v>
       </c>
       <c r="B69">
-        <v>3801.917370678545</v>
+        <v>3818.711881021324</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46290</v>
       </c>
       <c r="B70">
-        <v>3742.031522665141</v>
+        <v>3771.878768034167</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46297</v>
       </c>
       <c r="B71">
-        <v>3758.180903238913</v>
+        <v>3792.610643606671</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46304</v>
       </c>
       <c r="B72">
-        <v>3804.89804835492</v>
+        <v>3842.686882125496</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46311</v>
       </c>
       <c r="B73">
-        <v>3803.565124716391</v>
+        <v>3853.278961789743</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46318</v>
       </c>
       <c r="B74">
-        <v>3971.071866387134</v>
+        <v>4050.95447083194</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/XAUUSD_forecast.xlsx
+++ b/public/data/files/XAUUSD_forecast.xlsx
@@ -442,7 +442,7 @@
         <v>45849</v>
       </c>
       <c r="B7">
-        <v>3666.907777075309</v>
+        <v>3667.00694765142</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -450,7 +450,7 @@
         <v>45856</v>
       </c>
       <c r="B8">
-        <v>3563.409634364521</v>
+        <v>3563.543547454145</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -458,7 +458,7 @@
         <v>45863</v>
       </c>
       <c r="B9">
-        <v>3508.625792355444</v>
+        <v>3508.780465411047</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -466,7 +466,7 @@
         <v>45870</v>
       </c>
       <c r="B10">
-        <v>3480.880873257582</v>
+        <v>3481.044866984287</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -474,7 +474,7 @@
         <v>45877</v>
       </c>
       <c r="B11">
-        <v>3489.31783072748</v>
+        <v>3489.485865162137</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -482,7 +482,7 @@
         <v>45884</v>
       </c>
       <c r="B12">
-        <v>3502.072082905129</v>
+        <v>3502.242137110834</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -490,7 +490,7 @@
         <v>45891</v>
       </c>
       <c r="B13">
-        <v>3516.610997851548</v>
+        <v>3516.779792508758</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -498,7 +498,7 @@
         <v>45898</v>
       </c>
       <c r="B14">
-        <v>3529.162045670972</v>
+        <v>3529.328133212993</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -506,7 +506,7 @@
         <v>45905</v>
       </c>
       <c r="B15">
-        <v>3545.942721015294</v>
+        <v>3546.063650121745</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -514,7 +514,7 @@
         <v>45912</v>
       </c>
       <c r="B16">
-        <v>3453.221149119131</v>
+        <v>3453.188866471787</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -522,7 +522,7 @@
         <v>45919</v>
       </c>
       <c r="B17">
-        <v>3450.754211807039</v>
+        <v>3450.725687886644</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -530,7 +530,7 @@
         <v>45926</v>
       </c>
       <c r="B18">
-        <v>3450.799390348391</v>
+        <v>3450.77296682872</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -538,7 +538,7 @@
         <v>45933</v>
       </c>
       <c r="B19">
-        <v>3534.969062223913</v>
+        <v>3534.830482562455</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -546,7 +546,7 @@
         <v>45940</v>
       </c>
       <c r="B20">
-        <v>3633.962052112257</v>
+        <v>3633.696829032585</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -554,7 +554,7 @@
         <v>45947</v>
       </c>
       <c r="B21">
-        <v>3788.039272193641</v>
+        <v>3787.639291452689</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -562,7 +562,7 @@
         <v>45954</v>
       </c>
       <c r="B22">
-        <v>3858.490945216459</v>
+        <v>3858.133355328408</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -570,7 +570,7 @@
         <v>45961</v>
       </c>
       <c r="B23">
-        <v>3904.823586191436</v>
+        <v>3904.493144421788</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -578,7 +578,7 @@
         <v>45968</v>
       </c>
       <c r="B24">
-        <v>3889.47108280937</v>
+        <v>3889.186745352535</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -586,7 +586,7 @@
         <v>45975</v>
       </c>
       <c r="B25">
-        <v>3889.176105569643</v>
+        <v>3889.059265759558</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -594,7 +594,7 @@
         <v>45982</v>
       </c>
       <c r="B26">
-        <v>3994.352090784404</v>
+        <v>3994.315355331375</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -602,7 +602,7 @@
         <v>45989</v>
       </c>
       <c r="B27">
-        <v>4070.321760700661</v>
+        <v>4070.202199031974</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -610,7 +610,7 @@
         <v>45996</v>
       </c>
       <c r="B28">
-        <v>4110.840778305908</v>
+        <v>4110.693067421801</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -618,7 +618,7 @@
         <v>46003</v>
       </c>
       <c r="B29">
-        <v>4206.696096608788</v>
+        <v>4206.678218347407</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -626,7 +626,7 @@
         <v>46010</v>
       </c>
       <c r="B30">
-        <v>4200.681564533201</v>
+        <v>4200.615625044834</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -634,7 +634,7 @@
         <v>46017</v>
       </c>
       <c r="B31">
-        <v>4227.116734449025</v>
+        <v>4226.938820025844</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -642,7 +642,7 @@
         <v>46024</v>
       </c>
       <c r="B32">
-        <v>4247.947080063291</v>
+        <v>4247.768744944276</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -650,7 +650,7 @@
         <v>46031</v>
       </c>
       <c r="B33">
-        <v>4313.721440012039</v>
+        <v>4313.472801005195</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -658,7 +658,7 @@
         <v>46038</v>
       </c>
       <c r="B34">
-        <v>4407.17943338456</v>
+        <v>4406.867594556283</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -666,7 +666,7 @@
         <v>46045</v>
       </c>
       <c r="B35">
-        <v>4443.657092114022</v>
+        <v>4443.320581933799</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -674,7 +674,7 @@
         <v>46052</v>
       </c>
       <c r="B36">
-        <v>4547.126810166023</v>
+        <v>4546.680007145855</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -682,7 +682,7 @@
         <v>46059</v>
       </c>
       <c r="B37">
-        <v>4684.184886003792</v>
+        <v>4683.641631514278</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -690,7 +690,7 @@
         <v>46066</v>
       </c>
       <c r="B38">
-        <v>4768.379191899323</v>
+        <v>4767.695090767982</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -698,7 +698,7 @@
         <v>46073</v>
       </c>
       <c r="B39">
-        <v>4900.018940990887</v>
+        <v>4899.610077280188</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -706,7 +706,7 @@
         <v>46080</v>
       </c>
       <c r="B40">
-        <v>4941.815327879025</v>
+        <v>4941.366135207214</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -714,7 +714,7 @@
         <v>46087</v>
       </c>
       <c r="B41">
-        <v>5050.508795508555</v>
+        <v>5049.925818805428</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -722,7 +722,7 @@
         <v>46094</v>
       </c>
       <c r="B42">
-        <v>5214.374485358207</v>
+        <v>5214.051679170778</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>46101</v>
       </c>
       <c r="B43">
-        <v>5252.040209940966</v>
+        <v>5252.009751584293</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>46108</v>
       </c>
       <c r="B44">
-        <v>5286.499886916872</v>
+        <v>5286.888349917201</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>46115</v>
       </c>
       <c r="B45">
-        <v>5358.674446642377</v>
+        <v>5359.362849930598</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>46122</v>
       </c>
       <c r="B46">
-        <v>5432.356404380633</v>
+        <v>5433.245131140229</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>46129</v>
       </c>
       <c r="B47">
-        <v>5561.31241137958</v>
+        <v>5562.281949975812</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>46136</v>
       </c>
       <c r="B48">
-        <v>5497.313149938869</v>
+        <v>5498.531876204529</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>46143</v>
       </c>
       <c r="B49">
-        <v>5317.942714355051</v>
+        <v>5319.450795119361</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>46150</v>
       </c>
       <c r="B50">
-        <v>5202.735073688983</v>
+        <v>5204.150895958671</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>46157</v>
       </c>
       <c r="B51">
-        <v>5067.197911291538</v>
+        <v>5068.712559602223</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>46164</v>
       </c>
       <c r="B52">
-        <v>4955.525046527703</v>
+        <v>4956.889653059554</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>46171</v>
       </c>
       <c r="B53">
-        <v>4853.789274462441</v>
+        <v>4855.085401397779</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>46178</v>
       </c>
       <c r="B54">
-        <v>4802.676862615255</v>
+        <v>4804.141642707584</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>46185</v>
       </c>
       <c r="B55">
-        <v>4678.598855000095</v>
+        <v>4679.779352211757</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>46192</v>
       </c>
       <c r="B56">
-        <v>4562.680551905015</v>
+        <v>4563.513115933875</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>46199</v>
       </c>
       <c r="B57">
-        <v>4470.887985543791</v>
+        <v>4471.456870810346</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>46206</v>
       </c>
       <c r="B58">
-        <v>4465.875686247175</v>
+        <v>4466.455701207355</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>46213</v>
       </c>
       <c r="B59">
-        <v>4383.910891114885</v>
+        <v>4384.625783179473</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>46220</v>
       </c>
       <c r="B60">
-        <v>4222.517995152545</v>
+        <v>4223.451235810497</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>46227</v>
       </c>
       <c r="B61">
-        <v>4148.148454009641</v>
+        <v>4142.836154950199</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>46234</v>
       </c>
       <c r="B62">
-        <v>4097.879775646182</v>
+        <v>4095.150551422546</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>46241</v>
       </c>
       <c r="B63">
-        <v>4034.884824010433</v>
+        <v>4035.067561110171</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46248</v>
       </c>
       <c r="B64">
-        <v>3983.171874198959</v>
+        <v>3983.217437980455</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46255</v>
       </c>
       <c r="B65">
-        <v>3940.824687135705</v>
+        <v>3940.945067997148</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46262</v>
       </c>
       <c r="B66">
-        <v>3919.977566806858</v>
+        <v>3919.239593853348</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46269</v>
       </c>
       <c r="B67">
-        <v>3891.853397165917</v>
+        <v>3892.995191448006</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46276</v>
       </c>
       <c r="B68">
-        <v>3887.211261642009</v>
+        <v>3887.320241178183</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46283</v>
       </c>
       <c r="B69">
-        <v>3818.711881021324</v>
+        <v>3824.969405781432</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46290</v>
       </c>
       <c r="B70">
-        <v>3771.878768034167</v>
+        <v>3782.492476233594</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46297</v>
       </c>
       <c r="B71">
-        <v>3792.610643606671</v>
+        <v>3806.25131409699</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46304</v>
       </c>
       <c r="B72">
-        <v>3842.686882125496</v>
+        <v>3854.767303928239</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46311</v>
       </c>
       <c r="B73">
-        <v>3853.278961789743</v>
+        <v>3868.729061848447</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46318</v>
       </c>
       <c r="B74">
-        <v>4050.95447083194</v>
+        <v>4032.938124469719</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/XAUUSD_forecast.xlsx
+++ b/public/data/files/XAUUSD_forecast.xlsx
@@ -882,7 +882,7 @@
         <v>46234</v>
       </c>
       <c r="B62">
-        <v>4095.150551422546</v>
+        <v>4095.188940142897</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>46241</v>
       </c>
       <c r="B63">
-        <v>4035.067561110171</v>
+        <v>4035.193209116376</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46248</v>
       </c>
       <c r="B64">
-        <v>3983.217437980455</v>
+        <v>3983.742440487609</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46255</v>
       </c>
       <c r="B65">
-        <v>3940.945067997148</v>
+        <v>3941.686115570048</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46262</v>
       </c>
       <c r="B66">
-        <v>3919.239593853348</v>
+        <v>3920.228138504486</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46269</v>
       </c>
       <c r="B67">
-        <v>3892.995191448006</v>
+        <v>3893.949834738951</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46276</v>
       </c>
       <c r="B68">
-        <v>3887.320241178183</v>
+        <v>3889.438888908835</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46283</v>
       </c>
       <c r="B69">
-        <v>3824.969405781432</v>
+        <v>3824.923855468392</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46290</v>
       </c>
       <c r="B70">
-        <v>3782.492476233594</v>
+        <v>3782.512704038155</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46297</v>
       </c>
       <c r="B71">
-        <v>3806.25131409699</v>
+        <v>3805.261341784936</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46304</v>
       </c>
       <c r="B72">
-        <v>3854.767303928239</v>
+        <v>3854.716878645606</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46311</v>
       </c>
       <c r="B73">
-        <v>3868.729061848447</v>
+        <v>3868.704053942296</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46318</v>
       </c>
       <c r="B74">
-        <v>4032.938124469719</v>
+        <v>4032.907315779418</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/XAUUSD_forecast.xlsx
+++ b/public/data/files/XAUUSD_forecast.xlsx
@@ -442,7 +442,7 @@
         <v>45849</v>
       </c>
       <c r="B7">
-        <v>3667.00694765142</v>
+        <v>3667.102699586988</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -450,7 +450,7 @@
         <v>45856</v>
       </c>
       <c r="B8">
-        <v>3563.543547454145</v>
+        <v>3563.672871400059</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -458,7 +458,7 @@
         <v>45863</v>
       </c>
       <c r="B9">
-        <v>3508.780465411047</v>
+        <v>3508.929866943462</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -466,7 +466,7 @@
         <v>45870</v>
       </c>
       <c r="B10">
-        <v>3481.044866984287</v>
+        <v>3481.203310998869</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -474,7 +474,7 @@
         <v>45877</v>
       </c>
       <c r="B11">
-        <v>3489.485865162137</v>
+        <v>3489.648211664161</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -482,7 +482,7 @@
         <v>45884</v>
       </c>
       <c r="B12">
-        <v>3502.242137110834</v>
+        <v>3502.406433426948</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -490,7 +490,7 @@
         <v>45891</v>
       </c>
       <c r="B13">
-        <v>3516.779792508758</v>
+        <v>3516.942871072963</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -498,7 +498,7 @@
         <v>45898</v>
       </c>
       <c r="B14">
-        <v>3529.328133212993</v>
+        <v>3529.488596286113</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -506,7 +506,7 @@
         <v>45905</v>
       </c>
       <c r="B15">
-        <v>3546.063650121745</v>
+        <v>3546.180587364584</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -514,7 +514,7 @@
         <v>45912</v>
       </c>
       <c r="B16">
-        <v>3453.188866471787</v>
+        <v>3453.157728689299</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -522,7 +522,7 @@
         <v>45919</v>
       </c>
       <c r="B17">
-        <v>3450.725687886644</v>
+        <v>3450.698179743689</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -530,7 +530,7 @@
         <v>45926</v>
       </c>
       <c r="B18">
-        <v>3450.77296682872</v>
+        <v>3450.747487216965</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -538,7 +538,7 @@
         <v>45933</v>
       </c>
       <c r="B19">
-        <v>3534.830482562455</v>
+        <v>3534.696777365914</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -546,7 +546,7 @@
         <v>45940</v>
       </c>
       <c r="B20">
-        <v>3633.696829032585</v>
+        <v>3633.440871162575</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -554,7 +554,7 @@
         <v>45947</v>
       </c>
       <c r="B21">
-        <v>3787.639291452689</v>
+        <v>3787.253141803035</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -562,7 +562,7 @@
         <v>45954</v>
       </c>
       <c r="B22">
-        <v>3858.133355328408</v>
+        <v>3857.78807549313</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -570,7 +570,7 @@
         <v>45961</v>
       </c>
       <c r="B23">
-        <v>3904.493144421788</v>
+        <v>3904.173795589384</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -578,7 +578,7 @@
         <v>45968</v>
       </c>
       <c r="B24">
-        <v>3889.186745352535</v>
+        <v>3888.91181595909</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -586,7 +586,7 @@
         <v>45975</v>
       </c>
       <c r="B25">
-        <v>3889.059265759558</v>
+        <v>3888.946138639984</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -594,7 +594,7 @@
         <v>45982</v>
       </c>
       <c r="B26">
-        <v>3994.315355331375</v>
+        <v>3994.279694822888</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -602,7 +602,7 @@
         <v>45989</v>
       </c>
       <c r="B27">
-        <v>4070.202199031974</v>
+        <v>4070.086631476946</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -610,7 +610,7 @@
         <v>45996</v>
       </c>
       <c r="B28">
-        <v>4110.693067421801</v>
+        <v>4110.550301388247</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -618,7 +618,7 @@
         <v>46003</v>
       </c>
       <c r="B29">
-        <v>4206.678218347407</v>
+        <v>4206.661098782719</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -626,7 +626,7 @@
         <v>46010</v>
       </c>
       <c r="B30">
-        <v>4200.615625044834</v>
+        <v>4200.552187937235</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -634,7 +634,7 @@
         <v>46017</v>
       </c>
       <c r="B31">
-        <v>4226.938820025844</v>
+        <v>4226.767401211443</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -642,7 +642,7 @@
         <v>46024</v>
       </c>
       <c r="B32">
-        <v>4247.768744944276</v>
+        <v>4247.596814885103</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -650,7 +650,7 @@
         <v>46031</v>
       </c>
       <c r="B33">
-        <v>4313.472801005195</v>
+        <v>4313.232981945543</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -658,7 +658,7 @@
         <v>46038</v>
       </c>
       <c r="B34">
-        <v>4406.867594556283</v>
+        <v>4406.566669517096</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -666,7 +666,7 @@
         <v>46045</v>
       </c>
       <c r="B35">
-        <v>4443.320581933799</v>
+        <v>4442.995700875639</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -674,7 +674,7 @@
         <v>46052</v>
       </c>
       <c r="B36">
-        <v>4546.680007145855</v>
+        <v>4546.24846652485</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -682,7 +682,7 @@
         <v>46059</v>
       </c>
       <c r="B37">
-        <v>4683.641631514278</v>
+        <v>4683.116973969122</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -690,7 +690,7 @@
         <v>46066</v>
       </c>
       <c r="B38">
-        <v>4767.695090767982</v>
+        <v>4767.033463893363</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -698,7 +698,7 @@
         <v>46073</v>
       </c>
       <c r="B39">
-        <v>4899.610077280188</v>
+        <v>4899.215121706508</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -706,7 +706,7 @@
         <v>46080</v>
       </c>
       <c r="B40">
-        <v>4941.366135207214</v>
+        <v>4940.932208809067</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -714,7 +714,7 @@
         <v>46087</v>
       </c>
       <c r="B41">
-        <v>5049.925818805428</v>
+        <v>5049.362405206681</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -722,7 +722,7 @@
         <v>46094</v>
       </c>
       <c r="B42">
-        <v>5214.051679170778</v>
+        <v>5213.73918650117</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>46101</v>
       </c>
       <c r="B43">
-        <v>5252.009751584293</v>
+        <v>5251.978789420581</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>46108</v>
       </c>
       <c r="B44">
-        <v>5286.888349917201</v>
+        <v>5287.26160282628</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>46115</v>
       </c>
       <c r="B45">
-        <v>5359.362849930598</v>
+        <v>5360.026321061076</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>46122</v>
       </c>
       <c r="B46">
-        <v>5433.245131140229</v>
+        <v>5434.101915028056</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>46129</v>
       </c>
       <c r="B47">
-        <v>5562.281949975812</v>
+        <v>5563.216871466868</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>46136</v>
       </c>
       <c r="B48">
-        <v>5498.531876204529</v>
+        <v>5499.708289792046</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>46143</v>
       </c>
       <c r="B49">
-        <v>5319.450795119361</v>
+        <v>5320.907310424371</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>46150</v>
       </c>
       <c r="B50">
-        <v>5204.150895958671</v>
+        <v>5205.518857316666</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>46157</v>
       </c>
       <c r="B51">
-        <v>5068.712559602223</v>
+        <v>5070.176864331365</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>46164</v>
       </c>
       <c r="B52">
-        <v>4956.889653059554</v>
+        <v>4958.209405311636</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>46171</v>
       </c>
       <c r="B53">
-        <v>4855.085401397779</v>
+        <v>4856.339679776705</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>46178</v>
       </c>
       <c r="B54">
-        <v>4804.141642707584</v>
+        <v>4805.559210339492</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>46185</v>
       </c>
       <c r="B55">
-        <v>4679.779352211757</v>
+        <v>4680.921562265264</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>46192</v>
       </c>
       <c r="B56">
-        <v>4563.513115933875</v>
+        <v>4564.318077496389</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>46199</v>
       </c>
       <c r="B57">
-        <v>4471.456870810346</v>
+        <v>4472.005893798267</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>46206</v>
       </c>
       <c r="B58">
-        <v>4466.455701207355</v>
+        <v>4467.015481409129</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>46213</v>
       </c>
       <c r="B59">
-        <v>4384.625783179473</v>
+        <v>4385.316321759824</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>46220</v>
       </c>
       <c r="B60">
-        <v>4223.451235810497</v>
+        <v>4224.354097195977</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>46227</v>
       </c>
       <c r="B61">
-        <v>4142.836154950199</v>
+        <v>4137.983298950719</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>46234</v>
       </c>
       <c r="B62">
-        <v>4095.188940142897</v>
+        <v>4093.111169079884</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>46241</v>
       </c>
       <c r="B63">
-        <v>4035.193209116376</v>
+        <v>4036.436151883249</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46248</v>
       </c>
       <c r="B64">
-        <v>3983.742440487609</v>
+        <v>3986.972018929465</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46255</v>
       </c>
       <c r="B65">
-        <v>3941.686115570048</v>
+        <v>3946.410401343155</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46262</v>
       </c>
       <c r="B66">
-        <v>3920.228138504486</v>
+        <v>3926.823177569166</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46269</v>
       </c>
       <c r="B67">
-        <v>3893.949834738951</v>
+        <v>3902.261716044443</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46276</v>
       </c>
       <c r="B68">
-        <v>3889.438888908835</v>
+        <v>3897.722318908881</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46283</v>
       </c>
       <c r="B69">
-        <v>3824.923855468392</v>
+        <v>3837.740179668426</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46290</v>
       </c>
       <c r="B70">
-        <v>3782.512704038155</v>
+        <v>3800.673276362169</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46297</v>
       </c>
       <c r="B71">
-        <v>3805.261341784936</v>
+        <v>3826.130139479016</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46304</v>
       </c>
       <c r="B72">
-        <v>3854.716878645606</v>
+        <v>3876.341885341253</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46311</v>
       </c>
       <c r="B73">
-        <v>3868.704053942296</v>
+        <v>3895.504351384981</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46318</v>
       </c>
       <c r="B74">
-        <v>4032.907315779418</v>
+        <v>4052.793087739004</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/XAUUSD_forecast.xlsx
+++ b/public/data/files/XAUUSD_forecast.xlsx
@@ -383,7 +383,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B74"/>
+  <dimension ref="A1:B75"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" style="1" customWidth="1"/>
@@ -442,7 +442,7 @@
         <v>45849</v>
       </c>
       <c r="B7">
-        <v>3667.102699586988</v>
+        <v>3667.284631001332</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -450,7 +450,7 @@
         <v>45856</v>
       </c>
       <c r="B8">
-        <v>3563.672871400059</v>
+        <v>3563.918664003124</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -458,7 +458,7 @@
         <v>45863</v>
       </c>
       <c r="B9">
-        <v>3508.929866943462</v>
+        <v>3509.213897466959</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -466,7 +466,7 @@
         <v>45870</v>
       </c>
       <c r="B10">
-        <v>3481.203310998869</v>
+        <v>3481.504639083534</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -474,7 +474,7 @@
         <v>45877</v>
       </c>
       <c r="B11">
-        <v>3489.648211664161</v>
+        <v>3489.956957473936</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -482,7 +482,7 @@
         <v>45884</v>
       </c>
       <c r="B12">
-        <v>3502.406433426948</v>
+        <v>3502.718883039423</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -490,7 +490,7 @@
         <v>45891</v>
       </c>
       <c r="B13">
-        <v>3516.942871072963</v>
+        <v>3517.253002535631</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -498,7 +498,7 @@
         <v>45898</v>
       </c>
       <c r="B14">
-        <v>3529.488596286113</v>
+        <v>3529.793753658371</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -506,7 +506,7 @@
         <v>45905</v>
       </c>
       <c r="B15">
-        <v>3546.180587364584</v>
+        <v>3546.403249876285</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -514,7 +514,7 @@
         <v>45912</v>
       </c>
       <c r="B16">
-        <v>3453.157728689299</v>
+        <v>3453.098652715776</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -522,7 +522,7 @@
         <v>45919</v>
       </c>
       <c r="B17">
-        <v>3450.698179743689</v>
+        <v>3450.646001493869</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -530,7 +530,7 @@
         <v>45926</v>
       </c>
       <c r="B18">
-        <v>3450.747487216965</v>
+        <v>3450.699164682041</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -538,7 +538,7 @@
         <v>45933</v>
       </c>
       <c r="B19">
-        <v>3534.696777365914</v>
+        <v>3534.442997570976</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -546,7 +546,7 @@
         <v>45940</v>
       </c>
       <c r="B20">
-        <v>3633.440871162575</v>
+        <v>3632.954876801987</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -554,7 +554,7 @@
         <v>45947</v>
       </c>
       <c r="B21">
-        <v>3787.253141803035</v>
+        <v>3786.519565036729</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -562,7 +562,7 @@
         <v>45954</v>
       </c>
       <c r="B22">
-        <v>3857.78807549313</v>
+        <v>3857.131989850621</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -570,7 +570,7 @@
         <v>45961</v>
       </c>
       <c r="B23">
-        <v>3904.173795589384</v>
+        <v>3903.566219487819</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -578,7 +578,7 @@
         <v>45968</v>
       </c>
       <c r="B24">
-        <v>3888.91181595909</v>
+        <v>3888.388379054526</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -586,7 +586,7 @@
         <v>45975</v>
       </c>
       <c r="B25">
-        <v>3888.946138639984</v>
+        <v>3888.730341367165</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -594,7 +594,7 @@
         <v>45982</v>
       </c>
       <c r="B26">
-        <v>3994.279694822888</v>
+        <v>3994.211420265474</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -602,7 +602,7 @@
         <v>45989</v>
       </c>
       <c r="B27">
-        <v>4070.086631476946</v>
+        <v>4069.866704294588</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -610,7 +610,7 @@
         <v>45996</v>
       </c>
       <c r="B28">
-        <v>4110.550301388247</v>
+        <v>4110.278643658183</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -618,7 +618,7 @@
         <v>46003</v>
       </c>
       <c r="B29">
-        <v>4206.661098782719</v>
+        <v>4206.628956742146</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -626,7 +626,7 @@
         <v>46010</v>
       </c>
       <c r="B30">
-        <v>4200.552187937235</v>
+        <v>4200.432277669959</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -634,7 +634,7 @@
         <v>46017</v>
       </c>
       <c r="B31">
-        <v>4226.767401211443</v>
+        <v>4226.442685499932</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -642,7 +642,7 @@
         <v>46024</v>
       </c>
       <c r="B32">
-        <v>4247.596814885103</v>
+        <v>4247.270845462395</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -650,7 +650,7 @@
         <v>46031</v>
       </c>
       <c r="B33">
-        <v>4313.232981945543</v>
+        <v>4312.778000871433</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -658,7 +658,7 @@
         <v>46038</v>
       </c>
       <c r="B34">
-        <v>4406.566669517096</v>
+        <v>4405.995358789944</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -666,7 +666,7 @@
         <v>46045</v>
       </c>
       <c r="B35">
-        <v>4442.995700875639</v>
+        <v>4442.378505217086</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -674,7 +674,7 @@
         <v>46052</v>
       </c>
       <c r="B36">
-        <v>4546.24846652485</v>
+        <v>4545.428157990877</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -682,7 +682,7 @@
         <v>46059</v>
       </c>
       <c r="B37">
-        <v>4683.116973969122</v>
+        <v>4682.119770649044</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -690,7 +690,7 @@
         <v>46066</v>
       </c>
       <c r="B38">
-        <v>4767.033463893363</v>
+        <v>4765.773361024643</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -698,7 +698,7 @@
         <v>46073</v>
       </c>
       <c r="B39">
-        <v>4899.215121706508</v>
+        <v>4898.464201464307</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -706,7 +706,7 @@
         <v>46080</v>
       </c>
       <c r="B40">
-        <v>4940.932208809067</v>
+        <v>4940.107156912531</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -714,7 +714,7 @@
         <v>46087</v>
       </c>
       <c r="B41">
-        <v>5049.362405206681</v>
+        <v>5048.290478951236</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -722,7 +722,7 @@
         <v>46094</v>
       </c>
       <c r="B42">
-        <v>5213.73918650117</v>
+        <v>5213.143244518038</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>46101</v>
       </c>
       <c r="B43">
-        <v>5251.978789420581</v>
+        <v>5251.915756783597</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>46108</v>
       </c>
       <c r="B44">
-        <v>5287.26160282628</v>
+        <v>5287.965859551743</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>46115</v>
       </c>
       <c r="B45">
-        <v>5360.026321061076</v>
+        <v>5361.283665158508</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>46122</v>
       </c>
       <c r="B46">
-        <v>5434.101915028056</v>
+        <v>5435.726262852433</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>46129</v>
       </c>
       <c r="B47">
-        <v>5563.216871466868</v>
+        <v>5564.989987122456</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>46136</v>
       </c>
       <c r="B48">
-        <v>5499.708289792046</v>
+        <v>5501.942665737626</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>46143</v>
       </c>
       <c r="B49">
-        <v>5320.907310424371</v>
+        <v>5323.675822043917</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>46150</v>
       </c>
       <c r="B50">
-        <v>5205.518857316666</v>
+        <v>5208.120534903218</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>46157</v>
       </c>
       <c r="B51">
-        <v>5070.176864331365</v>
+        <v>5072.964097468067</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>46164</v>
       </c>
       <c r="B52">
-        <v>4958.209405311636</v>
+        <v>4960.722863053557</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>46171</v>
       </c>
       <c r="B53">
-        <v>4856.339679776705</v>
+        <v>4858.73048785389</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>46178</v>
       </c>
       <c r="B54">
-        <v>4805.559210339492</v>
+        <v>4808.261485064364</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>46185</v>
       </c>
       <c r="B55">
-        <v>4680.921562265264</v>
+        <v>4683.098290353535</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>46192</v>
       </c>
       <c r="B56">
-        <v>4564.318077496389</v>
+        <v>4565.850482710623</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>46199</v>
       </c>
       <c r="B57">
-        <v>4472.005893798267</v>
+        <v>4473.048350886973</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>46206</v>
       </c>
       <c r="B58">
-        <v>4467.015481409129</v>
+        <v>4468.078410998483</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>46213</v>
       </c>
       <c r="B59">
-        <v>4385.316321759824</v>
+        <v>4386.629123820961</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>46220</v>
       </c>
       <c r="B60">
-        <v>4224.354097195977</v>
+        <v>4226.07436134602</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>46227</v>
       </c>
       <c r="B61">
-        <v>4137.983298950719</v>
+        <v>4134.220234592726</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>46234</v>
       </c>
       <c r="B62">
-        <v>4093.111169079884</v>
+        <v>4090.321369488613</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>46241</v>
       </c>
       <c r="B63">
-        <v>4036.436151883249</v>
+        <v>4039.432330654533</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46248</v>
       </c>
       <c r="B64">
-        <v>3986.972018929465</v>
+        <v>3995.138233037041</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46255</v>
       </c>
       <c r="B65">
-        <v>3946.410401343155</v>
+        <v>3957.565915236908</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46262</v>
       </c>
       <c r="B66">
-        <v>3926.823177569166</v>
+        <v>3938.709511054734</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46269</v>
       </c>
       <c r="B67">
-        <v>3902.261716044443</v>
+        <v>3916.085697484938</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46276</v>
       </c>
       <c r="B68">
-        <v>3897.722318908881</v>
+        <v>3912.508460377744</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46283</v>
       </c>
       <c r="B69">
-        <v>3837.740179668426</v>
+        <v>3860.665975618186</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46290</v>
       </c>
       <c r="B70">
-        <v>3800.673276362169</v>
+        <v>3833.445275404981</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46297</v>
       </c>
       <c r="B71">
-        <v>3826.130139479016</v>
+        <v>3864.421807067302</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46304</v>
       </c>
       <c r="B72">
-        <v>3876.341885341253</v>
+        <v>3908.706089921778</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46311</v>
       </c>
       <c r="B73">
-        <v>3895.504351384981</v>
+        <v>3933.079659550198</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,15 @@
         <v>46318</v>
       </c>
       <c r="B74">
-        <v>4052.793087739004</v>
+        <v>4070.707283057092</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2">
+      <c r="A75" s="3">
+        <v>46325</v>
+      </c>
+      <c r="B75">
+        <v>4095.740403311014</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/XAUUSD_forecast.xlsx
+++ b/public/data/files/XAUUSD_forecast.xlsx
@@ -442,7 +442,7 @@
         <v>45849</v>
       </c>
       <c r="B7">
-        <v>3667.284631001332</v>
+        <v>3667.102699586988</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -450,7 +450,7 @@
         <v>45856</v>
       </c>
       <c r="B8">
-        <v>3563.918664003124</v>
+        <v>3563.672871400059</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -458,7 +458,7 @@
         <v>45863</v>
       </c>
       <c r="B9">
-        <v>3509.213897466959</v>
+        <v>3508.929866943462</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -466,7 +466,7 @@
         <v>45870</v>
       </c>
       <c r="B10">
-        <v>3481.504639083534</v>
+        <v>3481.203310998869</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -474,7 +474,7 @@
         <v>45877</v>
       </c>
       <c r="B11">
-        <v>3489.956957473936</v>
+        <v>3489.648211664161</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -482,7 +482,7 @@
         <v>45884</v>
       </c>
       <c r="B12">
-        <v>3502.718883039423</v>
+        <v>3502.406433426948</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -490,7 +490,7 @@
         <v>45891</v>
       </c>
       <c r="B13">
-        <v>3517.253002535631</v>
+        <v>3516.942871072963</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -498,7 +498,7 @@
         <v>45898</v>
       </c>
       <c r="B14">
-        <v>3529.793753658371</v>
+        <v>3529.488596286113</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -506,7 +506,7 @@
         <v>45905</v>
       </c>
       <c r="B15">
-        <v>3546.403249876285</v>
+        <v>3546.180587364584</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -514,7 +514,7 @@
         <v>45912</v>
       </c>
       <c r="B16">
-        <v>3453.098652715776</v>
+        <v>3453.157728689299</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -522,7 +522,7 @@
         <v>45919</v>
       </c>
       <c r="B17">
-        <v>3450.646001493869</v>
+        <v>3450.698179743689</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -530,7 +530,7 @@
         <v>45926</v>
       </c>
       <c r="B18">
-        <v>3450.699164682041</v>
+        <v>3450.747487216965</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -538,7 +538,7 @@
         <v>45933</v>
       </c>
       <c r="B19">
-        <v>3534.442997570976</v>
+        <v>3534.696777365914</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -546,7 +546,7 @@
         <v>45940</v>
       </c>
       <c r="B20">
-        <v>3632.954876801987</v>
+        <v>3633.440871162575</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -554,7 +554,7 @@
         <v>45947</v>
       </c>
       <c r="B21">
-        <v>3786.519565036729</v>
+        <v>3787.253141803035</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -562,7 +562,7 @@
         <v>45954</v>
       </c>
       <c r="B22">
-        <v>3857.131989850621</v>
+        <v>3857.78807549313</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -570,7 +570,7 @@
         <v>45961</v>
       </c>
       <c r="B23">
-        <v>3903.566219487819</v>
+        <v>3904.173795589384</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -578,7 +578,7 @@
         <v>45968</v>
       </c>
       <c r="B24">
-        <v>3888.388379054526</v>
+        <v>3888.91181595909</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -586,7 +586,7 @@
         <v>45975</v>
       </c>
       <c r="B25">
-        <v>3888.730341367165</v>
+        <v>3888.946138639984</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -594,7 +594,7 @@
         <v>45982</v>
       </c>
       <c r="B26">
-        <v>3994.211420265474</v>
+        <v>3994.279694822888</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -602,7 +602,7 @@
         <v>45989</v>
       </c>
       <c r="B27">
-        <v>4069.866704294588</v>
+        <v>4070.086631476946</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -610,7 +610,7 @@
         <v>45996</v>
       </c>
       <c r="B28">
-        <v>4110.278643658183</v>
+        <v>4110.550301388247</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -618,7 +618,7 @@
         <v>46003</v>
       </c>
       <c r="B29">
-        <v>4206.628956742146</v>
+        <v>4206.661098782719</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -626,7 +626,7 @@
         <v>46010</v>
       </c>
       <c r="B30">
-        <v>4200.432277669959</v>
+        <v>4200.552187937235</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -634,7 +634,7 @@
         <v>46017</v>
       </c>
       <c r="B31">
-        <v>4226.442685499932</v>
+        <v>4226.767401211443</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -642,7 +642,7 @@
         <v>46024</v>
       </c>
       <c r="B32">
-        <v>4247.270845462395</v>
+        <v>4247.596814885103</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -650,7 +650,7 @@
         <v>46031</v>
       </c>
       <c r="B33">
-        <v>4312.778000871433</v>
+        <v>4313.232981945543</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -658,7 +658,7 @@
         <v>46038</v>
       </c>
       <c r="B34">
-        <v>4405.995358789944</v>
+        <v>4406.566669517096</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -666,7 +666,7 @@
         <v>46045</v>
       </c>
       <c r="B35">
-        <v>4442.378505217086</v>
+        <v>4442.995700875639</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -674,7 +674,7 @@
         <v>46052</v>
       </c>
       <c r="B36">
-        <v>4545.428157990877</v>
+        <v>4546.24846652485</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -682,7 +682,7 @@
         <v>46059</v>
       </c>
       <c r="B37">
-        <v>4682.119770649044</v>
+        <v>4683.116973969122</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -690,7 +690,7 @@
         <v>46066</v>
       </c>
       <c r="B38">
-        <v>4765.773361024643</v>
+        <v>4767.033463893363</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -698,7 +698,7 @@
         <v>46073</v>
       </c>
       <c r="B39">
-        <v>4898.464201464307</v>
+        <v>4899.215121706508</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -706,7 +706,7 @@
         <v>46080</v>
       </c>
       <c r="B40">
-        <v>4940.107156912531</v>
+        <v>4940.932208809067</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -714,7 +714,7 @@
         <v>46087</v>
       </c>
       <c r="B41">
-        <v>5048.290478951236</v>
+        <v>5049.362405206681</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -722,7 +722,7 @@
         <v>46094</v>
       </c>
       <c r="B42">
-        <v>5213.143244518038</v>
+        <v>5213.73918650117</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>46101</v>
       </c>
       <c r="B43">
-        <v>5251.915756783597</v>
+        <v>5251.978789420581</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>46108</v>
       </c>
       <c r="B44">
-        <v>5287.965859551743</v>
+        <v>5287.26160282628</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>46115</v>
       </c>
       <c r="B45">
-        <v>5361.283665158508</v>
+        <v>5360.026321061076</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>46122</v>
       </c>
       <c r="B46">
-        <v>5435.726262852433</v>
+        <v>5434.101915028056</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>46129</v>
       </c>
       <c r="B47">
-        <v>5564.989987122456</v>
+        <v>5563.216871466868</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>46136</v>
       </c>
       <c r="B48">
-        <v>5501.942665737626</v>
+        <v>5499.708289792046</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>46143</v>
       </c>
       <c r="B49">
-        <v>5323.675822043917</v>
+        <v>5320.907310424371</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>46150</v>
       </c>
       <c r="B50">
-        <v>5208.120534903218</v>
+        <v>5205.518857316666</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>46157</v>
       </c>
       <c r="B51">
-        <v>5072.964097468067</v>
+        <v>5070.176864331365</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>46164</v>
       </c>
       <c r="B52">
-        <v>4960.722863053557</v>
+        <v>4958.209405311636</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>46171</v>
       </c>
       <c r="B53">
-        <v>4858.73048785389</v>
+        <v>4856.339679776705</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>46178</v>
       </c>
       <c r="B54">
-        <v>4808.261485064364</v>
+        <v>4805.559210339492</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>46185</v>
       </c>
       <c r="B55">
-        <v>4683.098290353535</v>
+        <v>4680.921562265264</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>46192</v>
       </c>
       <c r="B56">
-        <v>4565.850482710623</v>
+        <v>4564.318077496389</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>46199</v>
       </c>
       <c r="B57">
-        <v>4473.048350886973</v>
+        <v>4472.005893798267</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>46206</v>
       </c>
       <c r="B58">
-        <v>4468.078410998483</v>
+        <v>4467.015481409129</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>46213</v>
       </c>
       <c r="B59">
-        <v>4386.629123820961</v>
+        <v>4385.316321759824</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>46220</v>
       </c>
       <c r="B60">
-        <v>4226.07436134602</v>
+        <v>4224.354097195977</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>46227</v>
       </c>
       <c r="B61">
-        <v>4134.220234592726</v>
+        <v>4143.576077265614</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>46234</v>
       </c>
       <c r="B62">
-        <v>4090.321369488613</v>
+        <v>4093.940610507894</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>46241</v>
       </c>
       <c r="B63">
-        <v>4039.432330654533</v>
+        <v>4037.297491120786</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46248</v>
       </c>
       <c r="B64">
-        <v>3995.138233037041</v>
+        <v>3988.862513825022</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46255</v>
       </c>
       <c r="B65">
-        <v>3957.565915236908</v>
+        <v>3947.557378394098</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46262</v>
       </c>
       <c r="B66">
-        <v>3938.709511054734</v>
+        <v>3924.776414468398</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46269</v>
       </c>
       <c r="B67">
-        <v>3916.085697484938</v>
+        <v>3899.55908409705</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46276</v>
       </c>
       <c r="B68">
-        <v>3912.508460377744</v>
+        <v>3895.082935231238</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46283</v>
       </c>
       <c r="B69">
-        <v>3860.665975618186</v>
+        <v>3838.290966158644</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46290</v>
       </c>
       <c r="B70">
-        <v>3833.445275404981</v>
+        <v>3804.012899880115</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46297</v>
       </c>
       <c r="B71">
-        <v>3864.421807067302</v>
+        <v>3833.120120891514</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46304</v>
       </c>
       <c r="B72">
-        <v>3908.706089921778</v>
+        <v>3873.584414323417</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46311</v>
       </c>
       <c r="B73">
-        <v>3933.079659550198</v>
+        <v>3890.815031337521</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46318</v>
       </c>
       <c r="B74">
-        <v>4070.707283057092</v>
+        <v>4044.04579715992</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46325</v>
       </c>
       <c r="B75">
-        <v>4095.740403311014</v>
+        <v>4088.106495350269</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/XAUUSD_forecast.xlsx
+++ b/public/data/files/XAUUSD_forecast.xlsx
@@ -890,7 +890,7 @@
         <v>46241</v>
       </c>
       <c r="B63">
-        <v>4037.297491120786</v>
+        <v>4037.298994489214</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46248</v>
       </c>
       <c r="B64">
-        <v>3988.862513825022</v>
+        <v>3988.882111393243</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46255</v>
       </c>
       <c r="B65">
-        <v>3947.557378394098</v>
+        <v>3947.887927851341</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46262</v>
       </c>
       <c r="B66">
-        <v>3924.776414468398</v>
+        <v>3925.468121472048</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46269</v>
       </c>
       <c r="B67">
-        <v>3899.55908409705</v>
+        <v>3899.903729344754</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46276</v>
       </c>
       <c r="B68">
-        <v>3895.082935231238</v>
+        <v>3895.391096971836</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46283</v>
       </c>
       <c r="B69">
-        <v>3838.290966158644</v>
+        <v>3838.514004713725</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46290</v>
       </c>
       <c r="B70">
-        <v>3804.012899880115</v>
+        <v>3804.154338693103</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46297</v>
       </c>
       <c r="B71">
-        <v>3833.120120891514</v>
+        <v>3831.147622032342</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46304</v>
       </c>
       <c r="B72">
-        <v>3873.584414323417</v>
+        <v>3873.629091013674</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46311</v>
       </c>
       <c r="B73">
-        <v>3890.815031337521</v>
+        <v>3890.85082316529</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46318</v>
       </c>
       <c r="B74">
-        <v>4044.04579715992</v>
+        <v>4044.095736202401</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46325</v>
       </c>
       <c r="B75">
-        <v>4088.106495350269</v>
+        <v>4088.269828065314</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/XAUUSD_forecast.xlsx
+++ b/public/data/files/XAUUSD_forecast.xlsx
@@ -442,7 +442,7 @@
         <v>45849</v>
       </c>
       <c r="B7">
-        <v>3667.102699586988</v>
+        <v>3667.195206642848</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -450,7 +450,7 @@
         <v>45856</v>
       </c>
       <c r="B8">
-        <v>3563.672871400059</v>
+        <v>3563.797838077638</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -458,7 +458,7 @@
         <v>45863</v>
       </c>
       <c r="B9">
-        <v>3508.929866943462</v>
+        <v>3509.074261821001</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -466,7 +466,7 @@
         <v>45870</v>
       </c>
       <c r="B10">
-        <v>3481.203310998869</v>
+        <v>3481.356482123394</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -474,7 +474,7 @@
         <v>45877</v>
       </c>
       <c r="B11">
-        <v>3489.648211664161</v>
+        <v>3489.805154023634</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -482,7 +482,7 @@
         <v>45884</v>
       </c>
       <c r="B12">
-        <v>3502.406433426948</v>
+        <v>3502.565259214623</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -490,7 +490,7 @@
         <v>45891</v>
       </c>
       <c r="B13">
-        <v>3516.942871072963</v>
+        <v>3517.100518863754</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -498,7 +498,7 @@
         <v>45898</v>
       </c>
       <c r="B14">
-        <v>3529.488596286113</v>
+        <v>3529.643715640126</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -506,7 +506,7 @@
         <v>45905</v>
       </c>
       <c r="B15">
-        <v>3546.180587364584</v>
+        <v>3546.293726732662</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -514,7 +514,7 @@
         <v>45912</v>
       </c>
       <c r="B16">
-        <v>3453.157728689299</v>
+        <v>3453.127675999554</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -522,7 +522,7 @@
         <v>45919</v>
       </c>
       <c r="B17">
-        <v>3450.698179743689</v>
+        <v>3450.671634141192</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -530,7 +530,7 @@
         <v>45926</v>
       </c>
       <c r="B18">
-        <v>3450.747487216965</v>
+        <v>3450.722901901331</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -538,7 +538,7 @@
         <v>45933</v>
       </c>
       <c r="B19">
-        <v>3534.696777365914</v>
+        <v>3534.567694154057</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -546,7 +546,7 @@
         <v>45940</v>
       </c>
       <c r="B20">
-        <v>3633.440871162575</v>
+        <v>3633.193701915226</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -554,7 +554,7 @@
         <v>45947</v>
       </c>
       <c r="B21">
-        <v>3787.253141803035</v>
+        <v>3786.880118812481</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -562,7 +562,7 @@
         <v>45954</v>
       </c>
       <c r="B22">
-        <v>3857.78807549313</v>
+        <v>3857.454481304316</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -570,7 +570,7 @@
         <v>45961</v>
       </c>
       <c r="B23">
-        <v>3904.173795589384</v>
+        <v>3903.864991518273</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -578,7 +578,7 @@
         <v>45968</v>
       </c>
       <c r="B24">
-        <v>3888.91181595909</v>
+        <v>3888.645836767482</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -586,7 +586,7 @@
         <v>45975</v>
       </c>
       <c r="B25">
-        <v>3888.946138639984</v>
+        <v>3888.836551314049</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -594,7 +594,7 @@
         <v>45982</v>
       </c>
       <c r="B26">
-        <v>3994.279694822888</v>
+        <v>3994.245064065117</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -602,7 +602,7 @@
         <v>45989</v>
       </c>
       <c r="B27">
-        <v>4070.086631476946</v>
+        <v>4069.974861253781</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -610,7 +610,7 @@
         <v>45996</v>
       </c>
       <c r="B28">
-        <v>4110.550301388247</v>
+        <v>4110.412236206708</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -618,7 +618,7 @@
         <v>46003</v>
       </c>
       <c r="B29">
-        <v>4206.661098782719</v>
+        <v>4206.64469228989</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -626,7 +626,7 @@
         <v>46010</v>
       </c>
       <c r="B30">
-        <v>4200.552187937235</v>
+        <v>4200.491114933256</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -634,7 +634,7 @@
         <v>46017</v>
       </c>
       <c r="B31">
-        <v>4226.767401211443</v>
+        <v>4226.602130729954</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -642,7 +642,7 @@
         <v>46024</v>
       </c>
       <c r="B32">
-        <v>4247.596814885103</v>
+        <v>4247.430952992217</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -650,7 +650,7 @@
         <v>46031</v>
       </c>
       <c r="B33">
-        <v>4313.232981945543</v>
+        <v>4313.001524367126</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -658,7 +658,7 @@
         <v>46038</v>
       </c>
       <c r="B34">
-        <v>4406.566669517096</v>
+        <v>4406.276098401462</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -666,7 +666,7 @@
         <v>46045</v>
       </c>
       <c r="B35">
-        <v>4442.995700875639</v>
+        <v>4442.681858941665</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -674,7 +674,7 @@
         <v>46052</v>
       </c>
       <c r="B36">
-        <v>4546.24846652485</v>
+        <v>4545.831422113824</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -682,7 +682,7 @@
         <v>46059</v>
       </c>
       <c r="B37">
-        <v>4683.116973969122</v>
+        <v>4682.609978247155</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -690,7 +690,7 @@
         <v>46066</v>
       </c>
       <c r="B38">
-        <v>4767.033463893363</v>
+        <v>4766.393226190408</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -698,7 +698,7 @@
         <v>46073</v>
       </c>
       <c r="B39">
-        <v>4899.215121706508</v>
+        <v>4898.833379566048</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -706,7 +706,7 @@
         <v>46080</v>
       </c>
       <c r="B40">
-        <v>4940.932208809067</v>
+        <v>4940.512786791508</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -714,7 +714,7 @@
         <v>46087</v>
       </c>
       <c r="B41">
-        <v>5049.362405206681</v>
+        <v>5048.817592185505</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -722,7 +722,7 @@
         <v>46094</v>
       </c>
       <c r="B42">
-        <v>5213.73918650117</v>
+        <v>5213.43652575303</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>46101</v>
       </c>
       <c r="B43">
-        <v>5251.978789420581</v>
+        <v>5251.947427239569</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>46108</v>
       </c>
       <c r="B44">
-        <v>5287.26160282628</v>
+        <v>5287.620506668383</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>46115</v>
       </c>
       <c r="B45">
-        <v>5360.026321061076</v>
+        <v>5360.666182462781</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>46122</v>
       </c>
       <c r="B46">
-        <v>5434.101915028056</v>
+        <v>5434.928437020949</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>46129</v>
       </c>
       <c r="B47">
-        <v>5563.216871466868</v>
+        <v>5564.118987771225</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>46136</v>
       </c>
       <c r="B48">
-        <v>5499.708289792046</v>
+        <v>5500.84454833048</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>46143</v>
       </c>
       <c r="B49">
-        <v>5320.907310424371</v>
+        <v>5322.314846937352</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>46150</v>
       </c>
       <c r="B50">
-        <v>5205.518857316666</v>
+        <v>5206.841330513862</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>46157</v>
       </c>
       <c r="B51">
-        <v>5070.176864331365</v>
+        <v>5071.593278005927</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>46164</v>
       </c>
       <c r="B52">
-        <v>4958.209405311636</v>
+        <v>4959.486466314002</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>46171</v>
       </c>
       <c r="B53">
-        <v>4856.339679776705</v>
+        <v>4857.554089334368</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>46178</v>
       </c>
       <c r="B54">
-        <v>4805.559210339492</v>
+        <v>4806.931793941796</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>46185</v>
       </c>
       <c r="B55">
-        <v>4680.921562265264</v>
+        <v>4682.027305727814</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>46192</v>
       </c>
       <c r="B56">
-        <v>4564.318077496389</v>
+        <v>4565.096780314567</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>46199</v>
       </c>
       <c r="B57">
-        <v>4472.005893798267</v>
+        <v>4472.536070948956</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>46206</v>
       </c>
       <c r="B58">
-        <v>4467.015481409129</v>
+        <v>4467.556062510184</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>46213</v>
       </c>
       <c r="B59">
-        <v>4385.316321759824</v>
+        <v>4385.983722985424</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>46220</v>
       </c>
       <c r="B60">
-        <v>4224.354097195977</v>
+        <v>4225.228021276628</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>46227</v>
       </c>
       <c r="B61">
-        <v>4143.576077265614</v>
+        <v>4144.29380160749</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>46234</v>
       </c>
       <c r="B62">
-        <v>4093.940610507894</v>
+        <v>4090.136782205577</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>46241</v>
       </c>
       <c r="B63">
-        <v>4037.298994489214</v>
+        <v>4035.849780862063</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46248</v>
       </c>
       <c r="B64">
-        <v>3988.882111393243</v>
+        <v>3990.298113429881</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46255</v>
       </c>
       <c r="B65">
-        <v>3947.887927851341</v>
+        <v>3949.47944608971</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46262</v>
       </c>
       <c r="B66">
-        <v>3925.468121472048</v>
+        <v>3926.122627620297</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46269</v>
       </c>
       <c r="B67">
-        <v>3899.903729344754</v>
+        <v>3901.16809794706</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46276</v>
       </c>
       <c r="B68">
-        <v>3895.391096971836</v>
+        <v>3897.883242905077</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46283</v>
       </c>
       <c r="B69">
-        <v>3838.514004713725</v>
+        <v>3845.334331020331</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46290</v>
       </c>
       <c r="B70">
-        <v>3804.154338693103</v>
+        <v>3816.876596669294</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46297</v>
       </c>
       <c r="B71">
-        <v>3831.147622032342</v>
+        <v>3840.341192560654</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46304</v>
       </c>
       <c r="B72">
-        <v>3873.629091013674</v>
+        <v>3880.956375906653</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46311</v>
       </c>
       <c r="B73">
-        <v>3890.85082316529</v>
+        <v>3898.587234479237</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46318</v>
       </c>
       <c r="B74">
-        <v>4044.095736202401</v>
+        <v>4031.187996137114</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46325</v>
       </c>
       <c r="B75">
-        <v>4088.269828065314</v>
+        <v>4028.221972258968</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/XAUUSD_forecast.xlsx
+++ b/public/data/files/XAUUSD_forecast.xlsx
@@ -442,7 +442,7 @@
         <v>45849</v>
       </c>
       <c r="B7">
-        <v>3667.195206642848</v>
+        <v>3667.371124214793</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -450,7 +450,7 @@
         <v>45856</v>
       </c>
       <c r="B8">
-        <v>3563.797838077638</v>
+        <v>3564.035551584357</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -458,7 +458,7 @@
         <v>45863</v>
       </c>
       <c r="B9">
-        <v>3509.074261821001</v>
+        <v>3509.349005271999</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -466,7 +466,7 @@
         <v>45870</v>
       </c>
       <c r="B10">
-        <v>3481.356482123394</v>
+        <v>3481.648023962474</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -474,7 +474,7 @@
         <v>45877</v>
       </c>
       <c r="B11">
-        <v>3489.805154023634</v>
+        <v>3490.103870183018</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -482,7 +482,7 @@
         <v>45884</v>
       </c>
       <c r="B12">
-        <v>3502.565259214623</v>
+        <v>3502.867556182241</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -490,7 +490,7 @@
         <v>45891</v>
       </c>
       <c r="B13">
-        <v>3517.100518863754</v>
+        <v>3517.400571578684</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -498,7 +498,7 @@
         <v>45898</v>
       </c>
       <c r="B14">
-        <v>3529.643715640126</v>
+        <v>3529.938955834436</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -506,7 +506,7 @@
         <v>45905</v>
       </c>
       <c r="B15">
-        <v>3546.293726732662</v>
+        <v>3546.509327070344</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -514,7 +514,7 @@
         <v>45912</v>
       </c>
       <c r="B16">
-        <v>3453.127675999554</v>
+        <v>3453.0706068937</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -522,7 +522,7 @@
         <v>45919</v>
       </c>
       <c r="B17">
-        <v>3450.671634141192</v>
+        <v>3450.621235560671</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -530,7 +530,7 @@
         <v>45926</v>
       </c>
       <c r="B18">
-        <v>3450.722901901331</v>
+        <v>3450.676232483341</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -538,7 +538,7 @@
         <v>45933</v>
       </c>
       <c r="B19">
-        <v>3534.567694154057</v>
+        <v>3534.322467958785</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -546,7 +546,7 @@
         <v>45940</v>
       </c>
       <c r="B20">
-        <v>3633.193701915226</v>
+        <v>3632.723980778095</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -554,7 +554,7 @@
         <v>45947</v>
       </c>
       <c r="B21">
-        <v>3786.880118812481</v>
+        <v>3786.170866169804</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -562,7 +562,7 @@
         <v>45954</v>
       </c>
       <c r="B22">
-        <v>3857.454481304316</v>
+        <v>3856.820056327606</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -570,7 +570,7 @@
         <v>45961</v>
       </c>
       <c r="B23">
-        <v>3903.864991518273</v>
+        <v>3903.276999418127</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -578,7 +578,7 @@
         <v>45968</v>
       </c>
       <c r="B24">
-        <v>3888.645836767482</v>
+        <v>3888.139040961707</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -586,7 +586,7 @@
         <v>45975</v>
       </c>
       <c r="B25">
-        <v>3888.836551314049</v>
+        <v>3888.62735609209</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -594,7 +594,7 @@
         <v>45982</v>
       </c>
       <c r="B26">
-        <v>3994.245064065117</v>
+        <v>3994.178722884341</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -602,7 +602,7 @@
         <v>45989</v>
       </c>
       <c r="B27">
-        <v>4069.974861253781</v>
+        <v>4069.761988235164</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -610,7 +610,7 @@
         <v>45996</v>
       </c>
       <c r="B28">
-        <v>4110.412236206708</v>
+        <v>4110.149310048981</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -618,7 +618,7 @@
         <v>46003</v>
       </c>
       <c r="B29">
-        <v>4206.64469228989</v>
+        <v>4206.613853187821</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -626,7 +626,7 @@
         <v>46010</v>
       </c>
       <c r="B30">
-        <v>4200.491114933256</v>
+        <v>4200.37555683229</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -634,7 +634,7 @@
         <v>46017</v>
       </c>
       <c r="B31">
-        <v>4226.602130729954</v>
+        <v>4226.288764573095</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -642,7 +642,7 @@
         <v>46024</v>
       </c>
       <c r="B32">
-        <v>4247.430952992217</v>
+        <v>4247.116199647747</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -650,7 +650,7 @@
         <v>46031</v>
       </c>
       <c r="B33">
-        <v>4313.001524367126</v>
+        <v>4312.562012552557</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -658,7 +658,7 @@
         <v>46038</v>
       </c>
       <c r="B34">
-        <v>4406.276098401462</v>
+        <v>4405.723962645975</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -666,7 +666,7 @@
         <v>46045</v>
       </c>
       <c r="B35">
-        <v>4442.681858941665</v>
+        <v>4442.085124699604</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -674,7 +674,7 @@
         <v>46052</v>
       </c>
       <c r="B36">
-        <v>4545.831422113824</v>
+        <v>4545.038004459286</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -682,7 +682,7 @@
         <v>46059</v>
       </c>
       <c r="B37">
-        <v>4682.609978247155</v>
+        <v>4681.645533954736</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -690,7 +690,7 @@
         <v>46066</v>
       </c>
       <c r="B38">
-        <v>4766.393226190408</v>
+        <v>4765.172914922231</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -698,7 +698,7 @@
         <v>46073</v>
       </c>
       <c r="B39">
-        <v>4898.833379566048</v>
+        <v>4898.106979697398</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -706,7 +706,7 @@
         <v>46080</v>
       </c>
       <c r="B40">
-        <v>4940.512786791508</v>
+        <v>4939.714652618845</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -714,7 +714,7 @@
         <v>46087</v>
       </c>
       <c r="B41">
-        <v>5048.817592185505</v>
+        <v>5047.78022160911</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -722,7 +722,7 @@
         <v>46094</v>
       </c>
       <c r="B42">
-        <v>5213.43652575303</v>
+        <v>5212.858917426446</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>46101</v>
       </c>
       <c r="B43">
-        <v>5251.947427239569</v>
+        <v>5251.883859146628</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>46108</v>
       </c>
       <c r="B44">
-        <v>5287.620506668383</v>
+        <v>5288.298402249611</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>46115</v>
       </c>
       <c r="B45">
-        <v>5360.666182462781</v>
+        <v>5361.879916490338</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>46122</v>
       </c>
       <c r="B46">
-        <v>5434.928437020949</v>
+        <v>5436.496852670589</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>46129</v>
       </c>
       <c r="B47">
-        <v>5564.118987771225</v>
+        <v>5565.831444399511</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>46136</v>
       </c>
       <c r="B48">
-        <v>5500.84454833048</v>
+        <v>5503.004523946882</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>46143</v>
       </c>
       <c r="B49">
-        <v>5322.314846937352</v>
+        <v>5324.99249740312</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>46150</v>
       </c>
       <c r="B50">
-        <v>5206.841330513862</v>
+        <v>5209.358548567241</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>46157</v>
       </c>
       <c r="B51">
-        <v>5071.593278005927</v>
+        <v>5074.291475949005</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>46164</v>
       </c>
       <c r="B52">
-        <v>4959.486466314002</v>
+        <v>4961.920496936371</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>46171</v>
       </c>
       <c r="B53">
-        <v>4857.554089334368</v>
+        <v>4859.870620333669</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>46178</v>
       </c>
       <c r="B54">
-        <v>4806.931793941796</v>
+        <v>4809.550248629689</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>46185</v>
       </c>
       <c r="B55">
-        <v>4682.027305727814</v>
+        <v>4684.136119622741</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>46192</v>
       </c>
       <c r="B56">
-        <v>4565.096780314567</v>
+        <v>4566.580364251269</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>46199</v>
       </c>
       <c r="B57">
-        <v>4472.536070948956</v>
+        <v>4473.543619953946</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>46206</v>
       </c>
       <c r="B58">
-        <v>4467.556062510184</v>
+        <v>4468.583429847011</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>46213</v>
       </c>
       <c r="B59">
-        <v>4385.983722985424</v>
+        <v>4387.253588366336</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>46220</v>
       </c>
       <c r="B60">
-        <v>4225.228021276628</v>
+        <v>4226.894388641681</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>46227</v>
       </c>
       <c r="B61">
-        <v>4144.29380160749</v>
+        <v>4134.885114702442</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>46234</v>
       </c>
       <c r="B62">
-        <v>4090.136782205577</v>
+        <v>4086.902452723792</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>46241</v>
       </c>
       <c r="B63">
-        <v>4035.849780862063</v>
+        <v>4037.657553931368</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46248</v>
       </c>
       <c r="B64">
-        <v>3990.298113429881</v>
+        <v>3995.961263100259</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46255</v>
       </c>
       <c r="B65">
-        <v>3949.47944608971</v>
+        <v>3957.698526992847</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46262</v>
       </c>
       <c r="B66">
-        <v>3926.122627620297</v>
+        <v>3938.220746628454</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46269</v>
       </c>
       <c r="B67">
-        <v>3901.16809794706</v>
+        <v>3916.42841393106</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46276</v>
       </c>
       <c r="B68">
-        <v>3897.883242905077</v>
+        <v>3914.394678703468</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46283</v>
       </c>
       <c r="B69">
-        <v>3845.334331020331</v>
+        <v>3865.629477291285</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46290</v>
       </c>
       <c r="B70">
-        <v>3816.876596669294</v>
+        <v>3842.206934787123</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46297</v>
       </c>
       <c r="B71">
-        <v>3840.341192560654</v>
+        <v>3870.360028262616</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46304</v>
       </c>
       <c r="B72">
-        <v>3880.956375906653</v>
+        <v>3912.663845413968</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46311</v>
       </c>
       <c r="B73">
-        <v>3898.587234479237</v>
+        <v>3936.477675427233</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46318</v>
       </c>
       <c r="B74">
-        <v>4031.187996137114</v>
+        <v>4057.894439486103</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46325</v>
       </c>
       <c r="B75">
-        <v>4028.221972258968</v>
+        <v>4036.284781470456</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/XAUUSD_forecast.xlsx
+++ b/public/data/files/XAUUSD_forecast.xlsx
@@ -442,7 +442,7 @@
         <v>45849</v>
       </c>
       <c r="B7">
-        <v>3667.371124214793</v>
+        <v>3667.284631001332</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -450,7 +450,7 @@
         <v>45856</v>
       </c>
       <c r="B8">
-        <v>3564.035551584357</v>
+        <v>3563.918664003124</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -458,7 +458,7 @@
         <v>45863</v>
       </c>
       <c r="B9">
-        <v>3509.349005271999</v>
+        <v>3509.213897466959</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -466,7 +466,7 @@
         <v>45870</v>
       </c>
       <c r="B10">
-        <v>3481.648023962474</v>
+        <v>3481.504639083534</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -474,7 +474,7 @@
         <v>45877</v>
       </c>
       <c r="B11">
-        <v>3490.103870183018</v>
+        <v>3489.956957473936</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -482,7 +482,7 @@
         <v>45884</v>
       </c>
       <c r="B12">
-        <v>3502.867556182241</v>
+        <v>3502.718883039423</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -490,7 +490,7 @@
         <v>45891</v>
       </c>
       <c r="B13">
-        <v>3517.400571578684</v>
+        <v>3517.253002535631</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -498,7 +498,7 @@
         <v>45898</v>
       </c>
       <c r="B14">
-        <v>3529.938955834436</v>
+        <v>3529.793753658371</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -506,7 +506,7 @@
         <v>45905</v>
       </c>
       <c r="B15">
-        <v>3546.509327070344</v>
+        <v>3546.403249876285</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -514,7 +514,7 @@
         <v>45912</v>
       </c>
       <c r="B16">
-        <v>3453.0706068937</v>
+        <v>3453.098652715776</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -522,7 +522,7 @@
         <v>45919</v>
       </c>
       <c r="B17">
-        <v>3450.621235560671</v>
+        <v>3450.646001493869</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -530,7 +530,7 @@
         <v>45926</v>
       </c>
       <c r="B18">
-        <v>3450.676232483341</v>
+        <v>3450.699164682041</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -538,7 +538,7 @@
         <v>45933</v>
       </c>
       <c r="B19">
-        <v>3534.322467958785</v>
+        <v>3534.442997570976</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -546,7 +546,7 @@
         <v>45940</v>
       </c>
       <c r="B20">
-        <v>3632.723980778095</v>
+        <v>3632.954876801987</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -554,7 +554,7 @@
         <v>45947</v>
       </c>
       <c r="B21">
-        <v>3786.170866169804</v>
+        <v>3786.519565036729</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -562,7 +562,7 @@
         <v>45954</v>
       </c>
       <c r="B22">
-        <v>3856.820056327606</v>
+        <v>3857.131989850621</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -570,7 +570,7 @@
         <v>45961</v>
       </c>
       <c r="B23">
-        <v>3903.276999418127</v>
+        <v>3903.566219487819</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -578,7 +578,7 @@
         <v>45968</v>
       </c>
       <c r="B24">
-        <v>3888.139040961707</v>
+        <v>3888.388379054526</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -586,7 +586,7 @@
         <v>45975</v>
       </c>
       <c r="B25">
-        <v>3888.62735609209</v>
+        <v>3888.730341367165</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -594,7 +594,7 @@
         <v>45982</v>
       </c>
       <c r="B26">
-        <v>3994.178722884341</v>
+        <v>3994.211420265474</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -602,7 +602,7 @@
         <v>45989</v>
       </c>
       <c r="B27">
-        <v>4069.761988235164</v>
+        <v>4069.866704294588</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -610,7 +610,7 @@
         <v>45996</v>
       </c>
       <c r="B28">
-        <v>4110.149310048981</v>
+        <v>4110.278643658183</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -618,7 +618,7 @@
         <v>46003</v>
       </c>
       <c r="B29">
-        <v>4206.613853187821</v>
+        <v>4206.628956742146</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -626,7 +626,7 @@
         <v>46010</v>
       </c>
       <c r="B30">
-        <v>4200.37555683229</v>
+        <v>4200.432277669959</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -634,7 +634,7 @@
         <v>46017</v>
       </c>
       <c r="B31">
-        <v>4226.288764573095</v>
+        <v>4226.442685499932</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -642,7 +642,7 @@
         <v>46024</v>
       </c>
       <c r="B32">
-        <v>4247.116199647747</v>
+        <v>4247.270845462395</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -650,7 +650,7 @@
         <v>46031</v>
       </c>
       <c r="B33">
-        <v>4312.562012552557</v>
+        <v>4312.778000871433</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -658,7 +658,7 @@
         <v>46038</v>
       </c>
       <c r="B34">
-        <v>4405.723962645975</v>
+        <v>4405.995358789944</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -666,7 +666,7 @@
         <v>46045</v>
       </c>
       <c r="B35">
-        <v>4442.085124699604</v>
+        <v>4442.378505217086</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -674,7 +674,7 @@
         <v>46052</v>
       </c>
       <c r="B36">
-        <v>4545.038004459286</v>
+        <v>4545.428157990877</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -682,7 +682,7 @@
         <v>46059</v>
       </c>
       <c r="B37">
-        <v>4681.645533954736</v>
+        <v>4682.119770649044</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -690,7 +690,7 @@
         <v>46066</v>
       </c>
       <c r="B38">
-        <v>4765.172914922231</v>
+        <v>4765.773361024643</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -698,7 +698,7 @@
         <v>46073</v>
       </c>
       <c r="B39">
-        <v>4898.106979697398</v>
+        <v>4898.464201464307</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -706,7 +706,7 @@
         <v>46080</v>
       </c>
       <c r="B40">
-        <v>4939.714652618845</v>
+        <v>4940.107156912531</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -714,7 +714,7 @@
         <v>46087</v>
       </c>
       <c r="B41">
-        <v>5047.78022160911</v>
+        <v>5048.290478951236</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -722,7 +722,7 @@
         <v>46094</v>
       </c>
       <c r="B42">
-        <v>5212.858917426446</v>
+        <v>5213.143244518038</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>46101</v>
       </c>
       <c r="B43">
-        <v>5251.883859146628</v>
+        <v>5251.915756783597</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>46108</v>
       </c>
       <c r="B44">
-        <v>5288.298402249611</v>
+        <v>5287.965859551743</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>46115</v>
       </c>
       <c r="B45">
-        <v>5361.879916490338</v>
+        <v>5361.283665158508</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>46122</v>
       </c>
       <c r="B46">
-        <v>5436.496852670589</v>
+        <v>5435.726262852433</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>46129</v>
       </c>
       <c r="B47">
-        <v>5565.831444399511</v>
+        <v>5564.989987122456</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>46136</v>
       </c>
       <c r="B48">
-        <v>5503.004523946882</v>
+        <v>5501.942665737626</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>46143</v>
       </c>
       <c r="B49">
-        <v>5324.99249740312</v>
+        <v>5323.675822043917</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>46150</v>
       </c>
       <c r="B50">
-        <v>5209.358548567241</v>
+        <v>5208.120534903218</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>46157</v>
       </c>
       <c r="B51">
-        <v>5074.291475949005</v>
+        <v>5072.964097468067</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>46164</v>
       </c>
       <c r="B52">
-        <v>4961.920496936371</v>
+        <v>4960.722863053557</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>46171</v>
       </c>
       <c r="B53">
-        <v>4859.870620333669</v>
+        <v>4858.73048785389</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>46178</v>
       </c>
       <c r="B54">
-        <v>4809.550248629689</v>
+        <v>4808.261485064364</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>46185</v>
       </c>
       <c r="B55">
-        <v>4684.136119622741</v>
+        <v>4683.098290353535</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>46192</v>
       </c>
       <c r="B56">
-        <v>4566.580364251269</v>
+        <v>4565.850482710623</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>46199</v>
       </c>
       <c r="B57">
-        <v>4473.543619953946</v>
+        <v>4473.048350886973</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>46206</v>
       </c>
       <c r="B58">
-        <v>4468.583429847011</v>
+        <v>4468.078410998483</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>46213</v>
       </c>
       <c r="B59">
-        <v>4387.253588366336</v>
+        <v>4386.629123820961</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>46220</v>
       </c>
       <c r="B60">
-        <v>4226.894388641681</v>
+        <v>4226.07436134602</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>46227</v>
       </c>
       <c r="B61">
-        <v>4134.885114702442</v>
+        <v>4144.990287809551</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>46234</v>
       </c>
       <c r="B62">
-        <v>4086.902452723792</v>
+        <v>4089.589290425525</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>46241</v>
       </c>
       <c r="B63">
-        <v>4037.657553931368</v>
+        <v>4038.32144156612</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46248</v>
       </c>
       <c r="B64">
-        <v>3995.961263100259</v>
+        <v>3995.63797543578</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46255</v>
       </c>
       <c r="B65">
-        <v>3957.698526992847</v>
+        <v>3956.359815686755</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46262</v>
       </c>
       <c r="B66">
-        <v>3938.220746628454</v>
+        <v>3932.332006256227</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46269</v>
       </c>
       <c r="B67">
-        <v>3916.42841393106</v>
+        <v>3907.82588106853</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46276</v>
       </c>
       <c r="B68">
-        <v>3914.394678703468</v>
+        <v>3905.385378465683</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46283</v>
       </c>
       <c r="B69">
-        <v>3865.629477291285</v>
+        <v>3857.082387002961</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46290</v>
       </c>
       <c r="B70">
-        <v>3842.206934787123</v>
+        <v>3833.717693754027</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46297</v>
       </c>
       <c r="B71">
-        <v>3870.360028262616</v>
+        <v>3860.949049944745</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46304</v>
       </c>
       <c r="B72">
-        <v>3912.663845413968</v>
+        <v>3896.449298315358</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46311</v>
       </c>
       <c r="B73">
-        <v>3936.477675427233</v>
+        <v>3916.118628241603</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46318</v>
       </c>
       <c r="B74">
-        <v>4057.894439486103</v>
+        <v>4041.708879469688</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46325</v>
       </c>
       <c r="B75">
-        <v>4036.284781470456</v>
+        <v>4053.45913564173</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/XAUUSD_forecast.xlsx
+++ b/public/data/files/XAUUSD_forecast.xlsx
@@ -442,7 +442,7 @@
         <v>45849</v>
       </c>
       <c r="B7">
-        <v>3667.284631001332</v>
+        <v>3667.454828062395</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -450,7 +450,7 @@
         <v>45856</v>
       </c>
       <c r="B8">
-        <v>3563.918664003124</v>
+        <v>3564.148690251262</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -458,7 +458,7 @@
         <v>45863</v>
       </c>
       <c r="B9">
-        <v>3509.213897466959</v>
+        <v>3509.47980187157</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -466,7 +466,7 @@
         <v>45870</v>
       </c>
       <c r="B10">
-        <v>3481.504639083534</v>
+        <v>3481.786863516967</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -474,7 +474,7 @@
         <v>45877</v>
       </c>
       <c r="B11">
-        <v>3489.956957473936</v>
+        <v>3490.246124603244</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -482,7 +482,7 @@
         <v>45884</v>
       </c>
       <c r="B12">
-        <v>3502.718883039423</v>
+        <v>3503.011514006867</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -490,7 +490,7 @@
         <v>45891</v>
       </c>
       <c r="B13">
-        <v>3517.253002535631</v>
+        <v>3517.543459676879</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -498,7 +498,7 @@
         <v>45898</v>
       </c>
       <c r="B14">
-        <v>3529.793753658371</v>
+        <v>3530.079552108727</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -506,7 +506,7 @@
         <v>45905</v>
       </c>
       <c r="B15">
-        <v>3546.403249876285</v>
+        <v>3546.612118088841</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -514,7 +514,7 @@
         <v>45912</v>
       </c>
       <c r="B16">
-        <v>3453.098652715776</v>
+        <v>3453.043490022655</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -522,7 +522,7 @@
         <v>45919</v>
       </c>
       <c r="B17">
-        <v>3450.646001493869</v>
+        <v>3450.597293167832</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -530,7 +530,7 @@
         <v>45926</v>
       </c>
       <c r="B18">
-        <v>3450.699164682041</v>
+        <v>3450.654065094175</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -538,7 +538,7 @@
         <v>45933</v>
       </c>
       <c r="B19">
-        <v>3534.442997570976</v>
+        <v>3534.205900071407</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -546,7 +546,7 @@
         <v>45940</v>
       </c>
       <c r="B20">
-        <v>3632.954876801987</v>
+        <v>3632.500625846821</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -554,7 +554,7 @@
         <v>45947</v>
       </c>
       <c r="B21">
-        <v>3786.519565036729</v>
+        <v>3785.833447566466</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -562,7 +562,7 @@
         <v>45954</v>
       </c>
       <c r="B22">
-        <v>3857.131989850621</v>
+        <v>3856.518170976074</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -570,7 +570,7 @@
         <v>45961</v>
       </c>
       <c r="B23">
-        <v>3903.566219487819</v>
+        <v>3902.996881318801</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -578,7 +578,7 @@
         <v>45968</v>
       </c>
       <c r="B24">
-        <v>3888.388379054526</v>
+        <v>3887.897445430355</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -586,7 +586,7 @@
         <v>45975</v>
       </c>
       <c r="B25">
-        <v>3888.730341367165</v>
+        <v>3888.527451780966</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -594,7 +594,7 @@
         <v>45982</v>
       </c>
       <c r="B26">
-        <v>3994.211420265474</v>
+        <v>3994.146933496609</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -602,7 +602,7 @@
         <v>45989</v>
       </c>
       <c r="B27">
-        <v>4069.866704294588</v>
+        <v>4069.660551499573</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -610,7 +610,7 @@
         <v>45996</v>
       </c>
       <c r="B28">
-        <v>4110.278643658183</v>
+        <v>4110.024035074173</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -618,7 +618,7 @@
         <v>46003</v>
       </c>
       <c r="B29">
-        <v>4206.628956742146</v>
+        <v>4206.599345562039</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -626,7 +626,7 @@
         <v>46010</v>
       </c>
       <c r="B30">
-        <v>4200.432277669959</v>
+        <v>4200.320841375471</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -634,7 +634,7 @@
         <v>46017</v>
       </c>
       <c r="B31">
-        <v>4226.442685499932</v>
+        <v>4226.140087279398</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -642,7 +642,7 @@
         <v>46024</v>
       </c>
       <c r="B32">
-        <v>4247.270845462395</v>
+        <v>4246.966742311183</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -650,7 +650,7 @@
         <v>46031</v>
       </c>
       <c r="B33">
-        <v>4312.778000871433</v>
+        <v>4312.353186673094</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -658,7 +658,7 @@
         <v>46038</v>
       </c>
       <c r="B34">
-        <v>4405.995358789944</v>
+        <v>4405.461453547015</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -666,7 +666,7 @@
         <v>46045</v>
       </c>
       <c r="B35">
-        <v>4442.378505217086</v>
+        <v>4441.801235431345</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -674,7 +674,7 @@
         <v>46052</v>
       </c>
       <c r="B36">
-        <v>4545.428157990877</v>
+        <v>4544.660334387976</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -682,7 +682,7 @@
         <v>46059</v>
       </c>
       <c r="B37">
-        <v>4682.119770649044</v>
+        <v>4681.186502948837</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -690,7 +690,7 @@
         <v>46066</v>
       </c>
       <c r="B38">
-        <v>4765.773361024643</v>
+        <v>4764.590992760843</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -698,7 +698,7 @@
         <v>46073</v>
       </c>
       <c r="B39">
-        <v>4898.464201464307</v>
+        <v>4897.761144973205</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -706,7 +706,7 @@
         <v>46080</v>
       </c>
       <c r="B40">
-        <v>4940.107156912531</v>
+        <v>4939.334649455371</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -714,7 +714,7 @@
         <v>46087</v>
       </c>
       <c r="B41">
-        <v>5048.290478951236</v>
+        <v>5047.28602876536</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -722,7 +722,7 @@
         <v>46094</v>
       </c>
       <c r="B42">
-        <v>5213.143244518038</v>
+        <v>5212.583144181844</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>46101</v>
       </c>
       <c r="B43">
-        <v>5251.915756783597</v>
+        <v>5251.851805999075</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>46108</v>
       </c>
       <c r="B44">
-        <v>5287.965859551743</v>
+        <v>5288.618823202967</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>46115</v>
       </c>
       <c r="B45">
-        <v>5361.283665158508</v>
+        <v>5362.456007078068</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>46122</v>
       </c>
       <c r="B46">
-        <v>5435.726262852433</v>
+        <v>5437.241569745407</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>46129</v>
       </c>
       <c r="B47">
-        <v>5564.989987122456</v>
+        <v>5566.64483044289</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>46136</v>
       </c>
       <c r="B48">
-        <v>5501.942665737626</v>
+        <v>5504.031883508198</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>46143</v>
       </c>
       <c r="B49">
-        <v>5323.675822043917</v>
+        <v>5326.266991227201</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>46150</v>
       </c>
       <c r="B50">
-        <v>5208.120534903218</v>
+        <v>5210.557319319683</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>46157</v>
       </c>
       <c r="B51">
-        <v>5072.964097468067</v>
+        <v>5075.577434044726</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>46164</v>
       </c>
       <c r="B52">
-        <v>4960.722863053557</v>
+        <v>4963.081153305548</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>46171</v>
       </c>
       <c r="B53">
-        <v>4858.73048785389</v>
+        <v>4860.976127347818</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>46178</v>
       </c>
       <c r="B54">
-        <v>4808.261485064364</v>
+        <v>4810.79993228784</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>46185</v>
       </c>
       <c r="B55">
-        <v>4683.098290353535</v>
+        <v>4685.142300523421</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>46192</v>
       </c>
       <c r="B56">
-        <v>4565.850482710623</v>
+        <v>4567.287531784396</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>46199</v>
       </c>
       <c r="B57">
-        <v>4473.048350886973</v>
+        <v>4474.022707212007</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>46206</v>
       </c>
       <c r="B58">
-        <v>4468.078410998483</v>
+        <v>4469.071963625035</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>46213</v>
       </c>
       <c r="B59">
-        <v>4386.629123820961</v>
+        <v>4387.858113568122</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>46220</v>
       </c>
       <c r="B60">
-        <v>4226.07436134602</v>
+        <v>4227.689298388399</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>46227</v>
       </c>
       <c r="B61">
-        <v>4144.990287809551</v>
+        <v>4135.53127262578</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>46234</v>
       </c>
       <c r="B62">
-        <v>4089.589290425525</v>
+        <v>4088.082688998194</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>46241</v>
       </c>
       <c r="B63">
-        <v>4038.32144156612</v>
+        <v>4041.30562179238</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46248</v>
       </c>
       <c r="B64">
-        <v>3995.63797543578</v>
+        <v>4003.222656170326</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46255</v>
       </c>
       <c r="B65">
-        <v>3956.359815686755</v>
+        <v>3970.212900028128</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46262</v>
       </c>
       <c r="B66">
-        <v>3932.332006256227</v>
+        <v>3955.055382698944</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46269</v>
       </c>
       <c r="B67">
-        <v>3907.82588106853</v>
+        <v>3932.406267855715</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46276</v>
       </c>
       <c r="B68">
-        <v>3905.385378465683</v>
+        <v>3930.411990554286</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46283</v>
       </c>
       <c r="B69">
-        <v>3857.082387002961</v>
+        <v>3883.811781530032</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46290</v>
       </c>
       <c r="B70">
-        <v>3833.717693754027</v>
+        <v>3862.601653776069</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46297</v>
       </c>
       <c r="B71">
-        <v>3860.949049944745</v>
+        <v>3889.785395272143</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46304</v>
       </c>
       <c r="B72">
-        <v>3896.449298315358</v>
+        <v>3931.41406916602</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46311</v>
       </c>
       <c r="B73">
-        <v>3916.118628241603</v>
+        <v>3957.723039764662</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46318</v>
       </c>
       <c r="B74">
-        <v>4041.708879469688</v>
+        <v>4077.830233752496</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46325</v>
       </c>
       <c r="B75">
-        <v>4053.45913564173</v>
+        <v>4098.289881523859</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/XAUUSD_forecast.xlsx
+++ b/public/data/files/XAUUSD_forecast.xlsx
@@ -442,7 +442,7 @@
         <v>45849</v>
       </c>
       <c r="B7">
-        <v>3667.454828062395</v>
+        <v>3667.535875325358</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -450,7 +450,7 @@
         <v>45856</v>
       </c>
       <c r="B8">
-        <v>3564.148690251262</v>
+        <v>3564.258257479368</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -458,7 +458,7 @@
         <v>45863</v>
       </c>
       <c r="B9">
-        <v>3509.47980187157</v>
+        <v>3509.606490303137</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -466,7 +466,7 @@
         <v>45870</v>
       </c>
       <c r="B10">
-        <v>3481.786863516967</v>
+        <v>3481.921370370535</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -474,7 +474,7 @@
         <v>45877</v>
       </c>
       <c r="B11">
-        <v>3490.246124603244</v>
+        <v>3490.383938695205</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -482,7 +482,7 @@
         <v>45884</v>
       </c>
       <c r="B12">
-        <v>3503.011514006867</v>
+        <v>3503.150977199842</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -490,7 +490,7 @@
         <v>45891</v>
       </c>
       <c r="B13">
-        <v>3517.543459676879</v>
+        <v>3517.681885939456</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -498,7 +498,7 @@
         <v>45898</v>
       </c>
       <c r="B14">
-        <v>3530.079552108727</v>
+        <v>3530.215758080197</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -506,7 +506,7 @@
         <v>45905</v>
       </c>
       <c r="B15">
-        <v>3546.612118088841</v>
+        <v>3546.711773000184</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -514,7 +514,7 @@
         <v>45912</v>
       </c>
       <c r="B16">
-        <v>3453.043490022655</v>
+        <v>3453.017256746734</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -522,7 +522,7 @@
         <v>45919</v>
       </c>
       <c r="B17">
-        <v>3450.597293167832</v>
+        <v>3450.574133958977</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -530,7 +530,7 @@
         <v>45926</v>
       </c>
       <c r="B18">
-        <v>3450.654065094175</v>
+        <v>3450.632624934223</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -538,7 +538,7 @@
         <v>45933</v>
       </c>
       <c r="B19">
-        <v>3534.205900071407</v>
+        <v>3534.093101912695</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -546,7 +546,7 @@
         <v>45940</v>
       </c>
       <c r="B20">
-        <v>3632.500625846821</v>
+        <v>3632.284448893666</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -554,7 +554,7 @@
         <v>45947</v>
       </c>
       <c r="B21">
-        <v>3785.833447566466</v>
+        <v>3785.506771095381</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -562,7 +562,7 @@
         <v>45954</v>
       </c>
       <c r="B22">
-        <v>3856.518170976074</v>
+        <v>3856.225856310707</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -570,7 +570,7 @@
         <v>45961</v>
       </c>
       <c r="B23">
-        <v>3902.996881318801</v>
+        <v>3902.725442972775</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -578,7 +578,7 @@
         <v>45968</v>
       </c>
       <c r="B24">
-        <v>3887.897445430355</v>
+        <v>3887.663238323708</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -586,7 +586,7 @@
         <v>45975</v>
       </c>
       <c r="B25">
-        <v>3888.527451780966</v>
+        <v>3888.430493077759</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -594,7 +594,7 @@
         <v>45982</v>
       </c>
       <c r="B26">
-        <v>3994.146933496609</v>
+        <v>3994.116015662406</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -602,7 +602,7 @@
         <v>45989</v>
       </c>
       <c r="B27">
-        <v>4069.660551499573</v>
+        <v>4069.562242469307</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -610,7 +610,7 @@
         <v>45996</v>
       </c>
       <c r="B28">
-        <v>4110.024035074173</v>
+        <v>4109.902630786019</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -618,7 +618,7 @@
         <v>46003</v>
       </c>
       <c r="B29">
-        <v>4206.599345562039</v>
+        <v>4206.585400428818</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -626,7 +626,7 @@
         <v>46010</v>
       </c>
       <c r="B30">
-        <v>4200.320841375471</v>
+        <v>4200.268027825719</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -634,7 +634,7 @@
         <v>46017</v>
       </c>
       <c r="B31">
-        <v>4226.140087279398</v>
+        <v>4225.996391554826</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -642,7 +642,7 @@
         <v>46024</v>
       </c>
       <c r="B32">
-        <v>4246.966742311183</v>
+        <v>4246.82221805096</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -650,7 +650,7 @@
         <v>46031</v>
       </c>
       <c r="B33">
-        <v>4312.353186673094</v>
+        <v>4312.151174562836</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -658,7 +658,7 @@
         <v>46038</v>
       </c>
       <c r="B34">
-        <v>4405.461453547015</v>
+        <v>4405.207404177742</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -666,7 +666,7 @@
         <v>46045</v>
       </c>
       <c r="B35">
-        <v>4441.801235431345</v>
+        <v>4441.526385900295</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -674,7 +674,7 @@
         <v>46052</v>
       </c>
       <c r="B36">
-        <v>4544.660334387976</v>
+        <v>4544.294559893115</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -682,7 +682,7 @@
         <v>46059</v>
       </c>
       <c r="B37">
-        <v>4681.186502948837</v>
+        <v>4680.741960363215</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -690,7 +690,7 @@
         <v>46066</v>
       </c>
       <c r="B38">
-        <v>4764.590992760843</v>
+        <v>4764.026753391389</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -698,7 +698,7 @@
         <v>46073</v>
       </c>
       <c r="B39">
-        <v>4897.761144973205</v>
+        <v>4897.4261634359</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -706,7 +706,7 @@
         <v>46080</v>
       </c>
       <c r="B40">
-        <v>4939.334649455371</v>
+        <v>4938.96656180667</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -714,7 +714,7 @@
         <v>46087</v>
       </c>
       <c r="B41">
-        <v>5047.28602876536</v>
+        <v>5046.807157530932</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -722,7 +722,7 @@
         <v>46094</v>
       </c>
       <c r="B42">
-        <v>5212.583144181844</v>
+        <v>5212.3155477624</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>46101</v>
       </c>
       <c r="B43">
-        <v>5251.851805999075</v>
+        <v>5251.819660661973</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>46108</v>
       </c>
       <c r="B44">
-        <v>5288.618823202967</v>
+        <v>5288.927763013093</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>46115</v>
       </c>
       <c r="B45">
-        <v>5362.456007078068</v>
+        <v>5363.012937097606</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>46122</v>
       </c>
       <c r="B46">
-        <v>5437.241569745407</v>
+        <v>5437.961688332531</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>46129</v>
       </c>
       <c r="B47">
-        <v>5566.64483044289</v>
+        <v>5567.431520470568</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>46136</v>
       </c>
       <c r="B48">
-        <v>5504.031883508198</v>
+        <v>5505.026393186849</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>46143</v>
       </c>
       <c r="B49">
-        <v>5326.266991227201</v>
+        <v>5327.501289423117</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>46150</v>
       </c>
       <c r="B50">
-        <v>5210.557319319683</v>
+        <v>5211.718674700743</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>46157</v>
       </c>
       <c r="B51">
-        <v>5075.577434044726</v>
+        <v>5076.823869707379</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>46164</v>
       </c>
       <c r="B52">
-        <v>4963.081153305548</v>
+        <v>4964.206510112024</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>46171</v>
       </c>
       <c r="B53">
-        <v>4860.976127347818</v>
+        <v>4862.048552680559</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>46178</v>
       </c>
       <c r="B54">
-        <v>4810.79993228784</v>
+        <v>4812.012274962275</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>46185</v>
       </c>
       <c r="B55">
-        <v>4685.142300523421</v>
+        <v>4686.118250651564</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>46192</v>
       </c>
       <c r="B56">
-        <v>4567.287531784396</v>
+        <v>4567.973024931649</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>46199</v>
       </c>
       <c r="B57">
-        <v>4474.022707212007</v>
+        <v>4474.486388974856</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>46206</v>
       </c>
       <c r="B58">
-        <v>4469.071963625035</v>
+        <v>4469.544803125596</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>46213</v>
       </c>
       <c r="B59">
-        <v>4387.858113568122</v>
+        <v>4388.443634405217</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>46220</v>
       </c>
       <c r="B60">
-        <v>4227.689298388399</v>
+        <v>4228.460215323154</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>46227</v>
       </c>
       <c r="B61">
-        <v>4135.53127262578</v>
+        <v>4136.159466483142</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>46234</v>
       </c>
       <c r="B62">
-        <v>4088.082688998194</v>
+        <v>4089.146846981584</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>46241</v>
       </c>
       <c r="B63">
-        <v>4041.30562179238</v>
+        <v>4044.607358572184</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46248</v>
       </c>
       <c r="B64">
-        <v>4003.222656170326</v>
+        <v>4009.822538579395</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46255</v>
       </c>
       <c r="B65">
-        <v>3970.212900028128</v>
+        <v>3981.846691670255</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46262</v>
       </c>
       <c r="B66">
-        <v>3955.055382698944</v>
+        <v>3969.534570976447</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46269</v>
       </c>
       <c r="B67">
-        <v>3932.406267855715</v>
+        <v>3946.84186274175</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46276</v>
       </c>
       <c r="B68">
-        <v>3930.411990554286</v>
+        <v>3944.885316930428</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46283</v>
       </c>
       <c r="B69">
-        <v>3883.811781530032</v>
+        <v>3900.195037571494</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46290</v>
       </c>
       <c r="B70">
-        <v>3862.601653776069</v>
+        <v>3880.754524715941</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46297</v>
       </c>
       <c r="B71">
-        <v>3889.785395272143</v>
+        <v>3906.985530421582</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46304</v>
       </c>
       <c r="B72">
-        <v>3931.41406916602</v>
+        <v>3947.914120706973</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46311</v>
       </c>
       <c r="B73">
-        <v>3957.723039764662</v>
+        <v>3976.148452858831</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46318</v>
       </c>
       <c r="B74">
-        <v>4077.830233752496</v>
+        <v>4093.68578710609</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46325</v>
       </c>
       <c r="B75">
-        <v>4098.289881523859</v>
+        <v>4129.228980673659</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/XAUUSD_forecast.xlsx
+++ b/public/data/files/XAUUSD_forecast.xlsx
@@ -383,7 +383,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B75"/>
+  <dimension ref="A1:B76"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" style="1" customWidth="1"/>
@@ -874,7 +874,7 @@
         <v>46227</v>
       </c>
       <c r="B61">
-        <v>4136.159466483142</v>
+        <v>4146.961142940158</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>46234</v>
       </c>
       <c r="B62">
-        <v>4089.146846981584</v>
+        <v>4092.01369961087</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>46241</v>
       </c>
       <c r="B63">
-        <v>4044.607358572184</v>
+        <v>4047.766827996046</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46248</v>
       </c>
       <c r="B64">
-        <v>4009.822538579395</v>
+        <v>4011.315666147279</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46255</v>
       </c>
       <c r="B65">
-        <v>3981.846691670255</v>
+        <v>3976.340164869718</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46262</v>
       </c>
       <c r="B66">
-        <v>3969.534570976447</v>
+        <v>3953.90902650653</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46269</v>
       </c>
       <c r="B67">
-        <v>3946.84186274175</v>
+        <v>3932.159201598003</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46276</v>
       </c>
       <c r="B68">
-        <v>3944.885316930428</v>
+        <v>3931.632897154233</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46283</v>
       </c>
       <c r="B69">
-        <v>3900.195037571494</v>
+        <v>3894.823562895026</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46290</v>
       </c>
       <c r="B70">
-        <v>3880.754524715941</v>
+        <v>3884.881379291988</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46297</v>
       </c>
       <c r="B71">
-        <v>3906.985530421582</v>
+        <v>3916.794281845219</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46304</v>
       </c>
       <c r="B72">
-        <v>3947.914120706973</v>
+        <v>3945.300758136643</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46311</v>
       </c>
       <c r="B73">
-        <v>3976.148452858831</v>
+        <v>3969.335825052836</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46318</v>
       </c>
       <c r="B74">
-        <v>4093.68578710609</v>
+        <v>4079.930339117561</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,15 @@
         <v>46325</v>
       </c>
       <c r="B75">
-        <v>4129.228980673659</v>
+        <v>4104.437638598021</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2">
+      <c r="A76" s="3">
+        <v>46332</v>
+      </c>
+      <c r="B76">
+        <v>4133.557653286312</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/XAUUSD_forecast.xlsx
+++ b/public/data/files/XAUUSD_forecast.xlsx
@@ -442,7 +442,7 @@
         <v>45849</v>
       </c>
       <c r="B7">
-        <v>3667.535875325358</v>
+        <v>3667.614390489566</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -450,7 +450,7 @@
         <v>45856</v>
       </c>
       <c r="B8">
-        <v>3564.258257479368</v>
+        <v>3564.364419718002</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -458,7 +458,7 @@
         <v>45863</v>
       </c>
       <c r="B9">
-        <v>3509.606490303137</v>
+        <v>3509.729261056237</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -466,7 +466,7 @@
         <v>45870</v>
       </c>
       <c r="B10">
-        <v>3481.921370370535</v>
+        <v>3482.051744096981</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -474,7 +474,7 @@
         <v>45877</v>
       </c>
       <c r="B11">
-        <v>3490.383938695205</v>
+        <v>3490.517517038971</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -482,7 +482,7 @@
         <v>45884</v>
       </c>
       <c r="B12">
-        <v>3503.150977199842</v>
+        <v>3503.286152896248</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -490,7 +490,7 @@
         <v>45891</v>
       </c>
       <c r="B13">
-        <v>3517.681885939456</v>
+        <v>3517.816056019045</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -498,7 +498,7 @@
         <v>45898</v>
       </c>
       <c r="B14">
-        <v>3530.215758080197</v>
+        <v>3530.347776106576</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -506,7 +506,7 @@
         <v>45905</v>
       </c>
       <c r="B15">
-        <v>3546.711773000184</v>
+        <v>3546.808432891438</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -514,7 +514,7 @@
         <v>45912</v>
       </c>
       <c r="B16">
-        <v>3453.017256746734</v>
+        <v>3452.99186461267</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -522,7 +522,7 @@
         <v>45919</v>
       </c>
       <c r="B17">
-        <v>3450.574133958977</v>
+        <v>3450.551720169225</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -530,7 +530,7 @@
         <v>45926</v>
       </c>
       <c r="B18">
-        <v>3450.632624934223</v>
+        <v>3450.611876842484</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -538,7 +538,7 @@
         <v>45933</v>
       </c>
       <c r="B19">
-        <v>3534.093101912695</v>
+        <v>3533.983893685073</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -546,7 +546,7 @@
         <v>45940</v>
       </c>
       <c r="B20">
-        <v>3632.284448893666</v>
+        <v>3632.075109725165</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -554,7 +554,7 @@
         <v>45947</v>
       </c>
       <c r="B21">
-        <v>3785.506771095381</v>
+        <v>3785.190332286954</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -562,7 +562,7 @@
         <v>45954</v>
       </c>
       <c r="B22">
-        <v>3856.225856310707</v>
+        <v>3855.942664607428</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -570,7 +570,7 @@
         <v>45961</v>
       </c>
       <c r="B23">
-        <v>3902.725442972775</v>
+        <v>3902.462287830408</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -578,7 +578,7 @@
         <v>45968</v>
       </c>
       <c r="B24">
-        <v>3887.663238323708</v>
+        <v>3887.436086716513</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -586,7 +586,7 @@
         <v>45975</v>
       </c>
       <c r="B25">
-        <v>3888.430493077759</v>
+        <v>3888.336352385266</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -594,7 +594,7 @@
         <v>45982</v>
       </c>
       <c r="B26">
-        <v>3994.116015662406</v>
+        <v>3994.085934806464</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -602,7 +602,7 @@
         <v>45989</v>
       </c>
       <c r="B27">
-        <v>4069.562242469307</v>
+        <v>4069.46691872805</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -610,7 +610,7 @@
         <v>45996</v>
       </c>
       <c r="B28">
-        <v>4109.902630786019</v>
+        <v>4109.784920656244</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -618,7 +618,7 @@
         <v>46003</v>
       </c>
       <c r="B29">
-        <v>4206.585400428818</v>
+        <v>4206.571986749972</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -626,7 +626,7 @@
         <v>46010</v>
       </c>
       <c r="B30">
-        <v>4200.268027825719</v>
+        <v>4200.217019650318</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -634,7 +634,7 @@
         <v>46017</v>
       </c>
       <c r="B31">
-        <v>4225.996391554826</v>
+        <v>4225.857432431318</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -642,7 +642,7 @@
         <v>46024</v>
       </c>
       <c r="B32">
-        <v>4246.82221805096</v>
+        <v>4246.682387875513</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -650,7 +650,7 @@
         <v>46031</v>
       </c>
       <c r="B33">
-        <v>4312.151174562836</v>
+        <v>4311.955649715872</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -658,7 +658,7 @@
         <v>46038</v>
       </c>
       <c r="B34">
-        <v>4405.207404177742</v>
+        <v>4404.961414056957</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -666,7 +666,7 @@
         <v>46045</v>
       </c>
       <c r="B35">
-        <v>4441.526385900295</v>
+        <v>4441.260152682262</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -674,7 +674,7 @@
         <v>46052</v>
       </c>
       <c r="B36">
-        <v>4544.294559893115</v>
+        <v>4543.940129324438</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -682,7 +682,7 @@
         <v>46059</v>
       </c>
       <c r="B37">
-        <v>4680.741960363215</v>
+        <v>4680.311233192337</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -690,7 +690,7 @@
         <v>46066</v>
       </c>
       <c r="B38">
-        <v>4764.026753391389</v>
+        <v>4763.479405646455</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -698,7 +698,7 @@
         <v>46073</v>
       </c>
       <c r="B39">
-        <v>4897.4261634359</v>
+        <v>4897.101533961706</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -706,7 +706,7 @@
         <v>46080</v>
       </c>
       <c r="B40">
-        <v>4938.96656180667</v>
+        <v>4938.60983993523</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -714,7 +714,7 @@
         <v>46087</v>
       </c>
       <c r="B41">
-        <v>5046.807157530932</v>
+        <v>5046.342909882522</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -722,7 +722,7 @@
         <v>46094</v>
       </c>
       <c r="B42">
-        <v>5212.3155477624</v>
+        <v>5212.055772772602</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>46101</v>
       </c>
       <c r="B43">
-        <v>5251.819660661973</v>
+        <v>5251.787479050592</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>46108</v>
       </c>
       <c r="B44">
-        <v>5288.927763013093</v>
+        <v>5289.225818483194</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>46115</v>
       </c>
       <c r="B45">
-        <v>5363.012937097606</v>
+        <v>5363.551641955366</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>46122</v>
       </c>
       <c r="B46">
-        <v>5437.961688332531</v>
+        <v>5438.658400786773</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>46129</v>
       </c>
       <c r="B47">
-        <v>5567.431520470568</v>
+        <v>5568.192801693158</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>46136</v>
       </c>
       <c r="B48">
-        <v>5505.026393186849</v>
+        <v>5505.989598668441</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>46143</v>
       </c>
       <c r="B49">
-        <v>5327.501289423117</v>
+        <v>5328.697255716412</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>46150</v>
       </c>
       <c r="B50">
-        <v>5211.718674700743</v>
+        <v>5212.844331070975</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>46157</v>
       </c>
       <c r="B51">
-        <v>5076.823869707379</v>
+        <v>5078.032567353053</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>46164</v>
       </c>
       <c r="B52">
-        <v>4964.206510112024</v>
+        <v>4965.298145824265</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>46171</v>
       </c>
       <c r="B53">
-        <v>4862.048552680559</v>
+        <v>4863.089350306285</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>46178</v>
       </c>
       <c r="B54">
-        <v>4812.012274962275</v>
+        <v>4813.188914666115</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>46185</v>
       </c>
       <c r="B55">
-        <v>4686.118250651564</v>
+        <v>4687.065304698302</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>46192</v>
       </c>
       <c r="B56">
-        <v>4567.973024931649</v>
+        <v>4568.637821092981</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>46199</v>
       </c>
       <c r="B57">
-        <v>4474.486388974856</v>
+        <v>4474.935392917414</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>46206</v>
       </c>
       <c r="B58">
-        <v>4469.544803125596</v>
+        <v>4470.002689561607</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>46213</v>
       </c>
       <c r="B59">
-        <v>4388.443634405217</v>
+        <v>4389.011028603965</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>46220</v>
       </c>
       <c r="B60">
-        <v>4228.460215323154</v>
+        <v>4229.20819875192</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>46227</v>
       </c>
       <c r="B61">
-        <v>4146.961142940158</v>
+        <v>4136.770415422257</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>46234</v>
       </c>
       <c r="B62">
-        <v>4092.01369961087</v>
+        <v>4089.522379827938</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>46241</v>
       </c>
       <c r="B63">
-        <v>4047.766827996046</v>
+        <v>4045.770799993058</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46248</v>
       </c>
       <c r="B64">
-        <v>4011.315666147279</v>
+        <v>4012.595461128528</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46255</v>
       </c>
       <c r="B65">
-        <v>3976.340164869718</v>
+        <v>3987.771409540391</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46262</v>
       </c>
       <c r="B66">
-        <v>3953.90902650653</v>
+        <v>3981.375143136444</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46269</v>
       </c>
       <c r="B67">
-        <v>3932.159201598003</v>
+        <v>3958.874280259549</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46276</v>
       </c>
       <c r="B68">
-        <v>3931.632897154233</v>
+        <v>3956.846018155363</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46283</v>
       </c>
       <c r="B69">
-        <v>3894.823562895026</v>
+        <v>3913.771162417459</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46290</v>
       </c>
       <c r="B70">
-        <v>3884.881379291988</v>
+        <v>3898.16966685845</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46297</v>
       </c>
       <c r="B71">
-        <v>3916.794281845219</v>
+        <v>3921.093373098127</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46304</v>
       </c>
       <c r="B72">
-        <v>3945.300758136643</v>
+        <v>3961.466302142338</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46311</v>
       </c>
       <c r="B73">
-        <v>3969.335825052836</v>
+        <v>3991.269123320151</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46318</v>
       </c>
       <c r="B74">
-        <v>4079.930339117561</v>
+        <v>4105.368201863423</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46325</v>
       </c>
       <c r="B75">
-        <v>4104.437638598021</v>
+        <v>4145.885002331051</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46332</v>
       </c>
       <c r="B76">
-        <v>4133.557653286312</v>
+        <v>4205.319438619754</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/XAUUSD_forecast.xlsx
+++ b/public/data/files/XAUUSD_forecast.xlsx
@@ -874,7 +874,7 @@
         <v>46227</v>
       </c>
       <c r="B61">
-        <v>4136.770415422257</v>
+        <v>4147.581267299905</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>46234</v>
       </c>
       <c r="B62">
-        <v>4089.522379827938</v>
+        <v>4092.394028542771</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>46241</v>
       </c>
       <c r="B63">
-        <v>4045.770799993058</v>
+        <v>4048.756479269748</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46248</v>
       </c>
       <c r="B64">
-        <v>4012.595461128528</v>
+        <v>4013.14210415712</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46255</v>
       </c>
       <c r="B65">
-        <v>3987.771409540391</v>
+        <v>3980.375726169506</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46262</v>
       </c>
       <c r="B66">
-        <v>3981.375143136444</v>
+        <v>3959.747263250664</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46269</v>
       </c>
       <c r="B67">
-        <v>3958.874280259549</v>
+        <v>3939.673573460407</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46276</v>
       </c>
       <c r="B68">
-        <v>3956.846018155363</v>
+        <v>3939.768153253834</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46283</v>
       </c>
       <c r="B69">
-        <v>3913.771162417459</v>
+        <v>3906.3214148474</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46290</v>
       </c>
       <c r="B70">
-        <v>3898.16966685845</v>
+        <v>3899.675323409918</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46297</v>
       </c>
       <c r="B71">
-        <v>3921.093373098127</v>
+        <v>3929.731335901647</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46304</v>
       </c>
       <c r="B72">
-        <v>3961.466302142338</v>
+        <v>3958.411286186589</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46311</v>
       </c>
       <c r="B73">
-        <v>3991.269123320151</v>
+        <v>3982.460930128736</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46318</v>
       </c>
       <c r="B74">
-        <v>4105.368201863423</v>
+        <v>4085.937327974612</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46325</v>
       </c>
       <c r="B75">
-        <v>4145.885002331051</v>
+        <v>4104.989862510855</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46332</v>
       </c>
       <c r="B76">
-        <v>4205.319438619754</v>
+        <v>4130.156065181469</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/XAUUSD_forecast.xlsx
+++ b/public/data/files/XAUUSD_forecast.xlsx
@@ -442,7 +442,7 @@
         <v>45849</v>
       </c>
       <c r="B7">
-        <v>3667.614390489566</v>
+        <v>3667.690490383351</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -450,7 +450,7 @@
         <v>45856</v>
       </c>
       <c r="B8">
-        <v>3564.364419718002</v>
+        <v>3564.467333233321</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -458,7 +458,7 @@
         <v>45863</v>
       </c>
       <c r="B9">
-        <v>3509.729261056237</v>
+        <v>3509.848293026728</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -466,7 +466,7 @@
         <v>45870</v>
       </c>
       <c r="B10">
-        <v>3482.051744096981</v>
+        <v>3482.178172205791</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -474,7 +474,7 @@
         <v>45877</v>
       </c>
       <c r="B11">
-        <v>3490.517517038971</v>
+        <v>3490.647051844733</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -482,7 +482,7 @@
         <v>45884</v>
       </c>
       <c r="B12">
-        <v>3503.286152896248</v>
+        <v>3503.417235703534</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -490,7 +490,7 @@
         <v>45891</v>
       </c>
       <c r="B13">
-        <v>3517.816056019045</v>
+        <v>3517.946163128475</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -498,7 +498,7 @@
         <v>45898</v>
       </c>
       <c r="B14">
-        <v>3530.347776106576</v>
+        <v>3530.475796304929</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -506,7 +506,7 @@
         <v>45905</v>
       </c>
       <c r="B15">
-        <v>3546.808432891438</v>
+        <v>3546.902230528857</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -514,7 +514,7 @@
         <v>45912</v>
       </c>
       <c r="B16">
-        <v>3452.99186461267</v>
+        <v>3452.967273841487</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -522,7 +522,7 @@
         <v>45919</v>
       </c>
       <c r="B17">
-        <v>3450.551720169225</v>
+        <v>3450.530016420679</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -530,7 +530,7 @@
         <v>45926</v>
       </c>
       <c r="B18">
-        <v>3450.611876842484</v>
+        <v>3450.591787885898</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -538,7 +538,7 @@
         <v>45933</v>
       </c>
       <c r="B19">
-        <v>3533.983893685073</v>
+        <v>3533.878106836646</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -546,7 +546,7 @@
         <v>45940</v>
       </c>
       <c r="B20">
-        <v>3632.075109725165</v>
+        <v>3631.872289290149</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -554,7 +554,7 @@
         <v>45947</v>
       </c>
       <c r="B21">
-        <v>3785.190332286954</v>
+        <v>3784.88365774415</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -562,7 +562,7 @@
         <v>45954</v>
       </c>
       <c r="B22">
-        <v>3855.942664607428</v>
+        <v>3855.668175621749</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -570,7 +570,7 @@
         <v>45961</v>
       </c>
       <c r="B23">
-        <v>3902.462287830408</v>
+        <v>3902.207043091941</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -578,7 +578,7 @@
         <v>45968</v>
       </c>
       <c r="B24">
-        <v>3887.436086716513</v>
+        <v>3887.215677335029</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -586,7 +586,7 @@
         <v>45975</v>
       </c>
       <c r="B25">
-        <v>3888.336352385266</v>
+        <v>3888.24490932145</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -594,7 +594,7 @@
         <v>45982</v>
       </c>
       <c r="B26">
-        <v>3994.085934806464</v>
+        <v>3994.056658105517</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -602,7 +602,7 @@
         <v>45989</v>
       </c>
       <c r="B27">
-        <v>4069.46691872805</v>
+        <v>4069.374446374145</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -610,7 +610,7 @@
         <v>45996</v>
       </c>
       <c r="B28">
-        <v>4109.784920656244</v>
+        <v>4109.670738722377</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -618,7 +618,7 @@
         <v>46003</v>
       </c>
       <c r="B29">
-        <v>4206.571986749972</v>
+        <v>4206.559075677638</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -626,7 +626,7 @@
         <v>46010</v>
       </c>
       <c r="B30">
-        <v>4200.217019650318</v>
+        <v>4200.167726689173</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -634,7 +634,7 @@
         <v>46017</v>
       </c>
       <c r="B31">
-        <v>4225.857432431318</v>
+        <v>4225.72298067085</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -642,7 +642,7 @@
         <v>46024</v>
       </c>
       <c r="B32">
-        <v>4246.682387875513</v>
+        <v>4246.547027912233</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -650,7 +650,7 @@
         <v>46031</v>
       </c>
       <c r="B33">
-        <v>4311.955649715872</v>
+        <v>4311.76630606465</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -658,7 +658,7 @@
         <v>46038</v>
       </c>
       <c r="B34">
-        <v>4404.961414056957</v>
+        <v>4404.723107473264</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -666,7 +666,7 @@
         <v>46045</v>
       </c>
       <c r="B35">
-        <v>4441.260152682262</v>
+        <v>4441.002138297874</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -674,7 +674,7 @@
         <v>46052</v>
       </c>
       <c r="B36">
-        <v>4543.940129324438</v>
+        <v>4543.596524524239</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -682,7 +682,7 @@
         <v>46059</v>
       </c>
       <c r="B37">
-        <v>4680.311233192337</v>
+        <v>4679.893689342092</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -690,7 +690,7 @@
         <v>46066</v>
       </c>
       <c r="B38">
-        <v>4763.479405646455</v>
+        <v>4762.948204696327</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -698,7 +698,7 @@
         <v>46073</v>
       </c>
       <c r="B39">
-        <v>4897.101533961706</v>
+        <v>4896.786785697612</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -706,7 +706,7 @@
         <v>46080</v>
       </c>
       <c r="B40">
-        <v>4938.60983993523</v>
+        <v>4938.263967285608</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -714,7 +714,7 @@
         <v>46087</v>
       </c>
       <c r="B41">
-        <v>5046.342909882522</v>
+        <v>5045.89262934446</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -722,7 +722,7 @@
         <v>46094</v>
       </c>
       <c r="B42">
-        <v>5212.055772772602</v>
+        <v>5211.803483931271</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>46101</v>
       </c>
       <c r="B43">
-        <v>5251.787479050592</v>
+        <v>5251.755310504645</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>46108</v>
       </c>
       <c r="B44">
-        <v>5289.225818483194</v>
+        <v>5289.513546260658</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>46115</v>
       </c>
       <c r="B45">
-        <v>5363.551641955366</v>
+        <v>5364.07299742506</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>46122</v>
       </c>
       <c r="B46">
-        <v>5438.658400786773</v>
+        <v>5439.332824007279</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>46129</v>
       </c>
       <c r="B47">
-        <v>5568.192801693158</v>
+        <v>5568.929880215485</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>46136</v>
       </c>
       <c r="B48">
-        <v>5505.989598668441</v>
+        <v>5506.922950465493</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>46143</v>
       </c>
       <c r="B49">
-        <v>5328.697255716412</v>
+        <v>5329.856640863773</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>46150</v>
       </c>
       <c r="B50">
-        <v>5212.844331070975</v>
+        <v>5213.935901896763</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>46157</v>
       </c>
       <c r="B51">
-        <v>5078.032567353053</v>
+        <v>5079.20520617514</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>46164</v>
       </c>
       <c r="B52">
-        <v>4965.298145824265</v>
+        <v>4966.3575466532</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>46171</v>
       </c>
       <c r="B53">
-        <v>4863.089350306285</v>
+        <v>4864.099890779196</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>46178</v>
       </c>
       <c r="B54">
-        <v>4813.188914666115</v>
+        <v>4814.331395659736</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>46185</v>
       </c>
       <c r="B55">
-        <v>4687.065304698302</v>
+        <v>4687.984720384246</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>46192</v>
       </c>
       <c r="B56">
-        <v>4568.637821092981</v>
+        <v>4569.282840012766</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>46199</v>
       </c>
       <c r="B57">
-        <v>4474.935392917414</v>
+        <v>4475.370401808903</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>46206</v>
       </c>
       <c r="B58">
-        <v>4470.002689561607</v>
+        <v>4470.446318376597</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>46213</v>
       </c>
       <c r="B59">
-        <v>4389.011028603965</v>
+        <v>4389.561120931561</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>46220</v>
       </c>
       <c r="B60">
-        <v>4229.20819875192</v>
+        <v>4229.934247183232</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>46227</v>
       </c>
       <c r="B61">
-        <v>4147.581267299905</v>
+        <v>4137.364801974541</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>46234</v>
       </c>
       <c r="B62">
-        <v>4092.394028542771</v>
+        <v>4089.888811260491</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>46241</v>
       </c>
       <c r="B63">
-        <v>4048.756479269748</v>
+        <v>4046.832483064761</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46248</v>
       </c>
       <c r="B64">
-        <v>4013.14210415712</v>
+        <v>4015.092128531408</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46255</v>
       </c>
       <c r="B65">
-        <v>3980.375726169506</v>
+        <v>3993.072793843531</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46262</v>
       </c>
       <c r="B66">
-        <v>3959.747263250664</v>
+        <v>3991.941385242303</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46269</v>
       </c>
       <c r="B67">
-        <v>3939.673573460407</v>
+        <v>3969.774601109765</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46276</v>
       </c>
       <c r="B68">
-        <v>3939.768153253834</v>
+        <v>3967.698013053756</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46283</v>
       </c>
       <c r="B69">
-        <v>3906.3214148474</v>
+        <v>3926.076131157295</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46290</v>
       </c>
       <c r="B70">
-        <v>3899.675323409918</v>
+        <v>3913.245232218734</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46297</v>
       </c>
       <c r="B71">
-        <v>3929.731335901647</v>
+        <v>3933.712897908686</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46304</v>
       </c>
       <c r="B72">
-        <v>3958.411286186589</v>
+        <v>3973.531814413579</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46311</v>
       </c>
       <c r="B73">
-        <v>3982.460930128736</v>
+        <v>4004.58235540288</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46318</v>
       </c>
       <c r="B74">
-        <v>4085.937327974612</v>
+        <v>4115.034427940407</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46325</v>
       </c>
       <c r="B75">
-        <v>4104.989862510855</v>
+        <v>4156.945834162172</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46332</v>
       </c>
       <c r="B76">
-        <v>4130.156065181469</v>
+        <v>4205.299596131346</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/XAUUSD_forecast.xlsx
+++ b/public/data/files/XAUUSD_forecast.xlsx
@@ -874,7 +874,7 @@
         <v>46227</v>
       </c>
       <c r="B61">
-        <v>4137.364801974541</v>
+        <v>4148.184224636731</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>46234</v>
       </c>
       <c r="B62">
-        <v>4089.888811260491</v>
+        <v>4092.765027021941</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>46241</v>
       </c>
       <c r="B63">
-        <v>4046.832483064761</v>
+        <v>4059.785103684313</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46248</v>
       </c>
       <c r="B64">
-        <v>4015.092128531408</v>
+        <v>4026.472864372531</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46255</v>
       </c>
       <c r="B65">
-        <v>3993.072793843531</v>
+        <v>3995.782301071693</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46262</v>
       </c>
       <c r="B66">
-        <v>3991.941385242303</v>
+        <v>3978.270878369383</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46269</v>
       </c>
       <c r="B67">
-        <v>3969.774601109765</v>
+        <v>3960.714235093133</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46276</v>
       </c>
       <c r="B68">
-        <v>3967.698013053756</v>
+        <v>3964.794569366622</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46283</v>
       </c>
       <c r="B69">
-        <v>3926.076131157295</v>
+        <v>3939.74701226856</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46290</v>
       </c>
       <c r="B70">
-        <v>3913.245232218734</v>
+        <v>3939.639001842794</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46297</v>
       </c>
       <c r="B71">
-        <v>3933.712897908686</v>
+        <v>3975.660035337723</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46304</v>
       </c>
       <c r="B72">
-        <v>3973.531814413579</v>
+        <v>4011.225580540804</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46311</v>
       </c>
       <c r="B73">
-        <v>4004.58235540288</v>
+        <v>4044.620188609042</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46318</v>
       </c>
       <c r="B74">
-        <v>4115.034427940407</v>
+        <v>4168.198456266802</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46325</v>
       </c>
       <c r="B75">
-        <v>4156.945834162172</v>
+        <v>4223.733639545328</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46332</v>
       </c>
       <c r="B76">
-        <v>4205.299596131346</v>
+        <v>4426.663096030657</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/XAUUSD_forecast.xlsx
+++ b/public/data/files/XAUUSD_forecast.xlsx
@@ -442,7 +442,7 @@
         <v>45849</v>
       </c>
       <c r="B7">
-        <v>3667.690490383351</v>
+        <v>3667.764284757334</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -450,7 +450,7 @@
         <v>45856</v>
       </c>
       <c r="B8">
-        <v>3564.467333233321</v>
+        <v>3564.567144875177</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -458,7 +458,7 @@
         <v>45863</v>
       </c>
       <c r="B9">
-        <v>3509.848293026728</v>
+        <v>3509.963754385308</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -466,7 +466,7 @@
         <v>45870</v>
       </c>
       <c r="B10">
-        <v>3482.178172205791</v>
+        <v>3482.300831039625</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -474,7 +474,7 @@
         <v>45877</v>
       </c>
       <c r="B11">
-        <v>3490.647051844733</v>
+        <v>3490.772723873235</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -482,7 +482,7 @@
         <v>45884</v>
       </c>
       <c r="B12">
-        <v>3503.417235703534</v>
+        <v>3503.544408633934</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -490,7 +490,7 @@
         <v>45891</v>
       </c>
       <c r="B13">
-        <v>3517.946163128475</v>
+        <v>3518.072388966803</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -498,7 +498,7 @@
         <v>45898</v>
       </c>
       <c r="B14">
-        <v>3530.475796304929</v>
+        <v>3530.599997462874</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -506,7 +506,7 @@
         <v>45905</v>
       </c>
       <c r="B15">
-        <v>3546.902230528857</v>
+        <v>3546.99329096108</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -514,7 +514,7 @@
         <v>45912</v>
       </c>
       <c r="B16">
-        <v>3452.967273841487</v>
+        <v>3452.943447121373</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -522,7 +522,7 @@
         <v>45919</v>
       </c>
       <c r="B17">
-        <v>3450.530016420679</v>
+        <v>3450.508989536957</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -530,7 +530,7 @@
         <v>45926</v>
       </c>
       <c r="B18">
-        <v>3450.591787885898</v>
+        <v>3450.572327185832</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -538,7 +538,7 @@
         <v>45933</v>
       </c>
       <c r="B19">
-        <v>3533.878106836646</v>
+        <v>3533.7755831962</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -546,7 +546,7 @@
         <v>45940</v>
       </c>
       <c r="B20">
-        <v>3631.872289290149</v>
+        <v>3631.67568806396</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -554,7 +554,7 @@
         <v>45947</v>
       </c>
       <c r="B21">
-        <v>3784.88365774415</v>
+        <v>3784.586302788479</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -562,7 +562,7 @@
         <v>45954</v>
       </c>
       <c r="B22">
-        <v>3855.668175621749</v>
+        <v>3855.401994513722</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -570,7 +570,7 @@
         <v>45961</v>
       </c>
       <c r="B23">
-        <v>3902.207043091941</v>
+        <v>3901.959357958992</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -578,7 +578,7 @@
         <v>45968</v>
       </c>
       <c r="B24">
-        <v>3887.215677335029</v>
+        <v>3887.001715132291</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -586,7 +586,7 @@
         <v>45975</v>
       </c>
       <c r="B25">
-        <v>3888.24490932145</v>
+        <v>3888.156050220443</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -594,7 +594,7 @@
         <v>45982</v>
       </c>
       <c r="B26">
-        <v>3994.056658105517</v>
+        <v>3994.028154383229</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -602,7 +602,7 @@
         <v>45989</v>
       </c>
       <c r="B27">
-        <v>4069.374446374145</v>
+        <v>4069.284699393774</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -610,7 +610,7 @@
         <v>45996</v>
       </c>
       <c r="B28">
-        <v>4109.670738722377</v>
+        <v>4109.559928809471</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -618,7 +618,7 @@
         <v>46003</v>
       </c>
       <c r="B29">
-        <v>4206.559075677638</v>
+        <v>4206.546640367698</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -626,7 +626,7 @@
         <v>46010</v>
       </c>
       <c r="B30">
-        <v>4200.167726689173</v>
+        <v>4200.120064641</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -634,7 +634,7 @@
         <v>46017</v>
       </c>
       <c r="B31">
-        <v>4225.72298067085</v>
+        <v>4225.592821527927</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -642,7 +642,7 @@
         <v>46024</v>
       </c>
       <c r="B32">
-        <v>4246.547027912233</v>
+        <v>4246.415928235752</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -650,7 +650,7 @@
         <v>46031</v>
       </c>
       <c r="B33">
-        <v>4311.76630606465</v>
+        <v>4311.582856412189</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -658,7 +658,7 @@
         <v>46038</v>
       </c>
       <c r="B34">
-        <v>4404.723107473264</v>
+        <v>4404.49213160761</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -666,7 +666,7 @@
         <v>46045</v>
       </c>
       <c r="B35">
-        <v>4441.002138297874</v>
+        <v>4440.751969262161</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -674,7 +674,7 @@
         <v>46052</v>
       </c>
       <c r="B36">
-        <v>4543.596524524239</v>
+        <v>4543.26325833075</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -682,7 +682,7 @@
         <v>46059</v>
       </c>
       <c r="B37">
-        <v>4679.893689342092</v>
+        <v>4679.488734577561</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -690,7 +690,7 @@
         <v>46066</v>
       </c>
       <c r="B38">
-        <v>4762.948204696327</v>
+        <v>4762.432448717981</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -698,7 +698,7 @@
         <v>46073</v>
       </c>
       <c r="B39">
-        <v>4896.786785697612</v>
+        <v>4896.48147581804</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -706,7 +706,7 @@
         <v>46080</v>
       </c>
       <c r="B40">
-        <v>4938.263967285608</v>
+        <v>4937.928458027156</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -714,7 +714,7 @@
         <v>46087</v>
       </c>
       <c r="B41">
-        <v>5045.89262934446</v>
+        <v>5045.455697959124</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -722,7 +722,7 @@
         <v>46094</v>
       </c>
       <c r="B42">
-        <v>5211.803483931271</v>
+        <v>5211.558364683095</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>46101</v>
       </c>
       <c r="B43">
-        <v>5251.755310504645</v>
+        <v>5251.723198519883</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>46108</v>
       </c>
       <c r="B44">
-        <v>5289.513546260658</v>
+        <v>5289.791466124845</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>46115</v>
       </c>
       <c r="B45">
-        <v>5364.07299742506</v>
+        <v>5364.577824305209</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>46122</v>
       </c>
       <c r="B46">
-        <v>5439.332824007279</v>
+        <v>5439.986005286124</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>46129</v>
       </c>
       <c r="B47">
-        <v>5568.929880215485</v>
+        <v>5569.643887301118</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>46136</v>
       </c>
       <c r="B48">
-        <v>5506.922950465493</v>
+        <v>5507.827811109461</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>46143</v>
       </c>
       <c r="B49">
-        <v>5329.856640863773</v>
+        <v>5330.981091048086</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>46150</v>
       </c>
       <c r="B50">
-        <v>5213.935901896763</v>
+        <v>5214.99490530951</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>46157</v>
       </c>
       <c r="B51">
-        <v>5079.20520617514</v>
+        <v>5080.343367742375</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>46164</v>
       </c>
       <c r="B52">
-        <v>4966.3575466532</v>
+        <v>4967.386113160149</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>46171</v>
       </c>
       <c r="B53">
-        <v>4864.099890779196</v>
+        <v>4865.081467089423</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>46178</v>
       </c>
       <c r="B54">
-        <v>4814.331395659736</v>
+        <v>4815.441175012908</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>46185</v>
       </c>
       <c r="B55">
-        <v>4687.984720384246</v>
+        <v>4688.877683894803</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>46192</v>
       </c>
       <c r="B56">
-        <v>4569.282840012766</v>
+        <v>4569.908947951427</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>46199</v>
       </c>
       <c r="B57">
-        <v>4475.370401808903</v>
+        <v>4475.79205690882</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>46206</v>
       </c>
       <c r="B58">
-        <v>4470.446318376597</v>
+        <v>4470.876342710595</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>46213</v>
       </c>
       <c r="B59">
-        <v>4389.561120931561</v>
+        <v>4390.094687110818</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>46220</v>
       </c>
       <c r="B60">
-        <v>4229.934247183232</v>
+        <v>4230.63930257864</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>46227</v>
       </c>
       <c r="B61">
-        <v>4148.184224636731</v>
+        <v>4137.943274254175</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>46234</v>
       </c>
       <c r="B62">
-        <v>4092.765027021941</v>
+        <v>4090.246446421074</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>46241</v>
       </c>
       <c r="B63">
-        <v>4059.785103684313</v>
+        <v>4057.6813999169</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46248</v>
       </c>
       <c r="B64">
-        <v>4026.472864372531</v>
+        <v>4029.329884202428</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46255</v>
       </c>
       <c r="B65">
-        <v>3995.782301071693</v>
+        <v>4011.06200113595</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46262</v>
       </c>
       <c r="B66">
-        <v>3978.270878369383</v>
+        <v>4016.812334304048</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46269</v>
       </c>
       <c r="B67">
-        <v>3960.714235093133</v>
+        <v>3998.090063108716</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46276</v>
       </c>
       <c r="B68">
-        <v>3964.794569366622</v>
+        <v>3996.710983731929</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46283</v>
       </c>
       <c r="B69">
-        <v>3939.74701226856</v>
+        <v>3957.457913040188</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46290</v>
       </c>
       <c r="B70">
-        <v>3939.639001842794</v>
+        <v>3947.84246239027</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46297</v>
       </c>
       <c r="B71">
-        <v>3975.660035337723</v>
+        <v>3969.932760509313</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46304</v>
       </c>
       <c r="B72">
-        <v>4011.225580540804</v>
+        <v>4014.515375697323</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46311</v>
       </c>
       <c r="B73">
-        <v>4044.620188609042</v>
+        <v>4051.768367514909</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46318</v>
       </c>
       <c r="B74">
-        <v>4168.198456266802</v>
+        <v>4162.055452216228</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46325</v>
       </c>
       <c r="B75">
-        <v>4223.733639545328</v>
+        <v>4234.154831814999</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46332</v>
       </c>
       <c r="B76">
-        <v>4426.663096030657</v>
+        <v>4365.030182236888</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/XAUUSD_forecast.xlsx
+++ b/public/data/files/XAUUSD_forecast.xlsx
@@ -874,7 +874,7 @@
         <v>46227</v>
       </c>
       <c r="B61">
-        <v>4137.943274254175</v>
+        <v>4148.770704438129</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>46234</v>
       </c>
       <c r="B62">
-        <v>4090.246446421074</v>
+        <v>4093.127013547894</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>46241</v>
       </c>
       <c r="B63">
-        <v>4057.6813999169</v>
+        <v>4068.654064595938</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46248</v>
       </c>
       <c r="B64">
-        <v>4029.329884202428</v>
+        <v>4037.531147320081</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46255</v>
       </c>
       <c r="B65">
-        <v>4011.06200113595</v>
+        <v>4009.330019080515</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46262</v>
       </c>
       <c r="B66">
-        <v>4016.812334304048</v>
+        <v>3995.984885141357</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46269</v>
       </c>
       <c r="B67">
-        <v>3998.090063108716</v>
+        <v>3980.841757890585</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46276</v>
       </c>
       <c r="B68">
-        <v>3996.710983731929</v>
+        <v>3986.448671884537</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46283</v>
       </c>
       <c r="B69">
-        <v>3957.457913040188</v>
+        <v>3965.037933729338</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46290</v>
       </c>
       <c r="B70">
-        <v>3947.84246239027</v>
+        <v>3969.428888643183</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46297</v>
       </c>
       <c r="B71">
-        <v>3969.932760509313</v>
+        <v>4007.418659190565</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46304</v>
       </c>
       <c r="B72">
-        <v>4014.515375697323</v>
+        <v>4048.159049306264</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46311</v>
       </c>
       <c r="B73">
-        <v>4051.768367514909</v>
+        <v>4077.567652135283</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46318</v>
       </c>
       <c r="B74">
-        <v>4162.055452216228</v>
+        <v>4213.258050798318</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46325</v>
       </c>
       <c r="B75">
-        <v>4234.154831814999</v>
+        <v>4276.858303304034</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46332</v>
       </c>
       <c r="B76">
-        <v>4365.030182236888</v>
+        <v>4478.061543351761</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/XAUUSD_forecast.xlsx
+++ b/public/data/files/XAUUSD_forecast.xlsx
@@ -442,7 +442,7 @@
         <v>45849</v>
       </c>
       <c r="B7">
-        <v>3667.764284757334</v>
+        <v>3667.905363680941</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -450,7 +450,7 @@
         <v>45856</v>
       </c>
       <c r="B8">
-        <v>3564.567144875177</v>
+        <v>3564.758006986811</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -458,7 +458,7 @@
         <v>45863</v>
       </c>
       <c r="B9">
-        <v>3509.963754385308</v>
+        <v>3510.184589004301</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -466,7 +466,7 @@
         <v>45870</v>
       </c>
       <c r="B10">
-        <v>3482.300831039625</v>
+        <v>3482.535495259548</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -474,7 +474,7 @@
         <v>45877</v>
       </c>
       <c r="B11">
-        <v>3490.772723873235</v>
+        <v>3491.013150358539</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -482,7 +482,7 @@
         <v>45884</v>
       </c>
       <c r="B12">
-        <v>3503.544408633934</v>
+        <v>3503.787703965774</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -490,7 +490,7 @@
         <v>45891</v>
       </c>
       <c r="B13">
-        <v>3518.072388966803</v>
+        <v>3518.31387105174</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -498,7 +498,7 @@
         <v>45898</v>
       </c>
       <c r="B14">
-        <v>3530.599997462874</v>
+        <v>3530.837606075144</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -506,7 +506,7 @@
         <v>45905</v>
       </c>
       <c r="B15">
-        <v>3546.99329096108</v>
+        <v>3547.167665079478</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -514,7 +514,7 @@
         <v>45912</v>
       </c>
       <c r="B16">
-        <v>3452.943447121373</v>
+        <v>3452.897947810656</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -522,7 +522,7 @@
         <v>45919</v>
       </c>
       <c r="B17">
-        <v>3450.508989536957</v>
+        <v>3450.468843670493</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -530,7 +530,7 @@
         <v>45926</v>
       </c>
       <c r="B18">
-        <v>3450.572327185832</v>
+        <v>3450.535176381765</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -538,7 +538,7 @@
         <v>45933</v>
       </c>
       <c r="B19">
-        <v>3533.7755831962</v>
+        <v>3533.579740109556</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -546,7 +546,7 @@
         <v>45940</v>
       </c>
       <c r="B20">
-        <v>3631.67568806396</v>
+        <v>3631.3000340829</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -554,7 +554,7 @@
         <v>45947</v>
       </c>
       <c r="B21">
-        <v>3784.586302788479</v>
+        <v>3784.017903845943</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -562,7 +562,7 @@
         <v>45954</v>
       </c>
       <c r="B22">
-        <v>3855.401994513722</v>
+        <v>3854.893092420099</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -570,7 +570,7 @@
         <v>45961</v>
       </c>
       <c r="B23">
-        <v>3901.959357958992</v>
+        <v>3901.485363880432</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -578,7 +578,7 @@
         <v>45968</v>
       </c>
       <c r="B24">
-        <v>3887.001715132291</v>
+        <v>3886.592035501368</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -586,7 +586,7 @@
         <v>45975</v>
       </c>
       <c r="B25">
-        <v>3888.156050220443</v>
+        <v>3887.985660109865</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -594,7 +594,7 @@
         <v>45982</v>
       </c>
       <c r="B26">
-        <v>3994.028154383229</v>
+        <v>3993.973348822021</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -602,7 +602,7 @@
         <v>45989</v>
       </c>
       <c r="B27">
-        <v>4069.284699393774</v>
+        <v>4069.112913553147</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -610,7 +610,7 @@
         <v>45996</v>
       </c>
       <c r="B28">
-        <v>4109.559928809471</v>
+        <v>4109.347845082213</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -618,7 +618,7 @@
         <v>46003</v>
       </c>
       <c r="B29">
-        <v>4206.546640367698</v>
+        <v>4206.523098685166</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -626,7 +626,7 @@
         <v>46010</v>
       </c>
       <c r="B30">
-        <v>4200.120064641</v>
+        <v>4200.029322624843</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -634,7 +634,7 @@
         <v>46017</v>
       </c>
       <c r="B31">
-        <v>4225.592821527927</v>
+        <v>4225.344587940279</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -642,7 +642,7 @@
         <v>46024</v>
       </c>
       <c r="B32">
-        <v>4246.415928235752</v>
+        <v>4246.165733484557</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -650,7 +650,7 @@
         <v>46031</v>
       </c>
       <c r="B33">
-        <v>4311.582856412189</v>
+        <v>4311.232576237912</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -658,7 +658,7 @@
         <v>46038</v>
       </c>
       <c r="B34">
-        <v>4404.49213160761</v>
+        <v>4404.050865106444</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -666,7 +666,7 @@
         <v>46045</v>
       </c>
       <c r="B35">
-        <v>4440.751969262161</v>
+        <v>4440.273782758164</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -674,7 +674,7 @@
         <v>46052</v>
       </c>
       <c r="B36">
-        <v>4543.26325833075</v>
+        <v>4542.625934630682</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -682,7 +682,7 @@
         <v>46059</v>
       </c>
       <c r="B37">
-        <v>4679.488734577561</v>
+        <v>4678.714388200047</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -690,7 +690,7 @@
         <v>46066</v>
       </c>
       <c r="B38">
-        <v>4762.432448717981</v>
+        <v>4761.444661379686</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -698,7 +698,7 @@
         <v>46073</v>
       </c>
       <c r="B39">
-        <v>4896.48147581804</v>
+        <v>4895.897527938798</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -706,7 +706,7 @@
         <v>46080</v>
       </c>
       <c r="B40">
-        <v>4937.928458027156</v>
+        <v>4937.286726720728</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -714,7 +714,7 @@
         <v>46087</v>
       </c>
       <c r="B41">
-        <v>5045.455697959124</v>
+        <v>5044.619587022163</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -722,7 +722,7 @@
         <v>46094</v>
       </c>
       <c r="B42">
-        <v>5211.558364683095</v>
+        <v>5211.088454817682</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>46101</v>
       </c>
       <c r="B43">
-        <v>5251.723198519883</v>
+        <v>5251.659292795629</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>46108</v>
       </c>
       <c r="B44">
-        <v>5289.791466124845</v>
+        <v>5290.319794446176</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>46115</v>
       </c>
       <c r="B45">
-        <v>5364.577824305209</v>
+        <v>5365.540925608304</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>46122</v>
       </c>
       <c r="B46">
-        <v>5439.986005286124</v>
+        <v>5441.232514565472</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>46129</v>
       </c>
       <c r="B47">
-        <v>5569.643887301118</v>
+        <v>5571.00687166869</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>46136</v>
       </c>
       <c r="B48">
-        <v>5507.827811109461</v>
+        <v>5509.557107892257</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>46143</v>
       </c>
       <c r="B49">
-        <v>5330.981091048086</v>
+        <v>5333.131293692764</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>46150</v>
       </c>
       <c r="B50">
-        <v>5214.99490530951</v>
+        <v>5217.02084659227</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>46157</v>
       </c>
       <c r="B51">
-        <v>5080.343367742375</v>
+        <v>5082.522138399834</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>46164</v>
       </c>
       <c r="B52">
-        <v>4967.386113160149</v>
+        <v>4969.355953008828</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>46171</v>
       </c>
       <c r="B53">
-        <v>4865.081467089423</v>
+        <v>4866.962543165037</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>46178</v>
       </c>
       <c r="B54">
-        <v>4815.441175012908</v>
+        <v>4817.56805677424</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>46185</v>
       </c>
       <c r="B55">
-        <v>4688.877683894803</v>
+        <v>4690.588670952245</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>46192</v>
       </c>
       <c r="B56">
-        <v>4569.908947951427</v>
+        <v>4571.107651083526</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>46199</v>
       </c>
       <c r="B57">
-        <v>4475.79205690882</v>
+        <v>4476.597681513991</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>46206</v>
       </c>
       <c r="B58">
-        <v>4470.876342710595</v>
+        <v>4471.697997641354</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>46213</v>
       </c>
       <c r="B59">
-        <v>4390.094687110818</v>
+        <v>4391.11511983309</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>46220</v>
       </c>
       <c r="B60">
-        <v>4230.63930257864</v>
+        <v>4231.989942477361</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>46227</v>
       </c>
       <c r="B61">
-        <v>4148.770704438129</v>
+        <v>4139.054908544781</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>46234</v>
       </c>
       <c r="B62">
-        <v>4093.127013547894</v>
+        <v>4090.936488845552</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>46241</v>
       </c>
       <c r="B63">
-        <v>4068.654064595938</v>
+        <v>4074.535104026654</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46248</v>
       </c>
       <c r="B64">
-        <v>4037.531147320081</v>
+        <v>4051.577910376504</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46255</v>
       </c>
       <c r="B65">
-        <v>4009.330019080515</v>
+        <v>4039.6164271781</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46262</v>
       </c>
       <c r="B66">
-        <v>3995.984885141357</v>
+        <v>4053.666859318902</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46269</v>
       </c>
       <c r="B67">
-        <v>3980.841757890585</v>
+        <v>4041.458422349166</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46276</v>
       </c>
       <c r="B68">
-        <v>3986.448671884537</v>
+        <v>4041.798256152657</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46283</v>
       </c>
       <c r="B69">
-        <v>3965.037933729338</v>
+        <v>4006.678213656899</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46290</v>
       </c>
       <c r="B70">
-        <v>3969.428888643183</v>
+        <v>4001.597537693672</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46297</v>
       </c>
       <c r="B71">
-        <v>4007.418659190565</v>
+        <v>4025.972205100623</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46304</v>
       </c>
       <c r="B72">
-        <v>4048.159049306264</v>
+        <v>4077.86518076334</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46311</v>
       </c>
       <c r="B73">
-        <v>4077.567652135283</v>
+        <v>4117.129730482747</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46318</v>
       </c>
       <c r="B74">
-        <v>4213.258050798318</v>
+        <v>4227.208117584833</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46325</v>
       </c>
       <c r="B75">
-        <v>4276.858303304034</v>
+        <v>4321.644020076279</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46332</v>
       </c>
       <c r="B76">
-        <v>4478.061543351761</v>
+        <v>4466.177108374663</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/XAUUSD_forecast.xlsx
+++ b/public/data/files/XAUUSD_forecast.xlsx
@@ -442,7 +442,7 @@
         <v>45849</v>
       </c>
       <c r="B7">
-        <v>3667.905363680941</v>
+        <v>3667.835876812373</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -450,7 +450,7 @@
         <v>45856</v>
       </c>
       <c r="B8">
-        <v>3564.758006986811</v>
+        <v>3564.663992775738</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -458,7 +458,7 @@
         <v>45863</v>
       </c>
       <c r="B9">
-        <v>3510.184589004301</v>
+        <v>3510.075803369121</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -466,7 +466,7 @@
         <v>45870</v>
       </c>
       <c r="B10">
-        <v>3482.535495259548</v>
+        <v>3482.419886592918</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -474,7 +474,7 @@
         <v>45877</v>
       </c>
       <c r="B11">
-        <v>3491.013150358539</v>
+        <v>3490.894703275292</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -482,7 +482,7 @@
         <v>45884</v>
       </c>
       <c r="B12">
-        <v>3503.787703965774</v>
+        <v>3503.667843954896</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -490,7 +490,7 @@
         <v>45891</v>
       </c>
       <c r="B13">
-        <v>3518.31387105174</v>
+        <v>3518.194904563886</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -498,7 +498,7 @@
         <v>45898</v>
       </c>
       <c r="B14">
-        <v>3530.837606075144</v>
+        <v>3530.720547869654</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -506,7 +506,7 @@
         <v>45905</v>
       </c>
       <c r="B15">
-        <v>3547.167665079478</v>
+        <v>3547.08173207073</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -514,7 +514,7 @@
         <v>45912</v>
       </c>
       <c r="B16">
-        <v>3452.897947810656</v>
+        <v>3452.920349419472</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -522,7 +522,7 @@
         <v>45919</v>
       </c>
       <c r="B17">
-        <v>3450.468843670493</v>
+        <v>3450.48860837473</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -530,7 +530,7 @@
         <v>45926</v>
       </c>
       <c r="B18">
-        <v>3450.535176381765</v>
+        <v>3450.553465760519</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -538,7 +538,7 @@
         <v>45933</v>
       </c>
       <c r="B19">
-        <v>3533.579740109556</v>
+        <v>3533.676174186763</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -546,7 +546,7 @@
         <v>45940</v>
       </c>
       <c r="B20">
-        <v>3631.3000340829</v>
+        <v>3631.485024578485</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -554,7 +554,7 @@
         <v>45947</v>
       </c>
       <c r="B21">
-        <v>3784.017903845943</v>
+        <v>3784.297849316604</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -562,7 +562,7 @@
         <v>45954</v>
       </c>
       <c r="B22">
-        <v>3854.893092420099</v>
+        <v>3855.143749958011</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -570,7 +570,7 @@
         <v>45961</v>
       </c>
       <c r="B23">
-        <v>3901.485363880432</v>
+        <v>3901.718902037997</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -578,7 +578,7 @@
         <v>45968</v>
       </c>
       <c r="B24">
-        <v>3886.592035501368</v>
+        <v>3886.793921985181</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -586,7 +586,7 @@
         <v>45975</v>
       </c>
       <c r="B25">
-        <v>3887.985660109865</v>
+        <v>3888.069667674026</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -594,7 +594,7 @@
         <v>45982</v>
       </c>
       <c r="B26">
-        <v>3993.973348822021</v>
+        <v>3994.000394012118</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -602,7 +602,7 @@
         <v>45989</v>
       </c>
       <c r="B27">
-        <v>4069.112913553147</v>
+        <v>4069.197559088707</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -610,7 +610,7 @@
         <v>45996</v>
       </c>
       <c r="B28">
-        <v>4109.347845082213</v>
+        <v>4109.452343819584</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -618,7 +618,7 @@
         <v>46003</v>
       </c>
       <c r="B29">
-        <v>4206.523098685166</v>
+        <v>4206.534655811693</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -626,7 +626,7 @@
         <v>46010</v>
       </c>
       <c r="B30">
-        <v>4200.029322624843</v>
+        <v>4200.073954598156</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -634,7 +634,7 @@
         <v>46017</v>
       </c>
       <c r="B31">
-        <v>4225.344587940279</v>
+        <v>4225.466753626659</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -642,7 +642,7 @@
         <v>46024</v>
       </c>
       <c r="B32">
-        <v>4246.165733484557</v>
+        <v>4246.288891803099</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -650,7 +650,7 @@
         <v>46031</v>
       </c>
       <c r="B33">
-        <v>4311.232576237912</v>
+        <v>4311.405031005826</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -658,7 +658,7 @@
         <v>46038</v>
       </c>
       <c r="B34">
-        <v>4404.050865106444</v>
+        <v>4404.268154823305</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -666,7 +666,7 @@
         <v>46045</v>
       </c>
       <c r="B35">
-        <v>4440.273782758164</v>
+        <v>4440.509294306898</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -674,7 +674,7 @@
         <v>46052</v>
       </c>
       <c r="B36">
-        <v>4542.625934630682</v>
+        <v>4542.939872300952</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -682,7 +682,7 @@
         <v>46059</v>
       </c>
       <c r="B37">
-        <v>4678.714388200047</v>
+        <v>4679.095809739145</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -690,7 +690,7 @@
         <v>46066</v>
       </c>
       <c r="B38">
-        <v>4761.444661379686</v>
+        <v>4761.931475846234</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -698,7 +698,7 @@
         <v>46073</v>
       </c>
       <c r="B39">
-        <v>4895.897527938798</v>
+        <v>4896.185187477384</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -706,7 +706,7 @@
         <v>46080</v>
       </c>
       <c r="B40">
-        <v>4937.286726720728</v>
+        <v>4937.602854811126</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -714,7 +714,7 @@
         <v>46087</v>
       </c>
       <c r="B41">
-        <v>5044.619587022163</v>
+        <v>5045.031533517174</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -722,7 +722,7 @@
         <v>46094</v>
       </c>
       <c r="B42">
-        <v>5211.088454817682</v>
+        <v>5211.320115922223</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>46101</v>
       </c>
       <c r="B43">
-        <v>5251.659292795629</v>
+        <v>5251.691181393694</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>46108</v>
       </c>
       <c r="B44">
-        <v>5290.319794446176</v>
+        <v>5290.060063959791</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>46115</v>
       </c>
       <c r="B45">
-        <v>5365.540925608304</v>
+        <v>5365.066892648538</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>46122</v>
       </c>
       <c r="B46">
-        <v>5441.232514565472</v>
+        <v>5440.618927623547</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>46129</v>
       </c>
       <c r="B47">
-        <v>5571.00687166869</v>
+        <v>5570.335885067165</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>46136</v>
       </c>
       <c r="B48">
-        <v>5509.557107892257</v>
+        <v>5508.705461702195</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>46143</v>
       </c>
       <c r="B49">
-        <v>5333.131293692764</v>
+        <v>5332.072155539029</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>46150</v>
       </c>
       <c r="B50">
-        <v>5217.02084659227</v>
+        <v>5216.022771011394</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>46157</v>
       </c>
       <c r="B51">
-        <v>5082.522138399834</v>
+        <v>5081.44854295189</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>46164</v>
       </c>
       <c r="B52">
-        <v>4969.355953008828</v>
+        <v>4968.385166307925</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>46171</v>
       </c>
       <c r="B53">
-        <v>4866.962543165037</v>
+        <v>4866.035300036416</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>46178</v>
       </c>
       <c r="B54">
-        <v>4817.56805677424</v>
+        <v>4816.519628627933</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>46185</v>
       </c>
       <c r="B55">
-        <v>4690.588670952245</v>
+        <v>4689.745314864384</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>46192</v>
       </c>
       <c r="B56">
-        <v>4571.107651083526</v>
+        <v>4570.516961501604</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>46199</v>
       </c>
       <c r="B57">
-        <v>4476.597681513991</v>
+        <v>4476.200961060627</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>46206</v>
       </c>
       <c r="B58">
-        <v>4471.697997641354</v>
+        <v>4471.293376556908</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>46213</v>
       </c>
       <c r="B59">
-        <v>4391.11511983309</v>
+        <v>4390.612457394501</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>46220</v>
       </c>
       <c r="B60">
-        <v>4231.989942477361</v>
+        <v>4231.324254255935</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>46227</v>
       </c>
       <c r="B61">
-        <v>4139.054908544781</v>
+        <v>4149.34136059583</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>46234</v>
       </c>
       <c r="B62">
-        <v>4090.936488845552</v>
+        <v>4093.480293677791</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>46241</v>
       </c>
       <c r="B63">
-        <v>4074.535104026654</v>
+        <v>4076.842863217794</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46248</v>
       </c>
       <c r="B64">
-        <v>4051.577910376504</v>
+        <v>4047.688231743287</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46255</v>
       </c>
       <c r="B65">
-        <v>4039.6164271781</v>
+        <v>4021.784275755562</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46262</v>
       </c>
       <c r="B66">
-        <v>4053.666859318902</v>
+        <v>4010.714414386382</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46269</v>
       </c>
       <c r="B67">
-        <v>4041.458422349166</v>
+        <v>3998.163863607043</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46276</v>
       </c>
       <c r="B68">
-        <v>4041.798256152657</v>
+        <v>4005.498062276537</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46283</v>
       </c>
       <c r="B69">
-        <v>4006.678213656899</v>
+        <v>3987.585023445543</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46290</v>
       </c>
       <c r="B70">
-        <v>4001.597537693672</v>
+        <v>3995.984836625777</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46297</v>
       </c>
       <c r="B71">
-        <v>4025.972205100623</v>
+        <v>4035.762133117538</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46304</v>
       </c>
       <c r="B72">
-        <v>4077.86518076334</v>
+        <v>4081.062830582162</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46311</v>
       </c>
       <c r="B73">
-        <v>4117.129730482747</v>
+        <v>4106.811339715347</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46318</v>
       </c>
       <c r="B74">
-        <v>4227.208117584833</v>
+        <v>4251.357058139808</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46325</v>
       </c>
       <c r="B75">
-        <v>4321.644020076279</v>
+        <v>4318.916325476606</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46332</v>
       </c>
       <c r="B76">
-        <v>4466.177108374663</v>
+        <v>4508.573293953701</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/XAUUSD_forecast.xlsx
+++ b/public/data/files/XAUUSD_forecast.xlsx
@@ -442,7 +442,7 @@
         <v>45849</v>
       </c>
       <c r="B7">
-        <v>3667.835876812373</v>
+        <v>3667.972836866676</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -450,7 +450,7 @@
         <v>45856</v>
       </c>
       <c r="B8">
-        <v>3564.663992775738</v>
+        <v>3564.849310062085</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -458,7 +458,7 @@
         <v>45863</v>
       </c>
       <c r="B9">
-        <v>3510.075803369121</v>
+        <v>3510.290251766372</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -466,7 +466,7 @@
         <v>45870</v>
       </c>
       <c r="B10">
-        <v>3482.419886592918</v>
+        <v>3482.647804516644</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -474,7 +474,7 @@
         <v>45877</v>
       </c>
       <c r="B11">
-        <v>3490.894703275292</v>
+        <v>3491.128216288681</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -482,7 +482,7 @@
         <v>45884</v>
       </c>
       <c r="B12">
-        <v>3503.667843954896</v>
+        <v>3503.904141708159</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -490,7 +490,7 @@
         <v>45891</v>
       </c>
       <c r="B13">
-        <v>3518.194904563886</v>
+        <v>3518.429440369943</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -498,7 +498,7 @@
         <v>45898</v>
       </c>
       <c r="B14">
-        <v>3530.720547869654</v>
+        <v>3530.951321583989</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -506,7 +506,7 @@
         <v>45905</v>
       </c>
       <c r="B15">
-        <v>3547.08173207073</v>
+        <v>3547.251195011056</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -514,7 +514,7 @@
         <v>45912</v>
       </c>
       <c r="B16">
-        <v>3452.920349419472</v>
+        <v>3452.876211321478</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -522,7 +522,7 @@
         <v>45919</v>
       </c>
       <c r="B17">
-        <v>3450.48860837473</v>
+        <v>3450.449667900972</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -530,7 +530,7 @@
         <v>45926</v>
       </c>
       <c r="B18">
-        <v>3450.553465760519</v>
+        <v>3450.517433444434</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -538,7 +538,7 @@
         <v>45933</v>
       </c>
       <c r="B19">
-        <v>3533.676174186763</v>
+        <v>3533.486149491078</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -546,7 +546,7 @@
         <v>45940</v>
       </c>
       <c r="B20">
-        <v>3631.485024578485</v>
+        <v>3631.120467321771</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -554,7 +554,7 @@
         <v>45947</v>
       </c>
       <c r="B21">
-        <v>3784.297849316604</v>
+        <v>3783.746095730099</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -562,7 +562,7 @@
         <v>45954</v>
       </c>
       <c r="B22">
-        <v>3855.143749958011</v>
+        <v>3854.649692581869</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -570,7 +570,7 @@
         <v>45961</v>
       </c>
       <c r="B23">
-        <v>3901.718902037997</v>
+        <v>3901.25844964637</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -578,7 +578,7 @@
         <v>45968</v>
       </c>
       <c r="B24">
-        <v>3886.793921985181</v>
+        <v>3886.395807925497</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -586,7 +586,7 @@
         <v>45975</v>
       </c>
       <c r="B25">
-        <v>3888.069667674026</v>
+        <v>3887.903931403125</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -594,7 +594,7 @@
         <v>45982</v>
       </c>
       <c r="B26">
-        <v>3994.000394012118</v>
+        <v>3993.94699201461</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -602,7 +602,7 @@
         <v>45989</v>
       </c>
       <c r="B27">
-        <v>4069.197559088707</v>
+        <v>4069.030657194818</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -610,7 +610,7 @@
         <v>45996</v>
       </c>
       <c r="B28">
-        <v>4109.452343819584</v>
+        <v>4109.246301759695</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -618,7 +618,7 @@
         <v>46003</v>
       </c>
       <c r="B29">
-        <v>4206.534655811693</v>
+        <v>4206.511947210602</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -626,7 +626,7 @@
         <v>46010</v>
       </c>
       <c r="B30">
-        <v>4200.073954598156</v>
+        <v>4199.986099374069</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -634,7 +634,7 @@
         <v>46017</v>
       </c>
       <c r="B31">
-        <v>4225.466753626659</v>
+        <v>4225.226146862396</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -642,7 +642,7 @@
         <v>46024</v>
       </c>
       <c r="B32">
-        <v>4246.288891803099</v>
+        <v>4246.046279180371</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -650,7 +650,7 @@
         <v>46031</v>
       </c>
       <c r="B33">
-        <v>4311.405031005826</v>
+        <v>4311.065253460471</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -658,7 +658,7 @@
         <v>46038</v>
       </c>
       <c r="B34">
-        <v>4404.268154823305</v>
+        <v>4403.839968641556</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -666,7 +666,7 @@
         <v>46045</v>
       </c>
       <c r="B35">
-        <v>4440.509294306898</v>
+        <v>4440.045123053596</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -674,7 +674,7 @@
         <v>46052</v>
       </c>
       <c r="B36">
-        <v>4542.939872300952</v>
+        <v>4542.321038252454</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -682,7 +682,7 @@
         <v>46059</v>
       </c>
       <c r="B37">
-        <v>4679.095809739145</v>
+        <v>4678.34397354108</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -690,7 +690,7 @@
         <v>46066</v>
       </c>
       <c r="B38">
-        <v>4761.931475846234</v>
+        <v>4760.971415217023</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -698,7 +698,7 @@
         <v>46073</v>
       </c>
       <c r="B39">
-        <v>4896.185187477384</v>
+        <v>4895.618126861877</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -706,7 +706,7 @@
         <v>46080</v>
       </c>
       <c r="B40">
-        <v>4937.602854811126</v>
+        <v>4936.979667395119</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -714,7 +714,7 @@
         <v>46087</v>
       </c>
       <c r="B41">
-        <v>5045.031533517174</v>
+        <v>5044.219340366797</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -722,7 +722,7 @@
         <v>46094</v>
       </c>
       <c r="B42">
-        <v>5211.320115922223</v>
+        <v>5210.86311373137</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>46101</v>
       </c>
       <c r="B43">
-        <v>5251.691181393694</v>
+        <v>5251.627562272261</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>46108</v>
       </c>
       <c r="B44">
-        <v>5290.060063959791</v>
+        <v>5290.571083502862</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>46115</v>
       </c>
       <c r="B45">
-        <v>5365.066892648538</v>
+        <v>5366.000602941294</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>46122</v>
       </c>
       <c r="B46">
-        <v>5440.618927623547</v>
+        <v>5441.827634612493</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>46129</v>
       </c>
       <c r="B47">
-        <v>5570.335885067165</v>
+        <v>5571.657786025162</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>46136</v>
       </c>
       <c r="B48">
-        <v>5508.705461702195</v>
+        <v>5510.383885333955</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>46143</v>
       </c>
       <c r="B49">
-        <v>5332.072155539029</v>
+        <v>5334.159881356035</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>46150</v>
       </c>
       <c r="B50">
-        <v>5216.022771011394</v>
+        <v>5217.990403315231</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>46157</v>
       </c>
       <c r="B51">
-        <v>5081.44854295189</v>
+        <v>5083.565482225372</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>46164</v>
       </c>
       <c r="B52">
-        <v>4968.385166307925</v>
+        <v>4970.299651217358</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>46171</v>
       </c>
       <c r="B53">
-        <v>4866.035300036416</v>
+        <v>4867.864287304952</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>46178</v>
       </c>
       <c r="B54">
-        <v>4816.519628627933</v>
+        <v>4818.587689179677</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>46185</v>
       </c>
       <c r="B55">
-        <v>4689.745314864384</v>
+        <v>4691.408752048259</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>46192</v>
       </c>
       <c r="B56">
-        <v>4570.516961501604</v>
+        <v>4571.68174415049</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>46199</v>
       </c>
       <c r="B57">
-        <v>4476.200961060627</v>
+        <v>4476.982752502814</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>46206</v>
       </c>
       <c r="B58">
-        <v>4471.293376556908</v>
+        <v>4472.090750051936</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>46213</v>
       </c>
       <c r="B59">
-        <v>4390.612457394501</v>
+        <v>4391.603323266072</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>46220</v>
       </c>
       <c r="B60">
-        <v>4231.324254255935</v>
+        <v>4232.637161751661</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>46227</v>
       </c>
       <c r="B61">
-        <v>4149.34136059583</v>
+        <v>4139.589212497823</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>46234</v>
       </c>
       <c r="B62">
-        <v>4093.480293677791</v>
+        <v>4091.269448107414</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>46241</v>
       </c>
       <c r="B63">
-        <v>4076.842863217794</v>
+        <v>4082.043341737832</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46248</v>
       </c>
       <c r="B64">
-        <v>4047.688231743287</v>
+        <v>4061.456590941028</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46255</v>
       </c>
       <c r="B65">
-        <v>4021.784275755562</v>
+        <v>4052.298084452661</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46262</v>
       </c>
       <c r="B66">
-        <v>4010.714414386382</v>
+        <v>4069.909117138367</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46269</v>
       </c>
       <c r="B67">
-        <v>3998.163863607043</v>
+        <v>4060.581411576876</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46276</v>
       </c>
       <c r="B68">
-        <v>4005.498062276537</v>
+        <v>4061.703886076686</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46283</v>
       </c>
       <c r="B69">
-        <v>3987.585023445543</v>
+        <v>4028.355692821757</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46290</v>
       </c>
       <c r="B70">
-        <v>3995.984836625777</v>
+        <v>4025.004857537794</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46297</v>
       </c>
       <c r="B71">
-        <v>4035.762133117538</v>
+        <v>4050.271103279838</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46304</v>
       </c>
       <c r="B72">
-        <v>4081.062830582162</v>
+        <v>4105.227769421203</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46311</v>
       </c>
       <c r="B73">
-        <v>4106.811339715347</v>
+        <v>4141.746513629273</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46318</v>
       </c>
       <c r="B74">
-        <v>4251.357058139808</v>
+        <v>4253.526413741145</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46325</v>
       </c>
       <c r="B75">
-        <v>4318.916325476606</v>
+        <v>4352.301339499591</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46332</v>
       </c>
       <c r="B76">
-        <v>4508.573293953701</v>
+        <v>4491.777463132674</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/XAUUSD_forecast.xlsx
+++ b/public/data/files/XAUUSD_forecast.xlsx
@@ -383,7 +383,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B76"/>
+  <dimension ref="A1:B77"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" style="1" customWidth="1"/>
@@ -442,7 +442,7 @@
         <v>45849</v>
       </c>
       <c r="B7">
-        <v>3667.972836866676</v>
+        <v>3668.038382646262</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -450,7 +450,7 @@
         <v>45856</v>
       </c>
       <c r="B8">
-        <v>3564.849310062085</v>
+        <v>3564.938017589735</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -458,7 +458,7 @@
         <v>45863</v>
       </c>
       <c r="B9">
-        <v>3510.290251766372</v>
+        <v>3510.392924184646</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -466,7 +466,7 @@
         <v>45870</v>
       </c>
       <c r="B10">
-        <v>3482.647804516644</v>
+        <v>3482.756953550791</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -474,7 +474,7 @@
         <v>45877</v>
       </c>
       <c r="B11">
-        <v>3491.128216288681</v>
+        <v>3491.240043731661</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -482,7 +482,7 @@
         <v>45884</v>
       </c>
       <c r="B12">
-        <v>3503.904141708159</v>
+        <v>3504.017301616337</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -490,7 +490,7 @@
         <v>45891</v>
       </c>
       <c r="B13">
-        <v>3518.429440369943</v>
+        <v>3518.541755911617</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -498,7 +498,7 @@
         <v>45898</v>
       </c>
       <c r="B14">
-        <v>3530.951321583989</v>
+        <v>3531.061835491233</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -506,7 +506,7 @@
         <v>45905</v>
       </c>
       <c r="B15">
-        <v>3547.251195011056</v>
+        <v>3547.332421116272</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -514,7 +514,7 @@
         <v>45912</v>
       </c>
       <c r="B16">
-        <v>3452.876211321478</v>
+        <v>3452.855110787783</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -522,7 +522,7 @@
         <v>45919</v>
       </c>
       <c r="B17">
-        <v>3450.449667900972</v>
+        <v>3450.43105515577</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -530,7 +530,7 @@
         <v>45926</v>
       </c>
       <c r="B18">
-        <v>3450.517433444434</v>
+        <v>3450.500212847408</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -538,7 +538,7 @@
         <v>45933</v>
       </c>
       <c r="B19">
-        <v>3533.486149491078</v>
+        <v>3533.395278486937</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -546,7 +546,7 @@
         <v>45940</v>
       </c>
       <c r="B20">
-        <v>3631.120467321771</v>
+        <v>3630.946089418694</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -554,7 +554,7 @@
         <v>45947</v>
       </c>
       <c r="B21">
-        <v>3783.746095730099</v>
+        <v>3783.482075527183</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -562,7 +562,7 @@
         <v>45954</v>
       </c>
       <c r="B22">
-        <v>3854.649692581869</v>
+        <v>3854.413239901654</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -570,7 +570,7 @@
         <v>45961</v>
       </c>
       <c r="B23">
-        <v>3901.25844964637</v>
+        <v>3901.037881879398</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -578,7 +578,7 @@
         <v>45968</v>
       </c>
       <c r="B24">
-        <v>3886.395807925497</v>
+        <v>3886.205005135151</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -586,7 +586,7 @@
         <v>45975</v>
       </c>
       <c r="B25">
-        <v>3887.903931403125</v>
+        <v>3887.824390518468</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -594,7 +594,7 @@
         <v>45982</v>
       </c>
       <c r="B26">
-        <v>3993.94699201461</v>
+        <v>3993.921298083576</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -602,7 +602,7 @@
         <v>45989</v>
       </c>
       <c r="B27">
-        <v>4069.030657194818</v>
+        <v>4068.950690296018</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -610,7 +610,7 @@
         <v>45996</v>
       </c>
       <c r="B28">
-        <v>4109.246301759695</v>
+        <v>4109.147590302207</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -618,7 +618,7 @@
         <v>46003</v>
       </c>
       <c r="B29">
-        <v>4206.511947210602</v>
+        <v>4206.501181033364</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -626,7 +626,7 @@
         <v>46010</v>
       </c>
       <c r="B30">
-        <v>4199.986099374069</v>
+        <v>4199.944219739283</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -634,7 +634,7 @@
         <v>46017</v>
       </c>
       <c r="B31">
-        <v>4225.226146862396</v>
+        <v>4225.111263360543</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -642,7 +642,7 @@
         <v>46024</v>
       </c>
       <c r="B32">
-        <v>4246.046279180371</v>
+        <v>4245.930365014608</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -650,7 +650,7 @@
         <v>46031</v>
       </c>
       <c r="B33">
-        <v>4311.065253460471</v>
+        <v>4310.902837902406</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -658,7 +658,7 @@
         <v>46038</v>
       </c>
       <c r="B34">
-        <v>4403.839968641556</v>
+        <v>4403.63518850908</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -666,7 +666,7 @@
         <v>46045</v>
       </c>
       <c r="B35">
-        <v>4440.045123053596</v>
+        <v>4439.82302138553</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -674,7 +674,7 @@
         <v>46052</v>
       </c>
       <c r="B36">
-        <v>4542.321038252454</v>
+        <v>4542.024799093551</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -682,7 +682,7 @@
         <v>46059</v>
       </c>
       <c r="B37">
-        <v>4678.34397354108</v>
+        <v>4677.984097421525</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -690,7 +690,7 @@
         <v>46066</v>
       </c>
       <c r="B38">
-        <v>4760.971415217023</v>
+        <v>4760.511179501942</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -698,7 +698,7 @@
         <v>46073</v>
       </c>
       <c r="B39">
-        <v>4895.618126861877</v>
+        <v>4895.346634733738</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -706,7 +706,7 @@
         <v>46080</v>
       </c>
       <c r="B40">
-        <v>4936.979667395119</v>
+        <v>4936.681293310411</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -714,7 +714,7 @@
         <v>46087</v>
       </c>
       <c r="B41">
-        <v>5044.219340366797</v>
+        <v>5043.830304200666</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -722,7 +722,7 @@
         <v>46094</v>
       </c>
       <c r="B42">
-        <v>5210.86311373137</v>
+        <v>5210.643839220348</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>46101</v>
       </c>
       <c r="B43">
-        <v>5251.627562272261</v>
+        <v>5251.596015694528</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>46108</v>
       </c>
       <c r="B44">
-        <v>5290.571083502862</v>
+        <v>5290.81433050451</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>46115</v>
       </c>
       <c r="B45">
-        <v>5366.000602941294</v>
+        <v>5366.446564202593</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>46122</v>
       </c>
       <c r="B46">
-        <v>5441.827634612493</v>
+        <v>5442.405105243783</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>46129</v>
       </c>
       <c r="B47">
-        <v>5571.657786025162</v>
+        <v>5572.289512135258</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>46136</v>
       </c>
       <c r="B48">
-        <v>5510.383885333955</v>
+        <v>5511.186864680465</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>46143</v>
       </c>
       <c r="B49">
-        <v>5334.159881356035</v>
+        <v>5335.1592167327</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>46150</v>
       </c>
       <c r="B50">
-        <v>5217.990403315231</v>
+        <v>5218.932641421969</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>46157</v>
       </c>
       <c r="B51">
-        <v>5083.565482225372</v>
+        <v>5084.579829477825</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>46164</v>
       </c>
       <c r="B52">
-        <v>4970.299651217358</v>
+        <v>4971.21737461042</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>46171</v>
       </c>
       <c r="B53">
-        <v>4867.864287304952</v>
+        <v>4868.741564749758</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>46178</v>
       </c>
       <c r="B54">
-        <v>4818.587689179677</v>
+        <v>4819.579689719004</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>46185</v>
       </c>
       <c r="B55">
-        <v>4691.408752048259</v>
+        <v>4692.206504142772</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>46192</v>
       </c>
       <c r="B56">
-        <v>4571.68174415049</v>
+        <v>4572.239928132006</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>46199</v>
       </c>
       <c r="B57">
-        <v>4476.982752502814</v>
+        <v>4477.356677603277</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>46206</v>
       </c>
       <c r="B58">
-        <v>4472.090750051936</v>
+        <v>4472.472146643729</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>46213</v>
       </c>
       <c r="B59">
-        <v>4391.603323266072</v>
+        <v>4392.077680063521</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>46220</v>
       </c>
       <c r="B60">
-        <v>4232.637161751661</v>
+        <v>4233.266663875899</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>46227</v>
       </c>
       <c r="B61">
-        <v>4139.589212497823</v>
+        <v>4140.109889522299</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>46234</v>
       </c>
       <c r="B62">
-        <v>4091.269448107414</v>
+        <v>4091.594715986515</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>46241</v>
       </c>
       <c r="B63">
-        <v>4082.043341737832</v>
+        <v>4082.012618244842</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46248</v>
       </c>
       <c r="B64">
-        <v>4061.456590941028</v>
+        <v>4075.427316579784</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46255</v>
       </c>
       <c r="B65">
-        <v>4052.298084452661</v>
+        <v>4070.189781124694</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46262</v>
       </c>
       <c r="B66">
-        <v>4069.909117138367</v>
+        <v>4090.295040146546</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46269</v>
       </c>
       <c r="B67">
-        <v>4060.581411576876</v>
+        <v>4088.574060894955</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46276</v>
       </c>
       <c r="B68">
-        <v>4061.703886076686</v>
+        <v>4091.208607581934</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46283</v>
       </c>
       <c r="B69">
-        <v>4028.355692821757</v>
+        <v>4060.465353170897</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46290</v>
       </c>
       <c r="B70">
-        <v>4025.004857537794</v>
+        <v>4060.351073139472</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46297</v>
       </c>
       <c r="B71">
-        <v>4050.271103279838</v>
+        <v>4087.87086818875</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46304</v>
       </c>
       <c r="B72">
-        <v>4105.227769421203</v>
+        <v>4145.008323008199</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46311</v>
       </c>
       <c r="B73">
-        <v>4141.746513629273</v>
+        <v>4190.493115231661</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46318</v>
       </c>
       <c r="B74">
-        <v>4253.526413741145</v>
+        <v>4312.75293747676</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46325</v>
       </c>
       <c r="B75">
-        <v>4352.301339499591</v>
+        <v>4431.806378149402</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,15 @@
         <v>46332</v>
       </c>
       <c r="B76">
-        <v>4491.777463132674</v>
+        <v>4595.357949793498</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2">
+      <c r="A77" s="3">
+        <v>46339</v>
+      </c>
+      <c r="B77">
+        <v>4804.630449793497</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/XAUUSD_forecast.xlsx
+++ b/public/data/files/XAUUSD_forecast.xlsx
@@ -442,7 +442,7 @@
         <v>45849</v>
       </c>
       <c r="B7">
-        <v>3668.038382646262</v>
+        <v>3667.972836866676</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -450,7 +450,7 @@
         <v>45856</v>
       </c>
       <c r="B8">
-        <v>3564.938017589735</v>
+        <v>3564.849310062085</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -458,7 +458,7 @@
         <v>45863</v>
       </c>
       <c r="B9">
-        <v>3510.392924184646</v>
+        <v>3510.290251766372</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -466,7 +466,7 @@
         <v>45870</v>
       </c>
       <c r="B10">
-        <v>3482.756953550791</v>
+        <v>3482.647804516644</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -474,7 +474,7 @@
         <v>45877</v>
       </c>
       <c r="B11">
-        <v>3491.240043731661</v>
+        <v>3491.128216288681</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -482,7 +482,7 @@
         <v>45884</v>
       </c>
       <c r="B12">
-        <v>3504.017301616337</v>
+        <v>3503.904141708159</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -490,7 +490,7 @@
         <v>45891</v>
       </c>
       <c r="B13">
-        <v>3518.541755911617</v>
+        <v>3518.429440369943</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -498,7 +498,7 @@
         <v>45898</v>
       </c>
       <c r="B14">
-        <v>3531.061835491233</v>
+        <v>3530.951321583989</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -506,7 +506,7 @@
         <v>45905</v>
       </c>
       <c r="B15">
-        <v>3547.332421116272</v>
+        <v>3547.251195011056</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -514,7 +514,7 @@
         <v>45912</v>
       </c>
       <c r="B16">
-        <v>3452.855110787783</v>
+        <v>3452.876211321478</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -522,7 +522,7 @@
         <v>45919</v>
       </c>
       <c r="B17">
-        <v>3450.43105515577</v>
+        <v>3450.449667900972</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -530,7 +530,7 @@
         <v>45926</v>
       </c>
       <c r="B18">
-        <v>3450.500212847408</v>
+        <v>3450.517433444434</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -538,7 +538,7 @@
         <v>45933</v>
       </c>
       <c r="B19">
-        <v>3533.395278486937</v>
+        <v>3533.486149491078</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -546,7 +546,7 @@
         <v>45940</v>
       </c>
       <c r="B20">
-        <v>3630.946089418694</v>
+        <v>3631.120467321771</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -554,7 +554,7 @@
         <v>45947</v>
       </c>
       <c r="B21">
-        <v>3783.482075527183</v>
+        <v>3783.746095730099</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -562,7 +562,7 @@
         <v>45954</v>
       </c>
       <c r="B22">
-        <v>3854.413239901654</v>
+        <v>3854.649692581869</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -570,7 +570,7 @@
         <v>45961</v>
       </c>
       <c r="B23">
-        <v>3901.037881879398</v>
+        <v>3901.25844964637</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -578,7 +578,7 @@
         <v>45968</v>
       </c>
       <c r="B24">
-        <v>3886.205005135151</v>
+        <v>3886.395807925497</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -586,7 +586,7 @@
         <v>45975</v>
       </c>
       <c r="B25">
-        <v>3887.824390518468</v>
+        <v>3887.903931403125</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -594,7 +594,7 @@
         <v>45982</v>
       </c>
       <c r="B26">
-        <v>3993.921298083576</v>
+        <v>3993.94699201461</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -602,7 +602,7 @@
         <v>45989</v>
       </c>
       <c r="B27">
-        <v>4068.950690296018</v>
+        <v>4069.030657194818</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -610,7 +610,7 @@
         <v>45996</v>
       </c>
       <c r="B28">
-        <v>4109.147590302207</v>
+        <v>4109.246301759695</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -618,7 +618,7 @@
         <v>46003</v>
       </c>
       <c r="B29">
-        <v>4206.501181033364</v>
+        <v>4206.511947210602</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -626,7 +626,7 @@
         <v>46010</v>
       </c>
       <c r="B30">
-        <v>4199.944219739283</v>
+        <v>4199.986099374069</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -634,7 +634,7 @@
         <v>46017</v>
       </c>
       <c r="B31">
-        <v>4225.111263360543</v>
+        <v>4225.226146862396</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -642,7 +642,7 @@
         <v>46024</v>
       </c>
       <c r="B32">
-        <v>4245.930365014608</v>
+        <v>4246.046279180371</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -650,7 +650,7 @@
         <v>46031</v>
       </c>
       <c r="B33">
-        <v>4310.902837902406</v>
+        <v>4311.065253460471</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -658,7 +658,7 @@
         <v>46038</v>
       </c>
       <c r="B34">
-        <v>4403.63518850908</v>
+        <v>4403.839968641556</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -666,7 +666,7 @@
         <v>46045</v>
       </c>
       <c r="B35">
-        <v>4439.82302138553</v>
+        <v>4440.045123053596</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -674,7 +674,7 @@
         <v>46052</v>
       </c>
       <c r="B36">
-        <v>4542.024799093551</v>
+        <v>4542.321038252454</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -682,7 +682,7 @@
         <v>46059</v>
       </c>
       <c r="B37">
-        <v>4677.984097421525</v>
+        <v>4678.34397354108</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -690,7 +690,7 @@
         <v>46066</v>
       </c>
       <c r="B38">
-        <v>4760.511179501942</v>
+        <v>4760.971415217023</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -698,7 +698,7 @@
         <v>46073</v>
       </c>
       <c r="B39">
-        <v>4895.346634733738</v>
+        <v>4895.618126861877</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -706,7 +706,7 @@
         <v>46080</v>
       </c>
       <c r="B40">
-        <v>4936.681293310411</v>
+        <v>4936.979667395119</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -714,7 +714,7 @@
         <v>46087</v>
       </c>
       <c r="B41">
-        <v>5043.830304200666</v>
+        <v>5044.219340366797</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -722,7 +722,7 @@
         <v>46094</v>
       </c>
       <c r="B42">
-        <v>5210.643839220348</v>
+        <v>5210.86311373137</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>46101</v>
       </c>
       <c r="B43">
-        <v>5251.596015694528</v>
+        <v>5251.627562272261</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>46108</v>
       </c>
       <c r="B44">
-        <v>5290.81433050451</v>
+        <v>5290.571083502862</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>46115</v>
       </c>
       <c r="B45">
-        <v>5366.446564202593</v>
+        <v>5366.000602941294</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>46122</v>
       </c>
       <c r="B46">
-        <v>5442.405105243783</v>
+        <v>5441.827634612493</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>46129</v>
       </c>
       <c r="B47">
-        <v>5572.289512135258</v>
+        <v>5571.657786025162</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>46136</v>
       </c>
       <c r="B48">
-        <v>5511.186864680465</v>
+        <v>5510.383885333955</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>46143</v>
       </c>
       <c r="B49">
-        <v>5335.1592167327</v>
+        <v>5334.159881356035</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>46150</v>
       </c>
       <c r="B50">
-        <v>5218.932641421969</v>
+        <v>5217.990403315231</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>46157</v>
       </c>
       <c r="B51">
-        <v>5084.579829477825</v>
+        <v>5083.565482225372</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>46164</v>
       </c>
       <c r="B52">
-        <v>4971.21737461042</v>
+        <v>4970.299651217358</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>46171</v>
       </c>
       <c r="B53">
-        <v>4868.741564749758</v>
+        <v>4867.864287304952</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>46178</v>
       </c>
       <c r="B54">
-        <v>4819.579689719004</v>
+        <v>4818.587689179677</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>46185</v>
       </c>
       <c r="B55">
-        <v>4692.206504142772</v>
+        <v>4691.408752048259</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>46192</v>
       </c>
       <c r="B56">
-        <v>4572.239928132006</v>
+        <v>4571.68174415049</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>46199</v>
       </c>
       <c r="B57">
-        <v>4477.356677603277</v>
+        <v>4476.982752502814</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>46206</v>
       </c>
       <c r="B58">
-        <v>4472.472146643729</v>
+        <v>4472.090750051936</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>46213</v>
       </c>
       <c r="B59">
-        <v>4392.077680063521</v>
+        <v>4391.603323266072</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>46220</v>
       </c>
       <c r="B60">
-        <v>4233.266663875899</v>
+        <v>4232.637161751661</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>46227</v>
       </c>
       <c r="B61">
-        <v>4140.109889522299</v>
+        <v>4150.437652631406</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>46234</v>
       </c>
       <c r="B62">
-        <v>4091.594715986515</v>
+        <v>4094.161895426432</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>46241</v>
       </c>
       <c r="B63">
-        <v>4082.012618244842</v>
+        <v>4076.874258785379</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46248</v>
       </c>
       <c r="B64">
-        <v>4075.427316579784</v>
+        <v>4077.408775952844</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46255</v>
       </c>
       <c r="B65">
-        <v>4070.189781124694</v>
+        <v>4060.720933538299</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46262</v>
       </c>
       <c r="B66">
-        <v>4090.295040146546</v>
+        <v>4055.721021156932</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46269</v>
       </c>
       <c r="B67">
-        <v>4088.574060894955</v>
+        <v>4053.767842873918</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46276</v>
       </c>
       <c r="B68">
-        <v>4091.208607581934</v>
+        <v>4061.410826576358</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46283</v>
       </c>
       <c r="B69">
-        <v>4060.465353170897</v>
+        <v>4046.882026982721</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46290</v>
       </c>
       <c r="B70">
-        <v>4060.351073139472</v>
+        <v>4061.533509928147</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46297</v>
       </c>
       <c r="B71">
-        <v>4087.87086818875</v>
+        <v>4105.78453836097</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46304</v>
       </c>
       <c r="B72">
-        <v>4145.008323008199</v>
+        <v>4156.662684027939</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46311</v>
       </c>
       <c r="B73">
-        <v>4190.493115231661</v>
+        <v>4198.342303117128</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46318</v>
       </c>
       <c r="B74">
-        <v>4312.75293747676</v>
+        <v>4357.330256119134</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46325</v>
       </c>
       <c r="B75">
-        <v>4431.806378149402</v>
+        <v>4450.833439172747</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46332</v>
       </c>
       <c r="B76">
-        <v>4595.357949793498</v>
+        <v>4683.809037336821</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46339</v>
       </c>
       <c r="B77">
-        <v>4804.630449793497</v>
+        <v>4894.31153733682</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/XAUUSD_forecast.xlsx
+++ b/public/data/files/XAUUSD_forecast.xlsx
@@ -442,7 +442,7 @@
         <v>45849</v>
       </c>
       <c r="B7">
-        <v>3667.972836866676</v>
+        <v>3668.102082437388</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -450,7 +450,7 @@
         <v>45856</v>
       </c>
       <c r="B8">
-        <v>3564.849310062085</v>
+        <v>3565.024238680289</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -458,7 +458,7 @@
         <v>45863</v>
       </c>
       <c r="B9">
-        <v>3510.290251766372</v>
+        <v>3510.492731396091</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -466,7 +466,7 @@
         <v>45870</v>
       </c>
       <c r="B10">
-        <v>3482.647804516644</v>
+        <v>3482.863073832244</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -474,7 +474,7 @@
         <v>45877</v>
       </c>
       <c r="B11">
-        <v>3491.128216288681</v>
+        <v>3491.348767442479</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -482,7 +482,7 @@
         <v>45884</v>
       </c>
       <c r="B12">
-        <v>3503.904141708159</v>
+        <v>3504.127320113713</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -490,7 +490,7 @@
         <v>45891</v>
       </c>
       <c r="B13">
-        <v>3518.429440369943</v>
+        <v>3518.650953115704</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -498,7 +498,7 @@
         <v>45898</v>
       </c>
       <c r="B14">
-        <v>3530.951321583989</v>
+        <v>3531.169281065133</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -506,7 +506,7 @@
         <v>45905</v>
       </c>
       <c r="B15">
-        <v>3547.251195011056</v>
+        <v>3547.411437263577</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -514,7 +514,7 @@
         <v>45912</v>
       </c>
       <c r="B16">
-        <v>3452.876211321478</v>
+        <v>3452.834618724599</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -522,7 +522,7 @@
         <v>45919</v>
       </c>
       <c r="B17">
-        <v>3450.449667900972</v>
+        <v>3450.412981021039</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -530,7 +530,7 @@
         <v>45926</v>
       </c>
       <c r="B18">
-        <v>3450.517433444434</v>
+        <v>3450.483491884875</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -538,7 +538,7 @@
         <v>45933</v>
       </c>
       <c r="B19">
-        <v>3533.486149491078</v>
+        <v>3533.307010336763</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -546,7 +546,7 @@
         <v>45940</v>
       </c>
       <c r="B20">
-        <v>3631.120467321771</v>
+        <v>3630.776678855004</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -554,7 +554,7 @@
         <v>45947</v>
       </c>
       <c r="B21">
-        <v>3783.746095730099</v>
+        <v>3783.225513505959</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -562,7 +562,7 @@
         <v>45954</v>
       </c>
       <c r="B22">
-        <v>3854.649692581869</v>
+        <v>3854.183441295579</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -570,7 +570,7 @@
         <v>45961</v>
       </c>
       <c r="B23">
-        <v>3901.25844964637</v>
+        <v>3900.823398382254</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -578,7 +578,7 @@
         <v>45968</v>
       </c>
       <c r="B24">
-        <v>3886.395807925497</v>
+        <v>3886.019405718112</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -586,7 +586,7 @@
         <v>45975</v>
       </c>
       <c r="B25">
-        <v>3887.903931403125</v>
+        <v>3887.746951179697</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -594,7 +594,7 @@
         <v>45982</v>
       </c>
       <c r="B26">
-        <v>3993.94699201461</v>
+        <v>3993.896242740054</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -602,7 +602,7 @@
         <v>45989</v>
       </c>
       <c r="B27">
-        <v>4069.030657194818</v>
+        <v>4068.872918610771</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -610,7 +610,7 @@
         <v>45996</v>
       </c>
       <c r="B28">
-        <v>4109.246301759695</v>
+        <v>4109.051593947634</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -618,7 +618,7 @@
         <v>46003</v>
       </c>
       <c r="B29">
-        <v>4206.511947210602</v>
+        <v>4206.490781109222</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -626,7 +626,7 @@
         <v>46010</v>
       </c>
       <c r="B30">
-        <v>4199.986099374069</v>
+        <v>4199.903622537106</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -634,7 +634,7 @@
         <v>46017</v>
       </c>
       <c r="B31">
-        <v>4225.226146862396</v>
+        <v>4224.999780203651</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -642,7 +642,7 @@
         <v>46024</v>
       </c>
       <c r="B32">
-        <v>4246.046279180371</v>
+        <v>4245.817836598438</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -650,7 +650,7 @@
         <v>46031</v>
       </c>
       <c r="B33">
-        <v>4311.065253460471</v>
+        <v>4310.745117679066</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -658,7 +658,7 @@
         <v>46038</v>
       </c>
       <c r="B34">
-        <v>4403.839968641556</v>
+        <v>4403.436263492695</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -666,7 +666,7 @@
         <v>46045</v>
       </c>
       <c r="B35">
-        <v>4440.045123053596</v>
+        <v>4439.607200457793</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -674,7 +674,7 @@
         <v>46052</v>
       </c>
       <c r="B36">
-        <v>4542.321038252454</v>
+        <v>4541.73685447891</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -682,7 +682,7 @@
         <v>46059</v>
       </c>
       <c r="B37">
-        <v>4678.34397354108</v>
+        <v>4677.634317627054</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -690,7 +690,7 @@
         <v>46066</v>
       </c>
       <c r="B38">
-        <v>4760.971415217023</v>
+        <v>4760.063426457208</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -698,7 +698,7 @@
         <v>46073</v>
       </c>
       <c r="B39">
-        <v>4895.618126861877</v>
+        <v>4895.082721429748</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -706,7 +706,7 @@
         <v>46080</v>
       </c>
       <c r="B40">
-        <v>4936.979667395119</v>
+        <v>4936.391242202624</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -714,7 +714,7 @@
         <v>46087</v>
       </c>
       <c r="B41">
-        <v>5044.219340366797</v>
+        <v>5043.452015971327</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -722,7 +722,7 @@
         <v>46094</v>
       </c>
       <c r="B42">
-        <v>5210.86311373137</v>
+        <v>5210.430391115949</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>46101</v>
       </c>
       <c r="B43">
-        <v>5251.627562272261</v>
+        <v>5251.564675654576</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>46108</v>
       </c>
       <c r="B44">
-        <v>5290.571083502862</v>
+        <v>5291.049910298761</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>46115</v>
       </c>
       <c r="B45">
-        <v>5366.000602941294</v>
+        <v>5366.879411663233</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>46122</v>
       </c>
       <c r="B46">
-        <v>5441.827634612493</v>
+        <v>5442.96569659446</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>46129</v>
       </c>
       <c r="B47">
-        <v>5571.657786025162</v>
+        <v>5572.902883021177</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>46136</v>
       </c>
       <c r="B48">
-        <v>5510.383885333955</v>
+        <v>5511.967056156664</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>46143</v>
       </c>
       <c r="B49">
-        <v>5334.159881356035</v>
+        <v>5336.130525764474</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>46150</v>
       </c>
       <c r="B50">
-        <v>5217.990403315231</v>
+        <v>5219.848695003601</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>46157</v>
       </c>
       <c r="B51">
-        <v>5083.565482225372</v>
+        <v>5085.56636705151</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>46164</v>
       </c>
       <c r="B52">
-        <v>4970.299651217358</v>
+        <v>4972.110176893282</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>46171</v>
       </c>
       <c r="B53">
-        <v>4867.864287304952</v>
+        <v>4869.595353108509</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>46178</v>
       </c>
       <c r="B54">
-        <v>4818.587689179677</v>
+        <v>4820.545160736005</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>46185</v>
       </c>
       <c r="B55">
-        <v>4691.408752048259</v>
+        <v>4692.982822891295</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>46192</v>
       </c>
       <c r="B56">
-        <v>4571.68174415049</v>
+        <v>4572.782853139188</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>46199</v>
       </c>
       <c r="B57">
-        <v>4476.982752502814</v>
+        <v>4477.719931893421</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>46206</v>
       </c>
       <c r="B58">
-        <v>4472.090750051936</v>
+        <v>4472.842671241015</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>46213</v>
       </c>
       <c r="B59">
-        <v>4391.603323266072</v>
+        <v>4392.538768641859</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>46220</v>
       </c>
       <c r="B60">
-        <v>4232.637161751661</v>
+        <v>4233.87916074038</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>46227</v>
       </c>
       <c r="B61">
-        <v>4150.437652631406</v>
+        <v>4140.61744384307</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>46234</v>
       </c>
       <c r="B62">
-        <v>4094.161895426432</v>
+        <v>4091.912542014298</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>46241</v>
       </c>
       <c r="B63">
-        <v>4076.874258785379</v>
+        <v>4081.984791282643</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46248</v>
       </c>
       <c r="B64">
-        <v>4077.408775952844</v>
+        <v>4088.559373576924</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46255</v>
       </c>
       <c r="B65">
-        <v>4060.720933538299</v>
+        <v>4086.927548057661</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46262</v>
       </c>
       <c r="B66">
-        <v>4055.721021156932</v>
+        <v>4109.333989350789</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46269</v>
       </c>
       <c r="B67">
-        <v>4053.767842873918</v>
+        <v>4114.602283010254</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46276</v>
       </c>
       <c r="B68">
-        <v>4061.410826576358</v>
+        <v>4118.64836863266</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46283</v>
       </c>
       <c r="B69">
-        <v>4046.882026982721</v>
+        <v>4090.27620266511</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46290</v>
       </c>
       <c r="B70">
-        <v>4061.533509928147</v>
+        <v>4092.964254816561</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46297</v>
       </c>
       <c r="B71">
-        <v>4105.78453836097</v>
+        <v>4122.481892826977</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46304</v>
       </c>
       <c r="B72">
-        <v>4156.662684027939</v>
+        <v>4181.541010879406</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46311</v>
       </c>
       <c r="B73">
-        <v>4198.342303117128</v>
+        <v>4234.968103764611</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46318</v>
       </c>
       <c r="B74">
-        <v>4357.330256119134</v>
+        <v>4365.311333652053</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46325</v>
       </c>
       <c r="B75">
-        <v>4450.833439172747</v>
+        <v>4498.182090092208</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46332</v>
       </c>
       <c r="B76">
-        <v>4683.809037336821</v>
+        <v>4673.460833175056</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46339</v>
       </c>
       <c r="B77">
-        <v>4894.31153733682</v>
+        <v>4883.963333175055</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/XAUUSD_forecast.xlsx
+++ b/public/data/files/XAUUSD_forecast.xlsx
@@ -442,7 +442,7 @@
         <v>45849</v>
       </c>
       <c r="B7">
-        <v>3668.102082437388</v>
+        <v>3668.038382646262</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -450,7 +450,7 @@
         <v>45856</v>
       </c>
       <c r="B8">
-        <v>3565.024238680289</v>
+        <v>3564.938017589735</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -458,7 +458,7 @@
         <v>45863</v>
       </c>
       <c r="B9">
-        <v>3510.492731396091</v>
+        <v>3510.392924184646</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -466,7 +466,7 @@
         <v>45870</v>
       </c>
       <c r="B10">
-        <v>3482.863073832244</v>
+        <v>3482.756953550791</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -474,7 +474,7 @@
         <v>45877</v>
       </c>
       <c r="B11">
-        <v>3491.348767442479</v>
+        <v>3491.240043731661</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -482,7 +482,7 @@
         <v>45884</v>
       </c>
       <c r="B12">
-        <v>3504.127320113713</v>
+        <v>3504.017301616337</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -490,7 +490,7 @@
         <v>45891</v>
       </c>
       <c r="B13">
-        <v>3518.650953115704</v>
+        <v>3518.541755911617</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -498,7 +498,7 @@
         <v>45898</v>
       </c>
       <c r="B14">
-        <v>3531.169281065133</v>
+        <v>3531.061835491233</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -506,7 +506,7 @@
         <v>45905</v>
       </c>
       <c r="B15">
-        <v>3547.411437263577</v>
+        <v>3547.332421116272</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -514,7 +514,7 @@
         <v>45912</v>
       </c>
       <c r="B16">
-        <v>3452.834618724599</v>
+        <v>3452.855110787783</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -522,7 +522,7 @@
         <v>45919</v>
       </c>
       <c r="B17">
-        <v>3450.412981021039</v>
+        <v>3450.43105515577</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -530,7 +530,7 @@
         <v>45926</v>
       </c>
       <c r="B18">
-        <v>3450.483491884875</v>
+        <v>3450.500212847408</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -538,7 +538,7 @@
         <v>45933</v>
       </c>
       <c r="B19">
-        <v>3533.307010336763</v>
+        <v>3533.395278486937</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -546,7 +546,7 @@
         <v>45940</v>
       </c>
       <c r="B20">
-        <v>3630.776678855004</v>
+        <v>3630.946089418694</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -554,7 +554,7 @@
         <v>45947</v>
       </c>
       <c r="B21">
-        <v>3783.225513505959</v>
+        <v>3783.482075527183</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -562,7 +562,7 @@
         <v>45954</v>
       </c>
       <c r="B22">
-        <v>3854.183441295579</v>
+        <v>3854.413239901654</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -570,7 +570,7 @@
         <v>45961</v>
       </c>
       <c r="B23">
-        <v>3900.823398382254</v>
+        <v>3901.037881879398</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -578,7 +578,7 @@
         <v>45968</v>
       </c>
       <c r="B24">
-        <v>3886.019405718112</v>
+        <v>3886.205005135151</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -586,7 +586,7 @@
         <v>45975</v>
       </c>
       <c r="B25">
-        <v>3887.746951179697</v>
+        <v>3887.824390518468</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -594,7 +594,7 @@
         <v>45982</v>
       </c>
       <c r="B26">
-        <v>3993.896242740054</v>
+        <v>3993.921298083576</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -602,7 +602,7 @@
         <v>45989</v>
       </c>
       <c r="B27">
-        <v>4068.872918610771</v>
+        <v>4068.950690296018</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -610,7 +610,7 @@
         <v>45996</v>
       </c>
       <c r="B28">
-        <v>4109.051593947634</v>
+        <v>4109.147590302207</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -618,7 +618,7 @@
         <v>46003</v>
       </c>
       <c r="B29">
-        <v>4206.490781109222</v>
+        <v>4206.501181033364</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -626,7 +626,7 @@
         <v>46010</v>
       </c>
       <c r="B30">
-        <v>4199.903622537106</v>
+        <v>4199.944219739283</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -634,7 +634,7 @@
         <v>46017</v>
       </c>
       <c r="B31">
-        <v>4224.999780203651</v>
+        <v>4225.111263360543</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -642,7 +642,7 @@
         <v>46024</v>
       </c>
       <c r="B32">
-        <v>4245.817836598438</v>
+        <v>4245.930365014608</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -650,7 +650,7 @@
         <v>46031</v>
       </c>
       <c r="B33">
-        <v>4310.745117679066</v>
+        <v>4310.902837902406</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -658,7 +658,7 @@
         <v>46038</v>
       </c>
       <c r="B34">
-        <v>4403.436263492695</v>
+        <v>4403.63518850908</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -666,7 +666,7 @@
         <v>46045</v>
       </c>
       <c r="B35">
-        <v>4439.607200457793</v>
+        <v>4439.82302138553</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -674,7 +674,7 @@
         <v>46052</v>
       </c>
       <c r="B36">
-        <v>4541.73685447891</v>
+        <v>4542.024799093551</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -682,7 +682,7 @@
         <v>46059</v>
       </c>
       <c r="B37">
-        <v>4677.634317627054</v>
+        <v>4677.984097421525</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -690,7 +690,7 @@
         <v>46066</v>
       </c>
       <c r="B38">
-        <v>4760.063426457208</v>
+        <v>4760.511179501942</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -698,7 +698,7 @@
         <v>46073</v>
       </c>
       <c r="B39">
-        <v>4895.082721429748</v>
+        <v>4895.346634733738</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -706,7 +706,7 @@
         <v>46080</v>
       </c>
       <c r="B40">
-        <v>4936.391242202624</v>
+        <v>4936.681293310411</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -714,7 +714,7 @@
         <v>46087</v>
       </c>
       <c r="B41">
-        <v>5043.452015971327</v>
+        <v>5043.830304200666</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -722,7 +722,7 @@
         <v>46094</v>
       </c>
       <c r="B42">
-        <v>5210.430391115949</v>
+        <v>5210.643839220348</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>46101</v>
       </c>
       <c r="B43">
-        <v>5251.564675654576</v>
+        <v>5251.596015694528</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>46108</v>
       </c>
       <c r="B44">
-        <v>5291.049910298761</v>
+        <v>5290.81433050451</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>46115</v>
       </c>
       <c r="B45">
-        <v>5366.879411663233</v>
+        <v>5366.446564202593</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>46122</v>
       </c>
       <c r="B46">
-        <v>5442.96569659446</v>
+        <v>5442.405105243783</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>46129</v>
       </c>
       <c r="B47">
-        <v>5572.902883021177</v>
+        <v>5572.289512135258</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>46136</v>
       </c>
       <c r="B48">
-        <v>5511.967056156664</v>
+        <v>5511.186864680465</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>46143</v>
       </c>
       <c r="B49">
-        <v>5336.130525764474</v>
+        <v>5335.1592167327</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>46150</v>
       </c>
       <c r="B50">
-        <v>5219.848695003601</v>
+        <v>5218.932641421969</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>46157</v>
       </c>
       <c r="B51">
-        <v>5085.56636705151</v>
+        <v>5084.579829477825</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>46164</v>
       </c>
       <c r="B52">
-        <v>4972.110176893282</v>
+        <v>4971.21737461042</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>46171</v>
       </c>
       <c r="B53">
-        <v>4869.595353108509</v>
+        <v>4868.741564749758</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>46178</v>
       </c>
       <c r="B54">
-        <v>4820.545160736005</v>
+        <v>4819.579689719004</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>46185</v>
       </c>
       <c r="B55">
-        <v>4692.982822891295</v>
+        <v>4692.206504142772</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>46192</v>
       </c>
       <c r="B56">
-        <v>4572.782853139188</v>
+        <v>4572.239928132006</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>46199</v>
       </c>
       <c r="B57">
-        <v>4477.719931893421</v>
+        <v>4477.356677603277</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>46206</v>
       </c>
       <c r="B58">
-        <v>4472.842671241015</v>
+        <v>4472.472146643729</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>46213</v>
       </c>
       <c r="B59">
-        <v>4392.538768641859</v>
+        <v>4392.077680063521</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>46220</v>
       </c>
       <c r="B60">
-        <v>4233.87916074038</v>
+        <v>4233.266663875899</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>46227</v>
       </c>
       <c r="B61">
-        <v>4140.61744384307</v>
+        <v>4150.964437376027</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>46234</v>
       </c>
       <c r="B62">
-        <v>4091.912542014298</v>
+        <v>4094.490768145039</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>46241</v>
       </c>
       <c r="B63">
-        <v>4081.984791282643</v>
+        <v>4076.89241041065</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46248</v>
       </c>
       <c r="B64">
-        <v>4088.559373576924</v>
+        <v>4092.224775798727</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46255</v>
       </c>
       <c r="B65">
-        <v>4086.927548057661</v>
+        <v>4080.048980742492</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46262</v>
       </c>
       <c r="B66">
-        <v>4109.333989350789</v>
+        <v>4077.998038298635</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46269</v>
       </c>
       <c r="B67">
-        <v>4114.602283010254</v>
+        <v>4081.175600167395</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46276</v>
       </c>
       <c r="B68">
-        <v>4118.64836863266</v>
+        <v>4089.061500583338</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46283</v>
       </c>
       <c r="B69">
-        <v>4090.27620266511</v>
+        <v>4076.00919754683</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46290</v>
       </c>
       <c r="B70">
-        <v>4092.964254816561</v>
+        <v>4093.362614651977</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46297</v>
       </c>
       <c r="B71">
-        <v>4122.481892826977</v>
+        <v>4139.698692288517</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46304</v>
       </c>
       <c r="B72">
-        <v>4181.541010879406</v>
+        <v>4193.279952984432</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46311</v>
       </c>
       <c r="B73">
-        <v>4234.968103764611</v>
+        <v>4242.366148104965</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46318</v>
       </c>
       <c r="B74">
-        <v>4365.311333652053</v>
+        <v>4407.156781571659</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46325</v>
       </c>
       <c r="B75">
-        <v>4498.182090092208</v>
+        <v>4510.052259793338</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46332</v>
       </c>
       <c r="B76">
-        <v>4673.460833175056</v>
+        <v>4752.641472114906</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46339</v>
       </c>
       <c r="B77">
-        <v>4883.963333175055</v>
+        <v>5188.35771853053</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/XAUUSD_forecast.xlsx
+++ b/public/data/files/XAUUSD_forecast.xlsx
@@ -442,7 +442,7 @@
         <v>45849</v>
       </c>
       <c r="B7">
-        <v>3668.038382646262</v>
+        <v>3668.16401313603</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -450,7 +450,7 @@
         <v>45856</v>
       </c>
       <c r="B8">
-        <v>3564.938017589735</v>
+        <v>3565.108076414051</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -458,7 +458,7 @@
         <v>45863</v>
       </c>
       <c r="B9">
-        <v>3510.392924184646</v>
+        <v>3510.589791653512</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -466,7 +466,7 @@
         <v>45870</v>
       </c>
       <c r="B10">
-        <v>3482.756953550791</v>
+        <v>3482.966289642065</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -474,7 +474,7 @@
         <v>45877</v>
       </c>
       <c r="B11">
-        <v>3491.240043731661</v>
+        <v>3491.454514805754</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -482,7 +482,7 @@
         <v>45884</v>
       </c>
       <c r="B12">
-        <v>3504.017301616337</v>
+        <v>3504.234326160327</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -490,7 +490,7 @@
         <v>45891</v>
       </c>
       <c r="B13">
-        <v>3518.541755911617</v>
+        <v>3518.75716001068</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -498,7 +498,7 @@
         <v>45898</v>
       </c>
       <c r="B14">
-        <v>3531.061835491233</v>
+        <v>3531.273784282169</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -506,7 +506,7 @@
         <v>45905</v>
       </c>
       <c r="B15">
-        <v>3547.332421116272</v>
+        <v>3547.488332298419</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -514,7 +514,7 @@
         <v>45912</v>
       </c>
       <c r="B16">
-        <v>3452.855110787783</v>
+        <v>3452.814709207084</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -522,7 +522,7 @@
         <v>45919</v>
       </c>
       <c r="B17">
-        <v>3450.43105515577</v>
+        <v>3450.395422473059</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -530,7 +530,7 @@
         <v>45926</v>
       </c>
       <c r="B18">
-        <v>3450.500212847408</v>
+        <v>3450.46724914688</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -538,7 +538,7 @@
         <v>45933</v>
       </c>
       <c r="B19">
-        <v>3533.395278486937</v>
+        <v>3533.221234865166</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -546,7 +546,7 @@
         <v>45940</v>
       </c>
       <c r="B20">
-        <v>3630.946089418694</v>
+        <v>3630.612026534242</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -554,7 +554,7 @@
         <v>45947</v>
       </c>
       <c r="B21">
-        <v>3783.482075527183</v>
+        <v>3782.976098276432</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -562,7 +562,7 @@
         <v>45954</v>
       </c>
       <c r="B22">
-        <v>3854.413239901654</v>
+        <v>3853.960019928425</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -570,7 +570,7 @@
         <v>45961</v>
       </c>
       <c r="B23">
-        <v>3901.037881879398</v>
+        <v>3900.614751183634</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -578,7 +578,7 @@
         <v>45968</v>
       </c>
       <c r="B24">
-        <v>3886.205005135151</v>
+        <v>3885.838800123407</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -586,7 +586,7 @@
         <v>45975</v>
       </c>
       <c r="B25">
-        <v>3887.824390518468</v>
+        <v>3887.671531564629</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -594,7 +594,7 @@
         <v>45982</v>
       </c>
       <c r="B26">
-        <v>3993.921298083576</v>
+        <v>3993.871802842934</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -602,7 +602,7 @@
         <v>45989</v>
       </c>
       <c r="B27">
-        <v>4068.950690296018</v>
+        <v>4068.797252994681</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -610,7 +610,7 @@
         <v>45996</v>
       </c>
       <c r="B28">
-        <v>4109.147590302207</v>
+        <v>4108.958202262014</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -618,7 +618,7 @@
         <v>46003</v>
       </c>
       <c r="B29">
-        <v>4206.501181033364</v>
+        <v>4206.480729602273</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -626,7 +626,7 @@
         <v>46010</v>
       </c>
       <c r="B30">
-        <v>4199.944219739283</v>
+        <v>4199.864250217981</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -634,7 +634,7 @@
         <v>46017</v>
       </c>
       <c r="B31">
-        <v>4225.111263360543</v>
+        <v>4224.891549256055</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -642,7 +642,7 @@
         <v>46024</v>
       </c>
       <c r="B32">
-        <v>4245.930365014608</v>
+        <v>4245.708548355971</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -650,7 +650,7 @@
         <v>46031</v>
       </c>
       <c r="B33">
-        <v>4310.902837902406</v>
+        <v>4310.591892885148</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -658,7 +658,7 @@
         <v>46038</v>
       </c>
       <c r="B34">
-        <v>4403.63518850908</v>
+        <v>4403.242946985902</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -666,7 +666,7 @@
         <v>46045</v>
       </c>
       <c r="B35">
-        <v>4439.82302138553</v>
+        <v>4439.397398345201</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -674,7 +674,7 @@
         <v>46052</v>
       </c>
       <c r="B36">
-        <v>4542.024799093551</v>
+        <v>4541.456861664976</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -682,7 +682,7 @@
         <v>46059</v>
       </c>
       <c r="B37">
-        <v>4677.984097421525</v>
+        <v>4677.294216277848</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -690,7 +690,7 @@
         <v>46066</v>
       </c>
       <c r="B38">
-        <v>4760.511179501942</v>
+        <v>4759.627656390408</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -698,7 +698,7 @@
         <v>46073</v>
       </c>
       <c r="B39">
-        <v>4895.346634733738</v>
+        <v>4894.826074891596</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -706,7 +706,7 @@
         <v>46080</v>
       </c>
       <c r="B40">
-        <v>4936.681293310411</v>
+        <v>4936.109171619129</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -714,7 +714,7 @@
         <v>46087</v>
       </c>
       <c r="B41">
-        <v>5043.830304200666</v>
+        <v>5043.084038122656</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -722,7 +722,7 @@
         <v>46094</v>
       </c>
       <c r="B42">
-        <v>5210.643839220348</v>
+        <v>5210.222541672971</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>46101</v>
       </c>
       <c r="B43">
-        <v>5251.596015694528</v>
+        <v>5251.533561818238</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>46108</v>
       </c>
       <c r="B44">
-        <v>5290.81433050451</v>
+        <v>5291.278175043644</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>46115</v>
       </c>
       <c r="B45">
-        <v>5366.446564202593</v>
+        <v>5367.299712978211</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>46122</v>
       </c>
       <c r="B46">
-        <v>5442.405105243783</v>
+        <v>5443.510134820617</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>46129</v>
       </c>
       <c r="B47">
-        <v>5572.289512135258</v>
+        <v>5573.498684338889</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>46136</v>
       </c>
       <c r="B48">
-        <v>5511.186864680465</v>
+        <v>5512.725413752249</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>46143</v>
       </c>
       <c r="B49">
-        <v>5335.1592167327</v>
+        <v>5337.074967071912</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>46150</v>
       </c>
       <c r="B50">
-        <v>5218.932641421969</v>
+        <v>5220.739636477757</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>46157</v>
       </c>
       <c r="B51">
-        <v>5084.579829477825</v>
+        <v>5086.526218228111</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>46164</v>
       </c>
       <c r="B52">
-        <v>4971.21737461042</v>
+        <v>4972.979055765551</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>46171</v>
       </c>
       <c r="B53">
-        <v>4868.741564749758</v>
+        <v>4870.426578859004</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>46178</v>
       </c>
       <c r="B54">
-        <v>4819.579689719004</v>
+        <v>4821.485147031904</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>46185</v>
       </c>
       <c r="B55">
-        <v>4692.206504142772</v>
+        <v>4693.73855690152</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>46192</v>
       </c>
       <c r="B56">
-        <v>4572.239928132006</v>
+        <v>4573.311134454449</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>46199</v>
       </c>
       <c r="B57">
-        <v>4477.356677603277</v>
+        <v>4478.072963933366</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>46206</v>
       </c>
       <c r="B58">
-        <v>4472.472146643729</v>
+        <v>4473.202780656282</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>46213</v>
       </c>
       <c r="B59">
-        <v>4392.077680063521</v>
+        <v>4392.987135775095</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>46220</v>
       </c>
       <c r="B60">
-        <v>4233.266663875899</v>
+        <v>4234.475326917662</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>46227</v>
       </c>
       <c r="B61">
-        <v>4150.964437376027</v>
+        <v>4141.112355716215</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>46234</v>
       </c>
       <c r="B62">
-        <v>4094.490768145039</v>
+        <v>4092.2231659049</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>46241</v>
       </c>
       <c r="B63">
-        <v>4076.89241041065</v>
+        <v>4081.959665245538</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46248</v>
       </c>
       <c r="B64">
-        <v>4092.224775798727</v>
+        <v>4102.207868645417</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46255</v>
       </c>
       <c r="B65">
-        <v>4080.048980742492</v>
+        <v>4104.245118050799</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46262</v>
       </c>
       <c r="B66">
-        <v>4077.998038298635</v>
+        <v>4129.012846807349</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46269</v>
       </c>
       <c r="B67">
-        <v>4081.175600167395</v>
+        <v>4140.947412375575</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46276</v>
       </c>
       <c r="B68">
-        <v>4089.061500583338</v>
+        <v>4146.331542351139</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46283</v>
       </c>
       <c r="B69">
-        <v>4076.00919754683</v>
+        <v>4120.192517041372</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46290</v>
       </c>
       <c r="B70">
-        <v>4093.362614651977</v>
+        <v>4125.523728067197</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46297</v>
       </c>
       <c r="B71">
-        <v>4139.698692288517</v>
+        <v>4156.98284665907</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46304</v>
       </c>
       <c r="B72">
-        <v>4193.279952984432</v>
+        <v>4217.935864775998</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46311</v>
       </c>
       <c r="B73">
-        <v>4242.366148104965</v>
+        <v>4278.807101157374</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46318</v>
       </c>
       <c r="B74">
-        <v>4407.156781571659</v>
+        <v>4416.239665590244</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46325</v>
       </c>
       <c r="B75">
-        <v>4510.052259793338</v>
+        <v>4560.055142734512</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46332</v>
       </c>
       <c r="B76">
-        <v>4752.641472114906</v>
+        <v>4742.532084619208</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46339</v>
       </c>
       <c r="B77">
-        <v>5188.35771853053</v>
+        <v>5228.117286010426</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/XAUUSD_forecast.xlsx
+++ b/public/data/files/XAUUSD_forecast.xlsx
@@ -442,7 +442,7 @@
         <v>45849</v>
       </c>
       <c r="B7">
-        <v>3668.16401313603</v>
+        <v>3668.224247426043</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -450,7 +450,7 @@
         <v>45856</v>
       </c>
       <c r="B8">
-        <v>3565.108076414051</v>
+        <v>3565.189628251951</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -458,7 +458,7 @@
         <v>45863</v>
       </c>
       <c r="B9">
-        <v>3510.589791653512</v>
+        <v>3510.684216792409</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -466,7 +466,7 @@
         <v>45870</v>
       </c>
       <c r="B10">
-        <v>3482.966289642065</v>
+        <v>3483.066718556674</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -474,7 +474,7 @@
         <v>45877</v>
       </c>
       <c r="B11">
-        <v>3491.454514805754</v>
+        <v>3491.557406332586</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -482,7 +482,7 @@
         <v>45884</v>
       </c>
       <c r="B12">
-        <v>3504.234326160327</v>
+        <v>3504.338441756105</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -490,7 +490,7 @@
         <v>45891</v>
       </c>
       <c r="B13">
-        <v>3518.75716001068</v>
+        <v>3518.860497714315</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -498,7 +498,7 @@
         <v>45898</v>
       </c>
       <c r="B14">
-        <v>3531.273784282169</v>
+        <v>3531.3754643188</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -506,7 +506,7 @@
         <v>45905</v>
       </c>
       <c r="B15">
-        <v>3547.488332298419</v>
+        <v>3547.563190374226</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -514,7 +514,7 @@
         <v>45912</v>
       </c>
       <c r="B16">
-        <v>3452.814709207084</v>
+        <v>3452.795357761456</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -522,7 +522,7 @@
         <v>45919</v>
       </c>
       <c r="B17">
-        <v>3450.395422473059</v>
+        <v>3450.378357780768</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -530,7 +530,7 @@
         <v>45926</v>
       </c>
       <c r="B18">
-        <v>3450.46724914688</v>
+        <v>3450.451464428278</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -538,7 +538,7 @@
         <v>45933</v>
       </c>
       <c r="B19">
-        <v>3533.221234865166</v>
+        <v>3533.137848024268</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -546,7 +546,7 @@
         <v>45940</v>
       </c>
       <c r="B20">
-        <v>3630.612026534242</v>
+        <v>3630.451934924105</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -554,7 +554,7 @@
         <v>45947</v>
       </c>
       <c r="B21">
-        <v>3782.976098276432</v>
+        <v>3782.733535532965</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -562,7 +562,7 @@
         <v>45954</v>
       </c>
       <c r="B22">
-        <v>3853.960019928425</v>
+        <v>3853.742714103568</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -570,7 +570,7 @@
         <v>45961</v>
       </c>
       <c r="B23">
-        <v>3900.614751183634</v>
+        <v>3900.41170558773</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -578,7 +578,7 @@
         <v>45968</v>
       </c>
       <c r="B24">
-        <v>3885.838800123407</v>
+        <v>3885.662989879312</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -586,7 +586,7 @@
         <v>45975</v>
       </c>
       <c r="B25">
-        <v>3887.671531564629</v>
+        <v>3887.598054022996</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -594,7 +594,7 @@
         <v>45982</v>
       </c>
       <c r="B26">
-        <v>3993.871802842934</v>
+        <v>3993.847956333715</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -602,7 +602,7 @@
         <v>45989</v>
       </c>
       <c r="B27">
-        <v>4068.797252994681</v>
+        <v>4068.723609064425</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -610,7 +610,7 @@
         <v>45996</v>
       </c>
       <c r="B28">
-        <v>4108.958202262014</v>
+        <v>4108.867310716828</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -618,7 +618,7 @@
         <v>46003</v>
       </c>
       <c r="B29">
-        <v>4206.480729602273</v>
+        <v>4206.471009792109</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -626,7 +626,7 @@
         <v>46010</v>
       </c>
       <c r="B30">
-        <v>4199.864250217981</v>
+        <v>4199.826048601917</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -634,7 +634,7 @@
         <v>46017</v>
       </c>
       <c r="B31">
-        <v>4224.891549256055</v>
+        <v>4224.786430831457</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -642,7 +642,7 @@
         <v>46024</v>
       </c>
       <c r="B32">
-        <v>4245.708548355971</v>
+        <v>4245.602362906609</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -650,7 +650,7 @@
         <v>46031</v>
       </c>
       <c r="B33">
-        <v>4310.591892885148</v>
+        <v>4310.442974762895</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -658,7 +658,7 @@
         <v>46038</v>
       </c>
       <c r="B34">
-        <v>4403.242946985902</v>
+        <v>4403.055005988403</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -666,7 +666,7 @@
         <v>46045</v>
       </c>
       <c r="B35">
-        <v>4439.397398345201</v>
+        <v>4439.193367446049</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -674,7 +674,7 @@
         <v>46052</v>
       </c>
       <c r="B36">
-        <v>4541.456861664976</v>
+        <v>4541.184496492187</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -682,7 +682,7 @@
         <v>46059</v>
       </c>
       <c r="B37">
-        <v>4677.294216277848</v>
+        <v>4676.963398181791</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -690,7 +690,7 @@
         <v>46066</v>
       </c>
       <c r="B38">
-        <v>4759.627656390408</v>
+        <v>4759.203395855811</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -698,7 +698,7 @@
         <v>46073</v>
       </c>
       <c r="B39">
-        <v>4894.826074891596</v>
+        <v>4894.576399911757</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -706,7 +706,7 @@
         <v>46080</v>
       </c>
       <c r="B40">
-        <v>4936.109171619129</v>
+        <v>4935.834757586595</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -714,7 +714,7 @@
         <v>46087</v>
       </c>
       <c r="B41">
-        <v>5043.084038122656</v>
+        <v>5042.725956435965</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -722,7 +722,7 @@
         <v>46094</v>
       </c>
       <c r="B42">
-        <v>5210.222541672971</v>
+        <v>5210.020074782893</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>46101</v>
       </c>
       <c r="B43">
-        <v>5251.533561818238</v>
+        <v>5251.502691238455</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>46108</v>
       </c>
       <c r="B44">
-        <v>5291.278175043644</v>
+        <v>5291.499455883487</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>46115</v>
       </c>
       <c r="B45">
-        <v>5367.299712978211</v>
+        <v>5367.708003629445</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>46122</v>
       </c>
       <c r="B46">
-        <v>5443.510134820617</v>
+        <v>5444.039105182422</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>46129</v>
       </c>
       <c r="B47">
-        <v>5573.498684338889</v>
+        <v>5574.077657686802</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>46136</v>
       </c>
       <c r="B48">
-        <v>5512.725413752249</v>
+        <v>5513.462839071357</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>46143</v>
       </c>
       <c r="B49">
-        <v>5337.074967071912</v>
+        <v>5337.993636496924</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>46150</v>
       </c>
       <c r="B50">
-        <v>5220.739636477757</v>
+        <v>5221.606480708362</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>46157</v>
       </c>
       <c r="B51">
-        <v>5086.526218228111</v>
+        <v>5087.460446862351</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>46164</v>
       </c>
       <c r="B52">
-        <v>4972.979055765551</v>
+        <v>4973.824956577943</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>46171</v>
       </c>
       <c r="B53">
-        <v>4870.426578859004</v>
+        <v>4871.236120629248</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>46178</v>
       </c>
       <c r="B54">
-        <v>4821.485147031904</v>
+        <v>4822.400639549578</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>46185</v>
       </c>
       <c r="B55">
-        <v>4693.73855690152</v>
+        <v>4694.474510767481</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>46192</v>
       </c>
       <c r="B56">
-        <v>4573.311134454449</v>
+        <v>4573.825354825198</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>46199</v>
       </c>
       <c r="B57">
-        <v>4478.072963933366</v>
+        <v>4478.416197583301</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>46206</v>
       </c>
       <c r="B58">
-        <v>4473.202780656282</v>
+        <v>4473.552906543547</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>46213</v>
       </c>
       <c r="B59">
-        <v>4392.987135775095</v>
+        <v>4393.423298720609</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>46220</v>
       </c>
       <c r="B60">
-        <v>4234.475326917662</v>
+        <v>4235.055802054571</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>46227</v>
       </c>
       <c r="B61">
-        <v>4141.112355716215</v>
+        <v>4141.595082792942</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>46234</v>
       </c>
       <c r="B62">
-        <v>4092.2231659049</v>
+        <v>4092.52681796423</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>46241</v>
       </c>
       <c r="B63">
-        <v>4081.959665245538</v>
+        <v>4081.937058771853</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46248</v>
       </c>
       <c r="B64">
-        <v>4102.207868645417</v>
+        <v>4113.224612333566</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46255</v>
       </c>
       <c r="B65">
-        <v>4104.245118050799</v>
+        <v>4118.322753495684</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46262</v>
       </c>
       <c r="B66">
-        <v>4129.012846807349</v>
+        <v>4144.909965976831</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46269</v>
       </c>
       <c r="B67">
-        <v>4140.947412375575</v>
+        <v>4161.254594976118</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46276</v>
       </c>
       <c r="B68">
-        <v>4146.331542351139</v>
+        <v>4168.267882593234</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46283</v>
       </c>
       <c r="B69">
-        <v>4120.192517041372</v>
+        <v>4144.312353438518</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46290</v>
       </c>
       <c r="B70">
-        <v>4125.523728067197</v>
+        <v>4151.804456063295</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46297</v>
       </c>
       <c r="B71">
-        <v>4156.98284665907</v>
+        <v>4184.904227466834</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46304</v>
       </c>
       <c r="B72">
-        <v>4217.935864775998</v>
+        <v>4247.378919390172</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46311</v>
       </c>
       <c r="B73">
-        <v>4278.807101157374</v>
+        <v>4314.442409834326</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46318</v>
       </c>
       <c r="B74">
-        <v>4416.239665590244</v>
+        <v>4456.223185716253</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46325</v>
       </c>
       <c r="B75">
-        <v>4560.055142734512</v>
+        <v>4605.304520975091</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46332</v>
       </c>
       <c r="B76">
-        <v>4742.532084619208</v>
+        <v>4787.276804075707</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46339</v>
       </c>
       <c r="B77">
-        <v>5228.117286010426</v>
+        <v>5216.116481731763</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/XAUUSD_forecast.xlsx
+++ b/public/data/files/XAUUSD_forecast.xlsx
@@ -442,7 +442,7 @@
         <v>45849</v>
       </c>
       <c r="B7">
-        <v>3668.224247426043</v>
+        <v>3668.282854063651</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -450,7 +450,7 @@
         <v>45856</v>
       </c>
       <c r="B8">
-        <v>3565.189628251951</v>
+        <v>3565.268986413269</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -458,7 +458,7 @@
         <v>45863</v>
       </c>
       <c r="B9">
-        <v>3510.684216792409</v>
+        <v>3510.776112660337</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -466,7 +466,7 @@
         <v>45870</v>
       </c>
       <c r="B10">
-        <v>3483.066718556674</v>
+        <v>3483.164471893735</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -474,7 +474,7 @@
         <v>45877</v>
       </c>
       <c r="B11">
-        <v>3491.557406332586</v>
+        <v>3491.657556117776</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -482,7 +482,7 @@
         <v>45884</v>
       </c>
       <c r="B12">
-        <v>3504.338441756105</v>
+        <v>3504.439782403943</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -490,7 +490,7 @@
         <v>45891</v>
       </c>
       <c r="B13">
-        <v>3518.860497714315</v>
+        <v>3518.961080893522</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -498,7 +498,7 @@
         <v>45898</v>
       </c>
       <c r="B14">
-        <v>3531.3754643188</v>
+        <v>3531.474434003962</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -506,7 +506,7 @@
         <v>45905</v>
       </c>
       <c r="B15">
-        <v>3547.563190374226</v>
+        <v>3547.636091257609</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -514,7 +514,7 @@
         <v>45912</v>
       </c>
       <c r="B16">
-        <v>3452.795357761456</v>
+        <v>3452.776541264939</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -522,7 +522,7 @@
         <v>45919</v>
       </c>
       <c r="B17">
-        <v>3450.378357780768</v>
+        <v>3450.361766416372</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -530,7 +530,7 @@
         <v>45926</v>
       </c>
       <c r="B18">
-        <v>3450.451464428278</v>
+        <v>3450.436118645232</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -538,7 +538,7 @@
         <v>45933</v>
       </c>
       <c r="B19">
-        <v>3533.137848024268</v>
+        <v>3533.05675147382</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -546,7 +546,7 @@
         <v>45940</v>
       </c>
       <c r="B20">
-        <v>3630.451934924105</v>
+        <v>3630.296217268488</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -554,7 +554,7 @@
         <v>45947</v>
       </c>
       <c r="B21">
-        <v>3782.733535532965</v>
+        <v>3782.497546899269</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -562,7 +562,7 @@
         <v>45954</v>
       </c>
       <c r="B22">
-        <v>3853.742714103568</v>
+        <v>3853.531276242647</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -570,7 +570,7 @@
         <v>45961</v>
       </c>
       <c r="B23">
-        <v>3900.41170558773</v>
+        <v>3900.214039298813</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -578,7 +578,7 @@
         <v>45968</v>
       </c>
       <c r="B24">
-        <v>3885.662989879312</v>
+        <v>3885.491786872292</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -586,7 +586,7 @@
         <v>45975</v>
       </c>
       <c r="B25">
-        <v>3887.598054022996</v>
+        <v>3887.526444815364</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -594,7 +594,7 @@
         <v>45982</v>
       </c>
       <c r="B26">
-        <v>3993.847956333715</v>
+        <v>3993.824682175565</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -602,7 +602,7 @@
         <v>45989</v>
       </c>
       <c r="B27">
-        <v>4068.723609064425</v>
+        <v>4068.651906884155</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -610,7 +610,7 @@
         <v>45996</v>
       </c>
       <c r="B28">
-        <v>4108.867310716828</v>
+        <v>4108.778820299687</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -618,7 +618,7 @@
         <v>46003</v>
       </c>
       <c r="B29">
-        <v>4206.471009792109</v>
+        <v>4206.461605989329</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -626,7 +626,7 @@
         <v>46010</v>
       </c>
       <c r="B30">
-        <v>4199.826048601917</v>
+        <v>4199.788966636862</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -634,7 +634,7 @@
         <v>46017</v>
       </c>
       <c r="B31">
-        <v>4224.786430831457</v>
+        <v>4224.68429310102</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -642,7 +642,7 @@
         <v>46024</v>
       </c>
       <c r="B32">
-        <v>4245.602362906609</v>
+        <v>4245.499150498401</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -650,7 +650,7 @@
         <v>46031</v>
       </c>
       <c r="B33">
-        <v>4310.442974762895</v>
+        <v>4310.298184938423</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -658,7 +658,7 @@
         <v>46038</v>
       </c>
       <c r="B34">
-        <v>4403.055005988403</v>
+        <v>4402.872220183774</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -666,7 +666,7 @@
         <v>46045</v>
       </c>
       <c r="B35">
-        <v>4439.193367446049</v>
+        <v>4438.99487351887</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -674,7 +674,7 @@
         <v>46052</v>
       </c>
       <c r="B36">
-        <v>4541.184496492187</v>
+        <v>4540.919452145094</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -682,7 +682,7 @@
         <v>46059</v>
       </c>
       <c r="B37">
-        <v>4676.963398181791</v>
+        <v>4676.641489319274</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -690,7 +690,7 @@
         <v>46066</v>
       </c>
       <c r="B38">
-        <v>4759.203395855811</v>
+        <v>4758.79019595829</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -698,7 +698,7 @@
         <v>46073</v>
       </c>
       <c r="B39">
-        <v>4894.576399911757</v>
+        <v>4894.333417014481</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -706,7 +706,7 @@
         <v>46080</v>
       </c>
       <c r="B40">
-        <v>4935.834757586595</v>
+        <v>4935.567693384652</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -714,7 +714,7 @@
         <v>46087</v>
       </c>
       <c r="B41">
-        <v>5042.725956435965</v>
+        <v>5042.37737850092</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -722,7 +722,7 @@
         <v>46094</v>
       </c>
       <c r="B42">
-        <v>5210.020074782893</v>
+        <v>5209.822785245596</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>46101</v>
       </c>
       <c r="B43">
-        <v>5251.502691238455</v>
+        <v>5251.47207863428</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>46108</v>
       </c>
       <c r="B44">
-        <v>5291.499455883487</v>
+        <v>5291.714064479578</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>46115</v>
       </c>
       <c r="B45">
-        <v>5367.708003629445</v>
+        <v>5368.104789165367</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>46122</v>
       </c>
       <c r="B46">
-        <v>5444.039105182422</v>
+        <v>5444.553254872349</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>46129</v>
       </c>
       <c r="B47">
-        <v>5574.077657686802</v>
+        <v>5574.640503641733</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>46136</v>
       </c>
       <c r="B48">
-        <v>5513.462839071357</v>
+        <v>5514.18018487097</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>46143</v>
       </c>
       <c r="B49">
-        <v>5337.993636496924</v>
+        <v>5338.887571283622</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>46150</v>
       </c>
       <c r="B50">
-        <v>5221.606480708362</v>
+        <v>5222.45018880086</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>46157</v>
       </c>
       <c r="B51">
-        <v>5087.460446862351</v>
+        <v>5088.370061243029</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>46164</v>
       </c>
       <c r="B52">
-        <v>4973.824956577943</v>
+        <v>4974.648775707471</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>46171</v>
       </c>
       <c r="B53">
-        <v>4871.236120629248</v>
+        <v>4872.024812230896</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>46178</v>
       </c>
       <c r="B54">
-        <v>4822.400639549578</v>
+        <v>4823.292578780054</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>46185</v>
       </c>
       <c r="B55">
-        <v>4694.474510767481</v>
+        <v>4695.191447873056</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>46192</v>
       </c>
       <c r="B56">
-        <v>4573.825354825198</v>
+        <v>4574.326066579257</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>46199</v>
       </c>
       <c r="B57">
-        <v>4478.416197583301</v>
+        <v>4478.750033674451</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>46206</v>
       </c>
       <c r="B58">
-        <v>4473.552906543547</v>
+        <v>4473.893457101596</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>46213</v>
       </c>
       <c r="B59">
-        <v>4393.423298720609</v>
+        <v>4393.847747176507</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>46220</v>
       </c>
       <c r="B60">
-        <v>4235.055802054571</v>
+        <v>4235.621193084338</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>46227</v>
       </c>
       <c r="B61">
-        <v>4141.595082792942</v>
+        <v>4142.066061395228</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>46234</v>
       </c>
       <c r="B62">
-        <v>4092.52681796423</v>
+        <v>4092.823719485832</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>46241</v>
       </c>
       <c r="B63">
-        <v>4081.937058771853</v>
+        <v>4081.916803584384</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46248</v>
       </c>
       <c r="B64">
-        <v>4113.224612333566</v>
+        <v>4123.523213875159</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46255</v>
       </c>
       <c r="B65">
-        <v>4118.322753495684</v>
+        <v>4131.329447025633</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46262</v>
       </c>
       <c r="B66">
-        <v>4144.909965976831</v>
+        <v>4159.417430571706</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46269</v>
       </c>
       <c r="B67">
-        <v>4161.254594976118</v>
+        <v>4179.015157874665</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46276</v>
       </c>
       <c r="B68">
-        <v>4168.267882593234</v>
+        <v>4186.719588180414</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46283</v>
       </c>
       <c r="B69">
-        <v>4144.312353438518</v>
+        <v>4163.897752504085</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46290</v>
       </c>
       <c r="B70">
-        <v>4151.804456063295</v>
+        <v>4172.606102422454</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46297</v>
       </c>
       <c r="B71">
-        <v>4184.904227466834</v>
+        <v>4207.27454705085</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46304</v>
       </c>
       <c r="B72">
-        <v>4247.378919390172</v>
+        <v>4271.516906039999</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46311</v>
       </c>
       <c r="B73">
-        <v>4314.442409834326</v>
+        <v>4344.061245998888</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46318</v>
       </c>
       <c r="B74">
-        <v>4456.223185716253</v>
+        <v>4489.009707361669</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46325</v>
       </c>
       <c r="B75">
-        <v>4605.304520975091</v>
+        <v>4640.60047249756</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46332</v>
       </c>
       <c r="B76">
-        <v>4787.276804075707</v>
+        <v>4819.81804185734</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46339</v>
       </c>
       <c r="B77">
-        <v>5216.116481731763</v>
+        <v>5203.264308253907</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/XAUUSD_forecast.xlsx
+++ b/public/data/files/XAUUSD_forecast.xlsx
@@ -442,7 +442,7 @@
         <v>45849</v>
       </c>
       <c r="B7">
-        <v>3668.282854063651</v>
+        <v>3668.339898139201</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -450,7 +450,7 @@
         <v>45856</v>
       </c>
       <c r="B8">
-        <v>3565.268986413269</v>
+        <v>3565.34623822329</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -458,7 +458,7 @@
         <v>45863</v>
       </c>
       <c r="B9">
-        <v>3510.776112660337</v>
+        <v>3510.86557951228</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -466,7 +466,7 @@
         <v>45870</v>
       </c>
       <c r="B10">
-        <v>3483.164471893735</v>
+        <v>3483.259655122955</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -474,7 +474,7 @@
         <v>45877</v>
       </c>
       <c r="B11">
-        <v>3491.657556117776</v>
+        <v>3491.755072261043</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -482,7 +482,7 @@
         <v>45884</v>
       </c>
       <c r="B12">
-        <v>3504.439782403943</v>
+        <v>3504.538457536324</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -490,7 +490,7 @@
         <v>45891</v>
       </c>
       <c r="B13">
-        <v>3518.961080893522</v>
+        <v>3519.059018188</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -498,7 +498,7 @@
         <v>45898</v>
       </c>
       <c r="B14">
-        <v>3531.474434003962</v>
+        <v>3531.570800235926</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -506,7 +506,7 @@
         <v>45905</v>
       </c>
       <c r="B15">
-        <v>3547.636091257609</v>
+        <v>3547.707110610089</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -514,7 +514,7 @@
         <v>45912</v>
       </c>
       <c r="B16">
-        <v>3452.776541264939</v>
+        <v>3452.758237853873</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -522,7 +522,7 @@
         <v>45919</v>
       </c>
       <c r="B17">
-        <v>3450.361766416372</v>
+        <v>3450.345628973268</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -530,7 +530,7 @@
         <v>45926</v>
       </c>
       <c r="B18">
-        <v>3450.436118645232</v>
+        <v>3450.421193758574</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -538,7 +538,7 @@
         <v>45933</v>
       </c>
       <c r="B19">
-        <v>3533.05675147382</v>
+        <v>3532.977852195372</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -546,7 +546,7 @@
         <v>45940</v>
       </c>
       <c r="B20">
-        <v>3630.296217268488</v>
+        <v>3630.144696863059</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -554,7 +554,7 @@
         <v>45947</v>
       </c>
       <c r="B21">
-        <v>3782.497546899269</v>
+        <v>3782.267868865806</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -562,7 +562,7 @@
         <v>45954</v>
       </c>
       <c r="B22">
-        <v>3853.531276242647</v>
+        <v>3853.325471946619</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -570,7 +570,7 @@
         <v>45961</v>
       </c>
       <c r="B23">
-        <v>3900.214039298813</v>
+        <v>3900.021541614122</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -578,7 +578,7 @@
         <v>45968</v>
       </c>
       <c r="B24">
-        <v>3885.491786872292</v>
+        <v>3885.32501268139</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -586,7 +586,7 @@
         <v>45975</v>
       </c>
       <c r="B25">
-        <v>3887.526444815364</v>
+        <v>3887.456633871309</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -594,7 +594,7 @@
         <v>45982</v>
       </c>
       <c r="B26">
-        <v>3993.824682175565</v>
+        <v>3993.801960296323</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -602,7 +602,7 @@
         <v>45989</v>
       </c>
       <c r="B27">
-        <v>4068.651906884155</v>
+        <v>4068.582070676364</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -610,7 +610,7 @@
         <v>45996</v>
       </c>
       <c r="B28">
-        <v>4108.778820299687</v>
+        <v>4108.692637155404</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -618,7 +618,7 @@
         <v>46003</v>
       </c>
       <c r="B29">
-        <v>4206.461605989329</v>
+        <v>4206.452503458514</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -626,7 +626,7 @@
         <v>46010</v>
       </c>
       <c r="B30">
-        <v>4199.788966636862</v>
+        <v>4199.752956177445</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -634,7 +634,7 @@
         <v>46017</v>
       </c>
       <c r="B31">
-        <v>4224.68429310102</v>
+        <v>4224.585011550363</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -642,7 +642,7 @@
         <v>46024</v>
       </c>
       <c r="B32">
-        <v>4245.499150498401</v>
+        <v>4245.398788487654</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -650,7 +650,7 @@
         <v>46031</v>
       </c>
       <c r="B33">
-        <v>4310.298184938423</v>
+        <v>4310.157354719772</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -658,7 +658,7 @@
         <v>46038</v>
       </c>
       <c r="B34">
-        <v>4402.872220183774</v>
+        <v>4402.694381090933</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -666,7 +666,7 @@
         <v>46045</v>
       </c>
       <c r="B35">
-        <v>4438.99487351887</v>
+        <v>4438.801694795699</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -674,7 +674,7 @@
         <v>46052</v>
       </c>
       <c r="B36">
-        <v>4540.919452145094</v>
+        <v>4540.661438010191</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -682,7 +682,7 @@
         <v>46059</v>
       </c>
       <c r="B37">
-        <v>4676.641489319274</v>
+        <v>4676.328135447529</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -690,7 +690,7 @@
         <v>46066</v>
       </c>
       <c r="B38">
-        <v>4758.79019595829</v>
+        <v>4758.387630786695</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -698,7 +698,7 @@
         <v>46073</v>
       </c>
       <c r="B39">
-        <v>4894.333417014481</v>
+        <v>4894.096861424548</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -706,7 +706,7 @@
         <v>46080</v>
       </c>
       <c r="B40">
-        <v>4935.567693384652</v>
+        <v>4935.307688415673</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -714,7 +714,7 @@
         <v>46087</v>
       </c>
       <c r="B41">
-        <v>5042.37737850092</v>
+        <v>5042.037932304649</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -722,7 +722,7 @@
         <v>46094</v>
       </c>
       <c r="B42">
-        <v>5209.822785245596</v>
+        <v>5209.630478094648</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>46101</v>
       </c>
       <c r="B43">
-        <v>5251.47207863428</v>
+        <v>5251.441736639488</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>46108</v>
       </c>
       <c r="B44">
-        <v>5291.714064479578</v>
+        <v>5291.922294409935</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>46115</v>
       </c>
       <c r="B45">
-        <v>5368.104789165367</v>
+        <v>5368.490547256628</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>46122</v>
       </c>
       <c r="B46">
-        <v>5444.553254872349</v>
+        <v>5445.053195612751</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>46129</v>
       </c>
       <c r="B47">
-        <v>5574.640503641733</v>
+        <v>5575.187884547979</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>46136</v>
       </c>
       <c r="B48">
-        <v>5514.18018487097</v>
+        <v>5514.878258317034</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>46143</v>
       </c>
       <c r="B49">
-        <v>5338.887571283622</v>
+        <v>5339.757753930584</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>46150</v>
       </c>
       <c r="B50">
-        <v>5222.45018880086</v>
+        <v>5223.27167160217</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>46157</v>
       </c>
       <c r="B51">
-        <v>5088.370061243029</v>
+        <v>5089.256017658294</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>46164</v>
       </c>
       <c r="B52">
-        <v>4974.648775707471</v>
+        <v>4975.451363675907</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>46171</v>
       </c>
       <c r="B53">
-        <v>4872.024812230896</v>
+        <v>4872.79344546611</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>46178</v>
       </c>
       <c r="B54">
-        <v>4823.292578780054</v>
+        <v>4824.161857915296</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>46185</v>
       </c>
       <c r="B55">
-        <v>4695.191447873056</v>
+        <v>4695.890092984986</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>46192</v>
       </c>
       <c r="B56">
-        <v>4574.326066579257</v>
+        <v>4574.813793577888</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>46199</v>
       </c>
       <c r="B57">
-        <v>4478.750033674451</v>
+        <v>4479.074851546671</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>46206</v>
       </c>
       <c r="B58">
-        <v>4473.893457101596</v>
+        <v>4474.22481864112</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>46213</v>
       </c>
       <c r="B59">
-        <v>4393.847747176507</v>
+        <v>4394.260945085903</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>46220</v>
       </c>
       <c r="B60">
-        <v>4235.621193084338</v>
+        <v>4236.172076274217</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>46227</v>
       </c>
       <c r="B61">
-        <v>4142.066061395228</v>
+        <v>4142.525707709364</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>46234</v>
       </c>
       <c r="B62">
-        <v>4092.823719485832</v>
+        <v>4093.114083133096</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>46241</v>
       </c>
       <c r="B63">
-        <v>4081.916803584384</v>
+        <v>4081.898743436039</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46248</v>
       </c>
       <c r="B64">
-        <v>4123.523213875159</v>
+        <v>4133.240741359221</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46255</v>
       </c>
       <c r="B65">
-        <v>4131.329447025633</v>
+        <v>4143.596458896695</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46262</v>
       </c>
       <c r="B66">
-        <v>4159.417430571706</v>
+        <v>4172.932199228356</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46269</v>
       </c>
       <c r="B67">
-        <v>4179.015157874665</v>
+        <v>4195.513897482451</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46276</v>
       </c>
       <c r="B68">
-        <v>4186.719588180414</v>
+        <v>4203.904689548217</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46283</v>
       </c>
       <c r="B69">
-        <v>4163.897752504085</v>
+        <v>4182.136181868414</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46290</v>
       </c>
       <c r="B70">
-        <v>4172.606102422454</v>
+        <v>4191.90196074252</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46297</v>
       </c>
       <c r="B71">
-        <v>4207.27454705085</v>
+        <v>4228.008974286648</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46304</v>
       </c>
       <c r="B72">
-        <v>4271.516906039999</v>
+        <v>4293.872652682876</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46311</v>
       </c>
       <c r="B73">
-        <v>4344.061245998888</v>
+        <v>4371.389741849065</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46318</v>
       </c>
       <c r="B74">
-        <v>4489.009707361669</v>
+        <v>4518.721044096503</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46325</v>
       </c>
       <c r="B75">
-        <v>4640.60047249756</v>
+        <v>4671.504657844175</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46332</v>
       </c>
       <c r="B76">
-        <v>4819.81804185734</v>
+        <v>4847.090136223885</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46339</v>
       </c>
       <c r="B77">
-        <v>5203.264308253907</v>
+        <v>5195.260393710254</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/XAUUSD_forecast.xlsx
+++ b/public/data/files/XAUUSD_forecast.xlsx
@@ -383,7 +383,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B77"/>
+  <dimension ref="A1:B78"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" style="1" customWidth="1"/>
@@ -442,7 +442,7 @@
         <v>45849</v>
       </c>
       <c r="B7">
-        <v>3668.339898139201</v>
+        <v>3668.16401313603</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -450,7 +450,7 @@
         <v>45856</v>
       </c>
       <c r="B8">
-        <v>3565.34623822329</v>
+        <v>3565.108076414051</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -458,7 +458,7 @@
         <v>45863</v>
       </c>
       <c r="B9">
-        <v>3510.86557951228</v>
+        <v>3510.589791653512</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -466,7 +466,7 @@
         <v>45870</v>
       </c>
       <c r="B10">
-        <v>3483.259655122955</v>
+        <v>3482.966289642065</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -474,7 +474,7 @@
         <v>45877</v>
       </c>
       <c r="B11">
-        <v>3491.755072261043</v>
+        <v>3491.454514805754</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -482,7 +482,7 @@
         <v>45884</v>
       </c>
       <c r="B12">
-        <v>3504.538457536324</v>
+        <v>3504.234326160327</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -490,7 +490,7 @@
         <v>45891</v>
       </c>
       <c r="B13">
-        <v>3519.059018188</v>
+        <v>3518.75716001068</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -498,7 +498,7 @@
         <v>45898</v>
       </c>
       <c r="B14">
-        <v>3531.570800235926</v>
+        <v>3531.273784282169</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -506,7 +506,7 @@
         <v>45905</v>
       </c>
       <c r="B15">
-        <v>3547.707110610089</v>
+        <v>3547.488332298419</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -514,7 +514,7 @@
         <v>45912</v>
       </c>
       <c r="B16">
-        <v>3452.758237853873</v>
+        <v>3452.814709207084</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -522,7 +522,7 @@
         <v>45919</v>
       </c>
       <c r="B17">
-        <v>3450.345628973268</v>
+        <v>3450.395422473059</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -530,7 +530,7 @@
         <v>45926</v>
       </c>
       <c r="B18">
-        <v>3450.421193758574</v>
+        <v>3450.46724914688</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -538,7 +538,7 @@
         <v>45933</v>
       </c>
       <c r="B19">
-        <v>3532.977852195372</v>
+        <v>3533.221234865166</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -546,7 +546,7 @@
         <v>45940</v>
       </c>
       <c r="B20">
-        <v>3630.144696863059</v>
+        <v>3630.612026534242</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -554,7 +554,7 @@
         <v>45947</v>
       </c>
       <c r="B21">
-        <v>3782.267868865806</v>
+        <v>3782.976098276432</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -562,7 +562,7 @@
         <v>45954</v>
       </c>
       <c r="B22">
-        <v>3853.325471946619</v>
+        <v>3853.960019928425</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -570,7 +570,7 @@
         <v>45961</v>
       </c>
       <c r="B23">
-        <v>3900.021541614122</v>
+        <v>3900.614751183634</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -578,7 +578,7 @@
         <v>45968</v>
       </c>
       <c r="B24">
-        <v>3885.32501268139</v>
+        <v>3885.838800123407</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -586,7 +586,7 @@
         <v>45975</v>
       </c>
       <c r="B25">
-        <v>3887.456633871309</v>
+        <v>3887.671531564629</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -594,7 +594,7 @@
         <v>45982</v>
       </c>
       <c r="B26">
-        <v>3993.801960296323</v>
+        <v>3993.871802842934</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -602,7 +602,7 @@
         <v>45989</v>
       </c>
       <c r="B27">
-        <v>4068.582070676364</v>
+        <v>4068.797252994681</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -610,7 +610,7 @@
         <v>45996</v>
       </c>
       <c r="B28">
-        <v>4108.692637155404</v>
+        <v>4108.958202262014</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -618,7 +618,7 @@
         <v>46003</v>
       </c>
       <c r="B29">
-        <v>4206.452503458514</v>
+        <v>4206.480729602273</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -626,7 +626,7 @@
         <v>46010</v>
       </c>
       <c r="B30">
-        <v>4199.752956177445</v>
+        <v>4199.864250217981</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -634,7 +634,7 @@
         <v>46017</v>
       </c>
       <c r="B31">
-        <v>4224.585011550363</v>
+        <v>4224.891549256055</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -642,7 +642,7 @@
         <v>46024</v>
       </c>
       <c r="B32">
-        <v>4245.398788487654</v>
+        <v>4245.708548355971</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -650,7 +650,7 @@
         <v>46031</v>
       </c>
       <c r="B33">
-        <v>4310.157354719772</v>
+        <v>4310.591892885148</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -658,7 +658,7 @@
         <v>46038</v>
       </c>
       <c r="B34">
-        <v>4402.694381090933</v>
+        <v>4403.242946985902</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -666,7 +666,7 @@
         <v>46045</v>
       </c>
       <c r="B35">
-        <v>4438.801694795699</v>
+        <v>4439.397398345201</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -674,7 +674,7 @@
         <v>46052</v>
       </c>
       <c r="B36">
-        <v>4540.661438010191</v>
+        <v>4541.456861664976</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -682,7 +682,7 @@
         <v>46059</v>
       </c>
       <c r="B37">
-        <v>4676.328135447529</v>
+        <v>4677.294216277848</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -690,7 +690,7 @@
         <v>46066</v>
       </c>
       <c r="B38">
-        <v>4758.387630786695</v>
+        <v>4759.627656390408</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -698,7 +698,7 @@
         <v>46073</v>
       </c>
       <c r="B39">
-        <v>4894.096861424548</v>
+        <v>4894.826074891596</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -706,7 +706,7 @@
         <v>46080</v>
       </c>
       <c r="B40">
-        <v>4935.307688415673</v>
+        <v>4936.109171619129</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -714,7 +714,7 @@
         <v>46087</v>
       </c>
       <c r="B41">
-        <v>5042.037932304649</v>
+        <v>5043.084038122656</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -722,7 +722,7 @@
         <v>46094</v>
       </c>
       <c r="B42">
-        <v>5209.630478094648</v>
+        <v>5210.222541672971</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>46101</v>
       </c>
       <c r="B43">
-        <v>5251.441736639488</v>
+        <v>5251.533561818238</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>46108</v>
       </c>
       <c r="B44">
-        <v>5291.922294409935</v>
+        <v>5291.278175043644</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>46115</v>
       </c>
       <c r="B45">
-        <v>5368.490547256628</v>
+        <v>5367.299712978211</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>46122</v>
       </c>
       <c r="B46">
-        <v>5445.053195612751</v>
+        <v>5443.510134820617</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>46129</v>
       </c>
       <c r="B47">
-        <v>5575.187884547979</v>
+        <v>5573.498684338889</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>46136</v>
       </c>
       <c r="B48">
-        <v>5514.878258317034</v>
+        <v>5512.725413752249</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>46143</v>
       </c>
       <c r="B49">
-        <v>5339.757753930584</v>
+        <v>5337.074967071912</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>46150</v>
       </c>
       <c r="B50">
-        <v>5223.27167160217</v>
+        <v>5220.739636477757</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>46157</v>
       </c>
       <c r="B51">
-        <v>5089.256017658294</v>
+        <v>5086.526218228111</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>46164</v>
       </c>
       <c r="B52">
-        <v>4975.451363675907</v>
+        <v>4972.979055765551</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>46171</v>
       </c>
       <c r="B53">
-        <v>4872.79344546611</v>
+        <v>4870.426578859004</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>46178</v>
       </c>
       <c r="B54">
-        <v>4824.161857915296</v>
+        <v>4821.485147031904</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>46185</v>
       </c>
       <c r="B55">
-        <v>4695.890092984986</v>
+        <v>4693.73855690152</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>46192</v>
       </c>
       <c r="B56">
-        <v>4574.813793577888</v>
+        <v>4573.311134454449</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>46199</v>
       </c>
       <c r="B57">
-        <v>4479.074851546671</v>
+        <v>4478.072963933366</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>46206</v>
       </c>
       <c r="B58">
-        <v>4474.22481864112</v>
+        <v>4473.202780656282</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>46213</v>
       </c>
       <c r="B59">
-        <v>4394.260945085903</v>
+        <v>4392.987135775095</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>46220</v>
       </c>
       <c r="B60">
-        <v>4236.172076274217</v>
+        <v>4234.475326917662</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>46227</v>
       </c>
       <c r="B61">
-        <v>4142.525707709364</v>
+        <v>4151.977946182632</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>46234</v>
       </c>
       <c r="B62">
-        <v>4093.114083133096</v>
+        <v>4095.125952482337</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>46241</v>
       </c>
       <c r="B63">
-        <v>4081.898743436039</v>
+        <v>4076.932892592587</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46248</v>
       </c>
       <c r="B64">
-        <v>4133.240741359221</v>
+        <v>4103.85964357902</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46255</v>
       </c>
       <c r="B65">
-        <v>4143.596458896695</v>
+        <v>4108.226102147013</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46262</v>
       </c>
       <c r="B66">
-        <v>4172.932199228356</v>
+        <v>4110.908194759535</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46269</v>
       </c>
       <c r="B67">
-        <v>4195.513897482451</v>
+        <v>4117.240043072668</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46276</v>
       </c>
       <c r="B68">
-        <v>4203.904689548217</v>
+        <v>4129.206032269405</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46283</v>
       </c>
       <c r="B69">
-        <v>4182.136181868414</v>
+        <v>4118.449320866357</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46290</v>
       </c>
       <c r="B70">
-        <v>4191.90196074252</v>
+        <v>4139.339441920831</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46297</v>
       </c>
       <c r="B71">
-        <v>4228.008974286648</v>
+        <v>4188.359182133509</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46304</v>
       </c>
       <c r="B72">
-        <v>4293.872652682876</v>
+        <v>4245.576592787165</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46311</v>
       </c>
       <c r="B73">
-        <v>4371.389741849065</v>
+        <v>4303.28673388594</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46318</v>
       </c>
       <c r="B74">
-        <v>4518.721044096503</v>
+        <v>4474.002600491103</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46325</v>
       </c>
       <c r="B75">
-        <v>4671.504657844175</v>
+        <v>4585.029619244771</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46332</v>
       </c>
       <c r="B76">
-        <v>4847.090136223885</v>
+        <v>4821.51571189151</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,15 @@
         <v>46339</v>
       </c>
       <c r="B77">
-        <v>5195.260393710254</v>
+        <v>5163.878234180393</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2">
+      <c r="A78" s="3">
+        <v>46346</v>
+      </c>
+      <c r="B78">
+        <v>5178.408496206159</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/XAUUSD_forecast.xlsx
+++ b/public/data/files/XAUUSD_forecast.xlsx
@@ -442,7 +442,7 @@
         <v>45849</v>
       </c>
       <c r="B7">
-        <v>3668.16401313603</v>
+        <v>3668.395441318247</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -450,7 +450,7 @@
         <v>45856</v>
       </c>
       <c r="B8">
-        <v>3565.108076414051</v>
+        <v>3565.421466433657</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -458,7 +458,7 @@
         <v>45863</v>
       </c>
       <c r="B9">
-        <v>3510.589791653512</v>
+        <v>3510.952712375098</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -466,7 +466,7 @@
         <v>45870</v>
       </c>
       <c r="B10">
-        <v>3482.966289642065</v>
+        <v>3483.352368244946</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -474,7 +474,7 @@
         <v>45877</v>
       </c>
       <c r="B11">
-        <v>3491.454514805754</v>
+        <v>3491.850057255504</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -482,7 +482,7 @@
         <v>45884</v>
       </c>
       <c r="B12">
-        <v>3504.234326160327</v>
+        <v>3504.634570908768</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -490,7 +490,7 @@
         <v>45891</v>
       </c>
       <c r="B13">
-        <v>3518.75716001068</v>
+        <v>3519.154412600936</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -498,7 +498,7 @@
         <v>45898</v>
       </c>
       <c r="B14">
-        <v>3531.273784282169</v>
+        <v>3531.664664366748</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -506,7 +506,7 @@
         <v>45905</v>
       </c>
       <c r="B15">
-        <v>3547.488332298419</v>
+        <v>3547.776320248418</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -514,7 +514,7 @@
         <v>45912</v>
       </c>
       <c r="B16">
-        <v>3452.814709207084</v>
+        <v>3452.740426839217</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -522,7 +522,7 @@
         <v>45919</v>
       </c>
       <c r="B17">
-        <v>3450.395422473059</v>
+        <v>3450.329927090581</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -530,7 +530,7 @@
         <v>45926</v>
       </c>
       <c r="B18">
-        <v>3450.46724914688</v>
+        <v>3450.406672703336</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -538,7 +538,7 @@
         <v>45933</v>
       </c>
       <c r="B19">
-        <v>3533.221234865166</v>
+        <v>3532.901062137289</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -546,7 +546,7 @@
         <v>45940</v>
       </c>
       <c r="B20">
-        <v>3630.612026534242</v>
+        <v>3629.997206388437</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -554,7 +554,7 @@
         <v>45947</v>
       </c>
       <c r="B21">
-        <v>3782.976098276432</v>
+        <v>3782.044251811058</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -562,7 +562,7 @@
         <v>45954</v>
       </c>
       <c r="B22">
-        <v>3853.960019928425</v>
+        <v>3853.125079130726</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -570,7 +570,7 @@
         <v>45961</v>
       </c>
       <c r="B23">
-        <v>3900.614751183634</v>
+        <v>3899.834012678866</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -578,7 +578,7 @@
         <v>45968</v>
       </c>
       <c r="B24">
-        <v>3885.838800123407</v>
+        <v>3885.162497963186</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -586,7 +586,7 @@
         <v>45975</v>
       </c>
       <c r="B25">
-        <v>3887.671531564629</v>
+        <v>3887.388554565194</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -594,7 +594,7 @@
         <v>45982</v>
       </c>
       <c r="B26">
-        <v>3993.871802842934</v>
+        <v>3993.779771535131</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -602,7 +602,7 @@
         <v>45989</v>
       </c>
       <c r="B27">
-        <v>4068.797252994681</v>
+        <v>4068.514028555004</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -610,7 +610,7 @@
         <v>45996</v>
       </c>
       <c r="B28">
-        <v>4108.958202262014</v>
+        <v>4108.608672254721</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -618,7 +618,7 @@
         <v>46003</v>
       </c>
       <c r="B29">
-        <v>4206.480729602273</v>
+        <v>4206.443688347916</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -626,7 +626,7 @@
         <v>46010</v>
       </c>
       <c r="B30">
-        <v>4199.864250217981</v>
+        <v>4199.717971782176</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -634,7 +634,7 @@
         <v>46017</v>
       </c>
       <c r="B31">
-        <v>4224.891549256055</v>
+        <v>4224.488468480854</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -642,7 +642,7 @@
         <v>46024</v>
       </c>
       <c r="B32">
-        <v>4245.708548355971</v>
+        <v>4245.301160860409</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -650,7 +650,7 @@
         <v>46031</v>
       </c>
       <c r="B33">
-        <v>4310.591892885148</v>
+        <v>4310.020324450956</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -658,7 +658,7 @@
         <v>46038</v>
       </c>
       <c r="B34">
-        <v>4403.242946985902</v>
+        <v>4402.52129128259</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -666,7 +666,7 @@
         <v>46045</v>
       </c>
       <c r="B35">
-        <v>4439.397398345201</v>
+        <v>4438.613621164839</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -674,7 +674,7 @@
         <v>46052</v>
       </c>
       <c r="B36">
-        <v>4541.456861664976</v>
+        <v>4540.410178622667</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -682,7 +682,7 @@
         <v>46059</v>
       </c>
       <c r="B37">
-        <v>4677.294216277848</v>
+        <v>4676.023000813659</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -690,7 +690,7 @@
         <v>46066</v>
       </c>
       <c r="B38">
-        <v>4759.627656390408</v>
+        <v>4757.995295965346</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -698,7 +698,7 @@
         <v>46073</v>
       </c>
       <c r="B39">
-        <v>4894.826074891596</v>
+        <v>4893.866482115861</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -706,7 +706,7 @@
         <v>46080</v>
       </c>
       <c r="B40">
-        <v>4936.109171619129</v>
+        <v>4935.054467162</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -714,7 +714,7 @@
         <v>46087</v>
       </c>
       <c r="B41">
-        <v>5043.084038122656</v>
+        <v>5041.707264928509</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -722,7 +722,7 @@
         <v>46094</v>
       </c>
       <c r="B42">
-        <v>5210.222541672971</v>
+        <v>5209.44296797166</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>46101</v>
       </c>
       <c r="B43">
-        <v>5251.533561818238</v>
+        <v>5251.411676024324</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>46108</v>
       </c>
       <c r="B44">
-        <v>5291.278175043644</v>
+        <v>5292.124422450977</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>46115</v>
       </c>
       <c r="B45">
-        <v>5367.299712978211</v>
+        <v>5368.865729585194</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>46122</v>
       </c>
       <c r="B46">
-        <v>5443.510134820617</v>
+        <v>5445.539506044302</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>46129</v>
       </c>
       <c r="B47">
-        <v>5573.498684338889</v>
+        <v>5575.72042708255</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>46136</v>
       </c>
       <c r="B48">
-        <v>5512.725413752249</v>
+        <v>5515.557823984107</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>46143</v>
       </c>
       <c r="B49">
-        <v>5337.074967071912</v>
+        <v>5340.605115744134</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>46150</v>
       </c>
       <c r="B50">
-        <v>5220.739636477757</v>
+        <v>5224.071792931725</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>46157</v>
       </c>
       <c r="B51">
-        <v>5086.526218228111</v>
+        <v>5090.119223691117</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>46164</v>
       </c>
       <c r="B52">
-        <v>4972.979055765551</v>
+        <v>4976.233528033924</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>46171</v>
       </c>
       <c r="B53">
-        <v>4870.426578859004</v>
+        <v>4873.542772727242</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>46178</v>
       </c>
       <c r="B54">
-        <v>4821.485147031904</v>
+        <v>4825.009325768854</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>46185</v>
       </c>
       <c r="B55">
-        <v>4693.73855690152</v>
+        <v>4696.571134653468</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>46192</v>
       </c>
       <c r="B56">
-        <v>4573.311134454449</v>
+        <v>4575.289033020754</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>46199</v>
       </c>
       <c r="B57">
-        <v>4478.072963933366</v>
+        <v>4479.391010464889</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>46206</v>
       </c>
       <c r="B58">
-        <v>4473.202780656282</v>
+        <v>4474.547357028201</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>46213</v>
       </c>
       <c r="B59">
-        <v>4392.987135775095</v>
+        <v>4394.663332301797</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>46220</v>
       </c>
       <c r="B60">
-        <v>4234.475326917662</v>
+        <v>4236.7089991226</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>46227</v>
       </c>
       <c r="B61">
-        <v>4151.977946182632</v>
+        <v>4142.974418903176</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>46234</v>
       </c>
       <c r="B62">
-        <v>4095.125952482337</v>
+        <v>4093.398113307519</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>46241</v>
       </c>
       <c r="B63">
-        <v>4076.932892592587</v>
+        <v>4081.882733150104</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46248</v>
       </c>
       <c r="B64">
-        <v>4103.85964357902</v>
+        <v>4132.794108796805</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46255</v>
       </c>
       <c r="B65">
-        <v>4108.226102147013</v>
+        <v>4152.978967553811</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46262</v>
       </c>
       <c r="B66">
-        <v>4110.908194759535</v>
+        <v>4182.84684956903</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46269</v>
       </c>
       <c r="B67">
-        <v>4117.240043072668</v>
+        <v>4204.120667434092</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46276</v>
       </c>
       <c r="B68">
-        <v>4129.206032269405</v>
+        <v>4214.689293843659</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46283</v>
       </c>
       <c r="B69">
-        <v>4118.449320866357</v>
+        <v>4193.577674119252</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46290</v>
       </c>
       <c r="B70">
-        <v>4139.339441920831</v>
+        <v>4204.438158418128</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46297</v>
       </c>
       <c r="B71">
-        <v>4188.359182133509</v>
+        <v>4241.400612745198</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46304</v>
       </c>
       <c r="B72">
-        <v>4245.576592787165</v>
+        <v>4307.884806463817</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46311</v>
       </c>
       <c r="B73">
-        <v>4303.28673388594</v>
+        <v>4386.400216040873</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46318</v>
       </c>
       <c r="B74">
-        <v>4474.002600491103</v>
+        <v>4534.015276937028</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46325</v>
       </c>
       <c r="B75">
-        <v>4585.029619244771</v>
+        <v>4683.340844817672</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46332</v>
       </c>
       <c r="B76">
-        <v>4821.51571189151</v>
+        <v>4850.586632252722</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46339</v>
       </c>
       <c r="B77">
-        <v>5163.878234180393</v>
+        <v>5155.153624125658</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46346</v>
       </c>
       <c r="B78">
-        <v>5178.408496206159</v>
+        <v>4985.401847467762</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/XAUUSD_forecast.xlsx
+++ b/public/data/files/XAUUSD_forecast.xlsx
@@ -442,7 +442,7 @@
         <v>45849</v>
       </c>
       <c r="B7">
-        <v>3668.395441318247</v>
+        <v>3668.224247426043</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -450,7 +450,7 @@
         <v>45856</v>
       </c>
       <c r="B8">
-        <v>3565.421466433657</v>
+        <v>3565.189628251951</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -458,7 +458,7 @@
         <v>45863</v>
       </c>
       <c r="B9">
-        <v>3510.952712375098</v>
+        <v>3510.684216792409</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -466,7 +466,7 @@
         <v>45870</v>
       </c>
       <c r="B10">
-        <v>3483.352368244946</v>
+        <v>3483.066718556674</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -474,7 +474,7 @@
         <v>45877</v>
       </c>
       <c r="B11">
-        <v>3491.850057255504</v>
+        <v>3491.557406332586</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -482,7 +482,7 @@
         <v>45884</v>
       </c>
       <c r="B12">
-        <v>3504.634570908768</v>
+        <v>3504.338441756105</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -490,7 +490,7 @@
         <v>45891</v>
       </c>
       <c r="B13">
-        <v>3519.154412600936</v>
+        <v>3518.860497714315</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -498,7 +498,7 @@
         <v>45898</v>
       </c>
       <c r="B14">
-        <v>3531.664664366748</v>
+        <v>3531.3754643188</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -506,7 +506,7 @@
         <v>45905</v>
       </c>
       <c r="B15">
-        <v>3547.776320248418</v>
+        <v>3547.563190374226</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -514,7 +514,7 @@
         <v>45912</v>
       </c>
       <c r="B16">
-        <v>3452.740426839217</v>
+        <v>3452.795357761456</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -522,7 +522,7 @@
         <v>45919</v>
       </c>
       <c r="B17">
-        <v>3450.329927090581</v>
+        <v>3450.378357780768</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -530,7 +530,7 @@
         <v>45926</v>
       </c>
       <c r="B18">
-        <v>3450.406672703336</v>
+        <v>3450.451464428278</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -538,7 +538,7 @@
         <v>45933</v>
       </c>
       <c r="B19">
-        <v>3532.901062137289</v>
+        <v>3533.137848024268</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -546,7 +546,7 @@
         <v>45940</v>
       </c>
       <c r="B20">
-        <v>3629.997206388437</v>
+        <v>3630.451934924105</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -554,7 +554,7 @@
         <v>45947</v>
       </c>
       <c r="B21">
-        <v>3782.044251811058</v>
+        <v>3782.733535532965</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -562,7 +562,7 @@
         <v>45954</v>
       </c>
       <c r="B22">
-        <v>3853.125079130726</v>
+        <v>3853.742714103568</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -570,7 +570,7 @@
         <v>45961</v>
       </c>
       <c r="B23">
-        <v>3899.834012678866</v>
+        <v>3900.41170558773</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -578,7 +578,7 @@
         <v>45968</v>
       </c>
       <c r="B24">
-        <v>3885.162497963186</v>
+        <v>3885.662989879312</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -586,7 +586,7 @@
         <v>45975</v>
       </c>
       <c r="B25">
-        <v>3887.388554565194</v>
+        <v>3887.598054022996</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -594,7 +594,7 @@
         <v>45982</v>
       </c>
       <c r="B26">
-        <v>3993.779771535131</v>
+        <v>3993.847956333715</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -602,7 +602,7 @@
         <v>45989</v>
       </c>
       <c r="B27">
-        <v>4068.514028555004</v>
+        <v>4068.723609064425</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -610,7 +610,7 @@
         <v>45996</v>
       </c>
       <c r="B28">
-        <v>4108.608672254721</v>
+        <v>4108.867310716828</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -618,7 +618,7 @@
         <v>46003</v>
       </c>
       <c r="B29">
-        <v>4206.443688347916</v>
+        <v>4206.471009792109</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -626,7 +626,7 @@
         <v>46010</v>
       </c>
       <c r="B30">
-        <v>4199.717971782176</v>
+        <v>4199.826048601917</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -634,7 +634,7 @@
         <v>46017</v>
       </c>
       <c r="B31">
-        <v>4224.488468480854</v>
+        <v>4224.786430831457</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -642,7 +642,7 @@
         <v>46024</v>
       </c>
       <c r="B32">
-        <v>4245.301160860409</v>
+        <v>4245.602362906609</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -650,7 +650,7 @@
         <v>46031</v>
       </c>
       <c r="B33">
-        <v>4310.020324450956</v>
+        <v>4310.442974762895</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -658,7 +658,7 @@
         <v>46038</v>
       </c>
       <c r="B34">
-        <v>4402.52129128259</v>
+        <v>4403.055005988403</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -666,7 +666,7 @@
         <v>46045</v>
       </c>
       <c r="B35">
-        <v>4438.613621164839</v>
+        <v>4439.193367446049</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -674,7 +674,7 @@
         <v>46052</v>
       </c>
       <c r="B36">
-        <v>4540.410178622667</v>
+        <v>4541.184496492187</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -682,7 +682,7 @@
         <v>46059</v>
       </c>
       <c r="B37">
-        <v>4676.023000813659</v>
+        <v>4676.963398181791</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -690,7 +690,7 @@
         <v>46066</v>
       </c>
       <c r="B38">
-        <v>4757.995295965346</v>
+        <v>4759.203395855811</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -698,7 +698,7 @@
         <v>46073</v>
       </c>
       <c r="B39">
-        <v>4893.866482115861</v>
+        <v>4894.576399911757</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -706,7 +706,7 @@
         <v>46080</v>
       </c>
       <c r="B40">
-        <v>4935.054467162</v>
+        <v>4935.834757586595</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -714,7 +714,7 @@
         <v>46087</v>
       </c>
       <c r="B41">
-        <v>5041.707264928509</v>
+        <v>5042.725956435965</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -722,7 +722,7 @@
         <v>46094</v>
       </c>
       <c r="B42">
-        <v>5209.44296797166</v>
+        <v>5210.020074782893</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>46101</v>
       </c>
       <c r="B43">
-        <v>5251.411676024324</v>
+        <v>5251.502691238455</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>46108</v>
       </c>
       <c r="B44">
-        <v>5292.124422450977</v>
+        <v>5291.499455883487</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>46115</v>
       </c>
       <c r="B45">
-        <v>5368.865729585194</v>
+        <v>5367.708003629445</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>46122</v>
       </c>
       <c r="B46">
-        <v>5445.539506044302</v>
+        <v>5444.039105182422</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>46129</v>
       </c>
       <c r="B47">
-        <v>5575.72042708255</v>
+        <v>5574.077657686802</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>46136</v>
       </c>
       <c r="B48">
-        <v>5515.557823984107</v>
+        <v>5513.462839071357</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>46143</v>
       </c>
       <c r="B49">
-        <v>5340.605115744134</v>
+        <v>5337.993636496924</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>46150</v>
       </c>
       <c r="B50">
-        <v>5224.071792931725</v>
+        <v>5221.606480708362</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>46157</v>
       </c>
       <c r="B51">
-        <v>5090.119223691117</v>
+        <v>5087.460446862351</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>46164</v>
       </c>
       <c r="B52">
-        <v>4976.233528033924</v>
+        <v>4973.824956577943</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>46171</v>
       </c>
       <c r="B53">
-        <v>4873.542772727242</v>
+        <v>4871.236120629248</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>46178</v>
       </c>
       <c r="B54">
-        <v>4825.009325768854</v>
+        <v>4822.400639549578</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>46185</v>
       </c>
       <c r="B55">
-        <v>4696.571134653468</v>
+        <v>4694.474510767481</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>46192</v>
       </c>
       <c r="B56">
-        <v>4575.289033020754</v>
+        <v>4573.825354825198</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>46199</v>
       </c>
       <c r="B57">
-        <v>4479.391010464889</v>
+        <v>4478.416197583301</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>46206</v>
       </c>
       <c r="B58">
-        <v>4474.547357028201</v>
+        <v>4473.552906543547</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>46213</v>
       </c>
       <c r="B59">
-        <v>4394.663332301797</v>
+        <v>4393.423298720609</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>46220</v>
       </c>
       <c r="B60">
-        <v>4236.7089991226</v>
+        <v>4235.055802054571</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>46227</v>
       </c>
       <c r="B61">
-        <v>4142.974418903176</v>
+        <v>4152.465657803907</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>46234</v>
       </c>
       <c r="B62">
-        <v>4093.398113307519</v>
+        <v>4095.432751152544</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>46241</v>
       </c>
       <c r="B63">
-        <v>4081.882733150104</v>
+        <v>4076.954966892059</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46248</v>
       </c>
       <c r="B64">
-        <v>4132.794108796805</v>
+        <v>4103.520652933194</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46255</v>
       </c>
       <c r="B65">
-        <v>4152.978967553811</v>
+        <v>4118.543040590628</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46262</v>
       </c>
       <c r="B66">
-        <v>4182.84684956903</v>
+        <v>4123.025268812597</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46269</v>
       </c>
       <c r="B67">
-        <v>4204.120667434092</v>
+        <v>4129.358039462129</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46276</v>
       </c>
       <c r="B68">
-        <v>4214.689293843659</v>
+        <v>4144.336331279902</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46283</v>
       </c>
       <c r="B69">
-        <v>4193.577674119252</v>
+        <v>4134.111170688404</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46290</v>
       </c>
       <c r="B70">
-        <v>4204.438158418128</v>
+        <v>4155.852582730134</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46297</v>
       </c>
       <c r="B71">
-        <v>4241.400612745198</v>
+        <v>4205.708815679472</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46304</v>
       </c>
       <c r="B72">
-        <v>4307.884806463817</v>
+        <v>4264.278653198035</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46311</v>
       </c>
       <c r="B73">
-        <v>4386.400216040873</v>
+        <v>4324.478087273633</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46318</v>
       </c>
       <c r="B74">
-        <v>4534.015276937028</v>
+        <v>4497.066105134061</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46325</v>
       </c>
       <c r="B75">
-        <v>4683.340844817672</v>
+        <v>4609.75573885668</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46332</v>
       </c>
       <c r="B76">
-        <v>4850.586632252722</v>
+        <v>4839.205024846437</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46339</v>
       </c>
       <c r="B77">
-        <v>5155.153624125658</v>
+        <v>5144.415979089594</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46346</v>
       </c>
       <c r="B78">
-        <v>4985.401847467762</v>
+        <v>5138.006353110043</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/XAUUSD_forecast.xlsx
+++ b/public/data/files/XAUUSD_forecast.xlsx
@@ -442,7 +442,7 @@
         <v>45849</v>
       </c>
       <c r="B7">
-        <v>3668.224247426043</v>
+        <v>3668.44954206386</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -450,7 +450,7 @@
         <v>45856</v>
       </c>
       <c r="B8">
-        <v>3565.189628251951</v>
+        <v>3565.494749517899</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -458,7 +458,7 @@
         <v>45863</v>
       </c>
       <c r="B9">
-        <v>3510.684216792409</v>
+        <v>3511.03760138386</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -466,7 +466,7 @@
         <v>45870</v>
       </c>
       <c r="B10">
-        <v>3483.066718556674</v>
+        <v>3483.442706141038</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -474,7 +474,7 @@
         <v>45877</v>
       </c>
       <c r="B11">
-        <v>3491.557406332586</v>
+        <v>3491.94260834635</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -482,7 +482,7 @@
         <v>45884</v>
       </c>
       <c r="B12">
-        <v>3504.338441756105</v>
+        <v>3504.728220963094</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -490,7 +490,7 @@
         <v>45891</v>
       </c>
       <c r="B13">
-        <v>3518.860497714315</v>
+        <v>3519.247361859713</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -498,7 +498,7 @@
         <v>45898</v>
       </c>
       <c r="B14">
-        <v>3531.3754643188</v>
+        <v>3531.756122557202</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -506,7 +506,7 @@
         <v>45905</v>
       </c>
       <c r="B15">
-        <v>3547.563190374226</v>
+        <v>3547.843788385377</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -514,7 +514,7 @@
         <v>45912</v>
       </c>
       <c r="B16">
-        <v>3452.795357761456</v>
+        <v>3452.723088628761</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -522,7 +522,7 @@
         <v>45919</v>
       </c>
       <c r="B17">
-        <v>3450.378357780768</v>
+        <v>3450.314643383729</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -530,7 +530,7 @@
         <v>45926</v>
       </c>
       <c r="B18">
-        <v>3450.451464428278</v>
+        <v>3450.39253932393</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -538,7 +538,7 @@
         <v>45933</v>
       </c>
       <c r="B19">
-        <v>3533.137848024268</v>
+        <v>3532.826297887808</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -546,7 +546,7 @@
         <v>45940</v>
       </c>
       <c r="B20">
-        <v>3630.451934924105</v>
+        <v>3629.853587295738</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -554,7 +554,7 @@
         <v>45947</v>
       </c>
       <c r="B21">
-        <v>3782.733535532965</v>
+        <v>3781.826459099066</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -562,7 +562,7 @@
         <v>45954</v>
       </c>
       <c r="B22">
-        <v>3853.742714103568</v>
+        <v>3852.929887226679</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -570,7 +570,7 @@
         <v>45961</v>
       </c>
       <c r="B23">
-        <v>3900.41170558773</v>
+        <v>3899.651262797883</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -578,7 +578,7 @@
         <v>45968</v>
       </c>
       <c r="B24">
-        <v>3885.662989879312</v>
+        <v>3885.004081882903</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -586,7 +586,7 @@
         <v>45975</v>
       </c>
       <c r="B25">
-        <v>3887.598054022996</v>
+        <v>3887.322143508117</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -594,7 +594,7 @@
         <v>45982</v>
       </c>
       <c r="B26">
-        <v>3993.847956333715</v>
+        <v>3993.758097592456</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -602,7 +602,7 @@
         <v>45989</v>
       </c>
       <c r="B27">
-        <v>4068.723609064425</v>
+        <v>4068.447712278904</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -610,7 +610,7 @@
         <v>45996</v>
       </c>
       <c r="B28">
-        <v>4108.867310716828</v>
+        <v>4108.526841088225</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -618,7 +618,7 @@
         <v>46003</v>
       </c>
       <c r="B29">
-        <v>4206.471009792109</v>
+        <v>4206.435147625212</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -626,7 +626,7 @@
         <v>46010</v>
       </c>
       <c r="B30">
-        <v>4199.826048601917</v>
+        <v>4199.683970527283</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -634,7 +634,7 @@
         <v>46017</v>
       </c>
       <c r="B31">
-        <v>4224.786430831457</v>
+        <v>4224.394552551024</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -642,7 +642,7 @@
         <v>46024</v>
       </c>
       <c r="B32">
-        <v>4245.602362906609</v>
+        <v>4245.206157791939</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -650,7 +650,7 @@
         <v>46031</v>
       </c>
       <c r="B33">
-        <v>4310.442974762895</v>
+        <v>4309.886942916892</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -658,7 +658,7 @@
         <v>46038</v>
       </c>
       <c r="B34">
-        <v>4403.055005988403</v>
+        <v>4402.352763664612</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -666,7 +666,7 @@
         <v>46045</v>
       </c>
       <c r="B35">
-        <v>4439.193367446049</v>
+        <v>4438.430453416902</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -674,7 +674,7 @@
         <v>46052</v>
       </c>
       <c r="B36">
-        <v>4541.184496492187</v>
+        <v>4540.165412694078</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -682,7 +682,7 @@
         <v>46059</v>
       </c>
       <c r="B37">
-        <v>4676.963398181791</v>
+        <v>4675.725766966627</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -690,7 +690,7 @@
         <v>46066</v>
       </c>
       <c r="B38">
-        <v>4759.203395855811</v>
+        <v>4757.61280731341</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -698,7 +698,7 @@
         <v>46073</v>
       </c>
       <c r="B39">
-        <v>4894.576399911757</v>
+        <v>4893.642040932781</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -706,7 +706,7 @@
         <v>46080</v>
       </c>
       <c r="B40">
-        <v>4935.834757586595</v>
+        <v>4934.807768222847</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -714,7 +714,7 @@
         <v>46087</v>
       </c>
       <c r="B41">
-        <v>5042.725956435965</v>
+        <v>5041.38504134315</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -722,7 +722,7 @@
         <v>46094</v>
       </c>
       <c r="B42">
-        <v>5210.020074782893</v>
+        <v>5209.260078545607</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>46101</v>
       </c>
       <c r="B43">
-        <v>5251.502691238455</v>
+        <v>5251.381905893492</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>46108</v>
       </c>
       <c r="B44">
-        <v>5291.499455883487</v>
+        <v>5292.32070975251</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>46115</v>
       </c>
       <c r="B45">
-        <v>5367.708003629445</v>
+        <v>5369.230763582384</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>46122</v>
       </c>
       <c r="B46">
-        <v>5444.039105182422</v>
+        <v>5446.012733924672</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>46129</v>
       </c>
       <c r="B47">
-        <v>5574.077657686802</v>
+        <v>5576.238724617158</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>46136</v>
       </c>
       <c r="B48">
-        <v>5513.462839071357</v>
+        <v>5516.219606621808</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>46143</v>
       </c>
       <c r="B49">
-        <v>5337.993636496924</v>
+        <v>5341.430540119305</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>46150</v>
       </c>
       <c r="B50">
-        <v>5221.606480708362</v>
+        <v>5224.851372567329</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>46157</v>
       </c>
       <c r="B51">
-        <v>5087.460446862351</v>
+        <v>5090.960541268378</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>46164</v>
       </c>
       <c r="B52">
-        <v>4973.824956577943</v>
+        <v>4976.996036031109</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>46171</v>
       </c>
       <c r="B53">
-        <v>4871.236120629248</v>
+        <v>4874.273509406828</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>46178</v>
       </c>
       <c r="B54">
-        <v>4822.400639549578</v>
+        <v>4825.835789483999</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>46185</v>
       </c>
       <c r="B55">
-        <v>4694.474510767481</v>
+        <v>4697.235227436689</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>46192</v>
       </c>
       <c r="B56">
-        <v>4573.825354825198</v>
+        <v>4575.752257115689</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>46199</v>
       </c>
       <c r="B57">
-        <v>4478.416197583301</v>
+        <v>4479.698850925341</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>46206</v>
       </c>
       <c r="B58">
-        <v>4473.552906543547</v>
+        <v>4474.861419015369</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>46213</v>
       </c>
       <c r="B59">
-        <v>4393.423298720609</v>
+        <v>4395.055326124963</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>46220</v>
       </c>
       <c r="B60">
-        <v>4235.055802054571</v>
+        <v>4237.232482118216</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>46227</v>
       </c>
       <c r="B61">
-        <v>4152.465657803907</v>
+        <v>4143.412574172269</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>46234</v>
       </c>
       <c r="B62">
-        <v>4095.432751152544</v>
+        <v>4093.676006502933</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>46241</v>
       </c>
       <c r="B63">
-        <v>4076.954966892059</v>
+        <v>4081.868637745796</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46248</v>
       </c>
       <c r="B64">
-        <v>4103.520652933194</v>
+        <v>4132.360418088714</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46255</v>
       </c>
       <c r="B65">
-        <v>4118.543040590628</v>
+        <v>4160.600788462237</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46262</v>
       </c>
       <c r="B66">
-        <v>4123.025268812597</v>
+        <v>4190.671695058522</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46269</v>
       </c>
       <c r="B67">
-        <v>4129.358039462129</v>
+        <v>4210.558889672378</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46276</v>
       </c>
       <c r="B68">
-        <v>4144.336331279902</v>
+        <v>4222.671582497543</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46283</v>
       </c>
       <c r="B69">
-        <v>4134.111170688404</v>
+        <v>4202.361149070261</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46290</v>
       </c>
       <c r="B70">
-        <v>4155.852582730134</v>
+        <v>4213.801939747435</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46297</v>
       </c>
       <c r="B71">
-        <v>4205.708815679472</v>
+        <v>4251.458067132485</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46304</v>
       </c>
       <c r="B72">
-        <v>4264.278653198035</v>
+        <v>4318.352210245206</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46311</v>
       </c>
       <c r="B73">
-        <v>4324.478087273633</v>
+        <v>4397.497054717855</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46318</v>
       </c>
       <c r="B74">
-        <v>4497.066105134061</v>
+        <v>4544.357399827592</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46325</v>
       </c>
       <c r="B75">
-        <v>4609.75573885668</v>
+        <v>4689.117017968462</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46332</v>
       </c>
       <c r="B76">
-        <v>4839.205024846437</v>
+        <v>4847.527696198764</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46339</v>
       </c>
       <c r="B77">
-        <v>5144.415979089594</v>
+        <v>5114.792651548965</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46346</v>
       </c>
       <c r="B78">
-        <v>5138.006353110043</v>
+        <v>4944.602298445623</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/XAUUSD_forecast.xlsx
+++ b/public/data/files/XAUUSD_forecast.xlsx
@@ -442,7 +442,7 @@
         <v>45849</v>
       </c>
       <c r="B7">
-        <v>3668.44954206386</v>
+        <v>3668.282854063651</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -450,7 +450,7 @@
         <v>45856</v>
       </c>
       <c r="B8">
-        <v>3565.494749517899</v>
+        <v>3565.268986413269</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -458,7 +458,7 @@
         <v>45863</v>
       </c>
       <c r="B9">
-        <v>3511.03760138386</v>
+        <v>3510.776112660337</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -466,7 +466,7 @@
         <v>45870</v>
       </c>
       <c r="B10">
-        <v>3483.442706141038</v>
+        <v>3483.164471893735</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -474,7 +474,7 @@
         <v>45877</v>
       </c>
       <c r="B11">
-        <v>3491.94260834635</v>
+        <v>3491.657556117776</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -482,7 +482,7 @@
         <v>45884</v>
       </c>
       <c r="B12">
-        <v>3504.728220963094</v>
+        <v>3504.439782403943</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -490,7 +490,7 @@
         <v>45891</v>
       </c>
       <c r="B13">
-        <v>3519.247361859713</v>
+        <v>3518.961080893522</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -498,7 +498,7 @@
         <v>45898</v>
       </c>
       <c r="B14">
-        <v>3531.756122557202</v>
+        <v>3531.474434003962</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -506,7 +506,7 @@
         <v>45905</v>
       </c>
       <c r="B15">
-        <v>3547.843788385377</v>
+        <v>3547.636091257609</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -514,7 +514,7 @@
         <v>45912</v>
       </c>
       <c r="B16">
-        <v>3452.723088628761</v>
+        <v>3452.776541264939</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -522,7 +522,7 @@
         <v>45919</v>
       </c>
       <c r="B17">
-        <v>3450.314643383729</v>
+        <v>3450.361766416372</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -530,7 +530,7 @@
         <v>45926</v>
       </c>
       <c r="B18">
-        <v>3450.39253932393</v>
+        <v>3450.436118645232</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -538,7 +538,7 @@
         <v>45933</v>
       </c>
       <c r="B19">
-        <v>3532.826297887808</v>
+        <v>3533.05675147382</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -546,7 +546,7 @@
         <v>45940</v>
       </c>
       <c r="B20">
-        <v>3629.853587295738</v>
+        <v>3630.296217268488</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -554,7 +554,7 @@
         <v>45947</v>
       </c>
       <c r="B21">
-        <v>3781.826459099066</v>
+        <v>3782.497546899269</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -562,7 +562,7 @@
         <v>45954</v>
       </c>
       <c r="B22">
-        <v>3852.929887226679</v>
+        <v>3853.531276242647</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -570,7 +570,7 @@
         <v>45961</v>
       </c>
       <c r="B23">
-        <v>3899.651262797883</v>
+        <v>3900.214039298813</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -578,7 +578,7 @@
         <v>45968</v>
       </c>
       <c r="B24">
-        <v>3885.004081882903</v>
+        <v>3885.491786872292</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -586,7 +586,7 @@
         <v>45975</v>
       </c>
       <c r="B25">
-        <v>3887.322143508117</v>
+        <v>3887.526444815364</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -594,7 +594,7 @@
         <v>45982</v>
       </c>
       <c r="B26">
-        <v>3993.758097592456</v>
+        <v>3993.824682175565</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -602,7 +602,7 @@
         <v>45989</v>
       </c>
       <c r="B27">
-        <v>4068.447712278904</v>
+        <v>4068.651906884155</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -610,7 +610,7 @@
         <v>45996</v>
       </c>
       <c r="B28">
-        <v>4108.526841088225</v>
+        <v>4108.778820299687</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -618,7 +618,7 @@
         <v>46003</v>
       </c>
       <c r="B29">
-        <v>4206.435147625212</v>
+        <v>4206.461605989329</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -626,7 +626,7 @@
         <v>46010</v>
       </c>
       <c r="B30">
-        <v>4199.683970527283</v>
+        <v>4199.788966636862</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -634,7 +634,7 @@
         <v>46017</v>
       </c>
       <c r="B31">
-        <v>4224.394552551024</v>
+        <v>4224.68429310102</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -642,7 +642,7 @@
         <v>46024</v>
       </c>
       <c r="B32">
-        <v>4245.206157791939</v>
+        <v>4245.499150498401</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -650,7 +650,7 @@
         <v>46031</v>
       </c>
       <c r="B33">
-        <v>4309.886942916892</v>
+        <v>4310.298184938423</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -658,7 +658,7 @@
         <v>46038</v>
       </c>
       <c r="B34">
-        <v>4402.352763664612</v>
+        <v>4402.872220183774</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -666,7 +666,7 @@
         <v>46045</v>
       </c>
       <c r="B35">
-        <v>4438.430453416902</v>
+        <v>4438.99487351887</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -674,7 +674,7 @@
         <v>46052</v>
       </c>
       <c r="B36">
-        <v>4540.165412694078</v>
+        <v>4540.919452145094</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -682,7 +682,7 @@
         <v>46059</v>
       </c>
       <c r="B37">
-        <v>4675.725766966627</v>
+        <v>4676.641489319274</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -690,7 +690,7 @@
         <v>46066</v>
       </c>
       <c r="B38">
-        <v>4757.61280731341</v>
+        <v>4758.79019595829</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -698,7 +698,7 @@
         <v>46073</v>
       </c>
       <c r="B39">
-        <v>4893.642040932781</v>
+        <v>4894.333417014481</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -706,7 +706,7 @@
         <v>46080</v>
       </c>
       <c r="B40">
-        <v>4934.807768222847</v>
+        <v>4935.567693384652</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -714,7 +714,7 @@
         <v>46087</v>
       </c>
       <c r="B41">
-        <v>5041.38504134315</v>
+        <v>5042.37737850092</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -722,7 +722,7 @@
         <v>46094</v>
       </c>
       <c r="B42">
-        <v>5209.260078545607</v>
+        <v>5209.822785245596</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>46101</v>
       </c>
       <c r="B43">
-        <v>5251.381905893492</v>
+        <v>5251.47207863428</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>46108</v>
       </c>
       <c r="B44">
-        <v>5292.32070975251</v>
+        <v>5291.714064479578</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>46115</v>
       </c>
       <c r="B45">
-        <v>5369.230763582384</v>
+        <v>5368.104789165367</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>46122</v>
       </c>
       <c r="B46">
-        <v>5446.012733924672</v>
+        <v>5444.553254872349</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>46129</v>
       </c>
       <c r="B47">
-        <v>5576.238724617158</v>
+        <v>5574.640503641733</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>46136</v>
       </c>
       <c r="B48">
-        <v>5516.219606621808</v>
+        <v>5514.18018487097</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>46143</v>
       </c>
       <c r="B49">
-        <v>5341.430540119305</v>
+        <v>5338.887571283622</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>46150</v>
       </c>
       <c r="B50">
-        <v>5224.851372567329</v>
+        <v>5222.45018880086</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>46157</v>
       </c>
       <c r="B51">
-        <v>5090.960541268378</v>
+        <v>5088.370061243029</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>46164</v>
       </c>
       <c r="B52">
-        <v>4976.996036031109</v>
+        <v>4974.648775707471</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>46171</v>
       </c>
       <c r="B53">
-        <v>4874.273509406828</v>
+        <v>4872.024812230896</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>46178</v>
       </c>
       <c r="B54">
-        <v>4825.835789483999</v>
+        <v>4823.292578780054</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>46185</v>
       </c>
       <c r="B55">
-        <v>4697.235227436689</v>
+        <v>4695.191447873056</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>46192</v>
       </c>
       <c r="B56">
-        <v>4575.752257115689</v>
+        <v>4574.326066579257</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>46199</v>
       </c>
       <c r="B57">
-        <v>4479.698850925341</v>
+        <v>4478.750033674451</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>46206</v>
       </c>
       <c r="B58">
-        <v>4474.861419015369</v>
+        <v>4473.893457101596</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>46213</v>
       </c>
       <c r="B59">
-        <v>4395.055326124963</v>
+        <v>4393.847747176507</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>46220</v>
       </c>
       <c r="B60">
-        <v>4237.232482118216</v>
+        <v>4235.621193084338</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>46227</v>
       </c>
       <c r="B61">
-        <v>4143.412574172269</v>
+        <v>4152.941293233309</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>46234</v>
       </c>
       <c r="B62">
-        <v>4093.676006502933</v>
+        <v>4095.7326626667</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>46241</v>
       </c>
       <c r="B63">
-        <v>4081.868637745796</v>
+        <v>4076.978109709695</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46248</v>
       </c>
       <c r="B64">
-        <v>4132.360418088714</v>
+        <v>4103.192548886312</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46255</v>
       </c>
       <c r="B65">
-        <v>4160.600788462237</v>
+        <v>4132.178401220677</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46262</v>
       </c>
       <c r="B66">
-        <v>4190.671695058522</v>
+        <v>4139.652225576492</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46269</v>
       </c>
       <c r="B67">
-        <v>4210.558889672378</v>
+        <v>4147.3617450299</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46276</v>
       </c>
       <c r="B68">
-        <v>4222.671582497543</v>
+        <v>4165.817547823533</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46283</v>
       </c>
       <c r="B69">
-        <v>4202.361149070261</v>
+        <v>4156.267203677895</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46290</v>
       </c>
       <c r="B70">
-        <v>4213.801939747435</v>
+        <v>4179.491616843233</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46297</v>
       </c>
       <c r="B71">
-        <v>4251.458067132485</v>
+        <v>4230.247517983142</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46304</v>
       </c>
       <c r="B72">
-        <v>4318.352210245206</v>
+        <v>4290.435597387672</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46311</v>
       </c>
       <c r="B73">
-        <v>4397.497054717855</v>
+        <v>4353.803822947952</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46318</v>
       </c>
       <c r="B74">
-        <v>4544.357399827592</v>
+        <v>4530.961935866516</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46325</v>
       </c>
       <c r="B75">
-        <v>4689.117017968462</v>
+        <v>4647.942899449564</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46332</v>
       </c>
       <c r="B76">
-        <v>4847.527696198764</v>
+        <v>4876.78883216198</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46339</v>
       </c>
       <c r="B77">
-        <v>5114.792651548965</v>
+        <v>5168.57317592096</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46346</v>
       </c>
       <c r="B78">
-        <v>4944.602298445623</v>
+        <v>5212.165701861657</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/XAUUSD_forecast.xlsx
+++ b/public/data/files/XAUUSD_forecast.xlsx
@@ -442,7 +442,7 @@
         <v>45849</v>
       </c>
       <c r="B7">
-        <v>3668.282854063651</v>
+        <v>3668.502255841849</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -450,7 +450,7 @@
         <v>45856</v>
       </c>
       <c r="B8">
-        <v>3565.268986413269</v>
+        <v>3565.56616194432</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -458,7 +458,7 @@
         <v>45863</v>
       </c>
       <c r="B9">
-        <v>3510.776112660337</v>
+        <v>3511.120332092541</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -466,7 +466,7 @@
         <v>45870</v>
       </c>
       <c r="B10">
-        <v>3483.164471893735</v>
+        <v>3483.530758896585</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -474,7 +474,7 @@
         <v>45877</v>
       </c>
       <c r="B11">
-        <v>3491.657556117776</v>
+        <v>3492.032817862349</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -482,7 +482,7 @@
         <v>45884</v>
       </c>
       <c r="B12">
-        <v>3504.439782403943</v>
+        <v>3504.819501163134</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -490,7 +490,7 @@
         <v>45891</v>
       </c>
       <c r="B13">
-        <v>3518.961080893522</v>
+        <v>3519.337958749287</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -498,7 +498,7 @@
         <v>45898</v>
       </c>
       <c r="B14">
-        <v>3531.474434003962</v>
+        <v>3531.845266104818</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -506,7 +506,7 @@
         <v>45905</v>
       </c>
       <c r="B15">
-        <v>3547.636091257609</v>
+        <v>3547.909579852719</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -514,7 +514,7 @@
         <v>45912</v>
       </c>
       <c r="B16">
-        <v>3452.776541264939</v>
+        <v>3452.706204655438</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -522,7 +522,7 @@
         <v>45919</v>
       </c>
       <c r="B17">
-        <v>3450.361766416372</v>
+        <v>3450.299761380426</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -530,7 +530,7 @@
         <v>45926</v>
       </c>
       <c r="B18">
-        <v>3450.436118645232</v>
+        <v>3450.378778314418</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -538,7 +538,7 @@
         <v>45933</v>
       </c>
       <c r="B19">
-        <v>3533.05675147382</v>
+        <v>3532.753480373555</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -546,7 +546,7 @@
         <v>45940</v>
       </c>
       <c r="B20">
-        <v>3630.296217268488</v>
+        <v>3629.713689239732</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -554,7 +554,7 @@
         <v>45947</v>
       </c>
       <c r="B21">
-        <v>3782.497546899269</v>
+        <v>3781.614266246398</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -562,7 +562,7 @@
         <v>45954</v>
       </c>
       <c r="B22">
-        <v>3853.531276242647</v>
+        <v>3852.739696446055</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -570,7 +570,7 @@
         <v>45961</v>
       </c>
       <c r="B23">
-        <v>3900.214039298813</v>
+        <v>3899.473111798991</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -578,7 +578,7 @@
         <v>45968</v>
       </c>
       <c r="B24">
-        <v>3885.491786872292</v>
+        <v>3884.849611587673</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -586,7 +586,7 @@
         <v>45975</v>
       </c>
       <c r="B25">
-        <v>3887.526444815364</v>
+        <v>3887.257340354658</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -594,7 +594,7 @@
         <v>45982</v>
       </c>
       <c r="B26">
-        <v>3993.824682175565</v>
+        <v>3993.736920983281</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -602,7 +602,7 @@
         <v>45989</v>
       </c>
       <c r="B27">
-        <v>4068.651906884155</v>
+        <v>4068.3830570237</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -610,7 +610,7 @@
         <v>45996</v>
       </c>
       <c r="B28">
-        <v>4108.778820299687</v>
+        <v>4108.447063383273</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -618,7 +618,7 @@
         <v>46003</v>
       </c>
       <c r="B29">
-        <v>4206.461605989329</v>
+        <v>4206.42686901871</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -626,7 +626,7 @@
         <v>46010</v>
       </c>
       <c r="B30">
-        <v>4199.788966636862</v>
+        <v>4199.650911835658</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -634,7 +634,7 @@
         <v>46017</v>
       </c>
       <c r="B31">
-        <v>4224.68429310102</v>
+        <v>4224.30315835441</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -642,7 +642,7 @@
         <v>46024</v>
       </c>
       <c r="B32">
-        <v>4245.499150498401</v>
+        <v>4245.113675240805</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -650,7 +650,7 @@
         <v>46031</v>
       </c>
       <c r="B33">
-        <v>4310.298184938423</v>
+        <v>4309.757066794591</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -658,7 +658,7 @@
         <v>46038</v>
       </c>
       <c r="B34">
-        <v>4402.872220183774</v>
+        <v>4402.188620810884</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -666,7 +666,7 @@
         <v>46045</v>
       </c>
       <c r="B35">
-        <v>4438.99487351887</v>
+        <v>4438.252002548472</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -674,7 +674,7 @@
         <v>46052</v>
       </c>
       <c r="B36">
-        <v>4540.919452145094</v>
+        <v>4539.9268922138</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -682,7 +682,7 @@
         <v>46059</v>
       </c>
       <c r="B37">
-        <v>4676.641489319274</v>
+        <v>4675.436131659488</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -690,7 +690,7 @@
         <v>46066</v>
       </c>
       <c r="B38">
-        <v>4758.79019595829</v>
+        <v>4757.23979960291</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -698,7 +698,7 @@
         <v>46073</v>
       </c>
       <c r="B39">
-        <v>4894.333417014481</v>
+        <v>4893.423311777828</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -706,7 +706,7 @@
         <v>46080</v>
       </c>
       <c r="B40">
-        <v>4935.567693384652</v>
+        <v>4934.5673434239</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -714,7 +714,7 @@
         <v>46087</v>
       </c>
       <c r="B41">
-        <v>5042.37737850092</v>
+        <v>5041.070943293307</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -722,7 +722,7 @@
         <v>46094</v>
       </c>
       <c r="B42">
-        <v>5209.822785245596</v>
+        <v>5209.081641973456</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>46101</v>
       </c>
       <c r="B43">
-        <v>5251.47207863428</v>
+        <v>5251.352433863053</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>46108</v>
       </c>
       <c r="B44">
-        <v>5291.714064479578</v>
+        <v>5292.511402916142</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>46115</v>
       </c>
       <c r="B45">
-        <v>5368.104789165367</v>
+        <v>5369.58605402965</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>46122</v>
       </c>
       <c r="B46">
-        <v>5444.553254872349</v>
+        <v>5446.473398154698</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>46129</v>
       </c>
       <c r="B47">
-        <v>5574.640503641733</v>
+        <v>5576.743339395486</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>46136</v>
       </c>
       <c r="B48">
-        <v>5514.18018487097</v>
+        <v>5516.864293708843</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>46143</v>
       </c>
       <c r="B49">
-        <v>5338.887571283622</v>
+        <v>5342.234865572428</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>46150</v>
       </c>
       <c r="B50">
-        <v>5222.45018880086</v>
+        <v>5225.611189007166</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>46157</v>
       </c>
       <c r="B51">
-        <v>5088.370061243029</v>
+        <v>5091.780789484691</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>46164</v>
       </c>
       <c r="B52">
-        <v>4974.648775707471</v>
+        <v>4977.739617090097</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>46171</v>
       </c>
       <c r="B53">
-        <v>4872.024812230896</v>
+        <v>4874.986336133807</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>46178</v>
       </c>
       <c r="B54">
-        <v>4823.292578780054</v>
+        <v>4826.642017047014</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>46185</v>
       </c>
       <c r="B55">
-        <v>4695.191447873056</v>
+        <v>4697.882993964157</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>46192</v>
       </c>
       <c r="B56">
-        <v>4574.326066579257</v>
+        <v>4576.203914624923</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>46199</v>
       </c>
       <c r="B57">
-        <v>4478.750033674451</v>
+        <v>4479.99869586145</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>46206</v>
       </c>
       <c r="B58">
-        <v>4473.893457101596</v>
+        <v>4475.167333470279</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>46213</v>
       </c>
       <c r="B59">
-        <v>4393.847747176507</v>
+        <v>4395.437322725921</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>46220</v>
       </c>
       <c r="B60">
-        <v>4235.621193084338</v>
+        <v>4237.743020372875</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>46227</v>
       </c>
       <c r="B61">
-        <v>4152.941293233309</v>
+        <v>4143.840535720228</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>46234</v>
       </c>
       <c r="B62">
-        <v>4095.7326626667</v>
+        <v>4093.947951645719</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>46241</v>
       </c>
       <c r="B63">
-        <v>4076.978109709695</v>
+        <v>4081.856331640744</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46248</v>
       </c>
       <c r="B64">
-        <v>4103.192548886312</v>
+        <v>4131.93913554111</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46255</v>
       </c>
       <c r="B65">
-        <v>4132.178401220677</v>
+        <v>4171.461756282233</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46262</v>
       </c>
       <c r="B66">
-        <v>4139.652225576492</v>
+        <v>4202.38088021051</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46269</v>
       </c>
       <c r="B67">
-        <v>4147.3617450299</v>
+        <v>4221.834338725638</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46276</v>
       </c>
       <c r="B68">
-        <v>4165.817547823533</v>
+        <v>4235.443252311667</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46283</v>
       </c>
       <c r="B69">
-        <v>4156.267203677895</v>
+        <v>4216.325918428457</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46290</v>
       </c>
       <c r="B70">
-        <v>4179.491616843233</v>
+        <v>4228.845591883265</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46297</v>
       </c>
       <c r="B71">
-        <v>4230.247517983142</v>
+        <v>4268.769132377298</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46304</v>
       </c>
       <c r="B72">
-        <v>4290.435597387672</v>
+        <v>4335.51399327314</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46311</v>
       </c>
       <c r="B73">
-        <v>4353.803822947952</v>
+        <v>4416.089136567687</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46318</v>
       </c>
       <c r="B74">
-        <v>4530.961935866516</v>
+        <v>4564.439784837527</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46325</v>
       </c>
       <c r="B75">
-        <v>4647.942899449564</v>
+        <v>4708.158115312641</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46332</v>
       </c>
       <c r="B76">
-        <v>4876.78883216198</v>
+        <v>4862.655732891091</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46339</v>
       </c>
       <c r="B77">
-        <v>5168.57317592096</v>
+        <v>5112.582472699358</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46346</v>
       </c>
       <c r="B78">
-        <v>5212.165701861657</v>
+        <v>5017.043061034579</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/XAUUSD_forecast.xlsx
+++ b/public/data/files/XAUUSD_forecast.xlsx
@@ -442,7 +442,7 @@
         <v>45849</v>
       </c>
       <c r="B7">
-        <v>3668.502255841849</v>
+        <v>3668.553635310398</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -450,7 +450,7 @@
         <v>45856</v>
       </c>
       <c r="B8">
-        <v>3565.56616194432</v>
+        <v>3565.635774428289</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -458,7 +458,7 @@
         <v>45863</v>
       </c>
       <c r="B9">
-        <v>3511.120332092541</v>
+        <v>3511.200985761343</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -466,7 +466,7 @@
         <v>45870</v>
       </c>
       <c r="B10">
-        <v>3483.530758896585</v>
+        <v>3483.616612100085</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -474,7 +474,7 @@
         <v>45877</v>
       </c>
       <c r="B11">
-        <v>3492.032817862349</v>
+        <v>3492.120773522528</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -482,7 +482,7 @@
         <v>45884</v>
       </c>
       <c r="B12">
-        <v>3504.819501163134</v>
+        <v>3504.908500305347</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -490,7 +490,7 @@
         <v>45891</v>
       </c>
       <c r="B13">
-        <v>3519.337958749287</v>
+        <v>3519.426291420607</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -498,7 +498,7 @@
         <v>45898</v>
       </c>
       <c r="B14">
-        <v>3531.845266104818</v>
+        <v>3531.932181747367</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -506,7 +506,7 @@
         <v>45905</v>
       </c>
       <c r="B15">
-        <v>3547.909579852719</v>
+        <v>3547.973756307796</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -514,7 +514,7 @@
         <v>45912</v>
       </c>
       <c r="B16">
-        <v>3452.706204655438</v>
+        <v>3452.689757311178</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -522,7 +522,7 @@
         <v>45919</v>
       </c>
       <c r="B17">
-        <v>3450.299761380426</v>
+        <v>3450.285265461652</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -530,7 +530,7 @@
         <v>45926</v>
       </c>
       <c r="B18">
-        <v>3450.378778314418</v>
+        <v>3450.365375163422</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -538,7 +538,7 @@
         <v>45933</v>
       </c>
       <c r="B19">
-        <v>3532.753480373555</v>
+        <v>3532.682534581269</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -546,7 +546,7 @@
         <v>45940</v>
       </c>
       <c r="B20">
-        <v>3629.713689239732</v>
+        <v>3629.577369555376</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -554,7 +554,7 @@
         <v>45947</v>
       </c>
       <c r="B21">
-        <v>3781.614266246398</v>
+        <v>3781.407460152392</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -562,7 +562,7 @@
         <v>45954</v>
       </c>
       <c r="B22">
-        <v>3852.739696446055</v>
+        <v>3852.554317099486</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -570,7 +570,7 @@
         <v>45961</v>
       </c>
       <c r="B23">
-        <v>3899.473111798991</v>
+        <v>3899.299388443543</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -578,7 +578,7 @@
         <v>45968</v>
       </c>
       <c r="B24">
-        <v>3884.849611587673</v>
+        <v>3884.698941718379</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -586,7 +586,7 @@
         <v>45975</v>
       </c>
       <c r="B25">
-        <v>3887.257340354658</v>
+        <v>3887.194087623229</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -594,7 +594,7 @@
         <v>45982</v>
       </c>
       <c r="B26">
-        <v>3993.736920983281</v>
+        <v>3993.716224993204</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -602,7 +602,7 @@
         <v>45989</v>
       </c>
       <c r="B27">
-        <v>4068.3830570237</v>
+        <v>4068.320001170668</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -610,7 +610,7 @@
         <v>45996</v>
       </c>
       <c r="B28">
-        <v>4108.447063383273</v>
+        <v>4108.369262841888</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -618,7 +618,7 @@
         <v>46003</v>
       </c>
       <c r="B29">
-        <v>4206.42686901871</v>
+        <v>4206.418840963475</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -626,7 +626,7 @@
         <v>46010</v>
       </c>
       <c r="B30">
-        <v>4199.650911835658</v>
+        <v>4199.618757319507</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -634,7 +634,7 @@
         <v>46017</v>
       </c>
       <c r="B31">
-        <v>4224.30315835441</v>
+        <v>4224.214186030507</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -642,7 +642,7 @@
         <v>46024</v>
       </c>
       <c r="B32">
-        <v>4245.113675240805</v>
+        <v>4245.023614574337</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -650,7 +650,7 @@
         <v>46031</v>
       </c>
       <c r="B33">
-        <v>4309.757066794591</v>
+        <v>4309.630560146502</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -658,7 +658,7 @@
         <v>46038</v>
       </c>
       <c r="B34">
-        <v>4402.188620810884</v>
+        <v>4402.028694348717</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -666,7 +666,7 @@
         <v>46045</v>
       </c>
       <c r="B35">
-        <v>4438.252002548472</v>
+        <v>4438.078089118339</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -674,7 +674,7 @@
         <v>46052</v>
       </c>
       <c r="B36">
-        <v>4539.9268922138</v>
+        <v>4539.694381617863</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -682,7 +682,7 @@
         <v>46059</v>
       </c>
       <c r="B37">
-        <v>4675.436131659488</v>
+        <v>4675.153807833954</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -690,7 +690,7 @@
         <v>46066</v>
       </c>
       <c r="B38">
-        <v>4757.23979960291</v>
+        <v>4756.875925407074</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -698,7 +698,7 @@
         <v>46073</v>
       </c>
       <c r="B39">
-        <v>4893.423311777828</v>
+        <v>4893.210079859969</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -706,7 +706,7 @@
         <v>46080</v>
       </c>
       <c r="B40">
-        <v>4934.5673434239</v>
+        <v>4934.332956993289</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -714,7 +714,7 @@
         <v>46087</v>
       </c>
       <c r="B41">
-        <v>5041.070943293307</v>
+        <v>5040.764668264714</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -722,7 +722,7 @@
         <v>46094</v>
       </c>
       <c r="B42">
-        <v>5209.081641973456</v>
+        <v>5208.907498398734</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>46101</v>
       </c>
       <c r="B43">
-        <v>5251.352433863053</v>
+        <v>5251.32326621866</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>46108</v>
       </c>
       <c r="B44">
-        <v>5292.511402916142</v>
+        <v>5292.696734986253</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>46115</v>
       </c>
       <c r="B45">
-        <v>5369.58605402965</v>
+        <v>5369.931984534616</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>46122</v>
       </c>
       <c r="B46">
-        <v>5446.473398154698</v>
+        <v>5446.921990647643</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>46129</v>
       </c>
       <c r="B47">
-        <v>5576.743339395486</v>
+        <v>5577.234804542299</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>46136</v>
       </c>
       <c r="B48">
-        <v>5516.864293708843</v>
+        <v>5517.492537813407</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>46143</v>
       </c>
       <c r="B49">
-        <v>5342.234865572428</v>
+        <v>5343.018888546962</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>46150</v>
       </c>
       <c r="B50">
-        <v>5225.611189007166</v>
+        <v>5226.351982027229</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>46157</v>
       </c>
       <c r="B51">
-        <v>5091.780789484691</v>
+        <v>5092.58074722007</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>46164</v>
       </c>
       <c r="B52">
-        <v>4977.739617090097</v>
+        <v>4978.464965101324</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>46171</v>
       </c>
       <c r="B53">
-        <v>4874.986336133807</v>
+        <v>4875.681900850246</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>46178</v>
       </c>
       <c r="B54">
-        <v>4826.642017047014</v>
+        <v>4827.428739621735</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>46185</v>
       </c>
       <c r="B55">
-        <v>4697.882993964157</v>
+        <v>4698.51502685217</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>46192</v>
       </c>
       <c r="B56">
-        <v>4576.203914624923</v>
+        <v>4576.644432298242</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>46199</v>
       </c>
       <c r="B57">
-        <v>4479.99869586145</v>
+        <v>4480.290851758208</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>46206</v>
       </c>
       <c r="B58">
-        <v>4475.167333470279</v>
+        <v>4475.465412511066</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>46213</v>
       </c>
       <c r="B59">
-        <v>4395.437322725921</v>
+        <v>4395.809698461042</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>46220</v>
       </c>
       <c r="B60">
-        <v>4237.743020372875</v>
+        <v>4238.241085138141</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>46227</v>
       </c>
       <c r="B61">
-        <v>4143.840535720228</v>
+        <v>4144.258649677393</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>46234</v>
       </c>
       <c r="B62">
-        <v>4093.947951645719</v>
+        <v>4094.214130421173</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>46241</v>
       </c>
       <c r="B63">
-        <v>4081.856331640744</v>
+        <v>4081.845697922904</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46248</v>
       </c>
       <c r="B64">
-        <v>4131.93913554111</v>
+        <v>4131.529755522071</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46255</v>
       </c>
       <c r="B65">
-        <v>4171.461756282233</v>
+        <v>4186.813427587492</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46262</v>
       </c>
       <c r="B66">
-        <v>4202.38088021051</v>
+        <v>4219.331920828325</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46269</v>
       </c>
       <c r="B67">
-        <v>4221.834338725638</v>
+        <v>4240.761548513081</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46276</v>
       </c>
       <c r="B68">
-        <v>4235.443252311667</v>
+        <v>4254.670283876272</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46283</v>
       </c>
       <c r="B69">
-        <v>4216.325918428457</v>
+        <v>4236.921879122595</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46290</v>
       </c>
       <c r="B70">
-        <v>4228.845591883265</v>
+        <v>4252.912293450007</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46297</v>
       </c>
       <c r="B71">
-        <v>4268.769132377298</v>
+        <v>4294.440980977616</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46304</v>
       </c>
       <c r="B72">
-        <v>4335.51399327314</v>
+        <v>4362.607243688512</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46311</v>
       </c>
       <c r="B73">
-        <v>4416.089136567687</v>
+        <v>4444.118679633762</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46318</v>
       </c>
       <c r="B74">
-        <v>4564.439784837527</v>
+        <v>4596.676220339808</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46325</v>
       </c>
       <c r="B75">
-        <v>4708.158115312641</v>
+        <v>4742.986442700872</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46332</v>
       </c>
       <c r="B76">
-        <v>4862.655732891091</v>
+        <v>4898.156437841292</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46339</v>
       </c>
       <c r="B77">
-        <v>5112.582472699358</v>
+        <v>5140.6520749564</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46346</v>
       </c>
       <c r="B78">
-        <v>5017.043061034579</v>
+        <v>5125.128439812424</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/XAUUSD_forecast.xlsx
+++ b/public/data/files/XAUUSD_forecast.xlsx
@@ -442,7 +442,7 @@
         <v>45849</v>
       </c>
       <c r="B7">
-        <v>3668.553635310398</v>
+        <v>3668.603730495488</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -450,7 +450,7 @@
         <v>45856</v>
       </c>
       <c r="B8">
-        <v>3565.635774428289</v>
+        <v>3565.703654165675</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -458,7 +458,7 @@
         <v>45863</v>
       </c>
       <c r="B9">
-        <v>3511.200985761343</v>
+        <v>3511.279639622669</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -466,7 +466,7 @@
         <v>45870</v>
       </c>
       <c r="B10">
-        <v>3483.616612100085</v>
+        <v>3483.7003471202</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -474,7 +474,7 @@
         <v>45877</v>
       </c>
       <c r="B11">
-        <v>3492.120773522528</v>
+        <v>3492.206558720212</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -482,7 +482,7 @@
         <v>45884</v>
       </c>
       <c r="B12">
-        <v>3504.908500305347</v>
+        <v>3504.99530280645</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -490,7 +490,7 @@
         <v>45891</v>
       </c>
       <c r="B13">
-        <v>3519.426291420607</v>
+        <v>3519.512443676223</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -498,7 +498,7 @@
         <v>45898</v>
       </c>
       <c r="B14">
-        <v>3531.932181747367</v>
+        <v>3532.0169519439</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -506,7 +506,7 @@
         <v>45905</v>
       </c>
       <c r="B15">
-        <v>3547.973756307796</v>
+        <v>3548.036376425242</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -514,7 +514,7 @@
         <v>45912</v>
       </c>
       <c r="B16">
-        <v>3452.689757311178</v>
+        <v>3452.673729885822</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -522,7 +522,7 @@
         <v>45919</v>
       </c>
       <c r="B17">
-        <v>3450.285265461652</v>
+        <v>3450.271140807161</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -530,7 +530,7 @@
         <v>45926</v>
       </c>
       <c r="B18">
-        <v>3450.365375163422</v>
+        <v>3450.352316103274</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -538,7 +538,7 @@
         <v>45933</v>
       </c>
       <c r="B19">
-        <v>3532.682534581269</v>
+        <v>3532.613389300653</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -546,7 +546,7 @@
         <v>45940</v>
       </c>
       <c r="B20">
-        <v>3629.577369555376</v>
+        <v>3629.444492773896</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -554,7 +554,7 @@
         <v>45947</v>
       </c>
       <c r="B21">
-        <v>3781.407460152392</v>
+        <v>3781.205838387134</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -562,7 +562,7 @@
         <v>45954</v>
       </c>
       <c r="B22">
-        <v>3852.554317099486</v>
+        <v>3852.373568966768</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -570,7 +570,7 @@
         <v>45961</v>
       </c>
       <c r="B23">
-        <v>3899.299388443543</v>
+        <v>3899.129929880188</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -578,7 +578,7 @@
         <v>45968</v>
       </c>
       <c r="B24">
-        <v>3884.698941718379</v>
+        <v>3884.551933956822</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -586,7 +586,7 @@
         <v>45975</v>
       </c>
       <c r="B25">
-        <v>3887.194087623229</v>
+        <v>3887.132330528968</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -594,7 +594,7 @@
         <v>45982</v>
       </c>
       <c r="B26">
-        <v>3993.716224993204</v>
+        <v>3993.695993637305</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -602,7 +602,7 @@
         <v>45989</v>
       </c>
       <c r="B27">
-        <v>4068.320001170668</v>
+        <v>4068.258486111031</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -610,7 +610,7 @@
         <v>45996</v>
       </c>
       <c r="B28">
-        <v>4108.369262841888</v>
+        <v>4108.293366897901</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -618,7 +618,7 @@
         <v>46003</v>
       </c>
       <c r="B29">
-        <v>4206.418840963475</v>
+        <v>4206.411052551941</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -626,7 +626,7 @@
         <v>46010</v>
       </c>
       <c r="B30">
-        <v>4199.618757319507</v>
+        <v>4199.58747063541</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -634,7 +634,7 @@
         <v>46017</v>
       </c>
       <c r="B31">
-        <v>4224.214186030507</v>
+        <v>4224.12754090584</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -642,7 +642,7 @@
         <v>46024</v>
       </c>
       <c r="B32">
-        <v>4245.023614574337</v>
+        <v>4244.93588222278</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -650,7 +650,7 @@
         <v>46031</v>
       </c>
       <c r="B33">
-        <v>4309.630560146502</v>
+        <v>4309.507293952271</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -658,7 +658,7 @@
         <v>46038</v>
       </c>
       <c r="B34">
-        <v>4402.028694348717</v>
+        <v>4401.872824390421</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -666,7 +666,7 @@
         <v>46045</v>
       </c>
       <c r="B35">
-        <v>4438.078089118339</v>
+        <v>4437.908542651739</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -674,7 +674,7 @@
         <v>46052</v>
       </c>
       <c r="B36">
-        <v>4539.694381617863</v>
+        <v>4539.467657019295</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -682,7 +682,7 @@
         <v>46059</v>
       </c>
       <c r="B37">
-        <v>4675.153807833954</v>
+        <v>4674.87852268021</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -690,7 +690,7 @@
         <v>46066</v>
       </c>
       <c r="B38">
-        <v>4756.875925407074</v>
+        <v>4756.5208540314</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -698,7 +698,7 @@
         <v>46073</v>
       </c>
       <c r="B39">
-        <v>4893.210079859969</v>
+        <v>4893.002140998306</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -706,7 +706,7 @@
         <v>46080</v>
       </c>
       <c r="B40">
-        <v>4934.332956993289</v>
+        <v>4934.104384798263</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -714,7 +714,7 @@
         <v>46087</v>
       </c>
       <c r="B41">
-        <v>5040.764668264714</v>
+        <v>5040.46592852613</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -722,7 +722,7 @@
         <v>46094</v>
       </c>
       <c r="B42">
-        <v>5208.907498398734</v>
+        <v>5208.737495484962</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>46101</v>
       </c>
       <c r="B43">
-        <v>5251.32326621866</v>
+        <v>5251.294408057169</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>46108</v>
       </c>
       <c r="B44">
-        <v>5292.696734986253</v>
+        <v>5292.87692636159</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>46115</v>
       </c>
       <c r="B45">
-        <v>5369.931984534616</v>
+        <v>5370.268918893485</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>46122</v>
       </c>
       <c r="B46">
-        <v>5446.921990647643</v>
+        <v>5447.35897805543</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>46129</v>
       </c>
       <c r="B47">
-        <v>5577.234804542299</v>
+        <v>5577.713625919354</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>46136</v>
       </c>
       <c r="B48">
-        <v>5517.492537813407</v>
+        <v>5518.104958776796</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>46143</v>
       </c>
       <c r="B49">
-        <v>5343.018888546962</v>
+        <v>5343.783366012016</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>46150</v>
       </c>
       <c r="B50">
-        <v>5226.351982027229</v>
+        <v>5227.074455051579</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>46157</v>
       </c>
       <c r="B51">
-        <v>5092.58074722007</v>
+        <v>5093.3611555687</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>46164</v>
       </c>
       <c r="B52">
-        <v>4978.464965101324</v>
+        <v>4979.172740553324</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>46171</v>
       </c>
       <c r="B53">
-        <v>4875.681900850246</v>
+        <v>4876.360820741713</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>46178</v>
       </c>
       <c r="B54">
-        <v>4827.428739621735</v>
+        <v>4828.196653719895</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>46185</v>
       </c>
       <c r="B55">
-        <v>4698.51502685217</v>
+        <v>4699.131890483627</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>46192</v>
       </c>
       <c r="B56">
-        <v>4576.644432298242</v>
+        <v>4577.07421620261</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>46199</v>
       </c>
       <c r="B57">
-        <v>4480.290851758208</v>
+        <v>4480.575609683026</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>46206</v>
       </c>
       <c r="B58">
-        <v>4475.465412511066</v>
+        <v>4475.755952556515</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>46213</v>
       </c>
       <c r="B59">
-        <v>4395.809698461042</v>
+        <v>4396.172811091834</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>46220</v>
       </c>
       <c r="B60">
-        <v>4238.241085138141</v>
+        <v>4238.727125215359</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>46227</v>
       </c>
       <c r="B61">
-        <v>4144.258649677393</v>
+        <v>4144.667246962435</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>46234</v>
       </c>
       <c r="B62">
-        <v>4094.214130421173</v>
+        <v>4094.474717586249</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>46241</v>
       </c>
       <c r="B63">
-        <v>4081.845697922904</v>
+        <v>4081.836627685272</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46248</v>
       </c>
       <c r="B64">
-        <v>4131.529755522071</v>
+        <v>4131.131798689578</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46255</v>
       </c>
       <c r="B65">
-        <v>4186.813427587492</v>
+        <v>4201.265238473846</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46262</v>
       </c>
       <c r="B66">
-        <v>4219.331920828325</v>
+        <v>4234.969571529734</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46269</v>
       </c>
       <c r="B67">
-        <v>4240.761548513081</v>
+        <v>4258.189693064141</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46276</v>
       </c>
       <c r="B68">
-        <v>4254.670283876272</v>
+        <v>4272.166715986263</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46283</v>
       </c>
       <c r="B69">
-        <v>4236.921879122595</v>
+        <v>4256.236691311186</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46290</v>
       </c>
       <c r="B70">
-        <v>4252.912293450007</v>
+        <v>4274.645368779377</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46297</v>
       </c>
       <c r="B71">
-        <v>4294.440980977616</v>
+        <v>4318.87740883939</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46304</v>
       </c>
       <c r="B72">
-        <v>4362.607243688512</v>
+        <v>4389.268570932223</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46311</v>
       </c>
       <c r="B73">
-        <v>4444.118679633762</v>
+        <v>4472.609874746599</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46318</v>
       </c>
       <c r="B74">
-        <v>4596.676220339808</v>
+        <v>4628.141742038968</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46325</v>
       </c>
       <c r="B75">
-        <v>4742.986442700872</v>
+        <v>4775.306860570761</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46332</v>
       </c>
       <c r="B76">
-        <v>4898.156437841292</v>
+        <v>4930.639457940932</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46339</v>
       </c>
       <c r="B77">
-        <v>5140.6520749564</v>
+        <v>5172.550104538162</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46346</v>
       </c>
       <c r="B78">
-        <v>5125.128439812424</v>
+        <v>5215.718182167932</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/XAUUSD_forecast.xlsx
+++ b/public/data/files/XAUUSD_forecast.xlsx
@@ -442,7 +442,7 @@
         <v>45849</v>
       </c>
       <c r="B7">
-        <v>3668.603730495488</v>
+        <v>3668.65258895332</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -450,7 +450,7 @@
         <v>45856</v>
       </c>
       <c r="B8">
-        <v>3565.703654165675</v>
+        <v>3565.769865049097</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -458,7 +458,7 @@
         <v>45863</v>
       </c>
       <c r="B9">
-        <v>3511.279639622669</v>
+        <v>3511.356367127565</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -466,7 +466,7 @@
         <v>45870</v>
       </c>
       <c r="B10">
-        <v>3483.7003471202</v>
+        <v>3483.782041362559</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -474,7 +474,7 @@
         <v>45877</v>
       </c>
       <c r="B11">
-        <v>3492.206558720212</v>
+        <v>3492.290252786313</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -482,7 +482,7 @@
         <v>45884</v>
       </c>
       <c r="B12">
-        <v>3504.99530280645</v>
+        <v>3505.079988970059</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -490,7 +490,7 @@
         <v>45891</v>
       </c>
       <c r="B13">
-        <v>3519.512443676223</v>
+        <v>3519.596495235062</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -498,7 +498,7 @@
         <v>45898</v>
       </c>
       <c r="B14">
-        <v>3532.0169519439</v>
+        <v>3532.099655135271</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -506,7 +506,7 @@
         <v>45905</v>
       </c>
       <c r="B15">
-        <v>3548.036376425242</v>
+        <v>3548.097496074933</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -514,7 +514,7 @@
         <v>45912</v>
       </c>
       <c r="B16">
-        <v>3452.673729885822</v>
+        <v>3452.658106510637</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -522,7 +522,7 @@
         <v>45919</v>
       </c>
       <c r="B17">
-        <v>3450.271140807161</v>
+        <v>3450.257373345091</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -530,7 +530,7 @@
         <v>45926</v>
       </c>
       <c r="B18">
-        <v>3450.352316103274</v>
+        <v>3450.339588063012</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -538,7 +538,7 @@
         <v>45933</v>
       </c>
       <c r="B19">
-        <v>3532.613389300653</v>
+        <v>3532.545976886517</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -546,7 +546,7 @@
         <v>45940</v>
       </c>
       <c r="B20">
-        <v>3629.444492773896</v>
+        <v>3629.314930174985</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -554,7 +554,7 @@
         <v>45947</v>
       </c>
       <c r="B21">
-        <v>3781.205838387134</v>
+        <v>3781.009208532205</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -562,7 +562,7 @@
         <v>45954</v>
       </c>
       <c r="B22">
-        <v>3852.373568966768</v>
+        <v>3852.197280713537</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -570,7 +570,7 @@
         <v>45961</v>
       </c>
       <c r="B23">
-        <v>3899.129929880188</v>
+        <v>3898.964581138167</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -578,7 +578,7 @@
         <v>45968</v>
       </c>
       <c r="B24">
-        <v>3884.551933956822</v>
+        <v>3884.408456605266</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -586,7 +586,7 @@
         <v>45975</v>
       </c>
       <c r="B25">
-        <v>3887.132330528968</v>
+        <v>3887.072016828097</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -594,7 +594,7 @@
         <v>45982</v>
       </c>
       <c r="B26">
-        <v>3993.695993637305</v>
+        <v>3993.676211621502</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -602,7 +602,7 @@
         <v>45989</v>
       </c>
       <c r="B27">
-        <v>4068.258486111031</v>
+        <v>4068.198456064421</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -610,7 +610,7 @@
         <v>45996</v>
       </c>
       <c r="B28">
-        <v>4108.293366897901</v>
+        <v>4108.219306491646</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -618,7 +618,7 @@
         <v>46003</v>
       </c>
       <c r="B29">
-        <v>4206.411052551941</v>
+        <v>4206.403493488529</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -626,7 +626,7 @@
         <v>46010</v>
       </c>
       <c r="B30">
-        <v>4199.58747063541</v>
+        <v>4199.557017350721</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -634,7 +634,7 @@
         <v>46017</v>
       </c>
       <c r="B31">
-        <v>4224.12754090584</v>
+        <v>4224.043133162476</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -642,7 +642,7 @@
         <v>46024</v>
       </c>
       <c r="B32">
-        <v>4244.93588222278</v>
+        <v>4244.850389359546</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -650,7 +650,7 @@
         <v>46031</v>
       </c>
       <c r="B33">
-        <v>4309.507293952271</v>
+        <v>4309.387145675581</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -658,7 +658,7 @@
         <v>46038</v>
       </c>
       <c r="B34">
-        <v>4401.872824390421</v>
+        <v>4401.720859007046</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -666,7 +666,7 @@
         <v>46045</v>
       </c>
       <c r="B35">
-        <v>4437.908542651739</v>
+        <v>4437.7432010885</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -674,7 +674,7 @@
         <v>46052</v>
       </c>
       <c r="B36">
-        <v>4539.467657019295</v>
+        <v>4539.246505494798</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -682,7 +682,7 @@
         <v>46059</v>
       </c>
       <c r="B37">
-        <v>4674.87852268021</v>
+        <v>4674.610016765566</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -690,7 +690,7 @@
         <v>46066</v>
       </c>
       <c r="B38">
-        <v>4756.5208540314</v>
+        <v>4756.174270520675</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -698,7 +698,7 @@
         <v>46073</v>
       </c>
       <c r="B39">
-        <v>4893.002140998306</v>
+        <v>4892.79930097649</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -706,7 +706,7 @@
         <v>46080</v>
       </c>
       <c r="B40">
-        <v>4934.104384798263</v>
+        <v>4933.881413637415</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -714,7 +714,7 @@
         <v>46087</v>
       </c>
       <c r="B41">
-        <v>5040.46592852613</v>
+        <v>5040.174450240265</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -722,7 +722,7 @@
         <v>46094</v>
       </c>
       <c r="B42">
-        <v>5208.737495484962</v>
+        <v>5208.571487981219</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>46101</v>
       </c>
       <c r="B43">
-        <v>5251.294408057169</v>
+        <v>5251.26586341349</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>46108</v>
       </c>
       <c r="B44">
-        <v>5292.87692636159</v>
+        <v>5293.052185634797</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>46115</v>
       </c>
       <c r="B45">
-        <v>5370.268918893485</v>
+        <v>5370.597202349882</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>46122</v>
       </c>
       <c r="B46">
-        <v>5447.35897805543</v>
+        <v>5447.784803364488</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>46129</v>
       </c>
       <c r="B47">
-        <v>5577.713625919354</v>
+        <v>5578.180283841509</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>46136</v>
       </c>
       <c r="B48">
-        <v>5518.104958776796</v>
+        <v>5518.702145735488</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>46143</v>
       </c>
       <c r="B49">
-        <v>5343.783366012016</v>
+        <v>5344.529017871205</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>46150</v>
       </c>
       <c r="B50">
-        <v>5227.074455051579</v>
+        <v>5227.779277351179</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>46157</v>
       </c>
       <c r="B51">
-        <v>5093.3611555687</v>
+        <v>5094.122720094478</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>46164</v>
       </c>
       <c r="B52">
-        <v>4979.172740553324</v>
+        <v>4979.86357251211</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>46171</v>
       </c>
       <c r="B53">
-        <v>4876.360820741713</v>
+        <v>4877.023684033047</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>46178</v>
       </c>
       <c r="B54">
-        <v>4828.196653719895</v>
+        <v>4828.94642322053</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>46185</v>
       </c>
       <c r="B55">
-        <v>4699.131890483627</v>
+        <v>4699.734122663189</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>46192</v>
       </c>
       <c r="B56">
-        <v>4577.07421620261</v>
+        <v>4577.493652956817</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>46199</v>
       </c>
       <c r="B57">
-        <v>4480.575609683026</v>
+        <v>4480.853246240236</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>46206</v>
       </c>
       <c r="B58">
-        <v>4475.755952556515</v>
+        <v>4476.039235298393</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>46213</v>
       </c>
       <c r="B59">
-        <v>4396.172811091834</v>
+        <v>4396.527000915596</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>46220</v>
       </c>
       <c r="B60">
-        <v>4238.727125215359</v>
+        <v>4239.201568267621</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>46227</v>
       </c>
       <c r="B61">
-        <v>4144.667246962435</v>
+        <v>4145.066644090689</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>46234</v>
       </c>
       <c r="B62">
-        <v>4094.474717586249</v>
+        <v>4094.729881268976</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>46241</v>
       </c>
       <c r="B63">
-        <v>4081.836627685272</v>
+        <v>4081.829019417384</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46248</v>
       </c>
       <c r="B64">
-        <v>4131.131798689578</v>
+        <v>4130.744810348853</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46255</v>
       </c>
       <c r="B65">
-        <v>4201.265238473846</v>
+        <v>4215.332772278942</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46262</v>
       </c>
       <c r="B66">
-        <v>4234.969571529734</v>
+        <v>4250.149867480444</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46269</v>
       </c>
       <c r="B67">
-        <v>4258.189693064141</v>
+        <v>4275.125670455212</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46276</v>
       </c>
       <c r="B68">
-        <v>4272.166715986263</v>
+        <v>4288.651909709639</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46283</v>
       </c>
       <c r="B69">
-        <v>4256.236691311186</v>
+        <v>4274.450027720159</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46290</v>
       </c>
       <c r="B70">
-        <v>4274.645368779377</v>
+        <v>4294.88924547747</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46297</v>
       </c>
       <c r="B71">
-        <v>4318.87740883939</v>
+        <v>4341.556450110174</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46304</v>
       </c>
       <c r="B72">
-        <v>4389.268570932223</v>
+        <v>4414.007078028674</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46311</v>
       </c>
       <c r="B73">
-        <v>4472.609874746599</v>
+        <v>4499.030217672692</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46318</v>
       </c>
       <c r="B74">
-        <v>4628.141742038968</v>
+        <v>4656.931573360696</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46325</v>
       </c>
       <c r="B75">
-        <v>4775.306860570761</v>
+        <v>4804.230688161579</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46332</v>
       </c>
       <c r="B76">
-        <v>4930.639457940932</v>
+        <v>4958.999528875196</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46339</v>
       </c>
       <c r="B77">
-        <v>5172.550104538162</v>
+        <v>5198.475223461868</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46346</v>
       </c>
       <c r="B78">
-        <v>5215.718182167932</v>
+        <v>5274.924435060602</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/XAUUSD_forecast.xlsx
+++ b/public/data/files/XAUUSD_forecast.xlsx
@@ -383,7 +383,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B78"/>
+  <dimension ref="A1:B79"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" style="1" customWidth="1"/>
@@ -442,7 +442,7 @@
         <v>45849</v>
       </c>
       <c r="B7">
-        <v>3668.65258895332</v>
+        <v>3668.44954206386</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -450,7 +450,7 @@
         <v>45856</v>
       </c>
       <c r="B8">
-        <v>3565.769865049097</v>
+        <v>3565.494749517899</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -458,7 +458,7 @@
         <v>45863</v>
       </c>
       <c r="B9">
-        <v>3511.356367127565</v>
+        <v>3511.03760138386</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -466,7 +466,7 @@
         <v>45870</v>
       </c>
       <c r="B10">
-        <v>3483.782041362559</v>
+        <v>3483.442706141038</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -474,7 +474,7 @@
         <v>45877</v>
       </c>
       <c r="B11">
-        <v>3492.290252786313</v>
+        <v>3491.94260834635</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -482,7 +482,7 @@
         <v>45884</v>
       </c>
       <c r="B12">
-        <v>3505.079988970059</v>
+        <v>3504.728220963094</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -490,7 +490,7 @@
         <v>45891</v>
       </c>
       <c r="B13">
-        <v>3519.596495235062</v>
+        <v>3519.247361859713</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -498,7 +498,7 @@
         <v>45898</v>
       </c>
       <c r="B14">
-        <v>3532.099655135271</v>
+        <v>3531.756122557202</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -506,7 +506,7 @@
         <v>45905</v>
       </c>
       <c r="B15">
-        <v>3548.097496074933</v>
+        <v>3547.843788385377</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -514,7 +514,7 @@
         <v>45912</v>
       </c>
       <c r="B16">
-        <v>3452.658106510637</v>
+        <v>3452.723088628761</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -522,7 +522,7 @@
         <v>45919</v>
       </c>
       <c r="B17">
-        <v>3450.257373345091</v>
+        <v>3450.314643383729</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -530,7 +530,7 @@
         <v>45926</v>
       </c>
       <c r="B18">
-        <v>3450.339588063012</v>
+        <v>3450.39253932393</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -538,7 +538,7 @@
         <v>45933</v>
       </c>
       <c r="B19">
-        <v>3532.545976886517</v>
+        <v>3532.826297887808</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -546,7 +546,7 @@
         <v>45940</v>
       </c>
       <c r="B20">
-        <v>3629.314930174985</v>
+        <v>3629.853587295738</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -554,7 +554,7 @@
         <v>45947</v>
       </c>
       <c r="B21">
-        <v>3781.009208532205</v>
+        <v>3781.826459099066</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -562,7 +562,7 @@
         <v>45954</v>
       </c>
       <c r="B22">
-        <v>3852.197280713537</v>
+        <v>3852.929887226679</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -570,7 +570,7 @@
         <v>45961</v>
       </c>
       <c r="B23">
-        <v>3898.964581138167</v>
+        <v>3899.651262797883</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -578,7 +578,7 @@
         <v>45968</v>
       </c>
       <c r="B24">
-        <v>3884.408456605266</v>
+        <v>3885.004081882903</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -586,7 +586,7 @@
         <v>45975</v>
       </c>
       <c r="B25">
-        <v>3887.072016828097</v>
+        <v>3887.322143508117</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -594,7 +594,7 @@
         <v>45982</v>
       </c>
       <c r="B26">
-        <v>3993.676211621502</v>
+        <v>3993.758097592456</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -602,7 +602,7 @@
         <v>45989</v>
       </c>
       <c r="B27">
-        <v>4068.198456064421</v>
+        <v>4068.447712278904</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -610,7 +610,7 @@
         <v>45996</v>
       </c>
       <c r="B28">
-        <v>4108.219306491646</v>
+        <v>4108.526841088225</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -618,7 +618,7 @@
         <v>46003</v>
       </c>
       <c r="B29">
-        <v>4206.403493488529</v>
+        <v>4206.435147625212</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -626,7 +626,7 @@
         <v>46010</v>
       </c>
       <c r="B30">
-        <v>4199.557017350721</v>
+        <v>4199.683970527283</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -634,7 +634,7 @@
         <v>46017</v>
       </c>
       <c r="B31">
-        <v>4224.043133162476</v>
+        <v>4224.394552551024</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -642,7 +642,7 @@
         <v>46024</v>
       </c>
       <c r="B32">
-        <v>4244.850389359546</v>
+        <v>4245.206157791939</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -650,7 +650,7 @@
         <v>46031</v>
       </c>
       <c r="B33">
-        <v>4309.387145675581</v>
+        <v>4309.886942916892</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -658,7 +658,7 @@
         <v>46038</v>
       </c>
       <c r="B34">
-        <v>4401.720859007046</v>
+        <v>4402.352763664612</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -666,7 +666,7 @@
         <v>46045</v>
       </c>
       <c r="B35">
-        <v>4437.7432010885</v>
+        <v>4438.430453416902</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -674,7 +674,7 @@
         <v>46052</v>
       </c>
       <c r="B36">
-        <v>4539.246505494798</v>
+        <v>4540.165412694078</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -682,7 +682,7 @@
         <v>46059</v>
       </c>
       <c r="B37">
-        <v>4674.610016765566</v>
+        <v>4675.725766966627</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -690,7 +690,7 @@
         <v>46066</v>
       </c>
       <c r="B38">
-        <v>4756.174270520675</v>
+        <v>4757.61280731341</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -698,7 +698,7 @@
         <v>46073</v>
       </c>
       <c r="B39">
-        <v>4892.79930097649</v>
+        <v>4893.642040932781</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -706,7 +706,7 @@
         <v>46080</v>
       </c>
       <c r="B40">
-        <v>4933.881413637415</v>
+        <v>4934.807768222847</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -714,7 +714,7 @@
         <v>46087</v>
       </c>
       <c r="B41">
-        <v>5040.174450240265</v>
+        <v>5041.38504134315</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -722,7 +722,7 @@
         <v>46094</v>
       </c>
       <c r="B42">
-        <v>5208.571487981219</v>
+        <v>5209.260078545607</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>46101</v>
       </c>
       <c r="B43">
-        <v>5251.26586341349</v>
+        <v>5251.381905893492</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>46108</v>
       </c>
       <c r="B44">
-        <v>5293.052185634797</v>
+        <v>5292.32070975251</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>46115</v>
       </c>
       <c r="B45">
-        <v>5370.597202349882</v>
+        <v>5369.230763582384</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>46122</v>
       </c>
       <c r="B46">
-        <v>5447.784803364488</v>
+        <v>5446.012733924672</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>46129</v>
       </c>
       <c r="B47">
-        <v>5578.180283841509</v>
+        <v>5576.238724617158</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>46136</v>
       </c>
       <c r="B48">
-        <v>5518.702145735488</v>
+        <v>5516.219606621808</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>46143</v>
       </c>
       <c r="B49">
-        <v>5344.529017871205</v>
+        <v>5341.430540119305</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>46150</v>
       </c>
       <c r="B50">
-        <v>5227.779277351179</v>
+        <v>5224.851372567329</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>46157</v>
       </c>
       <c r="B51">
-        <v>5094.122720094478</v>
+        <v>5090.960541268378</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>46164</v>
       </c>
       <c r="B52">
-        <v>4979.86357251211</v>
+        <v>4976.996036031109</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>46171</v>
       </c>
       <c r="B53">
-        <v>4877.023684033047</v>
+        <v>4874.273509406828</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>46178</v>
       </c>
       <c r="B54">
-        <v>4828.94642322053</v>
+        <v>4825.835789483999</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>46185</v>
       </c>
       <c r="B55">
-        <v>4699.734122663189</v>
+        <v>4697.235227436689</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>46192</v>
       </c>
       <c r="B56">
-        <v>4577.493652956817</v>
+        <v>4575.752257115689</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>46199</v>
       </c>
       <c r="B57">
-        <v>4480.853246240236</v>
+        <v>4479.698850925341</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>46206</v>
       </c>
       <c r="B58">
-        <v>4476.039235298393</v>
+        <v>4474.861419015369</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>46213</v>
       </c>
       <c r="B59">
-        <v>4396.527000915596</v>
+        <v>4395.055326124963</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>46220</v>
       </c>
       <c r="B60">
-        <v>4239.201568267621</v>
+        <v>4237.232482118216</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>46227</v>
       </c>
       <c r="B61">
-        <v>4145.066644090689</v>
+        <v>4154.300008820161</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>46234</v>
       </c>
       <c r="B62">
-        <v>4094.729881268976</v>
+        <v>4096.593229875479</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>46241</v>
       </c>
       <c r="B63">
-        <v>4081.829019417384</v>
+        <v>4077.052953876782</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46248</v>
       </c>
       <c r="B64">
-        <v>4130.744810348853</v>
+        <v>4102.268782564225</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46255</v>
       </c>
       <c r="B65">
-        <v>4215.332772278942</v>
+        <v>4167.37797060263</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46262</v>
       </c>
       <c r="B66">
-        <v>4250.149867480444</v>
+        <v>4200.871903510024</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46269</v>
       </c>
       <c r="B67">
-        <v>4275.125670455212</v>
+        <v>4216.687356022559</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46276</v>
       </c>
       <c r="B68">
-        <v>4288.651909709639</v>
+        <v>4239.484703235986</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46283</v>
       </c>
       <c r="B69">
-        <v>4274.450027720159</v>
+        <v>4237.248701367762</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46290</v>
       </c>
       <c r="B70">
-        <v>4294.88924547747</v>
+        <v>4265.175160238483</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46297</v>
       </c>
       <c r="B71">
-        <v>4341.556450110174</v>
+        <v>4319.499876121308</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46304</v>
       </c>
       <c r="B72">
-        <v>4414.007078028674</v>
+        <v>4386.225445177681</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46311</v>
       </c>
       <c r="B73">
-        <v>4499.030217672692</v>
+        <v>4460.151220753198</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46318</v>
       </c>
       <c r="B74">
-        <v>4656.931573360696</v>
+        <v>4650.395423472578</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46325</v>
       </c>
       <c r="B75">
-        <v>4804.230688161579</v>
+        <v>4782.75799672109</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46332</v>
       </c>
       <c r="B76">
-        <v>4958.999528875196</v>
+        <v>5010.739238777565</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46339</v>
       </c>
       <c r="B77">
-        <v>5198.475223461868</v>
+        <v>5288.733346923287</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,15 @@
         <v>46346</v>
       </c>
       <c r="B78">
-        <v>5274.924435060602</v>
+        <v>5434.072399166921</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2">
+      <c r="A79" s="3">
+        <v>46353</v>
+      </c>
+      <c r="B79">
+        <v>5580.112879408987</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/XAUUSD_forecast.xlsx
+++ b/public/data/files/XAUUSD_forecast.xlsx
@@ -442,7 +442,7 @@
         <v>45849</v>
       </c>
       <c r="B7">
-        <v>3668.44954206386</v>
+        <v>3668.700255920871</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -450,7 +450,7 @@
         <v>45856</v>
       </c>
       <c r="B8">
-        <v>3565.494749517899</v>
+        <v>3565.834467868408</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -458,7 +458,7 @@
         <v>45863</v>
       </c>
       <c r="B9">
-        <v>3511.03760138386</v>
+        <v>3511.431238174297</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -466,7 +466,7 @@
         <v>45870</v>
       </c>
       <c r="B10">
-        <v>3483.442706141038</v>
+        <v>3483.861768508029</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -474,7 +474,7 @@
         <v>45877</v>
       </c>
       <c r="B11">
-        <v>3491.94260834635</v>
+        <v>3492.371931233626</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -482,7 +482,7 @@
         <v>45884</v>
       </c>
       <c r="B12">
-        <v>3504.728220963094</v>
+        <v>3505.162635234089</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -490,7 +490,7 @@
         <v>45891</v>
       </c>
       <c r="B13">
-        <v>3519.247361859713</v>
+        <v>3519.67852197807</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -498,7 +498,7 @@
         <v>45898</v>
       </c>
       <c r="B14">
-        <v>3531.756122557202</v>
+        <v>3532.180365985856</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -506,7 +506,7 @@
         <v>45905</v>
       </c>
       <c r="B15">
-        <v>3547.843788385377</v>
+        <v>3548.157168487396</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -514,7 +514,7 @@
         <v>45912</v>
       </c>
       <c r="B16">
-        <v>3452.723088628761</v>
+        <v>3452.642872106046</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -522,7 +522,7 @@
         <v>45919</v>
       </c>
       <c r="B17">
-        <v>3450.314643383729</v>
+        <v>3450.243949705346</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -530,7 +530,7 @@
         <v>45926</v>
       </c>
       <c r="B18">
-        <v>3450.39253932393</v>
+        <v>3450.32717862489</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -538,7 +538,7 @@
         <v>45933</v>
       </c>
       <c r="B19">
-        <v>3532.826297887808</v>
+        <v>3532.480233038544</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -546,7 +546,7 @@
         <v>45940</v>
       </c>
       <c r="B20">
-        <v>3629.853587295738</v>
+        <v>3629.188559372003</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -554,7 +554,7 @@
         <v>45947</v>
       </c>
       <c r="B21">
-        <v>3781.826459099066</v>
+        <v>3780.817387569663</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -562,7 +562,7 @@
         <v>45954</v>
       </c>
       <c r="B22">
-        <v>3852.929887226679</v>
+        <v>3852.025289350502</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -570,7 +570,7 @@
         <v>45961</v>
       </c>
       <c r="B23">
-        <v>3899.651262797883</v>
+        <v>3898.80319465687</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -578,7 +578,7 @@
         <v>45968</v>
       </c>
       <c r="B24">
-        <v>3885.004081882903</v>
+        <v>3884.268384195702</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -586,7 +586,7 @@
         <v>45975</v>
       </c>
       <c r="B25">
-        <v>3887.322143508117</v>
+        <v>3887.013096672913</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -594,7 +594,7 @@
         <v>45982</v>
       </c>
       <c r="B26">
-        <v>3993.758097592456</v>
+        <v>3993.656864306329</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -602,7 +602,7 @@
         <v>45989</v>
       </c>
       <c r="B27">
-        <v>4068.447712278904</v>
+        <v>4068.139857910327</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -610,7 +610,7 @@
         <v>45996</v>
       </c>
       <c r="B28">
-        <v>4108.526841088225</v>
+        <v>4108.147015860795</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -618,7 +618,7 @@
         <v>46003</v>
       </c>
       <c r="B29">
-        <v>4206.435147625212</v>
+        <v>4206.396154047959</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -626,7 +626,7 @@
         <v>46010</v>
       </c>
       <c r="B30">
-        <v>4199.683970527283</v>
+        <v>4199.527364820246</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -634,7 +634,7 @@
         <v>46017</v>
       </c>
       <c r="B31">
-        <v>4224.394552551024</v>
+        <v>4223.960877531574</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -642,7 +642,7 @@
         <v>46024</v>
       </c>
       <c r="B32">
-        <v>4245.206157791939</v>
+        <v>4244.76705160534</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -650,7 +650,7 @@
         <v>46031</v>
       </c>
       <c r="B33">
-        <v>4309.886942916892</v>
+        <v>4309.26999886305</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -658,7 +658,7 @@
         <v>46038</v>
       </c>
       <c r="B34">
-        <v>4402.352763664612</v>
+        <v>4401.572653740694</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -666,7 +666,7 @@
         <v>46045</v>
       </c>
       <c r="B35">
-        <v>4438.430453416902</v>
+        <v>4437.581910271332</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -674,7 +674,7 @@
         <v>46052</v>
       </c>
       <c r="B36">
-        <v>4540.165412694078</v>
+        <v>4539.030724422964</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -682,7 +682,7 @@
         <v>46059</v>
       </c>
       <c r="B37">
-        <v>4675.725766966627</v>
+        <v>4674.348043226145</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -690,7 +690,7 @@
         <v>46066</v>
       </c>
       <c r="B38">
-        <v>4757.61280731341</v>
+        <v>4755.835874735702</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -698,7 +698,7 @@
         <v>46073</v>
       </c>
       <c r="B39">
-        <v>4893.642040932781</v>
+        <v>4892.601374943568</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -706,7 +706,7 @@
         <v>46080</v>
       </c>
       <c r="B40">
-        <v>4934.807768222847</v>
+        <v>4933.663840583808</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -714,7 +714,7 @@
         <v>46087</v>
       </c>
       <c r="B41">
-        <v>5041.38504134315</v>
+        <v>5039.889972637889</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -722,7 +722,7 @@
         <v>46094</v>
       </c>
       <c r="B42">
-        <v>5209.260078545607</v>
+        <v>5208.409337317255</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>46101</v>
       </c>
       <c r="B43">
-        <v>5251.381905893492</v>
+        <v>5251.237635374298</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>46108</v>
       </c>
       <c r="B44">
-        <v>5292.32070975251</v>
+        <v>5293.222710366371</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>46115</v>
       </c>
       <c r="B45">
-        <v>5369.230763582384</v>
+        <v>5370.917162759199</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>46122</v>
       </c>
       <c r="B46">
-        <v>5446.012733924672</v>
+        <v>5448.199887372463</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>46129</v>
       </c>
       <c r="B47">
-        <v>5576.238724617158</v>
+        <v>5578.635234665127</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>46136</v>
       </c>
       <c r="B48">
-        <v>5516.219606621808</v>
+        <v>5519.284658995415</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>46143</v>
       </c>
       <c r="B49">
-        <v>5341.430540119305</v>
+        <v>5345.256529197699</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>46150</v>
       </c>
       <c r="B50">
-        <v>5224.851372567329</v>
+        <v>5228.467086085504</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>46157</v>
       </c>
       <c r="B51">
-        <v>5090.960541268378</v>
+        <v>5094.866112927479</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>46164</v>
       </c>
       <c r="B52">
-        <v>4976.996036031109</v>
+        <v>4980.538060461938</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>46171</v>
       </c>
       <c r="B53">
-        <v>4874.273509406828</v>
+        <v>4877.671051660358</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>46178</v>
       </c>
       <c r="B54">
-        <v>4825.835789483999</v>
+        <v>4829.678681250467</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>46185</v>
       </c>
       <c r="B55">
-        <v>4697.235227436689</v>
+        <v>4700.322236157812</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>46192</v>
       </c>
       <c r="B56">
-        <v>4575.752257115689</v>
+        <v>4577.903110878986</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>46199</v>
       </c>
       <c r="B57">
-        <v>4479.698850925341</v>
+        <v>4481.12402445578</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>46206</v>
       </c>
       <c r="B58">
-        <v>4474.861419015369</v>
+        <v>4476.315528602575</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>46213</v>
       </c>
       <c r="B59">
-        <v>4395.055326124963</v>
+        <v>4396.872591814812</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>46220</v>
       </c>
       <c r="B60">
-        <v>4237.232482118216</v>
+        <v>4239.664822041454</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>46227</v>
       </c>
       <c r="B61">
-        <v>4154.300008820161</v>
+        <v>4145.457143932907</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>46234</v>
       </c>
       <c r="B62">
-        <v>4096.593229875479</v>
+        <v>4094.979783254895</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>46241</v>
       </c>
       <c r="B63">
-        <v>4077.052953876782</v>
+        <v>4081.822778448297</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46248</v>
       </c>
       <c r="B64">
-        <v>4102.268782564225</v>
+        <v>4130.368358928408</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46255</v>
       </c>
       <c r="B65">
-        <v>4167.37797060263</v>
+        <v>4214.542480517088</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46262</v>
       </c>
       <c r="B66">
-        <v>4200.871903510024</v>
+        <v>4263.418704675658</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46269</v>
       </c>
       <c r="B67">
-        <v>4216.687356022559</v>
+        <v>4288.637469877824</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46276</v>
       </c>
       <c r="B68">
-        <v>4239.484703235986</v>
+        <v>4301.055115630956</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46283</v>
       </c>
       <c r="B69">
-        <v>4237.248701367762</v>
+        <v>4290.152345437751</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46290</v>
       </c>
       <c r="B70">
-        <v>4265.175160238483</v>
+        <v>4313.00016976325</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46297</v>
       </c>
       <c r="B71">
-        <v>4319.499876121308</v>
+        <v>4360.001763503212</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46304</v>
       </c>
       <c r="B72">
-        <v>4386.225445177681</v>
+        <v>4434.585572306783</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46311</v>
       </c>
       <c r="B73">
-        <v>4460.151220753198</v>
+        <v>4520.977124735962</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46318</v>
       </c>
       <c r="B74">
-        <v>4650.395423472578</v>
+        <v>4677.757529774619</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46325</v>
       </c>
       <c r="B75">
-        <v>4782.75799672109</v>
+        <v>4825.390219073062</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46332</v>
       </c>
       <c r="B76">
-        <v>5010.739238777565</v>
+        <v>4978.054089897347</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46339</v>
       </c>
       <c r="B77">
-        <v>5288.733346923287</v>
+        <v>5211.917070793143</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46346</v>
       </c>
       <c r="B78">
-        <v>5434.072399166921</v>
+        <v>5302.924826546717</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46353</v>
       </c>
       <c r="B79">
-        <v>5580.112879408987</v>
+        <v>5511.154826546715</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/XAUUSD_forecast.xlsx
+++ b/public/data/files/XAUUSD_forecast.xlsx
@@ -442,7 +442,7 @@
         <v>45849</v>
       </c>
       <c r="B7">
-        <v>3668.700255920871</v>
+        <v>3668.502255841849</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -450,7 +450,7 @@
         <v>45856</v>
       </c>
       <c r="B8">
-        <v>3565.834467868408</v>
+        <v>3565.56616194432</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -458,7 +458,7 @@
         <v>45863</v>
       </c>
       <c r="B9">
-        <v>3511.431238174297</v>
+        <v>3511.120332092541</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -466,7 +466,7 @@
         <v>45870</v>
       </c>
       <c r="B10">
-        <v>3483.861768508029</v>
+        <v>3483.530758896585</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -474,7 +474,7 @@
         <v>45877</v>
       </c>
       <c r="B11">
-        <v>3492.371931233626</v>
+        <v>3492.032817862349</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -482,7 +482,7 @@
         <v>45884</v>
       </c>
       <c r="B12">
-        <v>3505.162635234089</v>
+        <v>3504.819501163134</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -490,7 +490,7 @@
         <v>45891</v>
       </c>
       <c r="B13">
-        <v>3519.67852197807</v>
+        <v>3519.337958749287</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -498,7 +498,7 @@
         <v>45898</v>
       </c>
       <c r="B14">
-        <v>3532.180365985856</v>
+        <v>3531.845266104818</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -506,7 +506,7 @@
         <v>45905</v>
       </c>
       <c r="B15">
-        <v>3548.157168487396</v>
+        <v>3547.909579852719</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -514,7 +514,7 @@
         <v>45912</v>
       </c>
       <c r="B16">
-        <v>3452.642872106046</v>
+        <v>3452.706204655438</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -522,7 +522,7 @@
         <v>45919</v>
       </c>
       <c r="B17">
-        <v>3450.243949705346</v>
+        <v>3450.299761380426</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -530,7 +530,7 @@
         <v>45926</v>
       </c>
       <c r="B18">
-        <v>3450.32717862489</v>
+        <v>3450.378778314418</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -538,7 +538,7 @@
         <v>45933</v>
       </c>
       <c r="B19">
-        <v>3532.480233038544</v>
+        <v>3532.753480373555</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -546,7 +546,7 @@
         <v>45940</v>
       </c>
       <c r="B20">
-        <v>3629.188559372003</v>
+        <v>3629.713689239732</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -554,7 +554,7 @@
         <v>45947</v>
       </c>
       <c r="B21">
-        <v>3780.817387569663</v>
+        <v>3781.614266246398</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -562,7 +562,7 @@
         <v>45954</v>
       </c>
       <c r="B22">
-        <v>3852.025289350502</v>
+        <v>3852.739696446055</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -570,7 +570,7 @@
         <v>45961</v>
       </c>
       <c r="B23">
-        <v>3898.80319465687</v>
+        <v>3899.473111798991</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -578,7 +578,7 @@
         <v>45968</v>
       </c>
       <c r="B24">
-        <v>3884.268384195702</v>
+        <v>3884.849611587673</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -586,7 +586,7 @@
         <v>45975</v>
       </c>
       <c r="B25">
-        <v>3887.013096672913</v>
+        <v>3887.257340354658</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -594,7 +594,7 @@
         <v>45982</v>
       </c>
       <c r="B26">
-        <v>3993.656864306329</v>
+        <v>3993.736920983281</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -602,7 +602,7 @@
         <v>45989</v>
       </c>
       <c r="B27">
-        <v>4068.139857910327</v>
+        <v>4068.3830570237</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -610,7 +610,7 @@
         <v>45996</v>
       </c>
       <c r="B28">
-        <v>4108.147015860795</v>
+        <v>4108.447063383273</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -618,7 +618,7 @@
         <v>46003</v>
       </c>
       <c r="B29">
-        <v>4206.396154047959</v>
+        <v>4206.42686901871</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -626,7 +626,7 @@
         <v>46010</v>
       </c>
       <c r="B30">
-        <v>4199.527364820246</v>
+        <v>4199.650911835658</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -634,7 +634,7 @@
         <v>46017</v>
       </c>
       <c r="B31">
-        <v>4223.960877531574</v>
+        <v>4224.30315835441</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -642,7 +642,7 @@
         <v>46024</v>
       </c>
       <c r="B32">
-        <v>4244.76705160534</v>
+        <v>4245.113675240805</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -650,7 +650,7 @@
         <v>46031</v>
       </c>
       <c r="B33">
-        <v>4309.26999886305</v>
+        <v>4309.757066794591</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -658,7 +658,7 @@
         <v>46038</v>
       </c>
       <c r="B34">
-        <v>4401.572653740694</v>
+        <v>4402.188620810884</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -666,7 +666,7 @@
         <v>46045</v>
       </c>
       <c r="B35">
-        <v>4437.581910271332</v>
+        <v>4438.252002548472</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -674,7 +674,7 @@
         <v>46052</v>
       </c>
       <c r="B36">
-        <v>4539.030724422964</v>
+        <v>4539.9268922138</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -682,7 +682,7 @@
         <v>46059</v>
       </c>
       <c r="B37">
-        <v>4674.348043226145</v>
+        <v>4675.436131659488</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -690,7 +690,7 @@
         <v>46066</v>
       </c>
       <c r="B38">
-        <v>4755.835874735702</v>
+        <v>4757.23979960291</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -698,7 +698,7 @@
         <v>46073</v>
       </c>
       <c r="B39">
-        <v>4892.601374943568</v>
+        <v>4893.423311777828</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -706,7 +706,7 @@
         <v>46080</v>
       </c>
       <c r="B40">
-        <v>4933.663840583808</v>
+        <v>4934.5673434239</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -714,7 +714,7 @@
         <v>46087</v>
       </c>
       <c r="B41">
-        <v>5039.889972637889</v>
+        <v>5041.070943293307</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -722,7 +722,7 @@
         <v>46094</v>
       </c>
       <c r="B42">
-        <v>5208.409337317255</v>
+        <v>5209.081641973456</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>46101</v>
       </c>
       <c r="B43">
-        <v>5251.237635374298</v>
+        <v>5251.352433863053</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>46108</v>
       </c>
       <c r="B44">
-        <v>5293.222710366371</v>
+        <v>5292.511402916142</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>46115</v>
       </c>
       <c r="B45">
-        <v>5370.917162759199</v>
+        <v>5369.58605402965</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>46122</v>
       </c>
       <c r="B46">
-        <v>5448.199887372463</v>
+        <v>5446.473398154698</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>46129</v>
       </c>
       <c r="B47">
-        <v>5578.635234665127</v>
+        <v>5576.743339395486</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>46136</v>
       </c>
       <c r="B48">
-        <v>5519.284658995415</v>
+        <v>5516.864293708843</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>46143</v>
       </c>
       <c r="B49">
-        <v>5345.256529197699</v>
+        <v>5342.234865572428</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>46150</v>
       </c>
       <c r="B50">
-        <v>5228.467086085504</v>
+        <v>5225.611189007166</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>46157</v>
       </c>
       <c r="B51">
-        <v>5094.866112927479</v>
+        <v>5091.780789484691</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>46164</v>
       </c>
       <c r="B52">
-        <v>4980.538060461938</v>
+        <v>4977.739617090097</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>46171</v>
       </c>
       <c r="B53">
-        <v>4877.671051660358</v>
+        <v>4874.986336133807</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>46178</v>
       </c>
       <c r="B54">
-        <v>4829.678681250467</v>
+        <v>4826.642017047014</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>46185</v>
       </c>
       <c r="B55">
-        <v>4700.322236157812</v>
+        <v>4697.882993964157</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>46192</v>
       </c>
       <c r="B56">
-        <v>4577.903110878986</v>
+        <v>4576.203914624923</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>46199</v>
       </c>
       <c r="B57">
-        <v>4481.12402445578</v>
+        <v>4479.99869586145</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>46206</v>
       </c>
       <c r="B58">
-        <v>4476.315528602575</v>
+        <v>4475.167333470279</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>46213</v>
       </c>
       <c r="B59">
-        <v>4396.872591814812</v>
+        <v>4395.437322725921</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>46220</v>
       </c>
       <c r="B60">
-        <v>4239.664822041454</v>
+        <v>4237.743020372875</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>46227</v>
       </c>
       <c r="B61">
-        <v>4145.457143932907</v>
+        <v>4154.731508142031</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>46234</v>
       </c>
       <c r="B62">
-        <v>4094.979783254895</v>
+        <v>4096.867706326531</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>46241</v>
       </c>
       <c r="B63">
-        <v>4081.822778448297</v>
+        <v>4077.079414235765</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46248</v>
       </c>
       <c r="B64">
-        <v>4130.368358928408</v>
+        <v>4101.979583998513</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46255</v>
       </c>
       <c r="B65">
-        <v>4214.542480517088</v>
+        <v>4166.67530875079</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46262</v>
       </c>
       <c r="B66">
-        <v>4263.418704675658</v>
+        <v>4216.89084257334</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46269</v>
       </c>
       <c r="B67">
-        <v>4288.637469877824</v>
+        <v>4233.84757673785</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46276</v>
       </c>
       <c r="B68">
-        <v>4301.055115630956</v>
+        <v>4255.596133169482</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46283</v>
       </c>
       <c r="B69">
-        <v>4290.152345437751</v>
+        <v>4257.426498130539</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46290</v>
       </c>
       <c r="B70">
-        <v>4313.00016976325</v>
+        <v>4286.727868615724</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46297</v>
       </c>
       <c r="B71">
-        <v>4360.001763503212</v>
+        <v>4342.009273166135</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46304</v>
       </c>
       <c r="B72">
-        <v>4434.585572306783</v>
+        <v>4410.933718902131</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46311</v>
       </c>
       <c r="B73">
-        <v>4520.977124735962</v>
+        <v>4486.994483541623</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46318</v>
       </c>
       <c r="B74">
-        <v>4677.757529774619</v>
+        <v>4675.398173949068</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46325</v>
       </c>
       <c r="B75">
-        <v>4825.390219073062</v>
+        <v>4808.547032517785</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46332</v>
       </c>
       <c r="B76">
-        <v>4978.054089897347</v>
+        <v>5026.50836250604</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46339</v>
       </c>
       <c r="B77">
-        <v>5211.917070793143</v>
+        <v>5289.336812998143</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46346</v>
       </c>
       <c r="B78">
-        <v>5302.924826546717</v>
+        <v>5437.694781059167</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46353</v>
       </c>
       <c r="B79">
-        <v>5511.154826546715</v>
+        <v>5566.8424770019</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/XAUUSD_forecast.xlsx
+++ b/public/data/files/XAUUSD_forecast.xlsx
@@ -442,7 +442,7 @@
         <v>45849</v>
       </c>
       <c r="B7">
-        <v>3668.502255841849</v>
+        <v>3668.746774455567</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -450,7 +450,7 @@
         <v>45856</v>
       </c>
       <c r="B8">
-        <v>3565.56616194432</v>
+        <v>3565.897520496765</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -458,7 +458,7 @@
         <v>45863</v>
       </c>
       <c r="B9">
-        <v>3511.120332092541</v>
+        <v>3511.504319320547</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -466,7 +466,7 @@
         <v>45870</v>
       </c>
       <c r="B10">
-        <v>3483.530758896585</v>
+        <v>3483.939598734022</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -474,7 +474,7 @@
         <v>45877</v>
       </c>
       <c r="B11">
-        <v>3492.032817862349</v>
+        <v>3492.451665983723</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -482,7 +482,7 @@
         <v>45884</v>
       </c>
       <c r="B12">
-        <v>3504.819501163134</v>
+        <v>3505.24331440051</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -490,7 +490,7 @@
         <v>45891</v>
       </c>
       <c r="B13">
-        <v>3519.337958749287</v>
+        <v>3519.758596176352</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -498,7 +498,7 @@
         <v>45898</v>
       </c>
       <c r="B14">
-        <v>3531.845266104818</v>
+        <v>3532.259155608043</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -506,7 +506,7 @@
         <v>45905</v>
       </c>
       <c r="B15">
-        <v>3547.909579852719</v>
+        <v>3548.215444407652</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -514,7 +514,7 @@
         <v>45912</v>
       </c>
       <c r="B16">
-        <v>3452.706204655438</v>
+        <v>3452.628012333199</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -522,7 +522,7 @@
         <v>45919</v>
       </c>
       <c r="B17">
-        <v>3450.299761380426</v>
+        <v>3450.230857176422</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -530,7 +530,7 @@
         <v>45926</v>
       </c>
       <c r="B18">
-        <v>3450.378778314418</v>
+        <v>3450.315075984108</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -538,7 +538,7 @@
         <v>45933</v>
       </c>
       <c r="B19">
-        <v>3532.753480373555</v>
+        <v>3532.416096597177</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -546,7 +546,7 @@
         <v>45940</v>
       </c>
       <c r="B20">
-        <v>3629.713689239732</v>
+        <v>3629.065263927385</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -554,7 +554,7 @@
         <v>45947</v>
       </c>
       <c r="B21">
-        <v>3781.614266246398</v>
+        <v>3780.630201315225</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -562,7 +562,7 @@
         <v>45954</v>
       </c>
       <c r="B22">
-        <v>3852.739696446055</v>
+        <v>3851.857439731697</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -570,7 +570,7 @@
         <v>45961</v>
       </c>
       <c r="B23">
-        <v>3899.473111798991</v>
+        <v>3898.645629848651</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -578,7 +578,7 @@
         <v>45968</v>
       </c>
       <c r="B24">
-        <v>3884.849611587673</v>
+        <v>3884.131597126424</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -586,7 +586,7 @@
         <v>45975</v>
       </c>
       <c r="B25">
-        <v>3887.257340354658</v>
+        <v>3886.955522476545</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -594,7 +594,7 @@
         <v>45982</v>
       </c>
       <c r="B26">
-        <v>3993.736920983281</v>
+        <v>3993.637937672877</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -602,7 +602,7 @@
         <v>45989</v>
       </c>
       <c r="B27">
-        <v>4068.3830570237</v>
+        <v>4068.082641031448</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -610,7 +610,7 @@
         <v>45996</v>
       </c>
       <c r="B28">
-        <v>4108.447063383273</v>
+        <v>4108.076432345971</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -618,7 +618,7 @@
         <v>46003</v>
       </c>
       <c r="B29">
-        <v>4206.42686901871</v>
+        <v>4206.389025036859</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -626,7 +626,7 @@
         <v>46010</v>
       </c>
       <c r="B30">
-        <v>4199.650911835658</v>
+        <v>4199.498482072306</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -634,7 +634,7 @@
         <v>46017</v>
       </c>
       <c r="B31">
-        <v>4224.30315835441</v>
+        <v>4223.880693009789</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -642,7 +642,7 @@
         <v>46024</v>
       </c>
       <c r="B32">
-        <v>4245.113675240805</v>
+        <v>4244.685788754088</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -650,7 +650,7 @@
         <v>46031</v>
       </c>
       <c r="B33">
-        <v>4309.757066794591</v>
+        <v>4309.155742772447</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -658,7 +658,7 @@
         <v>46038</v>
       </c>
       <c r="B34">
-        <v>4402.188620810884</v>
+        <v>4401.428071152168</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -666,7 +666,7 @@
         <v>46045</v>
       </c>
       <c r="B35">
-        <v>4438.252002548472</v>
+        <v>4437.424523470951</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -674,7 +674,7 @@
         <v>46052</v>
       </c>
       <c r="B36">
-        <v>4539.9268922138</v>
+        <v>4538.820120869794</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -682,7 +682,7 @@
         <v>46059</v>
       </c>
       <c r="B37">
-        <v>4675.436131659488</v>
+        <v>4674.092367016363</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -690,7 +690,7 @@
         <v>46066</v>
       </c>
       <c r="B38">
-        <v>4757.23979960291</v>
+        <v>4755.505380494103</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -698,7 +698,7 @@
         <v>46073</v>
       </c>
       <c r="B39">
-        <v>4893.423311777828</v>
+        <v>4892.408186857467</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -706,7 +706,7 @@
         <v>46080</v>
       </c>
       <c r="B40">
-        <v>4934.5673434239</v>
+        <v>4933.451472374809</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -714,7 +714,7 @@
         <v>46087</v>
       </c>
       <c r="B41">
-        <v>5041.070943293307</v>
+        <v>5039.612247249937</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -722,7 +722,7 @@
         <v>46094</v>
       </c>
       <c r="B42">
-        <v>5209.081641973456</v>
+        <v>5208.250911225915</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>46101</v>
       </c>
       <c r="B43">
-        <v>5251.352433863053</v>
+        <v>5251.209726180016</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>46108</v>
       </c>
       <c r="B44">
-        <v>5292.511402916142</v>
+        <v>5293.388687798929</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>46115</v>
       </c>
       <c r="B45">
-        <v>5369.58605402965</v>
+        <v>5371.229111666556</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>46122</v>
       </c>
       <c r="B46">
-        <v>5446.473398154698</v>
+        <v>5448.604630056063</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>46129</v>
       </c>
       <c r="B47">
-        <v>5576.743339395486</v>
+        <v>5579.078912259729</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>46136</v>
       </c>
       <c r="B48">
-        <v>5516.864293708843</v>
+        <v>5519.853031770872</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>46143</v>
       </c>
       <c r="B49">
-        <v>5342.234865572428</v>
+        <v>5345.966552309928</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>46150</v>
       </c>
       <c r="B50">
-        <v>5225.611189007166</v>
+        <v>5229.138488199911</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>46157</v>
       </c>
       <c r="B51">
-        <v>5091.780789484691</v>
+        <v>5095.59197471428</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>46164</v>
       </c>
       <c r="B52">
-        <v>4977.739617090097</v>
+        <v>4981.196776018565</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>46171</v>
       </c>
       <c r="B53">
-        <v>4874.986336133807</v>
+        <v>4878.303458828985</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>46178</v>
       </c>
       <c r="B54">
-        <v>4826.642017047014</v>
+        <v>4830.394031936877</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>46185</v>
       </c>
       <c r="B55">
-        <v>4697.882993964157</v>
+        <v>4700.896720131775</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>46192</v>
       </c>
       <c r="B56">
-        <v>4576.203914624923</v>
+        <v>4578.30294105399</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>46199</v>
       </c>
       <c r="B57">
-        <v>4479.99869586145</v>
+        <v>4481.388194597901</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>46206</v>
       </c>
       <c r="B58">
-        <v>4475.167333470279</v>
+        <v>4476.585087344964</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>46213</v>
       </c>
       <c r="B59">
-        <v>4395.437322725921</v>
+        <v>4397.209892232047</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>46220</v>
       </c>
       <c r="B60">
-        <v>4237.743020372875</v>
+        <v>4240.117275505349</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>46227</v>
       </c>
       <c r="B61">
-        <v>4154.731508142031</v>
+        <v>4145.839036427792</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>46234</v>
       </c>
       <c r="B62">
-        <v>4096.867706326531</v>
+        <v>4095.224579260924</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>46241</v>
       </c>
       <c r="B63">
-        <v>4077.079414235765</v>
+        <v>4081.817816436196</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46248</v>
       </c>
       <c r="B64">
-        <v>4101.979583998513</v>
+        <v>4130.002034565177</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46255</v>
       </c>
       <c r="B65">
-        <v>4166.67530875079</v>
+        <v>4213.77153973854</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46262</v>
       </c>
       <c r="B66">
-        <v>4216.89084257334</v>
+        <v>4275.654325435953</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46269</v>
       </c>
       <c r="B67">
-        <v>4233.84757673785</v>
+        <v>4301.000109538846</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46276</v>
       </c>
       <c r="B68">
-        <v>4255.596133169482</v>
+        <v>4312.24871459053</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46283</v>
       </c>
       <c r="B69">
-        <v>4257.426498130539</v>
+        <v>4304.729133693678</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46290</v>
       </c>
       <c r="B70">
-        <v>4286.727868615724</v>
+        <v>4329.512339438493</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46297</v>
       </c>
       <c r="B71">
-        <v>4342.009273166135</v>
+        <v>4378.420031132506</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46304</v>
       </c>
       <c r="B72">
-        <v>4410.933718902131</v>
+        <v>4452.766567545557</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46311</v>
       </c>
       <c r="B73">
-        <v>4486.994483541623</v>
+        <v>4540.263985303352</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46318</v>
       </c>
       <c r="B74">
-        <v>4675.398173949068</v>
+        <v>4695.59361314271</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46325</v>
       </c>
       <c r="B75">
-        <v>4808.547032517785</v>
+        <v>4842.68032345058</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46332</v>
       </c>
       <c r="B76">
-        <v>5026.50836250604</v>
+        <v>4992.615847531149</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46339</v>
       </c>
       <c r="B77">
-        <v>5289.336812998143</v>
+        <v>5218.605851513782</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46346</v>
       </c>
       <c r="B78">
-        <v>5437.694781059167</v>
+        <v>5316.941757537897</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46353</v>
       </c>
       <c r="B79">
-        <v>5566.8424770019</v>
+        <v>5525.171757537895</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/XAUUSD_forecast.xlsx
+++ b/public/data/files/XAUUSD_forecast.xlsx
@@ -442,7 +442,7 @@
         <v>45849</v>
       </c>
       <c r="B7">
-        <v>3668.746774455567</v>
+        <v>3668.792185564974</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -450,7 +450,7 @@
         <v>45856</v>
       </c>
       <c r="B8">
-        <v>3565.897520496765</v>
+        <v>3565.959078063461</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -458,7 +458,7 @@
         <v>45863</v>
       </c>
       <c r="B9">
-        <v>3511.504319320547</v>
+        <v>3511.575673980581</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -466,7 +466,7 @@
         <v>45870</v>
       </c>
       <c r="B10">
-        <v>3483.939598734022</v>
+        <v>3484.015598920198</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -474,7 +474,7 @@
         <v>45877</v>
       </c>
       <c r="B11">
-        <v>3492.451665983723</v>
+        <v>3492.529525577849</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -482,7 +482,7 @@
         <v>45884</v>
       </c>
       <c r="B12">
-        <v>3505.24331440051</v>
+        <v>3505.322095848924</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -490,7 +490,7 @@
         <v>45891</v>
       </c>
       <c r="B13">
-        <v>3519.758596176352</v>
+        <v>3519.836786703238</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -498,7 +498,7 @@
         <v>45898</v>
       </c>
       <c r="B14">
-        <v>3532.259155608043</v>
+        <v>3532.336091770893</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -506,7 +506,7 @@
         <v>45905</v>
       </c>
       <c r="B15">
-        <v>3548.215444407652</v>
+        <v>3548.272372238432</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -514,7 +514,7 @@
         <v>45912</v>
       </c>
       <c r="B16">
-        <v>3452.628012333199</v>
+        <v>3452.61351354907</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -522,7 +522,7 @@
         <v>45919</v>
       </c>
       <c r="B17">
-        <v>3450.230857176422</v>
+        <v>3450.21808366537</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -530,7 +530,7 @@
         <v>45926</v>
       </c>
       <c r="B18">
-        <v>3450.315075984108</v>
+        <v>3450.303268911488</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -538,7 +538,7 @@
         <v>45933</v>
       </c>
       <c r="B19">
-        <v>3532.416096597177</v>
+        <v>3532.353509354261</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -546,7 +546,7 @@
         <v>45940</v>
       </c>
       <c r="B20">
-        <v>3629.065263927385</v>
+        <v>3628.944932995729</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -554,7 +554,7 @@
         <v>45947</v>
       </c>
       <c r="B21">
-        <v>3780.630201315225</v>
+        <v>3780.447483891945</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -562,7 +562,7 @@
         <v>45954</v>
       </c>
       <c r="B22">
-        <v>3851.857439731697</v>
+        <v>3851.693584088466</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -570,7 +570,7 @@
         <v>45961</v>
       </c>
       <c r="B23">
-        <v>3898.645629848651</v>
+        <v>3898.491752692202</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -578,7 +578,7 @@
         <v>45968</v>
       </c>
       <c r="B24">
-        <v>3884.131597126424</v>
+        <v>3883.997981323689</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -586,7 +586,7 @@
         <v>45975</v>
       </c>
       <c r="B25">
-        <v>3886.955522476545</v>
+        <v>3886.899248786727</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -594,7 +594,7 @@
         <v>45982</v>
       </c>
       <c r="B26">
-        <v>3993.637937672877</v>
+        <v>3993.619418290812</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -602,7 +602,7 @@
         <v>45989</v>
       </c>
       <c r="B27">
-        <v>4068.082641031448</v>
+        <v>4068.026757167985</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -610,7 +610,7 @@
         <v>45996</v>
       </c>
       <c r="B28">
-        <v>4108.076432345971</v>
+        <v>4108.007496209952</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -618,7 +618,7 @@
         <v>46003</v>
       </c>
       <c r="B29">
-        <v>4206.389025036859</v>
+        <v>4206.38209775842</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -626,7 +626,7 @@
         <v>46010</v>
       </c>
       <c r="B30">
-        <v>4199.498482072306</v>
+        <v>4199.470339703385</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -634,7 +634,7 @@
         <v>46017</v>
       </c>
       <c r="B31">
-        <v>4223.880693009789</v>
+        <v>4223.802502596578</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -642,7 +642,7 @@
         <v>46024</v>
       </c>
       <c r="B32">
-        <v>4244.685788754088</v>
+        <v>4244.606524518836</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -650,7 +650,7 @@
         <v>46031</v>
       </c>
       <c r="B33">
-        <v>4309.155742772447</v>
+        <v>4309.044272027792</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -658,7 +658,7 @@
         <v>46038</v>
       </c>
       <c r="B34">
-        <v>4401.428071152168</v>
+        <v>4401.286980400992</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -666,7 +666,7 @@
         <v>46045</v>
       </c>
       <c r="B35">
-        <v>4437.424523470951</v>
+        <v>4437.270900944973</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -674,7 +674,7 @@
         <v>46052</v>
       </c>
       <c r="B36">
-        <v>4538.820120869794</v>
+        <v>4538.614511017579</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -682,7 +682,7 @@
         <v>46059</v>
       </c>
       <c r="B37">
-        <v>4674.092367016363</v>
+        <v>4673.84276421145</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -690,7 +690,7 @@
         <v>46066</v>
       </c>
       <c r="B38">
-        <v>4755.505380494103</v>
+        <v>4755.182514770117</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -698,7 +698,7 @@
         <v>46073</v>
       </c>
       <c r="B39">
-        <v>4892.408186857467</v>
+        <v>4892.219568967608</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -706,7 +706,7 @@
         <v>46080</v>
       </c>
       <c r="B40">
-        <v>4933.451472374809</v>
+        <v>4933.244124844784</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -714,7 +714,7 @@
         <v>46087</v>
       </c>
       <c r="B41">
-        <v>5039.612247249937</v>
+        <v>5039.341037192993</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -722,7 +722,7 @@
         <v>46094</v>
       </c>
       <c r="B42">
-        <v>5208.250911225915</v>
+        <v>5208.096083390696</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>46101</v>
       </c>
       <c r="B43">
-        <v>5251.209726180016</v>
+        <v>5251.182137316357</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>46108</v>
       </c>
       <c r="B44">
-        <v>5293.388687798929</v>
+        <v>5293.550295517056</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>46115</v>
       </c>
       <c r="B45">
-        <v>5371.229111666556</v>
+        <v>5371.533345305782</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>46122</v>
       </c>
       <c r="B46">
-        <v>5448.604630056063</v>
+        <v>5448.999411839228</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>46129</v>
       </c>
       <c r="B47">
-        <v>5579.078912259729</v>
+        <v>5579.511729372745</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>46136</v>
       </c>
       <c r="B48">
-        <v>5519.853031770872</v>
+        <v>5520.40777179929</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>46143</v>
       </c>
       <c r="B49">
-        <v>5345.966552309928</v>
+        <v>5346.659708700981</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>46150</v>
       </c>
       <c r="B50">
-        <v>5229.138488199911</v>
+        <v>5229.794062190425</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>46157</v>
       </c>
       <c r="B51">
-        <v>5095.59197471428</v>
+        <v>5096.300916433798</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>46164</v>
       </c>
       <c r="B52">
-        <v>4981.196776018565</v>
+        <v>4981.840264525212</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>46171</v>
       </c>
       <c r="B53">
-        <v>4878.303458828985</v>
+        <v>4878.921416466406</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>46178</v>
       </c>
       <c r="B54">
-        <v>4830.394031936877</v>
+        <v>4831.093052041877</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>46185</v>
       </c>
       <c r="B55">
-        <v>4700.896720131775</v>
+        <v>4701.458041484504</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>46192</v>
       </c>
       <c r="B56">
-        <v>4578.30294105399</v>
+        <v>4578.693478327212</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>46199</v>
       </c>
       <c r="B57">
-        <v>4481.388194597901</v>
+        <v>4481.645994939204</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>46206</v>
       </c>
       <c r="B58">
-        <v>4476.585087344964</v>
+        <v>4476.848154187624</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>46213</v>
       </c>
       <c r="B59">
-        <v>4397.209892232047</v>
+        <v>4397.539196076357</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>46220</v>
       </c>
       <c r="B60">
-        <v>4240.117275505349</v>
+        <v>4240.559299911622</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>46227</v>
       </c>
       <c r="B61">
-        <v>4145.839036427792</v>
+        <v>4146.212599251462</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>46234</v>
       </c>
       <c r="B62">
-        <v>4095.224579260924</v>
+        <v>4095.464419197034</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>46241</v>
       </c>
       <c r="B63">
-        <v>4081.817816436196</v>
+        <v>4081.814050900361</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46248</v>
       </c>
       <c r="B64">
-        <v>4130.002034565177</v>
+        <v>4129.645447789902</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46255</v>
       </c>
       <c r="B65">
-        <v>4213.77153973854</v>
+        <v>4213.019265636476</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46262</v>
       </c>
       <c r="B66">
-        <v>4275.654325435953</v>
+        <v>4286.15397818365</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46269</v>
       </c>
       <c r="B67">
-        <v>4301.000109538846</v>
+        <v>4311.337579428509</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46276</v>
       </c>
       <c r="B68">
-        <v>4312.24871459053</v>
+        <v>4321.372834320066</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46283</v>
       </c>
       <c r="B69">
-        <v>4304.729133693678</v>
+        <v>4316.916983945478</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46290</v>
       </c>
       <c r="B70">
-        <v>4329.512339438493</v>
+        <v>4343.364821007914</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46297</v>
       </c>
       <c r="B71">
-        <v>4378.420031132506</v>
+        <v>4391.938903819308</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46304</v>
       </c>
       <c r="B72">
-        <v>4452.766567545557</v>
+        <v>4468.044129936231</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46311</v>
       </c>
       <c r="B73">
-        <v>4540.263985303352</v>
+        <v>4556.439262392855</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46318</v>
       </c>
       <c r="B74">
-        <v>4695.59361314271</v>
+        <v>4709.835461399208</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46325</v>
       </c>
       <c r="B75">
-        <v>4842.68032345058</v>
+        <v>4855.357145272335</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46332</v>
       </c>
       <c r="B76">
-        <v>4992.615847531149</v>
+        <v>5001.727911052231</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46339</v>
       </c>
       <c r="B77">
-        <v>5218.605851513782</v>
+        <v>5219.664193238053</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46346</v>
       </c>
       <c r="B78">
-        <v>5316.941757537897</v>
+        <v>5318.420308170045</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46353</v>
       </c>
       <c r="B79">
-        <v>5525.171757537895</v>
+        <v>5496.033035069792</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/XAUUSD_forecast.xlsx
+++ b/public/data/files/XAUUSD_forecast.xlsx
@@ -442,7 +442,7 @@
         <v>45849</v>
       </c>
       <c r="B7">
-        <v>3668.792185564974</v>
+        <v>3668.836528327345</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -450,7 +450,7 @@
         <v>45856</v>
       </c>
       <c r="B8">
-        <v>3565.959078063461</v>
+        <v>3566.019193114621</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -458,7 +458,7 @@
         <v>45863</v>
       </c>
       <c r="B9">
-        <v>3511.575673980581</v>
+        <v>3511.64536260862</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -466,7 +466,7 @@
         <v>45870</v>
       </c>
       <c r="B10">
-        <v>3484.015598920198</v>
+        <v>3484.089832839859</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -474,7 +474,7 @@
         <v>45877</v>
       </c>
       <c r="B11">
-        <v>3492.529525577849</v>
+        <v>3492.605575373142</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -482,7 +482,7 @@
         <v>45884</v>
       </c>
       <c r="B12">
-        <v>3505.322095848924</v>
+        <v>3505.39904573526</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -490,7 +490,7 @@
         <v>45891</v>
       </c>
       <c r="B13">
-        <v>3519.836786703238</v>
+        <v>3519.913159231575</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -498,7 +498,7 @@
         <v>45898</v>
       </c>
       <c r="B14">
-        <v>3532.336091770893</v>
+        <v>3532.411239094271</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -506,7 +506,7 @@
         <v>45905</v>
       </c>
       <c r="B15">
-        <v>3548.272372238432</v>
+        <v>3548.327998173625</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -514,7 +514,7 @@
         <v>45912</v>
       </c>
       <c r="B16">
-        <v>3452.61351354907</v>
+        <v>3452.599362764775</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -522,7 +522,7 @@
         <v>45919</v>
       </c>
       <c r="B17">
-        <v>3450.21808366537</v>
+        <v>3450.205617660649</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -530,7 +530,7 @@
         <v>45926</v>
       </c>
       <c r="B18">
-        <v>3450.303268911488</v>
+        <v>3450.291746718829</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -538,7 +538,7 @@
         <v>45933</v>
       </c>
       <c r="B19">
-        <v>3532.353509354261</v>
+        <v>3532.29241587722</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -546,7 +546,7 @@
         <v>45940</v>
       </c>
       <c r="B20">
-        <v>3628.944932995729</v>
+        <v>3628.827460992234</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -554,7 +554,7 @@
         <v>45947</v>
       </c>
       <c r="B21">
-        <v>3780.447483891945</v>
+        <v>3780.269077241054</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -562,7 +562,7 @@
         <v>45954</v>
       </c>
       <c r="B22">
-        <v>3851.693584088466</v>
+        <v>3851.533581596304</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -570,7 +570,7 @@
         <v>45961</v>
       </c>
       <c r="B23">
-        <v>3898.491752692202</v>
+        <v>3898.341435354021</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -578,7 +578,7 @@
         <v>45968</v>
       </c>
       <c r="B24">
-        <v>3883.997981323689</v>
+        <v>3883.867427926503</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -586,7 +586,7 @@
         <v>45975</v>
       </c>
       <c r="B25">
-        <v>3886.899248786727</v>
+        <v>3886.84423216789</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -594,7 +594,7 @@
         <v>45982</v>
       </c>
       <c r="B26">
-        <v>3993.619418290812</v>
+        <v>3993.601293288304</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -602,7 +602,7 @@
         <v>45989</v>
       </c>
       <c r="B27">
-        <v>4068.026757167985</v>
+        <v>4067.972160281997</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -610,7 +610,7 @@
         <v>45996</v>
       </c>
       <c r="B28">
-        <v>4108.007496209952</v>
+        <v>4107.940150469361</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -618,7 +618,7 @@
         <v>46003</v>
       </c>
       <c r="B29">
-        <v>4206.38209775842</v>
+        <v>4206.375363979784</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -626,7 +626,7 @@
         <v>46010</v>
       </c>
       <c r="B30">
-        <v>4199.470339703385</v>
+        <v>4199.442909780588</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -634,7 +634,7 @@
         <v>46017</v>
       </c>
       <c r="B31">
-        <v>4223.802502596578</v>
+        <v>4223.726233050638</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -642,7 +642,7 @@
         <v>46024</v>
       </c>
       <c r="B32">
-        <v>4244.606524518836</v>
+        <v>4244.529186295943</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -650,7 +650,7 @@
         <v>46031</v>
       </c>
       <c r="B33">
-        <v>4309.044272027792</v>
+        <v>4308.935486299079</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -658,7 +658,7 @@
         <v>46038</v>
       </c>
       <c r="B34">
-        <v>4401.286980400992</v>
+        <v>4401.149256855161</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -666,7 +666,7 @@
         <v>46045</v>
       </c>
       <c r="B35">
-        <v>4437.270900944973</v>
+        <v>4437.120909527768</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -674,7 +674,7 @@
         <v>46052</v>
       </c>
       <c r="B36">
-        <v>4538.614511017579</v>
+        <v>4538.413719633666</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -682,7 +682,7 @@
         <v>46059</v>
       </c>
       <c r="B37">
-        <v>4673.84276421145</v>
+        <v>4673.599021358688</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -690,7 +690,7 @@
         <v>46066</v>
       </c>
       <c r="B38">
-        <v>4755.182514770117</v>
+        <v>4754.867016948685</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -698,7 +698,7 @@
         <v>46073</v>
       </c>
       <c r="B39">
-        <v>4892.219568967608</v>
+        <v>4892.035361333465</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -706,7 +706,7 @@
         <v>46080</v>
       </c>
       <c r="B40">
-        <v>4933.244124844784</v>
+        <v>4933.041622397221</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -714,7 +714,7 @@
         <v>46087</v>
       </c>
       <c r="B41">
-        <v>5039.341037192993</v>
+        <v>5039.076116503832</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -722,7 +722,7 @@
         <v>46094</v>
       </c>
       <c r="B42">
-        <v>5208.096083390696</v>
+        <v>5207.944733116561</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>46101</v>
       </c>
       <c r="B43">
-        <v>5251.182137316357</v>
+        <v>5251.154869596518</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>46108</v>
       </c>
       <c r="B44">
-        <v>5293.550295517056</v>
+        <v>5293.707702057472</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>46115</v>
       </c>
       <c r="B45">
-        <v>5371.533345305782</v>
+        <v>5371.83014552603</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>46122</v>
       </c>
       <c r="B46">
-        <v>5448.999411839228</v>
+        <v>5449.384594769987</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>46129</v>
       </c>
       <c r="B47">
-        <v>5579.511729372745</v>
+        <v>5579.934078896285</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>46136</v>
       </c>
       <c r="B48">
-        <v>5520.40777179929</v>
+        <v>5520.949362842097</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>46143</v>
       </c>
       <c r="B49">
-        <v>5346.659708700981</v>
+        <v>5347.336590833555</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>46150</v>
       </c>
       <c r="B50">
-        <v>5229.794062190425</v>
+        <v>5230.434359746637</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>46157</v>
       </c>
       <c r="B51">
-        <v>5096.300916433798</v>
+        <v>5096.993521089335</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>46164</v>
       </c>
       <c r="B52">
-        <v>4981.840264525212</v>
+        <v>4982.469046540411</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>46171</v>
       </c>
       <c r="B53">
-        <v>4878.921416466406</v>
+        <v>4879.525412578201</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>46178</v>
       </c>
       <c r="B54">
-        <v>4831.093052041877</v>
+        <v>4831.77629248829</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>46185</v>
       </c>
       <c r="B55">
-        <v>4701.458041484504</v>
+        <v>4702.006646098755</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>46192</v>
       </c>
       <c r="B56">
-        <v>4578.693478327212</v>
+        <v>4579.075042230492</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>46199</v>
       </c>
       <c r="B57">
-        <v>4481.645994939204</v>
+        <v>4481.89765246488</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>46206</v>
       </c>
       <c r="B58">
-        <v>4476.848154187624</v>
+        <v>4477.104960300063</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>46213</v>
       </c>
       <c r="B59">
-        <v>4397.539196076357</v>
+        <v>4397.860783566823</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>46220</v>
       </c>
       <c r="B60">
-        <v>4240.559299911622</v>
+        <v>4240.991249787487</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>46227</v>
       </c>
       <c r="B61">
-        <v>4146.212599251462</v>
+        <v>4146.578098446769</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>46234</v>
       </c>
       <c r="B62">
-        <v>4095.464419197034</v>
+        <v>4095.69944741617</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>46241</v>
       </c>
       <c r="B63">
-        <v>4081.814050900361</v>
+        <v>4081.811404791591</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46248</v>
       </c>
       <c r="B64">
-        <v>4129.645447789902</v>
+        <v>4129.298228304785</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46255</v>
       </c>
       <c r="B65">
-        <v>4213.019265636476</v>
+        <v>4212.285005016073</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46262</v>
       </c>
       <c r="B66">
-        <v>4286.15397818365</v>
+        <v>4295.983944404103</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46269</v>
       </c>
       <c r="B67">
-        <v>4311.337579428509</v>
+        <v>4321.022302340147</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46276</v>
       </c>
       <c r="B68">
-        <v>4321.372834320066</v>
+        <v>4329.848215513958</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46283</v>
       </c>
       <c r="B69">
-        <v>4316.916983945478</v>
+        <v>4328.275761796872</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46290</v>
       </c>
       <c r="B70">
-        <v>4343.364821007914</v>
+        <v>4356.230429838362</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46297</v>
       </c>
       <c r="B71">
-        <v>4391.938903819308</v>
+        <v>4404.34229076216</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46304</v>
       </c>
       <c r="B72">
-        <v>4468.044129936231</v>
+        <v>4482.077832626543</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46311</v>
       </c>
       <c r="B73">
-        <v>4556.439262392855</v>
+        <v>4571.269153717073</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46318</v>
       </c>
       <c r="B74">
-        <v>4709.835461399208</v>
+        <v>4722.668805622277</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46325</v>
       </c>
       <c r="B75">
-        <v>4855.357145272335</v>
+        <v>4866.405581139795</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46332</v>
       </c>
       <c r="B76">
-        <v>5001.727911052231</v>
+        <v>5009.244619127629</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46339</v>
       </c>
       <c r="B77">
-        <v>5219.664193238053</v>
+        <v>5219.570770977823</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46346</v>
       </c>
       <c r="B78">
-        <v>5318.420308170045</v>
+        <v>5317.958181202866</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46353</v>
       </c>
       <c r="B79">
-        <v>5496.033035069792</v>
+        <v>5473.274131288756</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/XAUUSD_forecast.xlsx
+++ b/public/data/files/XAUUSD_forecast.xlsx
@@ -442,7 +442,7 @@
         <v>45849</v>
       </c>
       <c r="B7">
-        <v>3668.836528327345</v>
+        <v>3668.879840003762</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -450,7 +450,7 @@
         <v>45856</v>
       </c>
       <c r="B8">
-        <v>3566.019193114621</v>
+        <v>3566.077915762728</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -458,7 +458,7 @@
         <v>45863</v>
       </c>
       <c r="B9">
-        <v>3511.64536260862</v>
+        <v>3511.713442869524</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -466,7 +466,7 @@
         <v>45870</v>
       </c>
       <c r="B10">
-        <v>3484.089832839859</v>
+        <v>3484.162361338169</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -474,7 +474,7 @@
         <v>45877</v>
       </c>
       <c r="B11">
-        <v>3492.605575373142</v>
+        <v>3492.67987772535</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -482,7 +482,7 @@
         <v>45884</v>
       </c>
       <c r="B12">
-        <v>3505.39904573526</v>
+        <v>3505.474227176795</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -490,7 +490,7 @@
         <v>45891</v>
       </c>
       <c r="B13">
-        <v>3519.913159231575</v>
+        <v>3519.987776417433</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -498,7 +498,7 @@
         <v>45898</v>
       </c>
       <c r="B14">
-        <v>3532.411239094271</v>
+        <v>3532.484659229619</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -506,7 +506,7 @@
         <v>45905</v>
       </c>
       <c r="B15">
-        <v>3548.327998173625</v>
+        <v>3548.382366322717</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -514,7 +514,7 @@
         <v>45912</v>
       </c>
       <c r="B16">
-        <v>3452.599362764775</v>
+        <v>3452.585547606855</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -522,7 +522,7 @@
         <v>45919</v>
       </c>
       <c r="B17">
-        <v>3450.205617660649</v>
+        <v>3450.193448197625</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -530,7 +530,7 @@
         <v>45926</v>
       </c>
       <c r="B18">
-        <v>3450.291746718829</v>
+        <v>3450.280499226744</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -538,7 +538,7 @@
         <v>45933</v>
       </c>
       <c r="B19">
-        <v>3532.29241587722</v>
+        <v>3532.23276334564</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -546,7 +546,7 @@
         <v>45940</v>
       </c>
       <c r="B20">
-        <v>3628.827460992234</v>
+        <v>3628.712747284473</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -554,7 +554,7 @@
         <v>45947</v>
       </c>
       <c r="B21">
-        <v>3780.269077241054</v>
+        <v>3780.094830666957</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -562,7 +562,7 @@
         <v>45954</v>
       </c>
       <c r="B22">
-        <v>3851.533581596304</v>
+        <v>3851.377297971814</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -570,7 +570,7 @@
         <v>45961</v>
       </c>
       <c r="B23">
-        <v>3898.341435354021</v>
+        <v>3898.194555835734</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -578,7 +578,7 @@
         <v>45968</v>
       </c>
       <c r="B24">
-        <v>3883.867427926503</v>
+        <v>3883.739832992692</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -586,7 +586,7 @@
         <v>45975</v>
       </c>
       <c r="B25">
-        <v>3886.84423216789</v>
+        <v>3886.790431090963</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -594,7 +594,7 @@
         <v>45982</v>
       </c>
       <c r="B26">
-        <v>3993.601293288304</v>
+        <v>3993.583550323737</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -602,7 +602,7 @@
         <v>45989</v>
       </c>
       <c r="B27">
-        <v>4067.972160281997</v>
+        <v>4067.918806431008</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -610,7 +610,7 @@
         <v>45996</v>
       </c>
       <c r="B28">
-        <v>4107.940150469361</v>
+        <v>4107.874340737858</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -618,7 +618,7 @@
         <v>46003</v>
       </c>
       <c r="B29">
-        <v>4206.375363979784</v>
+        <v>4206.368815901953</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -626,7 +626,7 @@
         <v>46010</v>
       </c>
       <c r="B30">
-        <v>4199.442909780588</v>
+        <v>4199.416165751261</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -634,7 +634,7 @@
         <v>46017</v>
       </c>
       <c r="B31">
-        <v>4223.726233050638</v>
+        <v>4223.65181466386</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -642,7 +642,7 @@
         <v>46024</v>
       </c>
       <c r="B32">
-        <v>4244.529186295943</v>
+        <v>4244.453704946047</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -650,7 +650,7 @@
         <v>46031</v>
       </c>
       <c r="B33">
-        <v>4308.935486299079</v>
+        <v>4308.829290004594</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -658,7 +658,7 @@
         <v>46038</v>
       </c>
       <c r="B34">
-        <v>4401.149256855161</v>
+        <v>4401.014781728183</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -666,7 +666,7 @@
         <v>46045</v>
       </c>
       <c r="B35">
-        <v>4437.120909527768</v>
+        <v>4436.974422248868</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -674,7 +674,7 @@
         <v>46052</v>
       </c>
       <c r="B36">
-        <v>4538.413719633666</v>
+        <v>4538.217579575867</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -682,7 +682,7 @@
         <v>46059</v>
       </c>
       <c r="B37">
-        <v>4673.599021358688</v>
+        <v>4673.360934873465</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -690,7 +690,7 @@
         <v>46066</v>
       </c>
       <c r="B38">
-        <v>4754.867016948685</v>
+        <v>4754.558638129616</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -698,7 +698,7 @@
         <v>46073</v>
       </c>
       <c r="B39">
-        <v>4892.035361333465</v>
+        <v>4891.855411376235</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -706,7 +706,7 @@
         <v>46080</v>
       </c>
       <c r="B40">
-        <v>4933.041622397221</v>
+        <v>4932.843797513087</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -714,7 +714,7 @@
         <v>46087</v>
       </c>
       <c r="B41">
-        <v>5039.076116503832</v>
+        <v>5038.817269519172</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -722,7 +722,7 @@
         <v>46094</v>
       </c>
       <c r="B42">
-        <v>5207.944733116561</v>
+        <v>5207.79674502226</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>46101</v>
       </c>
       <c r="B43">
-        <v>5251.154869596518</v>
+        <v>5251.127923235048</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>46108</v>
       </c>
       <c r="B44">
-        <v>5293.707702057472</v>
+        <v>5293.861067473812</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>46115</v>
       </c>
       <c r="B45">
-        <v>5371.83014552603</v>
+        <v>5372.119780652097</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>46122</v>
       </c>
       <c r="B46">
-        <v>5449.384594769987</v>
+        <v>5449.760523613558</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>46129</v>
       </c>
       <c r="B47">
-        <v>5579.934078896285</v>
+        <v>5580.346335044049</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>46136</v>
       </c>
       <c r="B48">
-        <v>5520.949362842097</v>
+        <v>5521.478266080892</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>46143</v>
       </c>
       <c r="B49">
-        <v>5347.336590833555</v>
+        <v>5347.997763811249</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>46150</v>
       </c>
       <c r="B50">
-        <v>5230.434359746637</v>
+        <v>5231.059907282342</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>46157</v>
       </c>
       <c r="B51">
-        <v>5096.993521089335</v>
+        <v>5097.670345286502</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>46164</v>
       </c>
       <c r="B52">
-        <v>4982.469046540411</v>
+        <v>4983.08361922619</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>46171</v>
       </c>
       <c r="B53">
-        <v>4879.525412578201</v>
+        <v>4880.115913514483</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>46178</v>
       </c>
       <c r="B54">
-        <v>4831.77629248829</v>
+        <v>4832.444279784879</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>46185</v>
       </c>
       <c r="B55">
-        <v>4702.006646098755</v>
+        <v>4702.542960006051</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>46192</v>
       </c>
       <c r="B56">
-        <v>4579.075042230492</v>
+        <v>4579.447937845599</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>46199</v>
       </c>
       <c r="B57">
-        <v>4481.89765246488</v>
+        <v>4482.143383531474</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>46206</v>
       </c>
       <c r="B58">
-        <v>4477.104960300063</v>
+        <v>4477.355726030086</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>46213</v>
       </c>
       <c r="B59">
-        <v>4397.860783566823</v>
+        <v>4398.174922018135</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>46220</v>
       </c>
       <c r="B60">
-        <v>4240.991249787487</v>
+        <v>4241.413463860785</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>46227</v>
       </c>
       <c r="B61">
-        <v>4146.578098446769</v>
+        <v>4146.93578901513</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>46234</v>
       </c>
       <c r="B62">
-        <v>4095.69944741617</v>
+        <v>4095.929802952885</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>46241</v>
       </c>
       <c r="B63">
-        <v>4081.811404791591</v>
+        <v>4081.809806097604</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46248</v>
       </c>
       <c r="B64">
-        <v>4129.298228304785</v>
+        <v>4128.960023846082</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46255</v>
       </c>
       <c r="B65">
-        <v>4212.285005016073</v>
+        <v>4211.568134089135</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46262</v>
       </c>
       <c r="B66">
-        <v>4295.983944404103</v>
+        <v>4305.297561224046</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46269</v>
       </c>
       <c r="B67">
-        <v>4321.022302340147</v>
+        <v>4330.048665793821</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46276</v>
       </c>
       <c r="B68">
-        <v>4329.848215513958</v>
+        <v>4337.449609010472</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46283</v>
       </c>
       <c r="B69">
-        <v>4328.275761796872</v>
+        <v>4338.010435628157</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46290</v>
       </c>
       <c r="B70">
-        <v>4356.230429838362</v>
+        <v>4366.417902318911</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46297</v>
       </c>
       <c r="B71">
-        <v>4404.34229076216</v>
+        <v>4415.181932881215</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46304</v>
       </c>
       <c r="B72">
-        <v>4482.077832626543</v>
+        <v>4493.130451413022</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46311</v>
       </c>
       <c r="B73">
-        <v>4571.269153717073</v>
+        <v>4582.462529174669</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46318</v>
       </c>
       <c r="B74">
-        <v>4722.668805622277</v>
+        <v>4731.96357633833</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46325</v>
       </c>
       <c r="B75">
-        <v>4866.405581139795</v>
+        <v>4872.814054831555</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46332</v>
       </c>
       <c r="B76">
-        <v>5009.244619127629</v>
+        <v>5011.699823990275</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46339</v>
       </c>
       <c r="B77">
-        <v>5219.570770977823</v>
+        <v>5212.057269469609</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46346</v>
       </c>
       <c r="B78">
-        <v>5317.958181202866</v>
+        <v>5302.916898224277</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46353</v>
       </c>
       <c r="B79">
-        <v>5473.274131288756</v>
+        <v>5422.219518968684</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/XAUUSD_forecast.xlsx
+++ b/public/data/files/XAUUSD_forecast.xlsx
@@ -442,7 +442,7 @@
         <v>45849</v>
       </c>
       <c r="B7">
-        <v>3668.879840003762</v>
+        <v>3668.922156142537</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -450,7 +450,7 @@
         <v>45856</v>
       </c>
       <c r="B8">
-        <v>3566.077915762728</v>
+        <v>3566.135293825887</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -458,7 +458,7 @@
         <v>45863</v>
       </c>
       <c r="B9">
-        <v>3511.713442869524</v>
+        <v>3511.779969797808</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -466,7 +466,7 @@
         <v>45870</v>
       </c>
       <c r="B10">
-        <v>3484.162361338169</v>
+        <v>3484.233242498243</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -474,7 +474,7 @@
         <v>45877</v>
       </c>
       <c r="B11">
-        <v>3492.67987772535</v>
+        <v>3492.7524921591</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -482,7 +482,7 @@
         <v>45884</v>
       </c>
       <c r="B12">
-        <v>3505.474227176795</v>
+        <v>3505.547700424574</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -490,7 +490,7 @@
         <v>45891</v>
       </c>
       <c r="B13">
-        <v>3519.987776417433</v>
+        <v>3520.060698071304</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -498,7 +498,7 @@
         <v>45898</v>
       </c>
       <c r="B14">
-        <v>3532.484659229619</v>
+        <v>3532.556411028407</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -506,7 +506,7 @@
         <v>45905</v>
       </c>
       <c r="B15">
-        <v>3548.382366322717</v>
+        <v>3548.435518826907</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -514,7 +514,7 @@
         <v>45912</v>
       </c>
       <c r="B16">
-        <v>3452.585547606855</v>
+        <v>3452.572056281268</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -522,7 +522,7 @@
         <v>45919</v>
       </c>
       <c r="B17">
-        <v>3450.193448197625</v>
+        <v>3450.181564826489</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -530,7 +530,7 @@
         <v>45926</v>
       </c>
       <c r="B18">
-        <v>3450.280499226744</v>
+        <v>3450.269516734761</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -538,7 +538,7 @@
         <v>45933</v>
       </c>
       <c r="B19">
-        <v>3532.23276334564</v>
+        <v>3532.174501399274</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -546,7 +546,7 @@
         <v>45940</v>
       </c>
       <c r="B20">
-        <v>3628.712747284473</v>
+        <v>3628.600695905551</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -554,7 +554,7 @@
         <v>45947</v>
       </c>
       <c r="B21">
-        <v>3780.094830666957</v>
+        <v>3779.924600413612</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -562,7 +562,7 @@
         <v>45954</v>
       </c>
       <c r="B22">
-        <v>3851.377297971814</v>
+        <v>3851.224605097441</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -570,7 +570,7 @@
         <v>45961</v>
       </c>
       <c r="B23">
-        <v>3898.194555835734</v>
+        <v>3898.050997645256</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -578,7 +578,7 @@
         <v>45968</v>
       </c>
       <c r="B24">
-        <v>3883.739832992692</v>
+        <v>3883.615097224611</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -586,7 +586,7 @@
         <v>45975</v>
       </c>
       <c r="B25">
-        <v>3886.790431090963</v>
+        <v>3886.737805830285</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -594,7 +594,7 @@
         <v>45982</v>
       </c>
       <c r="B26">
-        <v>3993.583550323737</v>
+        <v>3993.566177559102</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -602,7 +602,7 @@
         <v>45989</v>
       </c>
       <c r="B27">
-        <v>4067.918806431008</v>
+        <v>4067.866653650152</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -610,7 +610,7 @@
         <v>45996</v>
       </c>
       <c r="B28">
-        <v>4107.874340737858</v>
+        <v>4107.810015079911</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -618,7 +618,7 @@
         <v>46003</v>
       </c>
       <c r="B29">
-        <v>4206.368815901953</v>
+        <v>4206.362446131972</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -626,7 +626,7 @@
         <v>46010</v>
       </c>
       <c r="B30">
-        <v>4199.416165751261</v>
+        <v>4199.390082359186</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -634,7 +634,7 @@
         <v>46017</v>
       </c>
       <c r="B31">
-        <v>4223.65181466386</v>
+        <v>4223.579181051377</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -642,7 +642,7 @@
         <v>46024</v>
       </c>
       <c r="B32">
-        <v>4244.453704946047</v>
+        <v>4244.380014590444</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -650,7 +650,7 @@
         <v>46031</v>
       </c>
       <c r="B33">
-        <v>4308.829290004594</v>
+        <v>4308.725592034039</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -658,7 +658,7 @@
         <v>46038</v>
       </c>
       <c r="B34">
-        <v>4401.014781728183</v>
+        <v>4400.88344174123</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -666,7 +666,7 @@
         <v>46045</v>
       </c>
       <c r="B35">
-        <v>4436.974422248868</v>
+        <v>4436.831317977533</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -674,7 +674,7 @@
         <v>46052</v>
       </c>
       <c r="B36">
-        <v>4538.217579575867</v>
+        <v>4538.025931331625</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -682,7 +682,7 @@
         <v>46059</v>
       </c>
       <c r="B37">
-        <v>4673.360934873465</v>
+        <v>4673.128310476564</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -690,7 +690,7 @@
         <v>46066</v>
       </c>
       <c r="B38">
-        <v>4754.558638129616</v>
+        <v>4754.257140477957</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -698,7 +698,7 @@
         <v>46073</v>
       </c>
       <c r="B39">
-        <v>4891.855411376235</v>
+        <v>4891.679573460954</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -706,7 +706,7 @@
         <v>46080</v>
       </c>
       <c r="B40">
-        <v>4932.843797513087</v>
+        <v>4932.650490292606</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -714,7 +714,7 @@
         <v>46087</v>
       </c>
       <c r="B41">
-        <v>5038.817269519172</v>
+        <v>5038.564290297099</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -722,7 +722,7 @@
         <v>46094</v>
       </c>
       <c r="B42">
-        <v>5207.79674502226</v>
+        <v>5207.6520087525</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>46101</v>
       </c>
       <c r="B43">
-        <v>5251.127923235048</v>
+        <v>5251.101297914229</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>46108</v>
       </c>
       <c r="B44">
-        <v>5293.861067473812</v>
+        <v>5294.010543859884</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>46115</v>
       </c>
       <c r="B45">
-        <v>5372.119780652097</v>
+        <v>5372.402506283874</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>46122</v>
       </c>
       <c r="B46">
-        <v>5449.760523613558</v>
+        <v>5450.127526868562</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>46129</v>
       </c>
       <c r="B47">
-        <v>5580.346335044049</v>
+        <v>5580.748854445676</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>46136</v>
       </c>
       <c r="B48">
-        <v>5521.478266080892</v>
+        <v>5521.994921417367</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>46143</v>
       </c>
       <c r="B49">
-        <v>5347.997763811249</v>
+        <v>5348.643766935992</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>46150</v>
       </c>
       <c r="B50">
-        <v>5231.059907282342</v>
+        <v>5231.671207362814</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>46157</v>
       </c>
       <c r="B51">
-        <v>5097.670345286502</v>
+        <v>5098.331920705903</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>46164</v>
       </c>
       <c r="B52">
-        <v>4983.08361922619</v>
+        <v>4983.68445764426</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>46171</v>
       </c>
       <c r="B53">
-        <v>4880.115913514483</v>
+        <v>4880.693365153628</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>46178</v>
       </c>
       <c r="B54">
-        <v>4832.444279784879</v>
+        <v>4833.097517358694</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>46185</v>
       </c>
       <c r="B55">
-        <v>4702.542960006051</v>
+        <v>4703.067390475697</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>46192</v>
       </c>
       <c r="B56">
-        <v>4579.447937845599</v>
+        <v>4579.812456610056</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>46199</v>
       </c>
       <c r="B57">
-        <v>4482.143383531474</v>
+        <v>4482.383394480161</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>46206</v>
       </c>
       <c r="B58">
-        <v>4477.355726030086</v>
+        <v>4477.60066152833</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>46213</v>
       </c>
       <c r="B59">
-        <v>4398.174922018135</v>
+        <v>4398.481866572885</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>46220</v>
       </c>
       <c r="B60">
-        <v>4241.413463860785</v>
+        <v>4241.826265925275</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>46227</v>
       </c>
       <c r="B61">
-        <v>4146.93578901513</v>
+        <v>4147.285915473412</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>46234</v>
       </c>
       <c r="B62">
-        <v>4095.929802952885</v>
+        <v>4096.155619751083</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>46241</v>
       </c>
       <c r="B63">
-        <v>4081.809806097604</v>
+        <v>4081.809187480286</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46248</v>
       </c>
       <c r="B64">
-        <v>4128.960023846082</v>
+        <v>4128.630499124994</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46255</v>
       </c>
       <c r="B65">
-        <v>4211.568134089135</v>
+        <v>4210.8680568768</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46262</v>
       </c>
       <c r="B66">
-        <v>4305.297561224046</v>
+        <v>4309.508919826712</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46269</v>
       </c>
       <c r="B67">
-        <v>4330.048665793821</v>
+        <v>4333.316139385287</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46276</v>
       </c>
       <c r="B68">
-        <v>4337.449609010472</v>
+        <v>4339.041377108668</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46283</v>
       </c>
       <c r="B69">
-        <v>4338.010435628157</v>
+        <v>4340.732836068386</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46290</v>
       </c>
       <c r="B70">
-        <v>4366.417902318911</v>
+        <v>4368.902200906121</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46297</v>
       </c>
       <c r="B71">
-        <v>4415.181932881215</v>
+        <v>4417.73928610885</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46304</v>
       </c>
       <c r="B72">
-        <v>4493.130451413022</v>
+        <v>4495.262794499164</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46311</v>
       </c>
       <c r="B73">
-        <v>4582.462529174669</v>
+        <v>4583.879594669009</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46318</v>
       </c>
       <c r="B74">
-        <v>4731.96357633833</v>
+        <v>4729.879893659867</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46325</v>
       </c>
       <c r="B75">
-        <v>4872.814054831555</v>
+        <v>4865.740128672764</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46332</v>
       </c>
       <c r="B76">
-        <v>5011.699823990275</v>
+        <v>4998.645184006343</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46339</v>
       </c>
       <c r="B77">
-        <v>5212.057269469609</v>
+        <v>5185.353407873677</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46346</v>
       </c>
       <c r="B78">
-        <v>5302.916898224277</v>
+        <v>5260.894303743225</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46353</v>
       </c>
       <c r="B79">
-        <v>5422.219518968684</v>
+        <v>5330.184893004512</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/XAUUSD_forecast.xlsx
+++ b/public/data/files/XAUUSD_forecast.xlsx
@@ -383,7 +383,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B79"/>
+  <dimension ref="A1:B80"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" style="1" customWidth="1"/>
@@ -442,7 +442,7 @@
         <v>45849</v>
       </c>
       <c r="B7">
-        <v>3668.922156142537</v>
+        <v>3668.963510676511</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -450,7 +450,7 @@
         <v>45856</v>
       </c>
       <c r="B8">
-        <v>3566.135293825887</v>
+        <v>3566.191372957641</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -458,7 +458,7 @@
         <v>45863</v>
       </c>
       <c r="B9">
-        <v>3511.779969797808</v>
+        <v>3511.844995945896</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -466,7 +466,7 @@
         <v>45870</v>
       </c>
       <c r="B10">
-        <v>3484.233242498243</v>
+        <v>3484.302531796067</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -474,7 +474,7 @@
         <v>45877</v>
       </c>
       <c r="B11">
-        <v>3492.7524921591</v>
+        <v>3492.823475526727</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -482,7 +482,7 @@
         <v>45884</v>
       </c>
       <c r="B12">
-        <v>3505.547700424574</v>
+        <v>3505.619523024238</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -490,7 +490,7 @@
         <v>45891</v>
       </c>
       <c r="B13">
-        <v>3520.060698071304</v>
+        <v>3520.131981317786</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -498,7 +498,7 @@
         <v>45898</v>
       </c>
       <c r="B14">
-        <v>3532.556411028407</v>
+        <v>3532.626550699256</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -506,7 +506,7 @@
         <v>45905</v>
       </c>
       <c r="B15">
-        <v>3548.435518826907</v>
+        <v>3548.487495967574</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -514,7 +514,7 @@
         <v>45912</v>
       </c>
       <c r="B16">
-        <v>3452.572056281268</v>
+        <v>3452.558877539884</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -522,7 +522,7 @@
         <v>45919</v>
       </c>
       <c r="B17">
-        <v>3450.181564826489</v>
+        <v>3450.169957582412</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -530,7 +530,7 @@
         <v>45926</v>
       </c>
       <c r="B18">
-        <v>3450.269516734761</v>
+        <v>3450.2587899935</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -538,7 +538,7 @@
         <v>45933</v>
       </c>
       <c r="B19">
-        <v>3532.174501399274</v>
+        <v>3532.117581996516</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -546,7 +546,7 @@
         <v>45940</v>
       </c>
       <c r="B20">
-        <v>3628.600695905551</v>
+        <v>3628.491215286966</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -554,7 +554,7 @@
         <v>45947</v>
       </c>
       <c r="B21">
-        <v>3779.924600413612</v>
+        <v>3779.758249269817</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -562,7 +562,7 @@
         <v>45954</v>
       </c>
       <c r="B22">
-        <v>3851.224605097441</v>
+        <v>3851.075380671709</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -570,7 +570,7 @@
         <v>45961</v>
       </c>
       <c r="B23">
-        <v>3898.050997645256</v>
+        <v>3897.910649489903</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -578,7 +578,7 @@
         <v>45968</v>
       </c>
       <c r="B24">
-        <v>3883.615097224611</v>
+        <v>3883.493125712965</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -586,7 +586,7 @@
         <v>45975</v>
       </c>
       <c r="B25">
-        <v>3886.737805830285</v>
+        <v>3886.686318367113</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -594,7 +594,7 @@
         <v>45982</v>
       </c>
       <c r="B26">
-        <v>3993.566177559102</v>
+        <v>3993.549163634924</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -602,7 +602,7 @@
         <v>45989</v>
       </c>
       <c r="B27">
-        <v>4067.866653650152</v>
+        <v>4067.815661842176</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -610,7 +610,7 @@
         <v>45996</v>
       </c>
       <c r="B28">
-        <v>4107.810015079911</v>
+        <v>4107.747123874343</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -618,7 +618,7 @@
         <v>46003</v>
       </c>
       <c r="B29">
-        <v>4206.362446131972</v>
+        <v>4206.356247657216</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -626,7 +626,7 @@
         <v>46010</v>
       </c>
       <c r="B30">
-        <v>4199.390082359186</v>
+        <v>4199.364635566752</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -634,7 +634,7 @@
         <v>46017</v>
       </c>
       <c r="B31">
-        <v>4223.579181051377</v>
+        <v>4223.508268956349</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -642,7 +642,7 @@
         <v>46024</v>
       </c>
       <c r="B32">
-        <v>4244.380014590444</v>
+        <v>4244.308052421618</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -650,7 +650,7 @@
         <v>46031</v>
       </c>
       <c r="B33">
-        <v>4308.725592034039</v>
+        <v>4308.624305490731</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -658,7 +658,7 @@
         <v>46038</v>
       </c>
       <c r="B34">
-        <v>4400.88344174123</v>
+        <v>4400.755128808392</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -666,7 +666,7 @@
         <v>46045</v>
       </c>
       <c r="B35">
-        <v>4436.831317977533</v>
+        <v>4436.691481091503</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -674,7 +674,7 @@
         <v>46052</v>
       </c>
       <c r="B36">
-        <v>4538.025931331625</v>
+        <v>4537.838622588271</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -682,7 +682,7 @@
         <v>46059</v>
       </c>
       <c r="B37">
-        <v>4673.128310476564</v>
+        <v>4672.900962669464</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -690,7 +690,7 @@
         <v>46066</v>
       </c>
       <c r="B38">
-        <v>4754.257140477957</v>
+        <v>4753.962296617028</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -698,7 +698,7 @@
         <v>46073</v>
       </c>
       <c r="B39">
-        <v>4891.679573460954</v>
+        <v>4891.507708506724</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -706,7 +706,7 @@
         <v>46080</v>
       </c>
       <c r="B40">
-        <v>4932.650490292606</v>
+        <v>4932.461548027799</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -714,7 +714,7 @@
         <v>46087</v>
       </c>
       <c r="B41">
-        <v>5038.564290297099</v>
+        <v>5038.316982076947</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -722,7 +722,7 @@
         <v>46094</v>
       </c>
       <c r="B42">
-        <v>5207.6520087525</v>
+        <v>5207.510418708542</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>46101</v>
       </c>
       <c r="B43">
-        <v>5251.101297914229</v>
+        <v>5251.074992843793</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>46108</v>
       </c>
       <c r="B44">
-        <v>5294.010543859884</v>
+        <v>5294.156275834917</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>46115</v>
       </c>
       <c r="B45">
-        <v>5372.402506283874</v>
+        <v>5372.678566039885</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>46122</v>
       </c>
       <c r="B46">
-        <v>5450.127526868562</v>
+        <v>5450.485917712535</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>46129</v>
       </c>
       <c r="B47">
-        <v>5580.748854445676</v>
+        <v>5581.141977165229</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>46136</v>
       </c>
       <c r="B48">
-        <v>5521.994921417367</v>
+        <v>5522.499748684573</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>46143</v>
       </c>
       <c r="B49">
-        <v>5348.643766935992</v>
+        <v>5349.275115160535</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>46150</v>
       </c>
       <c r="B50">
-        <v>5231.671207362814</v>
+        <v>5232.268740036675</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>46157</v>
       </c>
       <c r="B51">
-        <v>5098.331920705903</v>
+        <v>5098.978755478617</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>46164</v>
       </c>
       <c r="B52">
-        <v>4983.68445764426</v>
+        <v>4984.272015967224</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>46171</v>
       </c>
       <c r="B53">
-        <v>4880.693365153628</v>
+        <v>4881.258194009498</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>46178</v>
       </c>
       <c r="B54">
-        <v>4833.097517358694</v>
+        <v>4833.736486801436</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>46185</v>
       </c>
       <c r="B55">
-        <v>4703.067390475697</v>
+        <v>4703.580327033118</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>46192</v>
       </c>
       <c r="B56">
-        <v>4579.812456610056</v>
+        <v>4580.168877069772</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>46199</v>
       </c>
       <c r="B57">
-        <v>4482.383394480161</v>
+        <v>4482.617882208158</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>46206</v>
       </c>
       <c r="B58">
-        <v>4477.60066152833</v>
+        <v>4477.839967330115</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>46213</v>
       </c>
       <c r="B59">
-        <v>4398.481866572885</v>
+        <v>4398.781860884676</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>46220</v>
       </c>
       <c r="B60">
-        <v>4241.826265925275</v>
+        <v>4242.229965650027</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>46227</v>
       </c>
       <c r="B61">
-        <v>4147.285915473412</v>
+        <v>4147.628712378153</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>46234</v>
       </c>
       <c r="B62">
-        <v>4096.155619751083</v>
+        <v>4096.377026881357</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>46241</v>
       </c>
       <c r="B63">
-        <v>4081.809187480286</v>
+        <v>4081.809485941915</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46248</v>
       </c>
       <c r="B64">
-        <v>4128.630499124994</v>
+        <v>4128.309334840742</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46255</v>
       </c>
       <c r="B65">
-        <v>4210.8680568768</v>
+        <v>4210.184203712655</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46262</v>
       </c>
       <c r="B66">
-        <v>4309.508919826712</v>
+        <v>4308.60492118501</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46269</v>
       </c>
       <c r="B67">
-        <v>4333.316139385287</v>
+        <v>4333.671284118309</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46276</v>
       </c>
       <c r="B68">
-        <v>4339.041377108668</v>
+        <v>4338.507684876517</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46283</v>
       </c>
       <c r="B69">
-        <v>4340.732836068386</v>
+        <v>4338.631677211562</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46290</v>
       </c>
       <c r="B70">
-        <v>4368.902200906121</v>
+        <v>4362.722788584492</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46297</v>
       </c>
       <c r="B71">
-        <v>4417.73928610885</v>
+        <v>4411.557291415455</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46304</v>
       </c>
       <c r="B72">
-        <v>4495.262794499164</v>
+        <v>4488.960609985917</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46311</v>
       </c>
       <c r="B73">
-        <v>4583.879594669009</v>
+        <v>4577.171545661036</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46318</v>
       </c>
       <c r="B74">
-        <v>4729.879893659867</v>
+        <v>4719.079510942981</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46325</v>
       </c>
       <c r="B75">
-        <v>4865.740128672764</v>
+        <v>4848.434803284938</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46332</v>
       </c>
       <c r="B76">
-        <v>4998.645184006343</v>
+        <v>4974.515225902978</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46339</v>
       </c>
       <c r="B77">
-        <v>5185.353407873677</v>
+        <v>5145.375637283039</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46346</v>
       </c>
       <c r="B78">
-        <v>5260.894303743225</v>
+        <v>5201.774016584254</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,15 @@
         <v>46353</v>
       </c>
       <c r="B79">
-        <v>5330.184893004512</v>
+        <v>5220.470003640431</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2">
+      <c r="A80" s="3">
+        <v>46360</v>
+      </c>
+      <c r="B80">
+        <v>4997.926253640432</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/XAUUSD_forecast.xlsx
+++ b/public/data/files/XAUUSD_forecast.xlsx
@@ -442,7 +442,7 @@
         <v>45849</v>
       </c>
       <c r="B7">
-        <v>3668.963510676511</v>
+        <v>3669.003936013775</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -450,7 +450,7 @@
         <v>45856</v>
       </c>
       <c r="B8">
-        <v>3566.191372957641</v>
+        <v>3566.246196768055</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -458,7 +458,7 @@
         <v>45863</v>
       </c>
       <c r="B9">
-        <v>3511.844995945896</v>
+        <v>3511.908571522462</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -466,7 +466,7 @@
         <v>45870</v>
       </c>
       <c r="B10">
-        <v>3484.302531796067</v>
+        <v>3484.370282245107</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -474,7 +474,7 @@
         <v>45877</v>
       </c>
       <c r="B11">
-        <v>3492.823475526727</v>
+        <v>3492.892882156516</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -482,7 +482,7 @@
         <v>45884</v>
       </c>
       <c r="B12">
-        <v>3505.619523024238</v>
+        <v>3505.68974996613</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -490,7 +490,7 @@
         <v>45891</v>
       </c>
       <c r="B13">
-        <v>3520.131981317786</v>
+        <v>3520.201680744626</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -498,7 +498,7 @@
         <v>45898</v>
       </c>
       <c r="B14">
-        <v>3532.626550699256</v>
+        <v>3532.6951319546</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -506,7 +506,7 @@
         <v>45905</v>
       </c>
       <c r="B15">
-        <v>3548.487495967574</v>
+        <v>3548.538336267642</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -514,7 +514,7 @@
         <v>45912</v>
       </c>
       <c r="B16">
-        <v>3452.558877539884</v>
+        <v>3452.54600064928</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -522,7 +522,7 @@
         <v>45919</v>
       </c>
       <c r="B17">
-        <v>3450.169957582412</v>
+        <v>3450.158616957749</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -530,7 +530,7 @@
         <v>45926</v>
       </c>
       <c r="B18">
-        <v>3450.2587899935</v>
+        <v>3450.248310178778</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -538,7 +538,7 @@
         <v>45933</v>
       </c>
       <c r="B19">
-        <v>3532.117581996516</v>
+        <v>3532.06195928254</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -546,7 +546,7 @@
         <v>45940</v>
       </c>
       <c r="B20">
-        <v>3628.491215286966</v>
+        <v>3628.384218009615</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -554,7 +554,7 @@
         <v>45947</v>
       </c>
       <c r="B21">
-        <v>3779.758249269817</v>
+        <v>3779.595646201115</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -562,7 +562,7 @@
         <v>45954</v>
       </c>
       <c r="B22">
-        <v>3851.075380671709</v>
+        <v>3850.929507883006</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -570,7 +570,7 @@
         <v>45961</v>
       </c>
       <c r="B23">
-        <v>3897.910649489903</v>
+        <v>3897.773404989793</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -578,7 +578,7 @@
         <v>45968</v>
       </c>
       <c r="B24">
-        <v>3883.493125712965</v>
+        <v>3883.373827697394</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -586,7 +586,7 @@
         <v>45975</v>
       </c>
       <c r="B25">
-        <v>3886.686318367113</v>
+        <v>3886.635932299229</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -594,7 +594,7 @@
         <v>45982</v>
       </c>
       <c r="B26">
-        <v>3993.549163634924</v>
+        <v>3993.532497646674</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -602,7 +602,7 @@
         <v>45989</v>
       </c>
       <c r="B27">
-        <v>4067.815661842176</v>
+        <v>4067.765792674697</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -610,7 +610,7 @@
         <v>45996</v>
       </c>
       <c r="B28">
-        <v>4107.747123874343</v>
+        <v>4107.685619686887</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -618,7 +618,7 @@
         <v>46003</v>
       </c>
       <c r="B29">
-        <v>4206.356247657216</v>
+        <v>4206.350213821569</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -626,7 +626,7 @@
         <v>46010</v>
       </c>
       <c r="B30">
-        <v>4199.364635566752</v>
+        <v>4199.339802482675</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -634,7 +634,7 @@
         <v>46017</v>
       </c>
       <c r="B31">
-        <v>4223.508268956349</v>
+        <v>4223.439018068345</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -642,7 +642,7 @@
         <v>46024</v>
       </c>
       <c r="B32">
-        <v>4244.308052421618</v>
+        <v>4244.237758526807</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -650,7 +650,7 @@
         <v>46031</v>
       </c>
       <c r="B33">
-        <v>4308.624305490731</v>
+        <v>4308.525347451405</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -658,7 +658,7 @@
         <v>46038</v>
       </c>
       <c r="B34">
-        <v>4400.755128808392</v>
+        <v>4400.629739743216</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -666,7 +666,7 @@
         <v>46045</v>
       </c>
       <c r="B35">
-        <v>4436.691481091503</v>
+        <v>4436.554801167976</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -674,7 +674,7 @@
         <v>46052</v>
       </c>
       <c r="B36">
-        <v>4537.838622588271</v>
+        <v>4537.655507831956</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -682,7 +682,7 @@
         <v>46059</v>
       </c>
       <c r="B37">
-        <v>4672.900962669464</v>
+        <v>4672.67871424467</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -690,7 +690,7 @@
         <v>46066</v>
       </c>
       <c r="B38">
-        <v>4753.962296617028</v>
+        <v>4753.673889060884</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -698,7 +698,7 @@
         <v>46073</v>
       </c>
       <c r="B39">
-        <v>4891.507708506724</v>
+        <v>4891.33968362283</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -706,7 +706,7 @@
         <v>46080</v>
       </c>
       <c r="B40">
-        <v>4932.461548027799</v>
+        <v>4932.276824803432</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -714,7 +714,7 @@
         <v>46087</v>
       </c>
       <c r="B41">
-        <v>5038.316982076947</v>
+        <v>5038.075156774696</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -722,7 +722,7 @@
         <v>46094</v>
       </c>
       <c r="B42">
-        <v>5207.510418708542</v>
+        <v>5207.371873795842</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>46101</v>
       </c>
       <c r="B43">
-        <v>5251.074992843793</v>
+        <v>5251.049006814619</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>46108</v>
       </c>
       <c r="B44">
-        <v>5294.156275834917</v>
+        <v>5294.298400993944</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>46115</v>
       </c>
       <c r="B45">
-        <v>5372.678566039885</v>
+        <v>5372.948192249426</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>46122</v>
       </c>
       <c r="B46">
-        <v>5450.485917712535</v>
+        <v>5450.835994882436</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>46129</v>
       </c>
       <c r="B47">
-        <v>5581.141977165229</v>
+        <v>5581.526027649848</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>46136</v>
       </c>
       <c r="B48">
-        <v>5522.499748684573</v>
+        <v>5522.993148776548</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>46143</v>
       </c>
       <c r="B49">
-        <v>5349.275115160535</v>
+        <v>5349.892300444138</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>46150</v>
       </c>
       <c r="B50">
-        <v>5232.268740036675</v>
+        <v>5232.852964079739</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>46157</v>
       </c>
       <c r="B51">
-        <v>5098.978755478617</v>
+        <v>5099.611335471868</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>46164</v>
       </c>
       <c r="B52">
-        <v>4984.272015967224</v>
+        <v>4984.846728611212</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>46171</v>
       </c>
       <c r="B53">
-        <v>4881.258194009498</v>
+        <v>4881.810808267808</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>46178</v>
       </c>
       <c r="B54">
-        <v>4833.736486801436</v>
+        <v>4834.361649036266</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>46185</v>
       </c>
       <c r="B55">
-        <v>4703.580327033118</v>
+        <v>4704.082142412806</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>46192</v>
       </c>
       <c r="B56">
-        <v>4580.168877069772</v>
+        <v>4580.517465582504</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>46199</v>
       </c>
       <c r="B57">
-        <v>4482.617882208158</v>
+        <v>4482.84703470155</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>46206</v>
       </c>
       <c r="B58">
-        <v>4477.839967330115</v>
+        <v>4478.073834897994</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>46213</v>
       </c>
       <c r="B59">
-        <v>4398.781860884676</v>
+        <v>4399.075137755869</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>46220</v>
       </c>
       <c r="B60">
-        <v>4242.229965650027</v>
+        <v>4242.624859337048</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>46227</v>
       </c>
       <c r="B61">
-        <v>4147.628712378153</v>
+        <v>4147.964404819299</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>46234</v>
       </c>
       <c r="B62">
-        <v>4096.377026881357</v>
+        <v>4096.594148748322</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>46241</v>
       </c>
       <c r="B63">
-        <v>4081.809485941915</v>
+        <v>4081.810642517855</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46248</v>
       </c>
       <c r="B64">
-        <v>4128.309334840742</v>
+        <v>4127.996226760301</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46255</v>
       </c>
       <c r="B65">
-        <v>4210.184203712655</v>
+        <v>4209.516029839189</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46262</v>
       </c>
       <c r="B66">
-        <v>4308.60492118501</v>
+        <v>4307.720444529059</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46269</v>
       </c>
       <c r="B67">
-        <v>4333.671284118309</v>
+        <v>4332.806546599027</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46276</v>
       </c>
       <c r="B68">
-        <v>4338.507684876517</v>
+        <v>4336.59429944926</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46283</v>
       </c>
       <c r="B69">
-        <v>4338.631677211562</v>
+        <v>4335.046833281278</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46290</v>
       </c>
       <c r="B70">
-        <v>4362.722788584492</v>
+        <v>4356.44526541495</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46297</v>
       </c>
       <c r="B71">
-        <v>4411.557291415455</v>
+        <v>4404.80772312289</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46304</v>
       </c>
       <c r="B72">
-        <v>4488.960609985917</v>
+        <v>4481.74121083241</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46311</v>
       </c>
       <c r="B73">
-        <v>4577.171545661036</v>
+        <v>4569.249267139431</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46318</v>
       </c>
       <c r="B74">
-        <v>4719.079510942981</v>
+        <v>4706.919691307396</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46325</v>
       </c>
       <c r="B75">
-        <v>4848.434803284938</v>
+        <v>4829.801551231806</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46332</v>
       </c>
       <c r="B76">
-        <v>4974.515225902978</v>
+        <v>4949.183213577504</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46339</v>
       </c>
       <c r="B77">
-        <v>5145.375637283039</v>
+        <v>5105.315472133037</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46346</v>
       </c>
       <c r="B78">
-        <v>5201.774016584254</v>
+        <v>5145.109790985275</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46353</v>
       </c>
       <c r="B79">
-        <v>5220.470003640431</v>
+        <v>5127.446606348389</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46360</v>
       </c>
       <c r="B80">
-        <v>4997.926253640432</v>
+        <v>4904.90285634839</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/XAUUSD_forecast.xlsx
+++ b/public/data/files/XAUUSD_forecast.xlsx
@@ -442,7 +442,7 @@
         <v>45849</v>
       </c>
       <c r="B7">
-        <v>3669.003936013775</v>
+        <v>3669.043463122369</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -450,7 +450,7 @@
         <v>45856</v>
       </c>
       <c r="B8">
-        <v>3566.246196768055</v>
+        <v>3566.299806936784</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -458,7 +458,7 @@
         <v>45863</v>
       </c>
       <c r="B9">
-        <v>3511.908571522462</v>
+        <v>3511.970744521633</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -466,7 +466,7 @@
         <v>45870</v>
       </c>
       <c r="B10">
-        <v>3484.370282245107</v>
+        <v>3484.436544531403</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -474,7 +474,7 @@
         <v>45877</v>
       </c>
       <c r="B11">
-        <v>3492.892882156516</v>
+        <v>3492.960763991201</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -482,7 +482,7 @@
         <v>45884</v>
       </c>
       <c r="B12">
-        <v>3505.68974996613</v>
+        <v>3505.758433825535</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -490,7 +490,7 @@
         <v>45891</v>
       </c>
       <c r="B13">
-        <v>3520.201680744626</v>
+        <v>3520.269848541956</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -498,7 +498,7 @@
         <v>45898</v>
       </c>
       <c r="B14">
-        <v>3532.6951319546</v>
+        <v>3532.762206147689</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -506,7 +506,7 @@
         <v>45905</v>
       </c>
       <c r="B15">
-        <v>3548.538336267642</v>
+        <v>3548.588076586404</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -514,7 +514,7 @@
         <v>45912</v>
       </c>
       <c r="B16">
-        <v>3452.54600064928</v>
+        <v>3452.53341536164</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -522,7 +522,7 @@
         <v>45919</v>
       </c>
       <c r="B17">
-        <v>3450.158616957749</v>
+        <v>3450.147533876129</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -530,7 +530,7 @@
         <v>45926</v>
       </c>
       <c r="B18">
-        <v>3450.248310178778</v>
+        <v>3450.238068867461</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -538,7 +538,7 @@
         <v>45933</v>
       </c>
       <c r="B19">
-        <v>3532.06195928254</v>
+        <v>3532.007589466333</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -546,7 +546,7 @@
         <v>45940</v>
       </c>
       <c r="B20">
-        <v>3628.384218009615</v>
+        <v>3628.279620571505</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -554,7 +554,7 @@
         <v>45947</v>
       </c>
       <c r="B21">
-        <v>3779.595646201115</v>
+        <v>3779.436666006262</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -562,7 +562,7 @@
         <v>45954</v>
       </c>
       <c r="B22">
-        <v>3850.929507883006</v>
+        <v>3850.786875105073</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -570,7 +570,7 @@
         <v>45961</v>
       </c>
       <c r="B23">
-        <v>3897.773404989793</v>
+        <v>3897.639162409971</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -578,7 +578,7 @@
         <v>45968</v>
       </c>
       <c r="B24">
-        <v>3883.373827697394</v>
+        <v>3883.25711634252</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -586,7 +586,7 @@
         <v>45975</v>
       </c>
       <c r="B25">
-        <v>3886.635932299229</v>
+        <v>3886.586612756216</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -594,7 +594,7 @@
         <v>45982</v>
       </c>
       <c r="B26">
-        <v>3993.532497646674</v>
+        <v>3993.516169122505</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -602,7 +602,7 @@
         <v>45989</v>
       </c>
       <c r="B27">
-        <v>4067.765792674697</v>
+        <v>4067.717009484189</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -610,7 +610,7 @@
         <v>45996</v>
       </c>
       <c r="B28">
-        <v>4107.685619686887</v>
+        <v>4107.625457151071</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -618,7 +618,7 @@
         <v>46003</v>
       </c>
       <c r="B29">
-        <v>4206.350213821569</v>
+        <v>4206.344338303364</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -626,7 +626,7 @@
         <v>46010</v>
       </c>
       <c r="B30">
-        <v>4199.339802482675</v>
+        <v>4199.315561294767</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -634,7 +634,7 @@
         <v>46017</v>
       </c>
       <c r="B31">
-        <v>4223.439018068345</v>
+        <v>4223.371370854175</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -642,7 +642,7 @@
         <v>46024</v>
       </c>
       <c r="B32">
-        <v>4244.237758526807</v>
+        <v>4244.169075723544</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -650,7 +650,7 @@
         <v>46031</v>
       </c>
       <c r="B33">
-        <v>4308.525347451405</v>
+        <v>4308.42863874222</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -658,7 +658,7 @@
         <v>46038</v>
       </c>
       <c r="B34">
-        <v>4400.629739743216</v>
+        <v>4400.507175984883</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -666,7 +666,7 @@
         <v>46045</v>
       </c>
       <c r="B35">
-        <v>4436.554801167976</v>
+        <v>4436.421172695133</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -674,7 +674,7 @@
         <v>46052</v>
       </c>
       <c r="B36">
-        <v>4537.655507831956</v>
+        <v>4537.47644797306</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -682,7 +682,7 @@
         <v>46059</v>
       </c>
       <c r="B37">
-        <v>4672.67871424467</v>
+        <v>4672.461395828414</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -690,7 +690,7 @@
         <v>46066</v>
       </c>
       <c r="B38">
-        <v>4753.673889060884</v>
+        <v>4753.391709683296</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -698,7 +698,7 @@
         <v>46073</v>
       </c>
       <c r="B39">
-        <v>4891.33968362283</v>
+        <v>4891.175371768803</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -706,7 +706,7 @@
         <v>46080</v>
       </c>
       <c r="B40">
-        <v>4932.276824803432</v>
+        <v>4932.09618112419</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -714,7 +714,7 @@
         <v>46087</v>
       </c>
       <c r="B41">
-        <v>5038.075156774696</v>
+        <v>5037.838634511181</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -722,7 +722,7 @@
         <v>46094</v>
       </c>
       <c r="B42">
-        <v>5207.371873795842</v>
+        <v>5207.236277187529</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>46101</v>
       </c>
       <c r="B43">
-        <v>5251.049006814619</v>
+        <v>5251.023338247094</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>46108</v>
       </c>
       <c r="B44">
-        <v>5294.298400993944</v>
+        <v>5294.437050326194</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>46115</v>
       </c>
       <c r="B45">
-        <v>5372.948192249426</v>
+        <v>5373.211606597379</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>46122</v>
       </c>
       <c r="B46">
-        <v>5450.835994882436</v>
+        <v>5451.178043495267</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>46129</v>
       </c>
       <c r="B47">
-        <v>5581.526027649848</v>
+        <v>5581.901315614081</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>46136</v>
       </c>
       <c r="B48">
-        <v>5522.993148776548</v>
+        <v>5523.475504702605</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>46143</v>
       </c>
       <c r="B49">
-        <v>5349.892300444138</v>
+        <v>5350.495793018892</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>46150</v>
       </c>
       <c r="B50">
-        <v>5232.852964079739</v>
+        <v>5233.424318157518</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>46157</v>
       </c>
       <c r="B51">
-        <v>5099.611335471868</v>
+        <v>5100.230125491653</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>46164</v>
       </c>
       <c r="B52">
-        <v>4984.846728611212</v>
+        <v>4985.409011295813</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>46171</v>
       </c>
       <c r="B53">
-        <v>4881.810808267808</v>
+        <v>4882.351598756912</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>46178</v>
       </c>
       <c r="B54">
-        <v>4834.361649036266</v>
+        <v>4834.973445410871</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>46185</v>
       </c>
       <c r="B55">
-        <v>4704.082142412806</v>
+        <v>4704.573193450693</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>46192</v>
       </c>
       <c r="B56">
-        <v>4580.517465582504</v>
+        <v>4580.858476975858</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>46199</v>
       </c>
       <c r="B57">
-        <v>4482.84703470155</v>
+        <v>4483.071031532536</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>46206</v>
       </c>
       <c r="B58">
-        <v>4478.073834897994</v>
+        <v>4478.302447128049</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>46213</v>
       </c>
       <c r="B59">
-        <v>4399.075137755869</v>
+        <v>4399.361919733422</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>46220</v>
       </c>
       <c r="B60">
-        <v>4242.624859337048</v>
+        <v>4243.011230630956</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>46227</v>
       </c>
       <c r="B61">
-        <v>4147.964404819299</v>
+        <v>4148.293208885427</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>46234</v>
       </c>
       <c r="B62">
-        <v>4096.594148748322</v>
+        <v>4096.807105288416</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>46241</v>
       </c>
       <c r="B63">
-        <v>4081.810642517855</v>
+        <v>4081.812601993365</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46248</v>
       </c>
       <c r="B64">
-        <v>4127.996226760301</v>
+        <v>4127.690884859661</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46255</v>
       </c>
       <c r="B65">
-        <v>4209.516029839189</v>
+        <v>4208.863014090998</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46262</v>
       </c>
       <c r="B66">
-        <v>4307.720444529059</v>
+        <v>4306.854881431324</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46269</v>
       </c>
       <c r="B67">
-        <v>4332.806546599027</v>
+        <v>4335.579449680301</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46276</v>
       </c>
       <c r="B68">
-        <v>4336.59429944926</v>
+        <v>4339.078882709564</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46283</v>
       </c>
       <c r="B69">
-        <v>4335.046833281278</v>
+        <v>4336.518672399866</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46290</v>
       </c>
       <c r="B70">
-        <v>4356.44526541495</v>
+        <v>4355.916786806751</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46297</v>
       </c>
       <c r="B71">
-        <v>4404.80772312289</v>
+        <v>4404.089067382961</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46304</v>
       </c>
       <c r="B72">
-        <v>4481.74121083241</v>
+        <v>4480.796323291068</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46311</v>
       </c>
       <c r="B73">
-        <v>4569.249267139431</v>
+        <v>4568.043096066203</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46318</v>
       </c>
       <c r="B74">
-        <v>4706.919691307396</v>
+        <v>4702.719961858309</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46325</v>
       </c>
       <c r="B75">
-        <v>4829.801551231806</v>
+        <v>4821.005450347388</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46332</v>
       </c>
       <c r="B76">
-        <v>4949.183213577504</v>
+        <v>4935.964225015441</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46339</v>
       </c>
       <c r="B77">
-        <v>5105.315472133037</v>
+        <v>5082.098881428769</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46346</v>
       </c>
       <c r="B78">
-        <v>5145.109790985275</v>
+        <v>5114.030650828995</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46353</v>
       </c>
       <c r="B79">
-        <v>5127.446606348389</v>
+        <v>5084.853548304995</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46360</v>
       </c>
       <c r="B80">
-        <v>4904.90285634839</v>
+        <v>4647.547860914683</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/XAUUSD_forecast.xlsx
+++ b/public/data/files/XAUUSD_forecast.xlsx
@@ -442,7 +442,7 @@
         <v>45849</v>
       </c>
       <c r="B7">
-        <v>3669.043463122369</v>
+        <v>3669.082121609377</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -450,7 +450,7 @@
         <v>45856</v>
       </c>
       <c r="B8">
-        <v>3566.299806936784</v>
+        <v>3566.3522433187</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -458,7 +458,7 @@
         <v>45863</v>
       </c>
       <c r="B9">
-        <v>3511.970744521633</v>
+        <v>3512.031560843726</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -466,7 +466,7 @@
         <v>45870</v>
       </c>
       <c r="B10">
-        <v>3484.436544531403</v>
+        <v>3484.501367139867</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -474,7 +474,7 @@
         <v>45877</v>
       </c>
       <c r="B11">
-        <v>3492.960763991201</v>
+        <v>3493.027170717433</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -482,7 +482,7 @@
         <v>45884</v>
       </c>
       <c r="B12">
-        <v>3505.758433825535</v>
+        <v>3505.825624893772</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -490,7 +490,7 @@
         <v>45891</v>
       </c>
       <c r="B13">
-        <v>3520.269848541956</v>
+        <v>3520.336534632458</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -498,7 +498,7 @@
         <v>45898</v>
       </c>
       <c r="B14">
-        <v>3532.762206147689</v>
+        <v>3532.827822400668</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -506,7 +506,7 @@
         <v>45905</v>
       </c>
       <c r="B15">
-        <v>3548.588076586404</v>
+        <v>3548.636752208278</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -514,7 +514,7 @@
         <v>45912</v>
       </c>
       <c r="B16">
-        <v>3452.53341536164</v>
+        <v>3452.521111887616</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -522,7 +522,7 @@
         <v>45919</v>
       </c>
       <c r="B17">
-        <v>3450.147533876129</v>
+        <v>3450.136699668298</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -530,7 +530,7 @@
         <v>45926</v>
       </c>
       <c r="B18">
-        <v>3450.238068867461</v>
+        <v>3450.228058014962</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -538,7 +538,7 @@
         <v>45933</v>
       </c>
       <c r="B19">
-        <v>3532.007589466333</v>
+        <v>3531.954430705923</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -546,7 +546,7 @@
         <v>45940</v>
       </c>
       <c r="B20">
-        <v>3628.279620571505</v>
+        <v>3628.1773431709</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -554,7 +554,7 @@
         <v>45947</v>
       </c>
       <c r="B21">
-        <v>3779.436666006262</v>
+        <v>3779.281188996352</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -562,7 +562,7 @@
         <v>45954</v>
       </c>
       <c r="B22">
-        <v>3850.786875105073</v>
+        <v>3850.647375612524</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -570,7 +570,7 @@
         <v>45961</v>
       </c>
       <c r="B23">
-        <v>3897.639162409971</v>
+        <v>3897.507824409866</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -578,7 +578,7 @@
         <v>45968</v>
       </c>
       <c r="B24">
-        <v>3883.25711634252</v>
+        <v>3883.142908528347</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -586,7 +586,7 @@
         <v>45975</v>
       </c>
       <c r="B25">
-        <v>3886.586612756216</v>
+        <v>3886.538326319984</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -594,7 +594,7 @@
         <v>45982</v>
       </c>
       <c r="B26">
-        <v>3993.516169122505</v>
+        <v>3993.500168002299</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -602,7 +602,7 @@
         <v>45989</v>
       </c>
       <c r="B27">
-        <v>4067.717009484189</v>
+        <v>4067.669277186142</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -610,7 +610,7 @@
         <v>45996</v>
       </c>
       <c r="B28">
-        <v>4107.625457151071</v>
+        <v>4107.566592856794</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -618,7 +618,7 @@
         <v>46003</v>
       </c>
       <c r="B29">
-        <v>4206.344338303364</v>
+        <v>4206.338615094917</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -626,7 +626,7 @@
         <v>46010</v>
       </c>
       <c r="B30">
-        <v>4199.315561294767</v>
+        <v>4199.291891207365</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -634,7 +634,7 @@
         <v>46017</v>
       </c>
       <c r="B31">
-        <v>4223.371370854175</v>
+        <v>4223.305272400242</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -642,7 +642,7 @@
         <v>46024</v>
       </c>
       <c r="B32">
-        <v>4244.169075723544</v>
+        <v>4244.10194940629</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -650,7 +650,7 @@
         <v>46031</v>
       </c>
       <c r="B33">
-        <v>4308.42863874222</v>
+        <v>4308.334103729714</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -658,7 +658,7 @@
         <v>46038</v>
       </c>
       <c r="B34">
-        <v>4400.507175984883</v>
+        <v>4400.387343342493</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -666,7 +666,7 @@
         <v>46045</v>
       </c>
       <c r="B35">
-        <v>4436.421172695133</v>
+        <v>4436.29049480262</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -674,7 +674,7 @@
         <v>46052</v>
       </c>
       <c r="B36">
-        <v>4537.47644797306</v>
+        <v>4537.301309996059</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -682,7 +682,7 @@
         <v>46059</v>
       </c>
       <c r="B37">
-        <v>4672.461395828414</v>
+        <v>4672.248845453221</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -690,7 +690,7 @@
         <v>46066</v>
       </c>
       <c r="B38">
-        <v>4753.391709683296</v>
+        <v>4753.115559220483</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -698,7 +698,7 @@
         <v>46073</v>
       </c>
       <c r="B39">
-        <v>4891.175371768803</v>
+        <v>4891.014651436586</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -706,7 +706,7 @@
         <v>46080</v>
       </c>
       <c r="B40">
-        <v>4932.09618112419</v>
+        <v>4931.919483566098</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -714,7 +714,7 @@
         <v>46087</v>
       </c>
       <c r="B41">
-        <v>5037.838634511181</v>
+        <v>5037.607243170691</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -722,7 +722,7 @@
         <v>46094</v>
       </c>
       <c r="B42">
-        <v>5207.236277187529</v>
+        <v>5207.10353610252</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>46101</v>
       </c>
       <c r="B43">
-        <v>5251.023338247094</v>
+        <v>5250.997985234608</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>46108</v>
       </c>
       <c r="B44">
-        <v>5294.437050326194</v>
+        <v>5294.572348604136</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>46115</v>
       </c>
       <c r="B45">
-        <v>5373.211606597379</v>
+        <v>5373.469020725431</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>46122</v>
       </c>
       <c r="B46">
-        <v>5451.178043495267</v>
+        <v>5451.512335813502</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>46129</v>
       </c>
       <c r="B47">
-        <v>5581.901315614081</v>
+        <v>5582.268136864936</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>46136</v>
       </c>
       <c r="B48">
-        <v>5523.475504702605</v>
+        <v>5523.947182572068</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>46143</v>
       </c>
       <c r="B49">
-        <v>5350.495793018892</v>
+        <v>5351.08604257345</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>46150</v>
       </c>
       <c r="B50">
-        <v>5233.424318157518</v>
+        <v>5233.983221912499</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>46157</v>
       </c>
       <c r="B51">
-        <v>5100.230125491653</v>
+        <v>5100.835570408457</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>46164</v>
       </c>
       <c r="B52">
-        <v>4985.409011295813</v>
+        <v>4985.959262036682</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>46171</v>
       </c>
       <c r="B53">
-        <v>4882.351598756912</v>
+        <v>4882.880939857717</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>46178</v>
       </c>
       <c r="B54">
-        <v>4834.973445410871</v>
+        <v>4835.572298722136</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>46185</v>
       </c>
       <c r="B55">
-        <v>4704.573193450693</v>
+        <v>4705.053821920405</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>46192</v>
       </c>
       <c r="B56">
-        <v>4580.858476975858</v>
+        <v>4581.192155163211</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>46199</v>
       </c>
       <c r="B57">
-        <v>4483.071031532536</v>
+        <v>4483.290044323814</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>46206</v>
       </c>
       <c r="B58">
-        <v>4478.302447128049</v>
+        <v>4478.525978822726</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>46213</v>
       </c>
       <c r="B59">
-        <v>4399.361919733422</v>
+        <v>4399.642419666007</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>46220</v>
       </c>
       <c r="B60">
-        <v>4243.011230630956</v>
+        <v>4243.389351184147</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>46227</v>
       </c>
       <c r="B61">
-        <v>4148.293208885427</v>
+        <v>4148.615332102339</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>46234</v>
       </c>
       <c r="B62">
-        <v>4096.807105288416</v>
+        <v>4097.01601215854</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>46241</v>
       </c>
       <c r="B63">
-        <v>4081.812601993365</v>
+        <v>4081.815312642455</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46248</v>
       </c>
       <c r="B64">
-        <v>4127.690884859661</v>
+        <v>4127.39303252199</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46255</v>
       </c>
       <c r="B65">
-        <v>4208.863014090998</v>
+        <v>4208.224657658764</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46262</v>
       </c>
       <c r="B66">
-        <v>4306.854881431324</v>
+        <v>4306.007647750286</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46269</v>
       </c>
       <c r="B67">
-        <v>4335.579449680301</v>
+        <v>4339.011129491438</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46276</v>
       </c>
       <c r="B68">
-        <v>4339.078882709564</v>
+        <v>4342.471716505843</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46283</v>
       </c>
       <c r="B69">
-        <v>4336.518672399866</v>
+        <v>4339.023885666715</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46290</v>
       </c>
       <c r="B70">
-        <v>4355.916786806751</v>
+        <v>4356.632330086265</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46297</v>
       </c>
       <c r="B71">
-        <v>4404.089067382961</v>
+        <v>4404.757193890772</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46304</v>
       </c>
       <c r="B72">
-        <v>4480.796323291068</v>
+        <v>4481.280780035229</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46311</v>
       </c>
       <c r="B73">
-        <v>4568.043096066203</v>
+        <v>4568.353057213379</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46318</v>
       </c>
       <c r="B74">
-        <v>4702.719961858309</v>
+        <v>4700.418227818449</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46325</v>
       </c>
       <c r="B75">
-        <v>4821.005450347388</v>
+        <v>4814.743423755751</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46332</v>
       </c>
       <c r="B76">
-        <v>4935.964225015441</v>
+        <v>4926.037251628763</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46339</v>
       </c>
       <c r="B77">
-        <v>5082.098881428769</v>
+        <v>5063.957088804209</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46346</v>
       </c>
       <c r="B78">
-        <v>5114.030650828995</v>
+        <v>5090.835097303203</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46353</v>
       </c>
       <c r="B79">
-        <v>5084.853548304995</v>
+        <v>5057.058167635579</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46360</v>
       </c>
       <c r="B80">
-        <v>4647.547860914683</v>
+        <v>4700.040787986412</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/XAUUSD_forecast.xlsx
+++ b/public/data/files/XAUUSD_forecast.xlsx
@@ -442,7 +442,7 @@
         <v>45849</v>
       </c>
       <c r="B7">
-        <v>3669.082121609377</v>
+        <v>3669.119939794881</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -450,7 +450,7 @@
         <v>45856</v>
       </c>
       <c r="B8">
-        <v>3566.3522433187</v>
+        <v>3566.403544042669</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -458,7 +458,7 @@
         <v>45863</v>
       </c>
       <c r="B9">
-        <v>3512.031560843726</v>
+        <v>3512.091064408182</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -466,7 +466,7 @@
         <v>45870</v>
       </c>
       <c r="B10">
-        <v>3484.501367139867</v>
+        <v>3484.564796472451</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -474,7 +474,7 @@
         <v>45877</v>
       </c>
       <c r="B11">
-        <v>3493.027170717433</v>
+        <v>3493.092149886922</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -482,7 +482,7 @@
         <v>45884</v>
       </c>
       <c r="B12">
-        <v>3505.825624893772</v>
+        <v>3505.891371300861</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -490,7 +490,7 @@
         <v>45891</v>
       </c>
       <c r="B13">
-        <v>3520.336534632458</v>
+        <v>3520.40178679315</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -498,7 +498,7 @@
         <v>45898</v>
       </c>
       <c r="B14">
-        <v>3532.827822400668</v>
+        <v>3532.89202772441</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -506,7 +506,7 @@
         <v>45905</v>
       </c>
       <c r="B15">
-        <v>3548.636752208278</v>
+        <v>3548.684396925943</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -514,7 +514,7 @@
         <v>45912</v>
       </c>
       <c r="B16">
-        <v>3452.521111887616</v>
+        <v>3452.509080870986</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -522,7 +522,7 @@
         <v>45919</v>
       </c>
       <c r="B17">
-        <v>3450.136699668298</v>
+        <v>3450.126106049544</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -530,7 +530,7 @@
         <v>45926</v>
       </c>
       <c r="B18">
-        <v>3450.228058014962</v>
+        <v>3450.218269934212</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -538,7 +538,7 @@
         <v>45933</v>
       </c>
       <c r="B19">
-        <v>3531.954430705923</v>
+        <v>3531.902443001185</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -546,7 +546,7 @@
         <v>45940</v>
       </c>
       <c r="B20">
-        <v>3628.1773431709</v>
+        <v>3628.077309503703</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -554,7 +554,7 @@
         <v>45947</v>
       </c>
       <c r="B21">
-        <v>3779.281188996352</v>
+        <v>3779.129100694888</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -562,7 +562,7 @@
         <v>45954</v>
       </c>
       <c r="B22">
-        <v>3850.647375612524</v>
+        <v>3850.510907314904</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -570,7 +570,7 @@
         <v>45961</v>
       </c>
       <c r="B23">
-        <v>3897.507824409866</v>
+        <v>3897.379297808768</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -578,7 +578,7 @@
         <v>45968</v>
       </c>
       <c r="B24">
-        <v>3883.142908528347</v>
+        <v>3883.031124653904</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -586,7 +586,7 @@
         <v>45975</v>
       </c>
       <c r="B25">
-        <v>3886.538326319984</v>
+        <v>3886.491040950177</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -594,7 +594,7 @@
         <v>45982</v>
       </c>
       <c r="B26">
-        <v>3993.500168002299</v>
+        <v>3993.484484617859</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -602,7 +602,7 @@
         <v>45989</v>
       </c>
       <c r="B27">
-        <v>4067.669277186142</v>
+        <v>4067.622562190983</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -610,7 +610,7 @@
         <v>45996</v>
       </c>
       <c r="B28">
-        <v>4107.566592856794</v>
+        <v>4107.508985246036</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -618,7 +618,7 @@
         <v>46003</v>
       </c>
       <c r="B29">
-        <v>4206.338615094917</v>
+        <v>4206.333038483536</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -626,7 +626,7 @@
         <v>46010</v>
       </c>
       <c r="B30">
-        <v>4199.291891207365</v>
+        <v>4199.268772383042</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -634,7 +634,7 @@
         <v>46017</v>
       </c>
       <c r="B31">
-        <v>4223.305272400242</v>
+        <v>4223.240670265475</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -642,7 +642,7 @@
         <v>46024</v>
       </c>
       <c r="B32">
-        <v>4244.10194940629</v>
+        <v>4244.036327403237</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -650,7 +650,7 @@
         <v>46031</v>
       </c>
       <c r="B33">
-        <v>4308.334103729714</v>
+        <v>4308.241670125566</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -658,7 +658,7 @@
         <v>46038</v>
       </c>
       <c r="B34">
-        <v>4400.387343342493</v>
+        <v>4400.270151756102</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -666,7 +666,7 @@
         <v>46045</v>
       </c>
       <c r="B35">
-        <v>4436.29049480262</v>
+        <v>4436.162671009557</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -674,7 +674,7 @@
         <v>46052</v>
       </c>
       <c r="B36">
-        <v>4537.301309996059</v>
+        <v>4537.129966632009</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -682,7 +682,7 @@
         <v>46059</v>
       </c>
       <c r="B37">
-        <v>4672.248845453221</v>
+        <v>4672.040908158132</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -690,7 +690,7 @@
         <v>46066</v>
       </c>
       <c r="B38">
-        <v>4753.115559220483</v>
+        <v>4752.845246805193</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -698,7 +698,7 @@
         <v>46073</v>
       </c>
       <c r="B39">
-        <v>4891.014651436586</v>
+        <v>4890.85740635317</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -706,7 +706,7 @@
         <v>46080</v>
       </c>
       <c r="B40">
-        <v>4931.919483566098</v>
+        <v>4931.746604450364</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -714,7 +714,7 @@
         <v>46087</v>
       </c>
       <c r="B41">
-        <v>5037.607243170691</v>
+        <v>5037.380817987661</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -722,7 +722,7 @@
         <v>46094</v>
       </c>
       <c r="B42">
-        <v>5207.10353610252</v>
+        <v>5206.97356159732</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>46101</v>
       </c>
       <c r="B43">
-        <v>5250.997985234608</v>
+        <v>5250.972945582743</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>46108</v>
       </c>
       <c r="B44">
-        <v>5294.572348604136</v>
+        <v>5294.704414745481</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>46115</v>
       </c>
       <c r="B45">
-        <v>5373.469020725431</v>
+        <v>5373.7206367931</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>46122</v>
       </c>
       <c r="B46">
-        <v>5451.512335813502</v>
+        <v>5451.839131959603</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>46129</v>
       </c>
       <c r="B47">
-        <v>5582.268136864936</v>
+        <v>5582.626774072192</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>46136</v>
       </c>
       <c r="B48">
-        <v>5523.947182572068</v>
+        <v>5524.408532514783</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>46143</v>
       </c>
       <c r="B49">
-        <v>5351.08604257345</v>
+        <v>5351.663479360363</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>46150</v>
       </c>
       <c r="B50">
-        <v>5233.983221912499</v>
+        <v>5234.53007698182</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>46157</v>
       </c>
       <c r="B51">
-        <v>5100.835570408457</v>
+        <v>5101.428096211754</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>46164</v>
       </c>
       <c r="B52">
-        <v>4985.959262036682</v>
+        <v>4986.497862075716</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>46171</v>
       </c>
       <c r="B53">
-        <v>4882.880939857717</v>
+        <v>4883.399190357167</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>46178</v>
       </c>
       <c r="B54">
-        <v>4835.572298722136</v>
+        <v>4836.158614177357</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>46185</v>
       </c>
       <c r="B55">
-        <v>4705.053821920405</v>
+        <v>4705.524355317426</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>46192</v>
       </c>
       <c r="B56">
-        <v>4581.192155163211</v>
+        <v>4581.518733720644</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>46199</v>
       </c>
       <c r="B57">
-        <v>4483.290044323814</v>
+        <v>4483.50423718263</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>46206</v>
       </c>
       <c r="B58">
-        <v>4478.525978822726</v>
+        <v>4478.744597132754</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>46213</v>
       </c>
       <c r="B59">
-        <v>4399.642419666007</v>
+        <v>4399.916841225289</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>46220</v>
       </c>
       <c r="B60">
-        <v>4243.389351184147</v>
+        <v>4243.759481280715</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>46227</v>
       </c>
       <c r="B61">
-        <v>4148.615332102339</v>
+        <v>4148.930973846722</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>46234</v>
       </c>
       <c r="B62">
-        <v>4097.01601215854</v>
+        <v>4097.220980916006</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>46241</v>
       </c>
       <c r="B63">
-        <v>4081.815312642455</v>
+        <v>4081.818725986895</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46248</v>
       </c>
       <c r="B64">
-        <v>4127.39303252199</v>
+        <v>4127.102405788422</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46255</v>
       </c>
       <c r="B65">
-        <v>4208.224657658764</v>
+        <v>4207.600482928392</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46262</v>
       </c>
       <c r="B66">
-        <v>4306.007647750286</v>
+        <v>4305.178182470798</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46269</v>
       </c>
       <c r="B67">
-        <v>4339.011129491438</v>
+        <v>4342.292440673513</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46276</v>
       </c>
       <c r="B68">
-        <v>4342.471716505843</v>
+        <v>4345.826905307472</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46283</v>
       </c>
       <c r="B69">
-        <v>4339.023885666715</v>
+        <v>4341.628656314687</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46290</v>
       </c>
       <c r="B70">
-        <v>4356.632330086265</v>
+        <v>4357.926059700611</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46297</v>
       </c>
       <c r="B71">
-        <v>4404.757193890772</v>
+        <v>4406.383996856376</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46304</v>
       </c>
       <c r="B72">
-        <v>4481.280780035229</v>
+        <v>4483.027078354469</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46311</v>
       </c>
       <c r="B73">
-        <v>4568.353057213379</v>
+        <v>4570.253938785023</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46318</v>
       </c>
       <c r="B74">
-        <v>4700.418227818449</v>
+        <v>4700.350199824934</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46325</v>
       </c>
       <c r="B75">
-        <v>4814.743423755751</v>
+        <v>4811.706757588312</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46332</v>
       </c>
       <c r="B76">
-        <v>4926.037251628763</v>
+        <v>4921.190348902259</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46339</v>
       </c>
       <c r="B77">
-        <v>5063.957088804209</v>
+        <v>5053.495254839182</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46346</v>
       </c>
       <c r="B78">
-        <v>5090.835097303203</v>
+        <v>5079.215456709358</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46353</v>
       </c>
       <c r="B79">
-        <v>5057.058167635579</v>
+        <v>5048.701992517796</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46360</v>
       </c>
       <c r="B80">
-        <v>4700.040787986412</v>
+        <v>4764.442120838305</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/XAUUSD_forecast.xlsx
+++ b/public/data/files/XAUUSD_forecast.xlsx
@@ -442,7 +442,7 @@
         <v>45849</v>
       </c>
       <c r="B7">
-        <v>3669.119939794881</v>
+        <v>3669.156944781132</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -450,7 +450,7 @@
         <v>45856</v>
       </c>
       <c r="B8">
-        <v>3566.403544042669</v>
+        <v>3566.453745603976</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -458,7 +458,7 @@
         <v>45863</v>
       </c>
       <c r="B9">
-        <v>3512.091064408182</v>
+        <v>3512.149297259264</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -466,7 +466,7 @@
         <v>45870</v>
       </c>
       <c r="B10">
-        <v>3484.564796472451</v>
+        <v>3484.626876958778</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -474,7 +474,7 @@
         <v>45877</v>
       </c>
       <c r="B11">
-        <v>3493.092149886922</v>
+        <v>3493.155747029851</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -482,7 +482,7 @@
         <v>45884</v>
       </c>
       <c r="B12">
-        <v>3505.891371300861</v>
+        <v>3505.955719130351</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -490,7 +490,7 @@
         <v>45891</v>
       </c>
       <c r="B13">
-        <v>3520.40178679315</v>
+        <v>3520.465650769396</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -498,7 +498,7 @@
         <v>45898</v>
       </c>
       <c r="B14">
-        <v>3532.89202772441</v>
+        <v>3532.954867130705</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -506,7 +506,7 @@
         <v>45905</v>
       </c>
       <c r="B15">
-        <v>3548.684396925943</v>
+        <v>3548.73104311828</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -514,7 +514,7 @@
         <v>45912</v>
       </c>
       <c r="B16">
-        <v>3452.509080870986</v>
+        <v>3452.497313364967</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -522,7 +522,7 @@
         <v>45919</v>
       </c>
       <c r="B17">
-        <v>3450.126106049544</v>
+        <v>3450.115745098638</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -530,7 +530,7 @@
         <v>45926</v>
       </c>
       <c r="B18">
-        <v>3450.218269934212</v>
+        <v>3450.208697276041</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -538,7 +538,7 @@
         <v>45933</v>
       </c>
       <c r="B19">
-        <v>3531.902443001185</v>
+        <v>3531.851588093638</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -546,7 +546,7 @@
         <v>45940</v>
       </c>
       <c r="B20">
-        <v>3628.077309503703</v>
+        <v>3627.979446573996</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -554,7 +554,7 @@
         <v>45947</v>
       </c>
       <c r="B21">
-        <v>3779.129100694888</v>
+        <v>3778.980291557212</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -562,7 +562,7 @@
         <v>45954</v>
       </c>
       <c r="B22">
-        <v>3850.510907314904</v>
+        <v>3850.377372507849</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -570,7 +570,7 @@
         <v>45961</v>
       </c>
       <c r="B23">
-        <v>3897.379297808768</v>
+        <v>3897.253493366156</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -578,7 +578,7 @@
         <v>45968</v>
       </c>
       <c r="B24">
-        <v>3883.031124653904</v>
+        <v>3882.92168845322</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -586,7 +586,7 @@
         <v>45975</v>
       </c>
       <c r="B25">
-        <v>3886.491040950177</v>
+        <v>3886.444725914118</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -594,7 +594,7 @@
         <v>45982</v>
       </c>
       <c r="B26">
-        <v>3993.484484617859</v>
+        <v>3993.469109674255</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -602,7 +602,7 @@
         <v>45989</v>
       </c>
       <c r="B27">
-        <v>4067.622562190983</v>
+        <v>4067.576832325298</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -610,7 +610,7 @@
         <v>45996</v>
       </c>
       <c r="B28">
-        <v>4107.508985246036</v>
+        <v>4107.452594515164</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -618,7 +618,7 @@
         <v>46003</v>
       </c>
       <c r="B29">
-        <v>4206.333038483536</v>
+        <v>4206.327603033869</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -626,7 +626,7 @@
         <v>46010</v>
       </c>
       <c r="B30">
-        <v>4199.268772383042</v>
+        <v>4199.246185888284</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -634,7 +634,7 @@
         <v>46017</v>
       </c>
       <c r="B31">
-        <v>4223.240670265475</v>
+        <v>4223.177514344045</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -642,7 +642,7 @@
         <v>46024</v>
       </c>
       <c r="B32">
-        <v>4244.036327403237</v>
+        <v>4243.972159842546</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -650,7 +650,7 @@
         <v>46031</v>
       </c>
       <c r="B33">
-        <v>4308.241670125566</v>
+        <v>4308.151268804095</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -658,7 +658,7 @@
         <v>46038</v>
       </c>
       <c r="B34">
-        <v>4400.270151756102</v>
+        <v>4400.155515073224</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -666,7 +666,7 @@
         <v>46045</v>
       </c>
       <c r="B35">
-        <v>4436.162671009557</v>
+        <v>4436.037608988754</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -674,7 +674,7 @@
         <v>46052</v>
       </c>
       <c r="B36">
-        <v>4537.129966632009</v>
+        <v>4536.962296051979</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -682,7 +682,7 @@
         <v>46059</v>
       </c>
       <c r="B37">
-        <v>4672.040908158132</v>
+        <v>4671.837435614498</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -690,7 +690,7 @@
         <v>46066</v>
       </c>
       <c r="B38">
-        <v>4752.845246805193</v>
+        <v>4752.580589529776</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -698,7 +698,7 @@
         <v>46073</v>
       </c>
       <c r="B39">
-        <v>4890.85740635317</v>
+        <v>4890.703525202165</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -706,7 +706,7 @@
         <v>46080</v>
       </c>
       <c r="B40">
-        <v>4931.746604450364</v>
+        <v>4931.577421537986</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -714,7 +714,7 @@
         <v>46087</v>
       </c>
       <c r="B41">
-        <v>5037.380817987661</v>
+        <v>5037.159201159449</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -722,7 +722,7 @@
         <v>46094</v>
       </c>
       <c r="B42">
-        <v>5206.97356159732</v>
+        <v>5206.846268370449</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>46101</v>
       </c>
       <c r="B43">
-        <v>5250.972945582743</v>
+        <v>5250.948216844551</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>46108</v>
       </c>
       <c r="B44">
-        <v>5294.704414745481</v>
+        <v>5294.833362150328</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>46115</v>
       </c>
       <c r="B45">
-        <v>5373.7206367931</v>
+        <v>5373.966648001639</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>46122</v>
       </c>
       <c r="B46">
-        <v>5451.839131959603</v>
+        <v>5452.158680583507</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>46129</v>
       </c>
       <c r="B47">
-        <v>5582.626774072192</v>
+        <v>5582.977497488206</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>46136</v>
       </c>
       <c r="B48">
-        <v>5524.408532514783</v>
+        <v>5524.859889542175</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>46143</v>
       </c>
       <c r="B49">
-        <v>5351.663479360363</v>
+        <v>5352.228515232719</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>46150</v>
       </c>
       <c r="B50">
-        <v>5234.53007698182</v>
+        <v>5235.065267950448</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>46157</v>
       </c>
       <c r="B51">
-        <v>5101.428096211754</v>
+        <v>5102.008110998449</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>46164</v>
       </c>
       <c r="B52">
-        <v>4986.497862075716</v>
+        <v>4987.025176753367</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>46171</v>
       </c>
       <c r="B53">
-        <v>4883.399190357167</v>
+        <v>4883.906694249292</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>46178</v>
       </c>
       <c r="B54">
-        <v>4836.158614177357</v>
+        <v>4836.732780296536</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>46185</v>
       </c>
       <c r="B55">
-        <v>4705.524355317426</v>
+        <v>4705.985107594932</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>46192</v>
       </c>
       <c r="B56">
-        <v>4581.518733720644</v>
+        <v>4581.838436427754</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>46199</v>
       </c>
       <c r="B57">
-        <v>4483.50423718263</v>
+        <v>4483.713767106752</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>46206</v>
       </c>
       <c r="B58">
-        <v>4478.744597132754</v>
+        <v>4478.958461970486</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>46213</v>
       </c>
       <c r="B59">
-        <v>4399.916841225289</v>
+        <v>4400.18537939402</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>46220</v>
       </c>
       <c r="B60">
-        <v>4243.759481280715</v>
+        <v>4244.121870421998</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>46227</v>
       </c>
       <c r="B61">
-        <v>4148.930973846722</v>
+        <v>4149.240325736473</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>46234</v>
       </c>
       <c r="B62">
-        <v>4097.220980916006</v>
+        <v>4097.42211919013</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>46241</v>
       </c>
       <c r="B63">
-        <v>4081.818725986895</v>
+        <v>4081.822796573654</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46248</v>
       </c>
       <c r="B64">
-        <v>4127.102405788422</v>
+        <v>4126.818752657562</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46255</v>
       </c>
       <c r="B65">
-        <v>4207.600482928392</v>
+        <v>4206.990032390172</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46262</v>
       </c>
       <c r="B66">
-        <v>4305.178182470798</v>
+        <v>4304.365946607568</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46269</v>
       </c>
       <c r="B67">
-        <v>4342.292440673513</v>
+        <v>4345.432434106353</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46276</v>
       </c>
       <c r="B68">
-        <v>4345.826905307472</v>
+        <v>4349.063903583495</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46283</v>
       </c>
       <c r="B69">
-        <v>4341.628656314687</v>
+        <v>4344.031497633135</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46290</v>
       </c>
       <c r="B70">
-        <v>4357.926059700611</v>
+        <v>4359.33293397472</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46297</v>
       </c>
       <c r="B71">
-        <v>4406.383996856376</v>
+        <v>4407.770535780244</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46304</v>
       </c>
       <c r="B72">
-        <v>4483.027078354469</v>
+        <v>4484.491589569188</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46311</v>
       </c>
       <c r="B73">
-        <v>4570.253938785023</v>
+        <v>4571.813418340669</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46318</v>
       </c>
       <c r="B74">
-        <v>4700.350199824934</v>
+        <v>4699.942019225009</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46325</v>
       </c>
       <c r="B75">
-        <v>4811.706757588312</v>
+        <v>4808.343806713377</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46332</v>
       </c>
       <c r="B76">
-        <v>4921.190348902259</v>
+        <v>4915.691006714935</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46339</v>
       </c>
       <c r="B77">
-        <v>5053.495254839182</v>
+        <v>5042.285460078785</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46346</v>
       </c>
       <c r="B78">
-        <v>5079.215456709358</v>
+        <v>5066.109332356533</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46353</v>
       </c>
       <c r="B79">
-        <v>5048.701992517796</v>
+        <v>5036.641645260319</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46360</v>
       </c>
       <c r="B80">
-        <v>4764.442120838305</v>
+        <v>4795.560792368939</v>
       </c>
     </row>
   </sheetData>
